--- a/StudyCompanionAndroid/assets/Schedule.xlsx
+++ b/StudyCompanionAndroid/assets/Schedule.xlsx
@@ -593,13 +593,19 @@
           <t>10月1日 周四 ◆国庆假期
 ────────────
 14:00-15:00 物理
-新课 Phy Ch1 运动学 §1.1、§1.2
-· §1.1 速率
-· §1.2 距离与位移、标量与矢量
+术语与格式 Phy Ch1 运动学 §1.1、§1.2、§1.3、§1.4
+· 速览 §1.1 速率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.2 距离与位移、标量与矢量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.3 速率与速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.4 位移-时间图像（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 15:15-16:15 物理
-练习 Phy Ch1 运动学（§1.1、§1.2）
-· 做 §1.1 课后练习并批改
-· 做 §1.2 课后练习并批改</t>
+格式训练 Phy Ch1 运动学（§1.1、§1.2）
+· 节末 Questions 题 全部（约 25 分钟，p.17）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.20）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -621,13 +627,19 @@
           <t>10月3日 周六 ◆国庆假期
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch1 速度与加速度 §1.1、§1.2
-· §1.1 位移与速度 p.2
-· §1.2 加速度 p.9
+术语与格式 M1 Ch1 速度与加速度 §1.1、§1.2、§1.3、§1.4
+· 速览 §1.1 位移与速度 p.2（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.2 加速度 p.9（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.3 匀加速运动方程 p.11（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.4 位移-时间图像与多阶段问题 p.15（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 20:00-21:00 应用数学
-练习 M1 Ch1 速度与加速度（§1.1、§1.2）
-· 做 §1.1 课后练习并批改
-· 做 §1.2 课后练习并批改</t>
+格式训练 M1 Ch1 速度与加速度（§1.1、§1.2）
+· Ex 1A 题 全部（约 25 分钟，p.4）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1B 题 全部（约 25 分钟，p.10）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -639,9 +651,12 @@
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch1 多项式方程的根 §1.1、§1.2
-· §1.1 二次方程 p.2
-· §1.2 三次方程 p.5</t>
+术语与格式 FM Ch1 多项式方程的根 §1.1、§1.2、§1.3、§1.4
+· 速览 §1.1 二次方程 p.2（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.2 三次方程 p.5（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.3 四次方程 p.8（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.4 代换法 p.10（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
     </row>
@@ -651,13 +666,19 @@
           <t>10月5日 周一 ◆国庆假期
 ────────────
 14:00-15:00 纯数
-新课 P1 Ch1 二次方程 §1.1、§1.2
-· §1.1 因式分解法解二次方程 p.3
-· §1.2 配方法 p.6
+术语与格式 P1 Ch1 二次方程 §1.1、§1.2、§1.3、§1.4
+· 速览 §1.1 因式分解法解二次方程 p.3（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.2 配方法 p.6（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.3 求根公式 p.10（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.4 联立方程（一个线性一个二次） p.11（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 15:15-16:15 纯数
-练习 P1 Ch1 二次方程（§1.1、§1.2）
-· 做 §1.1 课后练习并批改
-· 做 §1.2 课后练习并批改</t>
+格式训练 P1 Ch1 二次方程（§1.1、§1.2）
+· Ex 1A 题 1–7（约 20 分钟，p.6）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1B 题 1–12（约 28 分钟，p.9）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -665,13 +686,19 @@
           <t>10月6日 周二 ◆国庆假期
 ────────────
 14:00-15:00 物理
-新课 Phy Ch1 运动学 §1.3、§1.4
-· §1.3 速率与速度
-· §1.4 位移-时间图像
+格式训练 Phy Ch1 运动学（§1.3、§1.4）
+· 节末 Questions 题 全部（约 25 分钟，p.23）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.25）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 物理
-练习 Phy Ch1 运动学（§1.3、§1.4）
-· 做 §1.3 课后练习并批改
-· 做 §1.4 课后练习并批改</t>
+术语与格式 Phy Ch1 运动学 §1.5、§1.6、§1.7、§1.8
+· 速览 §1.5 位移的合成（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.6 速度的合成（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.7 矢量的减法（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.8 其他标量与矢量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -679,13 +706,19 @@
           <t>10月7日 周三 ◆国庆假期
 ────────────
 14:00-15:00 纯数
-新课 P1 Ch1 二次方程 §1.3、§1.4
-· §1.3 求根公式 p.10
-· §1.4 联立方程（一个线性一个二次） p.11
+格式训练 P1 Ch1 二次方程（§1.3、§1.4）
+· Ex 1C 题 1–5（约 18 分钟，p.11）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1D 题 1–14（约 31 分钟，p.13）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 纯数
-练习 P1 Ch1 二次方程（§1.3、§1.4）
-· 做 §1.3 课后练习并批改
-· 做 §1.4 课后练习并批改</t>
+术语与格式 P1 Ch1 二次方程 §1.5、§1.6、§1.7、§1.8
+· 速览 §1.5 更复杂的二次方程 p.15（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.6 二次函数的最大值与最小值 p.17（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.7 二次不等式 p.21（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.8 二次方程根的个数（判别式） p.24（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -693,9 +726,12 @@
           <t>10月8日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch1 运动学 §1.5、§1.6
-· §1.5 位移的合成
-· §1.6 速度的合成</t>
+格式训练 Phy Ch1 运动学（§1.5、§1.6）
+· 节末 Questions 题 全部（约 25 分钟，p.28）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.30）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -727,9 +763,12 @@
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-练习 FM Ch1 多项式方程的根（§1.1、§1.2）
-· 做 §1.1 课后练习并批改
-· 做 §1.2 课后练习并批改</t>
+格式训练 FM Ch1 多项式方程的根（§1.1、§1.2）
+· Ex 1A 题 全部（约 25 分钟，p.4）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1B 题 全部（约 25 分钟，p.7）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
     </row>
@@ -739,9 +778,12 @@
           <t>10月12日 周一
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch1 二次方程 §1.5、§1.6
-· §1.5 更复杂的二次方程 p.15
-· §1.6 二次函数的最大值与最小值 p.17</t>
+格式训练 P1 Ch1 二次方程（§1.5、§1.6）
+· Ex 1E 题 1–5（约 18 分钟，p.16）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1F 题 1–12（约 28 分钟，p.20）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -749,9 +791,12 @@
           <t>10月13日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch1 运动学（§1.5、§1.6）
-· 做 §1.5 课后练习并批改
-· 做 §1.6 课后练习并批改</t>
+章末复习 Phy Ch1 运动学
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：用位移—时间与速度—时间图描述运动，区分标量与矢量
+· 过关自测：能画 v–t 图并求面积=位移、斜率=加速度；能分辨 x、v、a 三个量；Chapter 1 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -759,9 +804,12 @@
           <t>10月14日 周三
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch1 二次方程（§1.5、§1.6）
-· 做 §1.5 课后练习并批改
-· 做 §1.6 课后练习并批改</t>
+格式训练 P1 Ch1 二次方程（§1.7、§1.8）
+· Ex 1G 题 1–7（约 20 分钟，p.23）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1H 题 1–12（约 28 分钟，p.26）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -769,9 +817,12 @@
           <t>10月15日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch1 运动学 §1.7、§1.8
-· §1.7 矢量的减法
-· §1.8 其他标量与矢量</t>
+术语与格式 Phy Ch2 加速运动 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 加速度的含义（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.2 计算加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.3 加速度的单位（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.4 推导加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -789,13 +840,18 @@
           <t>10月17日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch1 速度与加速度 §1.3、§1.4
-· §1.3 匀加速运动方程 p.11
-· §1.4 位移-时间图像与多阶段问题 p.15
+格式训练 M1 Ch1 速度与加速度（§1.3、§1.4）
+· Ex 1C 题 全部（约 25 分钟，p.13）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1D 题 全部（约 25 分钟，p.17）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-练习 M1 Ch1 速度与加速度（§1.3、§1.4）
-· 做 §1.3 课后练习并批改
-· 做 §1.4 课后练习并批改</t>
+术语与格式 M1 Ch1 速度与加速度 §1.5、§1.6
+· 速览 §1.5 速度-时间图像与多阶段问题 p.22（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.6 不连续图像 p.27（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -803,13 +859,16 @@
           <t>10月18日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch1 ｜ Phy Ch1 ｜ M1 Ch1
+· 回顾：P1 Ch1 ｜ Phy Ch2 ｜ M1 Ch1
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch1 多项式方程的根 §1.3、§1.4
-· §1.3 四次方程 p.8
-· §1.4 代换法 p.10</t>
+章末复习 FM Ch1 多项式方程的根
+· 章末复习题 End-of-chapter review p.15，限时 30 分钟
+· 本章要会：能对任意多项式方程用因式定理找根、处理换元可化为二次的四次方程
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -819,9 +878,10 @@
           <t>10月19日 周一
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch1 二次方程 §1.7、§1.8
-· §1.7 二次不等式 p.21
-· §1.8 二次方程根的个数（判别式） p.24</t>
+术语与格式 P1 Ch1 二次方程 §1.9
+· 速览 §1.9 直线与二次曲线的交点 p.27（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -829,10 +889,14 @@
           <t>10月20日 周二
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch1 运动学
-· 章末复习题 End-of-chapter review
-新课 Phy Ch2 加速运动 §2.1、§2.2
-· §2.1 加速度的含义</t>
+格式训练 Phy Ch2 加速运动（§2.1、§2.2）
+· 节末 Questions 题 全部（约 25 分钟，p.41）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.42）
+格式训练 Phy Ch2 加速运动（§2.3、§2.4）
+· 节末 Questions 题 全部（约 25 分钟，p.43）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.45）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -840,10 +904,14 @@
           <t>10月21日 周三
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch1 二次方程（§1.7、§1.8）
-· 做 §1.7 课后练习并批改
-新课 P1 Ch1 二次方程 §1.9
-· §1.9 直线与二次曲线的交点 p.27</t>
+章末复习 P1 Ch1 二次方程
+· 章末复习题 End-of-chapter review p.31，限时 30 分钟
+· 本章要会：把任意二次式配方、用判别式判断根的个数、解二次不等式与「一个线性一个二次」的联立方程
+· 过关自测：Ex 1A–1I 各做过一遍且错题清零；能对 xx²+bx+c 在 20 秒内写出配方形式；能口述判别式三种情况
+术语与格式 P1 Ch2 函数 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 函数的定义 p.34（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.2 复合函数 p.39（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.3 反函数 p.43（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -851,9 +919,12 @@
           <t>10月22日 周四
 ────────────
 21:00-22:15 物理
-练习 Phy Ch2 加速运动（§2.1、§2.2）
-· 做 §2.1 课后练习并批改
-· 做 §2.2 课后练习并批改</t>
+术语与格式 Phy Ch2 加速运动 §2.5、§2.6、§2.7、§2.8
+· 速览 §2.5 推导位移（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.6 测量速度与加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.7 实验室中测定速度与加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.8 运动方程（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -863,8 +934,10 @@
 21:00-22:15 学术英语
 EAP 06
 · 学术词汇②：AWL Sublist 3-4
+· 词汇/术语入 Anki
 EAP 07
-· 摘要写作：压缩与转述学术文本（paraphrase）</t>
+· 摘要写作：压缩与转述学术文本（paraphrase）
+· 词汇/术语入 Anki</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -872,13 +945,19 @@
           <t>10月24日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch1 速度与加速度 §1.5、§1.6
-· §1.5 速度-时间图像与多阶段问题 p.22
-· §1.6 不连续图像 p.27
+章末复习 M1 Ch1 速度与加速度
+· 章末复习题 End-of-chapter review p.31，限时 30 分钟
+· 本章要会：区分位移/速度/加速度，用匀加速公式解多阶段直线运动
+· 过关自测：默写 v=u+at、s=ut+½at²、v²=u²+2as；能从 v–t 图读出位移；Ex 1A–1F 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
-章末复习 M1 Ch1 速度与加速度
-· 章末复习题 End-of-chapter review p.31
-· 限时完成并批改</t>
+术语与格式 M1 Ch2 一维力与运动 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 牛顿第一定律及力与加速度的关系 p.36（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.2 力的合成 p.39（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.3 重力与重力加速度 p.42（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.4 接触力与竖直方向运动 p.47（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -889,9 +968,12 @@
 ★ 10月测试：P1 Ch1｜物理 Ch1-2
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-章末复习 FM Ch1 多项式方程的根
-· 章末复习题 End-of-chapter review p.15
-· 限时完成并批改</t>
+术语与格式 FM Ch2 有理函数 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 竖直渐近线 p.17（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.2 斜渐近线 p.24（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.3 不等式 p.29（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.4 曲线之间的关系 p.34（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
     </row>
@@ -901,9 +983,12 @@
           <t>10月26日 周一
 ────────────
 21:00-22:15 纯数
-章末复习 P1 Ch1 二次方程
-· 章末复习题 End-of-chapter review p.31
-· 限时完成并批改</t>
+格式训练 P1 Ch2 函数（§2.1、§2.2）
+· Ex 2A 题 1–16（约 34 分钟，p.37）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 1–19（约 35 分钟，p.41）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -911,9 +996,12 @@
           <t>10月27日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch2 加速运动 §2.3、§2.4
-· §2.3 加速度的单位
-· §2.4 推导加速度</t>
+格式训练 Phy Ch2 加速运动（§2.5、§2.6）
+· 节末 Questions 题 全部（约 25 分钟，p.47）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.49）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -921,9 +1009,12 @@
           <t>10月28日 周三
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch2 函数 §2.1、§2.2
-· §2.1 函数的定义 p.34
-· §2.2 复合函数 p.39</t>
+格式训练 P1 Ch2 函数（§2.3、§2.4）
+· Ex 2C 题 1–16（约 34 分钟，p.46）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2D 题 1–6（约 19 分钟，p.50）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -931,9 +1022,12 @@
           <t>10月29日 周四
 ────────────
 21:00-22:15 物理
-练习 Phy Ch2 加速运动（§2.3、§2.4）
-· 做 §2.3 课后练习并批改
-· 做 §2.4 课后练习并批改</t>
+格式训练 Phy Ch2 加速运动（§2.7、§2.8）
+· 节末 Questions 题 全部（约 25 分钟，p.51）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.56）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -951,13 +1045,19 @@
           <t>10月31日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch2 一维力与运动 §2.1、§2.2
-· §2.1 牛顿第一定律及力与加速度的关系 p.36
-· §2.2 力的合成 p.39
+格式训练 M1 Ch2 一维力与运动（§2.1、§2.2）
+· Ex 2A 题 全部（约 25 分钟，p.38）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 全部（约 25 分钟，p.41）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-练习 M1 Ch2 一维力与运动（§2.1、§2.2）
-· 做 §2.1 课后练习并批改
-· 做 §2.2 课后练习并批改</t>
+章末复习 M1 Ch2 一维力与运动
+· 章末复习题 End-of-chapter review p.51，限时 30 分钟
+· 本章要会：牛顿第二定律 F=ma 在一维的应用、重量与法向力
+· 过关自测：能画一维受力图（free-body diagram）；能处理竖直方向运动；Ex 2A–2D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
@@ -1031,13 +1131,18 @@
           <t>7月1日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch15 原子结构 §15.11、§15.12
-· §15.11 粒子家族
-· §15.12 再看 β 衰变
+术语与格式 Phy Ch18 振动 §18.9、§18.10
+· 速览 §18.9 阻尼振动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §18.10 共振（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 物理
-练习 Phy Ch15 原子结构（§15.11、§15.12）
-· 做 §15.11 课后练习并批改
-· 做 §15.12 课后练习并批改</t>
+章末复习 Phy Ch18 振动
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：简谐运动、阻尼与共振
+· 过关自测：能默写 a=−ω²x 与 x=A cos ωt；能算周期 T=2π/ω；Chapter 18 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -1045,27 +1150,39 @@
           <t>7月2日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
-新课 FM Ch8 连续随机变量 §8.3、§8.4
-· §8.3 计算连续随机变量的 E(g(X)) p.174
-· §8.4 由 Y=g(X) 求 pdf 与 cdf p.178
+术语与格式 FM Ch12 概率母函数 §12.1、§12.2、§12.3、§12.4
+· 速览 §12.1 概率母函数 p.280（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §12.2 用 pgf 求 E(X) 与 Var(X) p.287（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §12.3 独立随机变量之和 p.292（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §12.4 三个及以上随机变量 p.298（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 15:15-16:15 进阶数学
-章末复习 FM Ch8 连续随机变量
-· 章末复习题 End-of-chapter review p.188
-· 限时完成并批改</t>
+格式训练 FM Ch12 概率母函数（§12.1、§12.2）
+· Ex 12A 题 全部（约 25 分钟，p.282）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 12B 题 全部（约 25 分钟，p.289）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
           <t>7月3日 周六 ◆暑假
 ────────────
-14:00-15:00 应用数学
-真题精练 9709 M1 2019 Paper 4
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案
-20:00-21:00 应用数学
-真题精练 9709 S1 2019 Paper 6
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案</t>
+14:00-15:00 进阶数学
+章末复习 FM Ch12 概率母函数
+· 章末复习题 End-of-chapter review p.304，限时 30 分钟
+· 本章要会：能用 pgf 求均值、方差与独立和
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+20:00-21:00 进阶数学
+术语与格式 FM Ch19 双曲函数 §19.1、§19.2、§19.3、§19.4
+· 速览 §19.1 双曲函数的指数形式 p.432（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §19.2 双曲恒等式 p.438（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §19.3 反双曲函数 p.440（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §19.4 反双曲函数的对数形式 p.442（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1073,13 +1190,16 @@
           <t>7月4日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch8 ｜ Phy Ch15 ｜ FM Ch8
+· 回顾：Phy Ch18 ｜ FM Ch19
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch9 推断统计 §9.1、§9.2
-· §9.1 t 分布 p.190
-· §9.2 两均值之差的假设检验 p.197</t>
+格式训练 FM Ch19 双曲函数（§19.1、§19.2）
+· Ex 19A 题 全部（约 25 分钟，p.434）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 19B 题 全部（约 25 分钟，p.439）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
     </row>
@@ -1089,13 +1209,17 @@
           <t>7月5日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-练习 P2/3 Ch8 进阶微积分（§8.3、§8.4）
-· 做 §8.3 课后练习并批改
-· 做 §8.4 课后练习并批改
-15:15-16:15 纯数
-新课 P2/3 Ch8 进阶微积分 §8.5、§8.6
-· §8.5 部分分式在积分中的应用 p.194
-· §8.6 分部积分法 p.197</t>
+真题精练 9709 P3 2022 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 进阶数学
+章末复习 FM Ch19 双曲函数
+· 章末复习题 End-of-chapter review p.446，限时 30 分钟
+· 本章要会：能默写双曲函数的指数定义与恒等式、反双曲函数对数形式
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -1103,27 +1227,39 @@
           <t>7月6日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch15 原子结构 §15.13
-· §15.13 另一种核力
-· 精读课本+做例题，整理笔记
+术语与格式 Phy Ch19 热物理 §19.1、§19.2、§19.3、§19.4
+· 速览 §19.1 物态变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §19.2 能量变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §19.3 内能（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §19.4 温度的含义（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 15:15-16:15 物理
-章末复习 Phy Ch15 原子结构
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+格式训练 Phy Ch19 热物理（§19.1、§19.2）
+· 节末 Questions 题 全部（约 25 分钟，p.543）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.544）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>7月7日 周三 ◆暑假
 ────────────
-14:00-15:00 纯数
-练习 P2/3 Ch8 进阶微积分（§8.5、§8.6）
-· 做 §8.5 课后练习并批改
-· 做 §8.6 课后练习并批改
-15:15-16:15 纯数
-新课 P2/3 Ch8 进阶微积分 §8.7
-· §8.7 进阶积分技巧 p.201
-· 精读课本+做例题，整理笔记</t>
+14:00-15:00 进阶数学
+术语与格式 FM Ch20 矩阵 2 §20.1、§20.2、§20.3、§20.4
+· 速览 §20.1 特征值与特征向量 p.448（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §20.2 矩阵代数 p.451（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §20.3 对角化 p.461（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §20.4 方程组 p.465（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+15:15-16:15 进阶数学
+格式训练 FM Ch20 矩阵 2（§20.1、§20.2）
+· Ex 20A 题 全部（约 25 分钟，p.450）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 20B 题 全部（约 25 分钟，p.453）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1131,13 +1267,18 @@
           <t>7月8日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy P1 实验技能 §P1.1–P1.5、§P1.6–P1.11
-· §P1.1–P1.5 实验操作与不确定度（一）
-· §P1.6–P1.11 数据处理与误差合成（二）
+格式训练 Phy Ch19 热物理（§19.3、§19.4）
+· 节末 Questions 题 全部（约 25 分钟，p.551）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.552）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 物理
-章末复习 Phy P1 实验技能
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+术语与格式 Phy Ch19 热物理 §19.5、§19.6
+· 速览 §19.5 温度计（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §19.6 计算能量变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1145,27 +1286,39 @@
           <t>7月9日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
-练习 FM Ch9 推断统计（§9.1、§9.2）
-· 做 §9.1 课后练习并批改
-· 做 §9.2 课后练习并批改
+章末复习 FM Ch20 矩阵 2
+· 章末复习题 End-of-chapter review p.471，限时 30 分钟
+· 本章要会：能求特征值与特征向量、对角化并解方程组
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 进阶数学
-新课 FM Ch9 推断统计 §9.3、§9.4
-· §9.3 配对 t 检验 p.203
-· §9.4 小样本均值的置信区间 p.207</t>
+术语与格式 FM Ch21 微分（进阶） §21.1、§21.2、§21.3、§21.4
+· 速览 §21.1 隐函数 p.473（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §21.2 参数方程 p.478（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §21.3 双曲函数与反函数 p.481（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §21.4 麦克劳林级数 p.488（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
           <t>7月10日 周六 ◆暑假
 ────────────
-14:00-15:00 应用数学
-真题精练 9709 M1 2020 Paper 4
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案
-20:00-21:00 应用数学
-真题精练 9709 S1 2020 Paper 6
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案</t>
+14:00-15:00 进阶数学
+格式训练 FM Ch21 微分（进阶）（§21.1、§21.2）
+· Ex 21A 题 全部（约 25 分钟，p.475）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 21B 题 全部（约 25 分钟，p.480）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+20:00-21:00 进阶数学
+章末复习 FM Ch21 微分（进阶）
+· 章末复习题 End-of-chapter review p.496，限时 30 分钟
+· 本章要会：能用隐函数/参数方程求导并写出 Maclaurin 展开
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1173,13 +1326,16 @@
           <t>7月11日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch8 ｜ Phy Ch15 ｜ FM Ch9
+· 回顾：Phy Ch19 ｜ FM Ch21
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-练习 FM Ch9 推断统计（§9.3、§9.4）
-· 做 §9.3 课后练习并批改
-· 做 §9.4 课后练习并批改</t>
+术语与格式 FM Ch22 积分（进阶） §22.1、§22.2、§22.3、§22.4
+· 速览 §22.1 积分技巧 p.498（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §22.2 递推公式 p.503（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §22.3 弧长与表面积 p.509（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §22.4 面积的极限 p.515（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
     </row>
@@ -1188,14 +1344,20 @@
         <is>
           <t>7月12日 周一 ◆暑假
 ────────────
-14:00-15:00 纯数
-章末复习 P2/3 Ch8 进阶微积分
-· 章末复习题 End-of-chapter review p.203
-· 限时完成并批改
-15:15-16:15 纯数
-新课 P2/3 Ch9 向量 §9.1、§9.2
-· §9.1 位移（平移）向量 p.211
-· §9.2 位置向量 p.220</t>
+14:00-15:00 进阶数学
+格式训练 FM Ch22 积分（进阶）（§22.1、§22.2）
+· Ex 22A 题 全部（约 25 分钟，p.500）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 22B 题 全部（约 25 分钟，p.505）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+15:15-16:15 进阶数学
+章末复习 FM Ch22 积分（进阶）
+· 章末复习题 End-of-chapter review p.523，限时 30 分钟
+· 本章要会：能选对积分技巧、用递推公式、求弧长与旋转面面积
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1203,27 +1365,39 @@
           <t>7月13日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch16 圆周运动 §16.1、§16.2
-· §16.1 描述圆周运动
-· §16.2 弧度
+章末复习 Phy Ch19 热物理
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：比热容、潜热、理想气体与热力学第一定律
+· 过关自测：能默写 Q=mcΔθ 与 Q=ml；能列 ΔU=Q+W；Chapter 19 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
-练习 Phy Ch16 圆周运动（§16.1、§16.2）
-· 做 §16.1 课后练习并批改
-· 做 §16.2 课后练习并批改</t>
+术语与格式 Phy Ch20 理想气体 §20.1、§20.2、§20.3、§20.4
+· 速览 §20.1 气体的粒子模型（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §20.2 解释压强（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §20.3 测量气体（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §20.4 玻意耳定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>7月14日 周三 ◆暑假
 ────────────
-14:00-15:00 纯数
-练习 P2/3 Ch9 向量（§9.1、§9.2）
-· 做 §9.1 课后练习并批改
-· 做 §9.2 课后练习并批改
-15:15-16:15 纯数
-新课 P2/3 Ch9 向量 §9.3、§9.4
-· §9.3 数量积 p.225
-· §9.4 直线的向量方程 p.231</t>
+14:00-15:00 进阶数学
+术语与格式 FM Ch23 复数（进阶） §23.1、§23.2、§23.3、§23.4
+· 速览 §23.1 棣莫弗定理 p.525（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §23.2 正弦与余弦的幂 p.529（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §23.3 单位根 p.532（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §23.4 复数求和 p.537（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+15:15-16:15 进阶数学
+格式训练 FM Ch23 复数（进阶）（§23.1、§23.2）
+· Ex 23A 题 全部（约 25 分钟，p.527）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 23B 题 全部（约 25 分钟，p.531）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1231,13 +1405,19 @@
           <t>7月15日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch16 圆周运动 §16.3、§16.4
-· §16.3 恒定速率、变化速度
-· §16.4 角速度
+格式训练 Phy Ch20 理想气体（§20.1、§20.2）
+· 节末 Questions 题 全部（约 25 分钟，p.571）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.572）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 物理
-练习 Phy Ch16 圆周运动（§16.3、§16.4）
-· 做 §16.3 课后练习并批改
-· 做 §16.4 课后练习并批改</t>
+格式训练 Phy Ch20 理想气体（§20.3、§20.4）
+· 节末 Questions 题 全部（约 25 分钟，p.574）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.575）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1245,27 +1425,39 @@
           <t>7月16日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
-新课 FM Ch9 推断统计 §9.5
-· §9.5 均值之差的置信区间 p.210
-· 精读课本+做例题，整理笔记
+章末复习 FM Ch23 复数（进阶）
+· 章末复习题 End-of-chapter review p.543，限时 30 分钟
+· 本章要会：能用 de Moivre 定理求幂、根与复数和
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 进阶数学
-章末复习 FM Ch9 推断统计
-· 章末复习题 End-of-chapter review p.219
-· 限时完成并批改</t>
+术语与格式 FM Ch24 微分方程（进阶） §24.1、§24.2、§24.3、§24.4
+· 速览 §24.1 一阶微分方程 p.545（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §24.2 二阶微分方程：齐次情形 p.550（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §24.3 二阶微分方程：非齐次情形 p.557（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §24.4 微分方程的代换法 p.565（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>7月17日 周六 ◆暑假
 ────────────
-14:00-15:00 应用数学
-真题精练 9709 M1 2021 Paper 4
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案
-20:00-21:00 应用数学
-真题精练 9709 S1 2021 Paper 6
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案</t>
+14:00-15:00 进阶数学
+格式训练 FM Ch24 微分方程（进阶）（§24.1、§24.2）
+· Ex 24A 题 全部（约 25 分钟，p.547）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 24B 题 全部（约 25 分钟，p.552）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+20:00-21:00 进阶数学
+章末复习 FM Ch24 微分方程（进阶）
+· 章末复习题 End-of-chapter review p.575，限时 30 分钟
+· 本章要会：能解一阶与二阶（齐次/非齐次）微分方程
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1273,13 +1465,14 @@
           <t>7月18日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch9 ｜ Phy Ch16 ｜ FM Ch9
+· 回顾：Phy Ch20 ｜ FM Ch24
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch10 卡方检验 §10.1、§10.2
-· §10.1 建立假设 p.221
-· §10.2 离散分布的拟合优度 p.227</t>
+真题精练 9231 FP1 2019 Paper 1
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
     </row>
@@ -1288,14 +1481,16 @@
         <is>
           <t>7月19日 周一 ◆暑假
 ────────────
-14:00-15:00 纯数
-练习 P2/3 Ch9 向量（§9.3、§9.4）
-· 做 §9.3 课后练习并批改
-· 做 §9.4 课后练习并批改
-15:15-16:15 纯数
-新课 P2/3 Ch9 向量 §9.5
-· §9.5 两直线的交点 p.236
-· 精读课本+做例题，整理笔记</t>
+14:00-15:00 进阶数学
+真题精练 9231 FP2 2019 Paper 2
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 进阶数学
+真题精练 9231 FS 2019 Paper 3
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1303,27 +1498,35 @@
           <t>7月20日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch16 圆周运动 §16.5、§16.6
-· §16.5 向心力
-· §16.6 计算加速度与力
+术语与格式 Phy Ch20 理想气体 §20.5、§20.6、§20.7、§20.8
+· 速览 §20.5 温度变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §20.6 理想气体方程（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §20.7 气体建模：动力学模型（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §20.8 温度与分子能量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 15:15-16:15 物理
-练习 Phy Ch16 圆周运动（§16.5、§16.6）
-· 做 §16.5 课后练习并批改
-· 做 §16.6 课后练习并批改</t>
+格式训练 Phy Ch20 理想气体（§20.5、§20.6）
+· 节末 Questions 题 全部（约 25 分钟，p.577）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.580）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>7月21日 周三 ◆暑假
 ────────────
-14:00-15:00 纯数
-章末复习 P2/3 Ch9 向量
-· 章末复习题 End-of-chapter review p.240
-· 限时完成并批改
-15:15-16:15 纯数
-新课 P2/3 Ch10 微分方程 §10.1、§10.2
-· §10.1 分离变量法 p.245
-· §10.2 由实际问题建立微分方程 p.252</t>
+14:00-15:00 进阶数学
+真题精练 9231 FM 2019 Paper 4
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 进阶数学
+真题精练 9231 FP1 2020 Paper 1
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1331,13 +1534,19 @@
           <t>7月22日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch16 圆周运动 §16.7
-· §16.7 向心力的来源
-· 精读课本+做例题，整理笔记
+章末复习 Phy Ch20 理想气体
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：理想气体状态方程与分子运动论
+· 过关自测：能默写 pV=nRT 与 pV=NkT；能解释压强与温度的微观意义；Chapter 20 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
-章末复习 Phy Ch16 圆周运动
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+术语与格式 Phy Ch21 匀强电场 §21.1、§21.2、§21.3、§21.4
+· 速览 §21.1 吸引与排斥（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §21.2 电场概念（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §21.3 电场强度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §21.4 电荷受到的力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1345,27 +1554,29 @@
           <t>7月23日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
-练习 FM Ch10 卡方检验（§10.1、§10.2）
-· 做 §10.1 课后练习并批改
-· 做 §10.2 课后练习并批改
+真题精练 9231 FP2 2020 Paper 2
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 15:15-16:15 进阶数学
-新课 FM Ch10 卡方检验 §10.3、§10.4
-· §10.3 连续分布的拟合优度 p.231
-· §10.4 列联表检验相关性 p.237</t>
+真题精练 9231 FS 2020 Paper 3
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>7月24日 周六 ◆暑假
 ────────────
-14:00-15:00 应用数学
-真题精练 9709 M1 2022 Paper 4
-· 力学/概率统计真题卷
+14:00-15:00 进阶数学
+真题精练 9231 FM 2020 Paper 4
+· 进阶数学真题卷
 · 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 20:00-21:00 应用数学
-真题精练 9709 S1 2022 Paper 6
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1376,9 +1587,8 @@
 ★ 暑期测试：P2/3 Ch6-8｜物理 Ch13-16
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-章末复习 FM Ch10 卡方检验
-· 章末复习题 End-of-chapter review p.248
-· 限时完成并批改</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
     </row>
@@ -1388,13 +1598,11 @@
           <t>7月26日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-章末复习 P2/3 Ch10 微分方程
-· 章末复习题 End-of-chapter review p.252
-· 限时完成并批改
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 纯数
-新课 P2/3 Ch11 复数 §11.1、§11.2
-· §11.1 虚数 p.267
-· §11.2 复数 p.269</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1402,13 +1610,19 @@
           <t>7月27日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch17 引力场 §17.1、§17.2
-· §17.1 表示引力场
-· §17.2 重力场强度 g
+格式训练 Phy Ch21 匀强电场（§21.1、§21.2）
+· 节末 Questions 题 全部（约 25 分钟，p.595）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.597）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 物理
-练习 Phy Ch17 引力场（§17.1、§17.2）
-· 做 §17.1 课后练习并批改
-· 做 §17.2 课后练习并批改</t>
+章末复习 Phy Ch21 匀强电场
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：匀强电场、电势与电容器
+· 过关自测：能默写 E=V/d 与 F=qE；能算电容器储能 W=½QV；Chapter 21 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1416,13 +1630,11 @@
           <t>7月28日 周三 ◆暑假
 ────────────
 14:00-15:00 纯数
-练习 P2/3 Ch11 复数（§11.1、§11.2）
-· 做 §11.1 课后练习并批改
-· 做 §11.2 课后练习并批改
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 纯数
-新课 P2/3 Ch11 复数 §11.3、§11.4
-· §11.3 复平面 p.273
-· §11.4 解方程 p.283</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1430,27 +1642,27 @@
           <t>7月29日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch17 引力场 §17.3、§17.4
-· §17.3 引力场中的能量
-· §17.4 引力势
+真题精练 9702 AS 2019 Paper 1
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 15:15-16:15 物理
-练习 Phy Ch17 引力场（§17.3、§17.4）
-· 做 §17.3 课后练习并批改
-· 做 §17.4 课后练习并批改</t>
+真题精练 9702 AS 2019 Paper 2
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>7月30日 周五 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-新课 FM Ch11 非参数检验 §11.1、§11.2
-· §11.1 非参数检验概述 p.250
-· §11.2 单样本符号检验 p.251
-15:15-16:15 进阶数学
-练习 FM Ch11 非参数检验（§11.1、§11.2）
-· 做 §11.1 课后练习并批改
-· 做 §11.2 课后练习并批改</t>
+14:00-15:00 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1458,13 +1670,11 @@
           <t>7月31日 周六 ◆暑假
 ────────────
 14:00-15:00 应用数学
-真题精练 9709 M1 2023 Paper 4
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 20:00-21:00 应用数学
-真题精练 9709 S1 2023 Paper 6
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
@@ -1541,13 +1751,12 @@
           <t>8月1日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch11 ｜ Phy Ch17 ｜ FM Ch11
+· 回顾：Phy Ch21
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch11 非参数检验 §11.3、§11.4
-· §11.3 单样本 Wilcoxon 符号秩检验 p.254
-· §11.4 配对样本符号检验 p.260</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
     </row>
@@ -1557,13 +1766,11 @@
           <t>8月2日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-练习 P2/3 Ch11 复数（§11.3、§11.4）
-· 做 §11.3 课后练习并批改
-· 做 §11.4 课后练习并批改
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 纯数
-新课 P2/3 Ch11 复数 §11.5
-· §11.5 轨迹 p.288
-· 精读课本+做例题，整理笔记</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1571,13 +1778,15 @@
           <t>8月3日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch17 引力场 §17.5、§17.6
-· §17.5 在引力下运行
-· §17.6 轨道周期
+真题精练 9702 AS 2020 Paper 1
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 15:15-16:15 物理
-练习 Phy Ch17 引力场（§17.5、§17.6）
-· 做 §17.5 课后练习并批改
-· 做 §17.6 课后练习并批改</t>
+真题精练 9702 AS 2020 Paper 2
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1585,13 +1794,11 @@
           <t>8月4日 周三 ◆暑假
 ────────────
 14:00-15:00 纯数
-章末复习 P2/3 Ch11 复数
-· 章末复习题 End-of-chapter review p.288
-· 限时完成并批改
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 纯数
-真题精练 9709 P1 2019 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1599,41 +1806,39 @@
           <t>8月5日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch17 引力场 §17.7
-· §17.7 绕地球运行
-· 精读课本+做例题，整理笔记
+真题精练 9702 AS 2021 Paper 1
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 15:15-16:15 物理
-章末复习 Phy Ch17 引力场
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+真题精练 9702 AS 2021 Paper 2
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>8月6日 周五 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-练习 FM Ch11 非参数检验（§11.3、§11.4）
-· 做 §11.3 课后练习并批改
-· 做 §11.4 课后练习并批改
-15:15-16:15 进阶数学
-新课 FM Ch11 非参数检验 §11.5、§11.6
-· §11.5 Wilcoxon 配对符号秩检验 p.263
-· §11.6 Wilcoxon 秩和检验 p.266</t>
+14:00-15:00 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>8月7日 周六 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-章末复习 FM Ch11 非参数检验
-· 章末复习题 End-of-chapter review p.277
-· 限时完成并批改
-20:00-21:00 进阶数学
-新课 FM Ch12 概率母函数 §12.1、§12.2
-· §12.1 概率母函数 p.280
-· §12.2 用 pgf 求 E(X) 与 Var(X) p.287</t>
+14:00-15:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+20:00-21:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1641,13 +1846,12 @@
           <t>8月8日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch11 ｜ Phy Ch17 ｜ FM Ch12
+· 回顾：整理本周笔记
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-练习 FM Ch12 概率母函数（§12.1、§12.2）
-· 做 §12.1 课后练习并批改
-· 做 §12.2 课后练习并批改</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
     </row>
@@ -1657,83 +1861,75 @@
           <t>8月9日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-真题精练 9709 P3 2019 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>8月10日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+真题精练 9702 AS 2022 Paper 1
+· 物理 AS 真题（选择题/结构题）
 · 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 物理
+真题精练 9702 AS 2022 Paper 2
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>8月11日 周三 ◆暑假
+────────────
+14:00-15:00 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 纯数
-真题精练 9709 P1 2020 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>8月10日 周二 ◆暑假
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>8月12日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch18 振动 §18.1、§18.2
-· §18.1 自由振动与受迫振动
-· §18.2 观察振动
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 物理
-练习 Phy Ch18 振动（§18.1、§18.2）
-· 做 §18.1 课后练习并批改
-· 做 §18.2 课后练习并批改</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>8月11日 周三 ◆暑假
-────────────
-14:00-15:00 纯数
-真题精练 9709 P3 2020 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-15:15-16:15 纯数
-真题精练 9709 P1 2021 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>8月12日 周四 ◆暑假
-────────────
-14:00-15:00 物理
-新课 Phy Ch18 振动 §18.3、§18.4
-· §18.3 描述振动
-· §18.4 简谐运动
-15:15-16:15 物理
-练习 Phy Ch18 振动（§18.3、§18.4）
-· 做 §18.3 课后练习并批改
-· 做 §18.4 课后练习并批改</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>8月13日 周五 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-新课 FM Ch12 概率母函数 §12.3、§12.4
-· §12.3 独立随机变量之和 p.292
-· §12.4 三个及以上随机变量 p.298
-15:15-16:15 进阶数学
-章末复习 FM Ch12 概率母函数
-· 章末复习题 End-of-chapter review p.304
-· 限时完成并批改</t>
+14:00-15:00 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>8月14日 周六 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-新课 FM Ch19 双曲函数 §19.1、§19.2
-· §19.1 双曲函数的指数形式 p.432
-· §19.2 双曲恒等式 p.438
-20:00-21:00 进阶数学
-练习 FM Ch19 双曲函数（§19.1、§19.2）
-· 做 §19.1 课后练习并批改
-· 做 §19.2 课后练习并批改</t>
+14:00-15:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+20:00-21:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -1741,13 +1937,12 @@
           <t>8月15日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：Phy Ch18 ｜ FM Ch19
+· 回顾：整理本周笔记
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch19 双曲函数 §19.3、§19.4
-· §19.3 反双曲函数 p.440
-· §19.4 反双曲函数的对数形式 p.442</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
     </row>
@@ -1757,13 +1952,11 @@
           <t>8月16日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-真题精练 9709 P3 2021 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 纯数
-真题精练 9709 P1 2022 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1771,13 +1964,11 @@
           <t>8月17日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch18 振动 §18.5、§18.6
-· §18.5 简谐运动的图像表示
-· §18.6 频率与角频率
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 物理
-练习 Phy Ch18 振动（§18.5、§18.6）
-· 做 §18.5 课后练习并批改
-· 做 §18.6 课后练习并批改</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1785,13 +1976,11 @@
           <t>8月18日 周三 ◆暑假
 ────────────
 14:00-15:00 纯数
-真题精练 9709 P3 2022 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 纯数
-真题精练 9709 P1 2023 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1799,41 +1988,35 @@
           <t>8月19日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch18 振动 §18.7、§18.8
-· §18.7 简谐运动方程
-· §18.8 简谐运动中的能量变化
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 物理
-练习 Phy Ch18 振动（§18.7、§18.8）
-· 做 §18.7 课后练习并批改
-· 做 §18.8 课后练习并批改</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>8月20日 周五 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-章末复习 FM Ch19 双曲函数
-· 章末复习题 End-of-chapter review p.446
-· 限时完成并批改
-15:15-16:15 进阶数学
-新课 FM Ch20 矩阵 2 §20.1、§20.2
-· §20.1 特征值与特征向量 p.448
-· §20.2 矩阵代数 p.451</t>
+14:00-15:00 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>8月21日 周六 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-练习 FM Ch20 矩阵 2（§20.1、§20.2）
-· 做 §20.1 课后练习并批改
-· 做 §20.2 课后练习并批改
-20:00-21:00 进阶数学
-新课 FM Ch20 矩阵 2 §20.3、§20.4
-· §20.3 对角化 p.461
-· §20.4 方程组 p.465</t>
+14:00-15:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+20:00-21:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1841,13 +2024,12 @@
           <t>8月22日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：Phy Ch18 ｜ FM Ch20
+· 回顾：整理本周笔记
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch20 矩阵 2
-· 章末复习题 End-of-chapter review p.471
-· 限时完成并批改</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
     </row>
@@ -1857,13 +2039,11 @@
           <t>8月23日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-真题精练 9709 P3 2023 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 纯数
-真题精练 9709 P1 2024 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1871,13 +2051,11 @@
           <t>8月24日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch18 振动 §18.9、§18.10
-· §18.9 阻尼振动
-· §18.10 共振
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 物理
-章末复习 Phy Ch18 振动
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1885,13 +2063,11 @@
           <t>8月25日 周三 ◆暑假
 ────────────
 14:00-15:00 纯数
-真题精练 9709 P3 2024 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-15:15-16:15 进阶数学
-新课 FM Ch21 微分（进阶） §21.1、§21.2
-· §21.1 隐函数 p.473
-· §21.2 参数方程 p.478</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1899,41 +2075,35 @@
           <t>8月26日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch19 热物理 §19.1、§19.2
-· §19.1 物态变化
-· §19.2 能量变化
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 物理
-练习 Phy Ch19 热物理（§19.1、§19.2）
-· 做 §19.1 课后练习并批改
-· 做 §19.2 课后练习并批改</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>8月27日 周五 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-练习 FM Ch21 微分（进阶）（§21.1、§21.2）
-· 做 §21.1 课后练习并批改
-· 做 §21.2 课后练习并批改
-15:15-16:15 进阶数学
-新课 FM Ch21 微分（进阶） §21.3、§21.4
-· §21.3 双曲函数与反函数 p.481
-· §21.4 麦克劳林级数 p.488</t>
+14:00-15:00 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>8月28日 周六 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-章末复习 FM Ch21 微分（进阶）
-· 章末复习题 End-of-chapter review p.496
-· 限时完成并批改
-20:00-21:00 进阶数学
-新课 FM Ch22 积分（进阶） §22.1、§22.2
-· §22.1 积分技巧 p.498
-· §22.2 递推公式 p.503</t>
+14:00-15:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+20:00-21:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1944,9 +2114,8 @@
 ★ 暑期总测试：三科综合卷（P2/3 + 物理 + FM，真题限时）
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-练习 FM Ch22 积分（进阶）（§22.1、§22.2）
-· 做 §22.1 课后练习并批改
-· 做 §22.2 课后练习并批改</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
     </row>
@@ -1955,14 +2124,12 @@
         <is>
           <t>8月30日 周一 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-新课 FM Ch22 积分（进阶） §22.3、§22.4
-· §22.3 弧长与表面积 p.509
-· §22.4 面积的极限 p.515
-15:15-16:15 进阶数学
-章末复习 FM Ch22 积分（进阶）
-· 章末复习题 End-of-chapter review p.523
-· 限时完成并批改</t>
+14:00-15:00 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1970,13 +2137,11 @@
           <t>8月31日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch19 热物理 §19.3、§19.4
-· §19.3 内能
-· §19.4 温度的含义
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
 15:15-16:15 物理
-练习 Phy Ch19 热物理（§19.3、§19.4）
-· 做 §19.3 课后练习并批改
-· 做 §19.4 课后练习并批改</t>
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2054,10 +2219,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="C5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2075,17 +2240,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="C6" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ch19 2、Ch20 8、Ch21 4、真题 12</t>
+          <t>（全部排完）</t>
         </is>
       </c>
     </row>
@@ -2096,10 +2261,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2117,17 +2282,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ch23 4、Ch24 4、真题 12</t>
+          <t>（全部排完）</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2384,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch1 ｜ 物理 Phy Ch2 ｜ 应用数学 M1 Ch1 ｜ 进阶数学 FM Ch1</t>
+          <t>纯数 P1 Ch2 ｜ 物理 Phy Ch2 ｜ 应用数学 M1 Ch2 ｜ 进阶数学 FM Ch2</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2401,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch3 ｜ 物理 Phy Ch2 ｜ 应用数学 M1 Ch3 ｜ 进阶数学 FM Ch3</t>
+          <t>纯数 P1 Ch4 ｜ 物理 Phy Ch3 ｜ 应用数学 M1 Ch4 ｜ 进阶数学 FM Ch4</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2418,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch5 ｜ 物理 Phy Ch4 ｜ 应用数学 M1 Ch5 ｜ 进阶数学 FM Ch4</t>
+          <t>纯数 P1 Ch6 ｜ 物理 Phy Ch5 ｜ 应用数学 M1 Ch7 ｜ 进阶数学 FM Ch5</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2435,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch7 ｜ 物理 Phy Ch6 ｜ 应用数学 M1 Ch8 ｜ 进阶数学 FM Ch6</t>
+          <t>纯数 P1 Ch9 ｜ 物理 Phy Ch7 ｜ 应用数学 S1 Ch1 ｜ 进阶数学 FM Ch7</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2452,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch9 ｜ 物理 Phy Ch8 ｜ 应用数学 S1 Ch1 ｜ 进阶数学 FM Ch7</t>
+          <t>纯数 P2/3 Ch2 ｜ 物理 Phy Ch12 ｜ 应用数学 S1 Ch3 ｜ 进阶数学 FM Ch14</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2469,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch2 ｜ 物理 Phy Ch10 ｜ 应用数学 S1 Ch2 ｜ 进阶数学 FM Ch14</t>
+          <t>纯数 P2/3 Ch4 ｜ 物理 Phy Ch13 ｜ 应用数学 S1 Ch5 ｜ 进阶数学 FM Ch15</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2486,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch3 ｜ 物理 Phy Ch12 ｜ 应用数学 S1 Ch4 ｜ 进阶数学 FM Ch15</t>
+          <t>纯数 P2/3 Ch7 ｜ 物理 Phy Ch15 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch16</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2503,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch5 ｜ 物理 Phy Ch14 ｜ 应用数学 S1 Ch6 ｜ 进阶数学 FM Ch16</t>
+          <t>纯数 P2/3 Ch9 ｜ 物理 Phy Ch16 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch8</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2520,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch7 ｜ 物理 Phy Ch15 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch8</t>
+          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch18 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch11</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2537,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch10 ｜ 物理 Phy Ch16 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch10</t>
+          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch21 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch24</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2554,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch19 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch22</t>
+          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch21 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch24</t>
         </is>
       </c>
     </row>
@@ -2727,9 +2892,12 @@
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch2 有理函数 §2.1、§2.2
-· §2.1 竖直渐近线 p.17
-· §2.2 斜渐近线 p.24</t>
+格式训练 FM Ch2 有理函数（§2.1、§2.2）
+· Ex 2A 题 全部（约 25 分钟，p.19）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 全部（约 25 分钟，p.26）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
     </row>
@@ -2739,9 +2907,12 @@
           <t>11月2日 周一
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch2 函数（§2.1、§2.2）
-· 做 §2.1 课后练习并批改
-· 做 §2.2 课后练习并批改</t>
+术语与格式 P1 Ch2 函数 §2.5、§2.6、§2.7、§2.8
+· 速览 §2.5 函数的图像变换 p.51（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.6 反射变换 p.55（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.7 伸缩变换 p.57（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.8 复合变换 p.59（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -2749,10 +2920,14 @@
           <t>11月3日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch2 加速运动 §2.5、§2.6
-· §2.5 推导位移
-练习 Phy Ch2 加速运动（§2.5、§2.6）
-· 做 §2.5 课后练习并批改</t>
+术语与格式 Phy Ch2 加速运动 §2.9、§2.10、§2.11、§2.12
+· 速览 §2.9 运动方程的推导（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.10 匀变速与非匀变速（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.11 重力加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 Phy Ch2 加速运动（§2.9、§2.10）
+· 节末 Questions 题 全部（约 25 分钟，p.59）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.60）</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -2760,10 +2935,14 @@
           <t>11月4日 周三
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch2 函数 §2.3、§2.4
-· §2.3 反函数 p.43
-练习 P1 Ch2 函数（§2.3、§2.4）
-· 做 §2.3 课后练习并批改</t>
+格式训练 P1 Ch2 函数（§2.5、§2.6）
+· Ex 2E 题 1–7（约 20 分钟，p.54）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2F 题 1–4（约 16 分钟，p.56）
+章末复习 P1 Ch2 函数
+· 章末复习题 End-of-chapter review p.67，限时 30 分钟
+· 本章要会：判断映射是否为一对一、求反函数与复合函数、画 y=f(x) 的图象变换
+· 过关自测：能不看笔记写出 4 种图象变换（平移/拉伸/反射）的规则；Ex 2A–2H 错题清零；能解释「定义域限制」从哪来</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -2771,9 +2950,12 @@
           <t>11月5日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch2 加速运动 §2.7、§2.8
-· §2.7 实验室中测定速度与加速度
-· §2.8 运动方程</t>
+格式训练 Phy Ch2 加速运动（§2.11、§2.12）
+· 节末 Questions 题 全部（约 25 分钟，p.62）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.67）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -2791,190 +2973,241 @@
           <t>11月7日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch2 一维力与运动 §2.3、§2.4
-· §2.3 重力与重力加速度 p.42
-· §2.4 接触力与竖直方向运动 p.47
+术语与格式 M1 Ch3 二维力 §3.1、§3.2、§3.3、§3.4
+· 速览 §3.1 平衡问题中力的水平/竖直分解 p.54（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.2 其他角度平衡问题中的力的分解 p.59（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.3 力的三角形与拉密定理 p.62（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.4 斜面上的非平衡问题 p.66（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 20:00-21:00 应用数学
-章末复习 M1 Ch2 一维力与运动
-· 章末复习题 End-of-chapter review p.51
-· 限时完成并批改</t>
+格式训练 M1 Ch3 二维力（§3.1、§3.2）
+· Ex 3A 题 全部（约 25 分钟，p.56）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3B 题 全部（约 25 分钟，p.61）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
           <t>11月8日 周日
-────────────
-14:00-15:00 复习/测试
-· 回顾：P1 Ch2 ｜ Phy Ch2 ｜ M1 Ch2
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-练习 FM Ch2 有理函数（§2.1、§2.2）
-· 做 §2.1 课后练习并批改
-· 做 §2.2 课后练习并批改</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>11月9日 周一
-────────────
-21:00-22:15 纯数
-新课 P1 Ch2 函数 §2.5、§2.6
-· §2.5 函数的图像变换 p.51
-· §2.6 反射变换 p.55</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>11月10日 周二
-────────────
-21:00-22:15 物理
-练习 Phy Ch2 加速运动（§2.7、§2.8）
-· 做 §2.7 课后练习并批改
-· 做 §2.8 课后练习并批改</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>11月11日 周三
-────────────
-21:00-22:15 纯数
-练习 P1 Ch2 函数（§2.5、§2.6）
-· 做 §2.5 课后练习并批改
-· 做 §2.6 课后练习并批改</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>11月12日 周四
-────────────
-21:00-22:15 物理
-新课 Phy Ch2 加速运动 §2.9、§2.10
-· §2.9 运动方程的推导
-· §2.10 匀变速与非匀变速</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>11月13日 周五
-────────────
-21:00-22:15 学术英语
-EAP 10
-· 学术写作①：说明文（explanatory essay）结构
-· 词汇/术语入 Anki</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>11月14日 周六
-────────────
-14:00-15:00 应用数学
-新课 M1 Ch3 二维力 §3.1、§3.2
-· §3.1 平衡问题中力的水平/竖直分解 p.54
-· §3.2 其他角度平衡问题中的力的分解 p.59
-20:00-21:00 应用数学
-练习 M1 Ch3 二维力（§3.1、§3.2）
-· 做 §3.1 课后练习并批改
-· 做 §3.2 课后练习并批改</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>11月15日 周日
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P1 Ch2 ｜ Phy Ch2 ｜ M1 Ch3
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch2 有理函数 §2.3、§2.4
-· §2.3 不等式 p.29
-· §2.4 曲线之间的关系 p.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>11月16日 周一
+章末复习 FM Ch2 有理函数
+· 章末复习题 End-of-chapter review p.44，限时 30 分钟
+· 本章要会：能找出竖直/斜渐近线并画出有理函数草图
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>11月9日 周一
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch2 函数 §2.7、§2.8
-· §2.7 伸缩变换 p.57
-· §2.8 复合变换 p.59</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>11月17日 周二
+术语与格式 P1 Ch3 坐标几何 §3.1、§3.2、§3.3、§3.4
+· 速览 §3.1 线段长度与中点 p.72（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.2 平行与垂直 p.75（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.3 直线的方程 p.78（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.4 圆的方程 p.82（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>11月10日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch2 加速运动（§2.9、§2.10）
-· 做 §2.9 课后练习并批改
-新课 Phy Ch2 加速运动 §2.11、§2.12
-· §2.11 重力加速度</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>11月18日 周三
+术语与格式 Phy Ch2 加速运动 §2.13、§2.14
+· 速览 §2.13 二维运动：抛体（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.14 理解抛体运动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>11月11日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P1 Ch2 函数
-· 章末复习题 End-of-chapter review p.67
-新课 P1 Ch3 坐标几何 §3.1、§3.2
-· §3.1 线段长度与中点 p.72</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>11月19日 周四
+格式训练 P1 Ch3 坐标几何（§3.1、§3.2）
+· Ex 3A 题 1–12（约 28 分钟，p.74）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3B 题 1–11（约 26 分钟，p.77）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>11月12日 周四
 ────────────
 21:00-22:15 物理
-练习 Phy Ch2 加速运动（§2.11、§2.12）
-· 做 §2.11 课后练习并批改
-· 做 §2.12 课后练习并批改</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>11月20日 周五
+章末复习 Phy Ch2 加速运动
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：用四个匀加速公式与图象解多阶段运动
+· 过关自测：四个公式默写全对；能从 v–t 图求位移；能处理自由落体与抛体；Chapter 2 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>11月13日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 11
-· 学术词汇③：AWL Sublist 5-6
-EAP 12
-· 图表描述：数据、趋势与比较（Task 1）</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>11月21日 周六
+EAP 10
+· 学术写作①：说明文（explanatory essay）结构
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>11月14日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch3 二维力 §3.3、§3.4
-· §3.3 力的三角形与拉密定理 p.62
-· §3.4 斜面上的非平衡问题 p.66
+格式训练 M1 Ch3 二维力（§3.3、§3.4）
+· Ex 3C 题 全部（约 25 分钟，p.64）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3D 题 全部（约 25 分钟，p.68）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-练习 M1 Ch3 二维力（§3.3、§3.4）
-· 做 §3.3 课后练习并批改
-· 做 §3.4 课后练习并批改</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>11月22日 周日
+术语与格式 M1 Ch3 二维力 §3.5
+· 速览 §3.5 求合力与加速度方向 p.71（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>11月15日 周日
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P1 Ch3 ｜ Phy Ch2 ｜ M1 Ch3
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch2 有理函数
-· 章末复习题 End-of-chapter review p.44
-· 限时完成并批改</t>
+术语与格式 FM Ch3 级数求和 §3.1、§3.2
+· 速览 §3.1 Σr、Σr²、Σr³ 求和公式 p.46（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.2 收敛级数 p.51（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>11月16日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P1 Ch3 坐标几何（§3.3、§3.4）
+· Ex 3C 题 1–16（约 34 分钟，p.80）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3D 题 1–17（约 35 分钟，p.87）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>11月17日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch3 动力学 §3.1、§3.2、§3.3、§3.4
+· 速览 §3.1 力、质量与加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.2 识别力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.3 重力、摩擦与引力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 Phy Ch3 动力学（§3.1、§3.2）
+· 节末 Questions 题 全部（约 25 分钟，p.87）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.88）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>11月18日 周三
+────────────
+21:00-22:15 纯数
+术语与格式 P1 Ch3 坐标几何 §3.5
+· 速览 §3.5 直线与圆的交点问题 p.88（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+章末复习 P1 Ch3 坐标几何
+· 章末复习题 End-of-chapter review p.92，限时 30 分钟
+· 本章要会：求两点间距离与中点、直线方程、直线交点与垂直/平行条件
+· 过关自测：能把「两点式/斜截式/一般式」互相转换；Ex 3A–3E 错题清零；圆与直线关系的 3 种情况能画图说明</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>11月19日 周四
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch3 动力学（§3.3、§3.4）
+· 节末 Questions 题 全部（约 25 分钟，p.89）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.94）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>11月20日 周五
+────────────
+21:00-22:15 学术英语
+EAP 11
+· 学术词汇③：AWL Sublist 5-6
+· 词汇/术语入 Anki
+EAP 12
+· 图表描述：数据、趋势与比较（Task 1）
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>11月21日 周六
+────────────
+14:00-15:00 应用数学
+章末复习 M1 Ch3 二维力
+· 章末复习题 End-of-chapter review p.77，限时 30 分钟
+· 本章要会：二维受力分解、平衡方程、Lami 定理、斜面上的合成
+· 过关自测：能把任意方向的力分解到水平和竖直；能对斜面问题分解成平行/垂直分量；Ex 3A–3E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+20:00-21:00 应用数学
+术语与格式 M1 Ch4 摩擦力 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 摩擦力作为接触力的一部分 p.83（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.2 摩擦极限 p.90（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.3 运动不同阶段摩擦方向的变化 p.95（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.4 摩擦角 p.100（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>11月22日 周日
+────────────
+14:00-15:00 复习/测试
+· 回顾：P1 Ch3 ｜ Phy Ch3 ｜ M1 Ch4
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+章末复习 FM Ch3 级数求和
+· 章末复习题 End-of-chapter review p.57，限时 30 分钟
+· 本章要会：能默写 Σr、Σr²、Σr³ 公式并求无穷等比级数和
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -2984,9 +3217,12 @@
           <t>11月23日 周一
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch3 坐标几何（§3.1、§3.2）
-· 做 §3.1 课后练习并批改
-· 做 §3.2 课后练习并批改</t>
+术语与格式 P1 Ch4 弧度制 §4.1、§4.2、§4.3
+· 速览 §4.1 弧度 p.101（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.2 弧长 p.104（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.3 扇形面积 p.107（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -2994,9 +3230,12 @@
           <t>11月24日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch2 加速运动 §2.13、§2.14
-· §2.13 二维运动：抛体
-· §2.14 理解抛体运动</t>
+术语与格式 Phy Ch3 动力学 §3.5、§3.6、§3.7
+· 速览 §3.5 在流体中运动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.6 牛顿第三定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.7 理解 SI 单位（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3004,9 +3243,12 @@
           <t>11月25日 周三
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch3 坐标几何 §3.3、§3.4
-· §3.3 直线的方程 p.78
-· §3.4 圆的方程 p.82</t>
+格式训练 P1 Ch4 弧度制（§4.1、§4.2）
+· Ex 4A 题 1–9（约 24 分钟，p.102）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 1–10（约 25 分钟，p.105）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -3014,9 +3256,12 @@
           <t>11月26日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch2 加速运动
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+格式训练 Phy Ch3 动力学（§3.5、§3.6）
+· 节末 Questions 题 全部（约 25 分钟，p.98）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.101）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -3034,13 +3279,19 @@
           <t>11月28日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch3 二维力 §3.5
-· §3.5 求合力与加速度方向 p.71
-· 精读课本+做例题，整理笔记
+格式训练 M1 Ch4 摩擦力（§4.1、§4.2）
+· Ex 4A 题 全部（约 25 分钟，p.85）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 全部（约 25 分钟，p.92）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-章末复习 M1 Ch3 二维力
-· 章末复习题 End-of-chapter review p.77
-· 限时完成并批改</t>
+章末复习 M1 Ch4 摩擦力
+· 章末复习题 End-of-chapter review p.105，限时 30 分钟
+· 本章要会：摩擦作为接触力、极限摩擦 F=μN、摩擦方向随运动变化
+· 过关自测：能判断摩擦方向（与相对运动/趋势相反）；能区分「静止」与「滑动」两种方程；Ex 4A–4D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3051,9 +3302,12 @@
 ★ 11月测试：P1 Ch1-3｜物理 Ch1-2
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-新课 FM Ch3 级数求和 §3.1、§3.2
-· §3.1 Σr、Σr²、Σr³ 求和公式 p.46
-· §3.2 收敛级数 p.51</t>
+术语与格式 FM Ch4 矩阵 1 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 矩阵运算 p.59（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.2 逆矩阵 p.65（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.3 行列式 p.72（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.4 矩阵变换 p.76（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
     </row>
@@ -3063,9 +3317,12 @@
           <t>11月30日 周一
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch3 坐标几何（§3.3、§3.4）
-· 做 §3.3 课后练习并批改
-· 做 §3.4 课后练习并批改</t>
+章末复习 P1 Ch4 弧度制
+· 章末复习题 End-of-chapter review p.112，限时 30 分钟
+· 本章要会：弧度制、扇形弧长与面积、弧度下的三角比
+· 过关自测：弧长 s=rθ 与面积 A=½r²θ 能默写；Ex 4A–4C 错题清零；能在 30 秒内把 60°/90°/180° 换成弧度
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -3142,10 +3399,14 @@
           <t>12月1日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch3 动力学 §3.1、§3.2
-· §3.1 力、质量与加速度
-练习 Phy Ch3 动力学（§3.1、§3.2）
-· 做 §3.1 课后练习并批改</t>
+章末复习 Phy Ch3 动力学
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：牛顿三定律、动量与冲量、平衡与合力
+· 过关自测：能画受力图；能区分质量与重量；能解连接体问题；Chapter 3 EXAM-STYLE QUESTIONS 限时做完并批改
+术语与格式 Phy Ch4 力 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 力的合成（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.2 矢量的分量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.3 重心（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -3153,10 +3414,14 @@
           <t>12月2日 周三
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch3 坐标几何 §3.5
-· §3.5 直线与圆的交点问题 p.88
-章末复习 P1 Ch3 坐标几何
-· 章末复习题 End-of-chapter review p.92</t>
+术语与格式 P1 Ch5 三角学 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 0°–90° 之间的角 p.118（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.2 角的一般定义 p.121（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.3 任意角的三角比 p.123（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 P1 Ch5 三角学（§5.1、§5.2）
+· Ex 5A 题 1–6（约 19 分钟，p.120）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5B 题 1–9（约 24 分钟，p.122）</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -3164,9 +3429,12 @@
           <t>12月3日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch3 动力学 §3.3、§3.4
-· §3.3 重力、摩擦与引力
-· §3.4 质量与惯性</t>
+格式训练 Phy Ch4 力（§4.1、§4.2）
+· 节末 Questions 题 全部（约 25 分钟，p.116）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.120）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -3184,13 +3452,19 @@
           <t>12月5日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch4 摩擦力 §4.1、§4.2
-· §4.1 摩擦力作为接触力的一部分 p.83
-· §4.2 摩擦极限 p.90
+术语与格式 M1 Ch5 连接体 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 牛顿第三定律 p.109（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.2 杆连接的物体 p.110（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.3 绳连接的物体 p.114（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.4 电梯中的物体 p.121（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 20:00-21:00 应用数学
-练习 M1 Ch4 摩擦力（§4.1、§4.2）
-· 做 §4.1 课后练习并批改
-· 做 §4.2 课后练习并批改</t>
+格式训练 M1 Ch5 连接体（§5.1、§5.2）
+· Ex 5A 题 全部（约 25 分钟，p.109）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5B 题 全部（约 25 分钟，p.112）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -3198,13 +3472,16 @@
           <t>12月6日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch3 ｜ Phy Ch3 ｜ M1 Ch4
+· 回顾：P1 Ch5 ｜ Phy Ch4 ｜ M1 Ch5
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch3 级数求和
-· 章末复习题 End-of-chapter review p.57
-· 限时完成并批改</t>
+格式训练 FM Ch4 矩阵 1（§4.1、§4.2）
+· Ex 4A 题 全部（约 25 分钟，p.61）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 全部（约 25 分钟，p.67）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
     </row>
@@ -3214,9 +3491,12 @@
           <t>12月7日 周一
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch4 弧度制 §4.1、§4.2
-· §4.1 弧度 p.101
-· §4.2 弧长 p.104</t>
+格式训练 P1 Ch5 三角学（§5.3、§5.4）
+· Ex 5C 题 1–13（约 30 分钟，p.126）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5D 题 1–17（约 35 分钟，p.134）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -3224,9 +3504,12 @@
           <t>12月8日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch3 动力学（§3.3、§3.4）
-· 做 §3.3 课后练习并批改
-· 做 §3.4 课后练习并批改</t>
+格式训练 Phy Ch4 力（§4.3、§4.4）
+· 节末 Questions 题 全部（约 25 分钟，p.122）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.127）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3234,9 +3517,12 @@
           <t>12月9日 周三
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch4 弧度制（§4.1、§4.2）
-· 做 §4.1 课后练习并批改
-· 做 §4.2 课后练习并批改</t>
+术语与格式 P1 Ch5 三角学 §5.5、§5.6、§5.7、§5.8
+· 速览 §5.5 反三角函数 p.136（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.6 三角方程 p.140（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.7 三角恒等式 p.145（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.8 更复杂的三角方程 p.149（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -3244,9 +3530,10 @@
           <t>12月10日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch3 动力学 §3.5、§3.6
-· §3.5 在流体中运动
-· §3.6 牛顿第三定律</t>
+术语与格式 Phy Ch4 力 §4.5
+· 速览 §4.5 力偶的力矩（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -3264,13 +3551,19 @@
           <t>12月12日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch4 摩擦力 §4.3、§4.4
-· §4.3 运动不同阶段摩擦方向的变化 p.95
-· §4.4 摩擦角 p.100
+章末复习 M1 Ch5 连接体
+· 章末复习题 End-of-chapter review p.125，限时 30 分钟
+· 本章要会：连接体（杆/绳/滑轮/升降机）的受力与加速度
+· 过关自测：能对每个物体分别列 F=ma 并解联立；能处理升降机超重/失重；Ex 5A–5D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
-章末复习 M1 Ch4 摩擦力
-· 章末复习题 End-of-chapter review p.105
-· 限时完成并批改</t>
+术语与格式 M1 Ch6 直线上的一般运动 §6.1、§6.2、§6.3、§6.4
+· 速览 §6.1 速度作为位移对时间的导数 p.130（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.2 加速度作为速度对时间的导数 p.134（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.3 位移作为速度对时间的积分 p.139（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.4 速度作为加速度对时间的积分 p.148（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -3278,13 +3571,16 @@
           <t>12月13日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch4 ｜ Phy Ch3 ｜ M1 Ch4
+· 回顾：P1 Ch5 ｜ Phy Ch4 ｜ M1 Ch6
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch4 矩阵 1 §4.1、§4.2
-· §4.1 矩阵运算 p.59
-· §4.2 逆矩阵 p.65</t>
+章末复习 FM Ch4 矩阵 1
+· 章末复习题 End-of-chapter review p.92，限时 30 分钟
+· 本章要会：能算矩阵乘法、逆矩阵、行列式，并用矩阵表示常见变换
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -3294,9 +3590,12 @@
           <t>12月14日 周一
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch4 弧度制 §4.3
-· §4.3 扇形面积 p.107
-· 精读课本+做例题，整理笔记</t>
+格式训练 P1 Ch5 三角学（§5.5、§5.6）
+· Ex 5E 题 1–9（约 24 分钟，p.139）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5F 题 1–11（约 26 分钟，p.144）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -3304,10 +3603,14 @@
           <t>12月15日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch3 动力学（§3.5、§3.6）
-· 做 §3.5 课后练习并批改
-新课 Phy Ch3 动力学 §3.7
-· §3.7 理解 SI 单位</t>
+章末复习 Phy Ch4 力
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：力矩、平衡、重心、压强与密度
+· 过关自测：能对悬空/靠墙物体列力矩方程；能把力分解到任意方向；Chapter 4 EXAM-STYLE QUESTIONS 限时做完并批改
+术语与格式 Phy Ch5 功、能与功率 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 做功与能量转移（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.2 重力势能（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.3 动能（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3315,10 +3618,14 @@
           <t>12月16日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P1 Ch4 弧度制
-· 章末复习题 End-of-chapter review p.112
-新课 P1 Ch5 三角学 §5.1、§5.2
-· §5.1 0°–90° 之间的角 p.118</t>
+章末复习 P1 Ch5 三角学
+· 章末复习题 End-of-chapter review p.153，限时 30 分钟
+· 本章要会：六个三角函数的图象与恒等式、解三角方程、和角公式与 R sin(θ±α)
+· 过关自测：能默写 sin²+cos²=1 及两个变形、和角公式、倍角公式；Ex 5A–5H 错题清零；能口述「为什么解三角方程要注意区间」
+术语与格式 P1 Ch6 数列 §6.1、§6.2、§6.3、§6.4
+· 速览 §6.1 (a+b)^n 的二项式展开 p.156（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.2 二项式系数 p.160（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.3 等差数列 p.166（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -3326,9 +3633,12 @@
           <t>12月17日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch3 动力学
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+格式训练 Phy Ch5 功、能与功率（§5.1、§5.2）
+· 节末 Questions 题 全部（约 25 分钟，p.142）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.146）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3338,8 +3648,10 @@
 21:00-22:15 学术英语
 EAP 16
 · 学术讨论：seminar 发言、提问与回应
+· 词汇/术语入 Anki
 EAP 17
-· 学术写作③：报告与实验报告结构</t>
+· 学术写作③：报告与实验报告结构
+· 词汇/术语入 Anki</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -3347,13 +3659,19 @@
           <t>12月19日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch5 连接体 §5.1、§5.2
-· §5.1 牛顿第三定律 p.109
-· §5.2 杆连接的物体 p.110
+格式训练 M1 Ch6 直线上的一般运动（§6.1、§6.2）
+· Ex 6A 题 全部（约 25 分钟，p.132）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6B 题 全部（约 25 分钟，p.136）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-练习 M1 Ch5 连接体（§5.1、§5.2）
-· 做 §5.1 课后练习并批改
-· 做 §5.2 课后练习并批改</t>
+章末复习 M1 Ch6 直线上的一般运动
+· 章末复习题 End-of-chapter review p.153，限时 30 分钟
+· 本章要会：用微积分描述直线运动（v=ds/dt，a=dv/dt，s=∫v dt）
+· 过关自测：能在「x–t / v–t / a–t」三种描述间互相转换；Ex 6A–6D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -3361,13 +3679,15 @@
           <t>12月20日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch5 ｜ Phy Ch3 ｜ M1 Ch5
+· 回顾：P1 Ch6 ｜ Phy Ch5 ｜ M1 Ch6
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-练习 FM Ch4 矩阵 1（§4.1、§4.2）
-· 做 §4.1 课后练习并批改
-· 做 §4.2 课后练习并批改</t>
+术语与格式 FM Ch5 极坐标 §5.1、§5.2
+· 速览 §5.1 极坐标系 p.94（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.2 极坐标的应用 p.103（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -3377,9 +3697,12 @@
           <t>12月21日 周一
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch5 三角学（§5.1、§5.2）
-· 做 §5.1 课后练习并批改
-· 做 §5.2 课后练习并批改</t>
+格式训练 P1 Ch6 数列（§6.1、§6.2）
+· Ex 6A 题 1–16（约 34 分钟，p.158）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6B 题 1–15（约 32 分钟，p.165）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3387,9 +3710,12 @@
           <t>12月22日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch4 力 §4.1、§4.2
-· §4.1 力的合成
-· §4.2 矢量的分量</t>
+格式训练 Phy Ch5 功、能与功率（§5.3、§5.4）
+· 节末 Questions 题 全部（约 25 分钟，p.148）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.149）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -3397,9 +3723,12 @@
           <t>12月23日 周三
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch5 三角学 §5.3、§5.4
-· §5.3 任意角的三角比 p.123
-· §5.4 三角函数的图像 p.127</t>
+格式训练 P1 Ch6 数列（§6.3、§6.4）
+· Ex 6C 题 1–20（约 35 分钟，p.170）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6D 题 1–16（约 34 分钟，p.174）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3407,13 +3736,19 @@
           <t>12月24日 周四 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 物理
-练习 Phy Ch4 力（§4.1、§4.2）
-· 做 §4.1 课后练习并批改
-· 做 §4.2 课后练习并批改
+术语与格式 Phy Ch5 功、能与功率 §5.5、§5.6、§5.7
+· 速览 §5.5 下降、上升、下降：能量变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.6 能量转移（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.7 功率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 物理
-新课 Phy Ch4 力 §4.3、§4.4
-· §4.3 重心
-· §4.4 力的转动效应（力矩）</t>
+格式训练 Phy Ch5 功、能与功率（§5.5、§5.6）
+· 节末 Questions 题 全部（约 25 分钟，p.152）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.153）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -3435,13 +3770,18 @@
           <t>12月26日 周六 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch5 连接体 §5.3、§5.4
-· §5.3 绳连接的物体 p.114
-· §5.4 电梯中的物体 p.121
+术语与格式 M1 Ch7 动量 §7.1、§7.2
+· 速览 §7.1 动量 p.159（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.2 碰撞与动量守恒 p.161（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
-章末复习 M1 Ch5 连接体
-· 章末复习题 End-of-chapter review p.125
-· 限时完成并批改</t>
+章末复习 M1 Ch7 动量
+· 章末复习题 End-of-chapter review p.167，限时 30 分钟
+· 本章要会：动量与动量守恒、碰撞问题
+· 过关自测：能判断动量守恒适用于哪个方向；能处理粘连与反弹两类碰撞；Ex 7A–7B 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -3452,9 +3792,12 @@
 ★ 12月测试：P1 Ch1-5｜物理 Ch1-4
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-新课 FM Ch4 矩阵 1 §4.3、§4.4
-· §4.3 行列式 p.72
-· §4.4 矩阵变换 p.76</t>
+章末复习 FM Ch5 极坐标
+· 章末复习题 End-of-chapter review p.117，限时 30 分钟
+· 本章要会：能把曲线在直角坐标与极坐标间转换并求交面积
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -3464,13 +3807,18 @@
           <t>12月28日 周一 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 纯数
-练习 P1 Ch5 三角学（§5.3、§5.4）
-· 做 §5.3 课后练习并批改
-· 做 §5.4 课后练习并批改
+术语与格式 P1 Ch6 数列 §6.5、§6.6
+· 速览 §6.5 无穷等比级数 p.175（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.6 综合等差与等比数列 p.180（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 纯数
-新课 P1 Ch5 三角学 §5.5、§5.6
-· §5.5 反三角函数 p.136
-· §5.6 三角方程 p.140</t>
+章末复习 P1 Ch6 数列
+· 章末复习题 End-of-chapter review p.183，限时 30 分钟
+· 本章要会：等差/等比数列通项与求和、无穷等比级数收敛条件
+· 过关自测：默写等差/等比通项与求和公式；能判断 |r|&lt;1；Ex 6A–6F 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -3478,13 +3826,19 @@
           <t>12月29日 周二 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 物理
-练习 Phy Ch4 力（§4.3、§4.4）
-· 做 §4.3 课后练习并批改
-· 做 §4.4 课后练习并批改
+章末复习 Phy Ch5 功、能与功率
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：功、功率、效率、动能与势能转换
+· 过关自测：能算 W=Fs cosθ 与 P=W/t、P=Fv；能列能量守恒式；Chapter 5 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
-新课 Phy Ch4 力 §4.5
-· §4.5 力偶的力矩
-· 精读课本+做例题，整理笔记</t>
+术语与格式 Phy Ch6 动量 §6.1、§6.2、§6.3、§6.4
+· 速览 §6.1 动量的概念（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.2 碰撞建模（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.3 理解碰撞（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.4 爆炸与撞击（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3492,13 +3846,19 @@
           <t>12月30日 周三 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 纯数
-练习 P1 Ch5 三角学（§5.5、§5.6）
-· 做 §5.5 课后练习并批改
-· 做 §5.6 课后练习并批改
+术语与格式 P1 Ch7 微分 §7.1、§7.2、§7.3、§7.4
+· 速览 §7.1 导数与梯度函数 p.191（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.2 链式法则 p.198（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.3 切线与法线 p.201（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.4 二阶导数 p.205（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 15:15-16:15 纯数
-新课 P1 Ch5 三角学 §5.7、§5.8
-· §5.7 三角恒等式 p.145
-· §5.8 更复杂的三角方程 p.149</t>
+格式训练 P1 Ch7 微分（§7.1、§7.2）
+· Ex 7A 题 1–19（约 35 分钟，p.197）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 7B 题 1–8（约 22 分钟，p.201）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3506,13 +3866,19 @@
           <t>12月31日 周四 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 物理
-章末复习 Phy Ch4 力
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki
+格式训练 Phy Ch6 动量（§6.1、§6.2）
+· 节末 Questions 题 全部（约 25 分钟，p.167）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.170）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 物理
-新课 Phy Ch5 功、能与功率 §5.1、§5.2
-· §5.1 做功与能量转移
-· §5.2 重力势能</t>
+格式训练 Phy Ch6 动量（§6.3、§6.4）
+· 节末 Questions 题 全部（约 25 分钟，p.175）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.178）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E6" s="3" t="n"/>
@@ -3603,13 +3969,19 @@
           <t>1月2日 周六 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch6 直线上的一般运动 §6.1、§6.2
-· §6.1 速度作为位移对时间的导数 p.130
-· §6.2 加速度作为速度对时间的导数 p.134
+术语与格式 M1 Ch8 功与能 §8.1、§8.2、§8.3
+· 速览 §8.1 力做的功 p.171（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.2 动能 p.177（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.3 重力势能 p.179（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
-练习 M1 Ch6 直线上的一般运动（§6.1、§6.2）
-· 做 §6.1 课后练习并批改
-· 做 §6.2 课后练习并批改</t>
+格式训练 M1 Ch8 功与能（§8.1、§8.2）
+· Ex 8A 题 全部（约 25 分钟，p.173）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 全部（约 25 分钟，p.178）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -3617,13 +3989,16 @@
           <t>1月3日 周日 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch5 ｜ Phy Ch5 ｜ M1 Ch6
+· 回顾：P1 Ch7 ｜ Phy Ch6 ｜ M1 Ch8
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch4 矩阵 1
-· 章末复习题 End-of-chapter review p.92
-· 限时完成并批改</t>
+术语与格式 FM Ch6 向量（进阶） §6.1、§6.2、§6.3
+· 速览 §6.1 向量积（叉积） p.119（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.2 直线的向量方程 p.123（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.3 平面 p.128（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -3633,9 +4008,12 @@
           <t>1月4日 周一
 ────────────
 21:00-22:15 纯数
-章末复习 P1 Ch5 三角学
-· 章末复习题 End-of-chapter review p.153
-· 限时完成并批改</t>
+章末复习 P1 Ch7 微分
+· 章末复习题 End-of-chapter review p.209，限时 30 分钟
+· 本章要会：用导数定义求导、求切线/法线、判断增减性
+· 过关自测：能把 (x+h) 展开法做一遍；Ex 7A–7D 错题清零；能说清「驻点不一定是极值点」并举反例
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -3643,9 +4021,12 @@
           <t>1月5日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch5 功、能与功率（§5.1、§5.2）
-· 做 §5.1 课后练习并批改
-· 做 §5.2 课后练习并批改</t>
+术语与格式 Phy Ch6 动量 §6.5、§6.6、§6.7
+· 速览 §6.5 二维碰撞（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.6 动量与牛顿定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.7 理解运动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -3653,10 +4034,14 @@
           <t>1月6日 周三
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch6 数列 §6.1、§6.2
-· §6.1 (a+b)^n 的二项式展开 p.156
-练习 P1 Ch6 数列（§6.1、§6.2）
-· 做 §6.1 课后练习并批改</t>
+术语与格式 P1 Ch8 进阶微分 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 增函数与减函数 p.213（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.2 驻点 p.216（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.3 实际最大最小值问题 p.221（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 P1 Ch8 进阶微分（§8.1、§8.2）
+· Ex 8A 题 1–9（约 24 分钟，p.215）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 1–13（约 30 分钟，p.220）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -3664,10 +4049,14 @@
           <t>1月7日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch5 功、能与功率 §5.3、§5.4
-· §5.3 动能
-练习 Phy Ch5 功、能与功率（§5.3、§5.4）
-· 做 §5.3 课后练习并批改</t>
+格式训练 Phy Ch6 动量（§6.5、§6.6）
+· 节末 Questions 题 全部（约 25 分钟，p.181）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.183）
+章末复习 Phy Ch6 动量
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：动量守恒与碰撞（含弹性/非弹性）
+· 过关自测：能判断动量守恒的方向；能用动能计算判断碰撞类型；Chapter 6 EXAM-STYLE QUESTIONS 限时做完并批改</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -3685,13 +4074,19 @@
           <t>1月9日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch6 直线上的一般运动 §6.3、§6.4
-· §6.3 位移作为速度对时间的积分 p.139
-· §6.4 速度作为加速度对时间的积分 p.148
+章末复习 M1 Ch8 功与能
+· 章末复习题 End-of-chapter review p.183，限时 30 分钟
+· 本章要会：功、动能、重力势能的定义与计算
+· 过关自测：默写 W=Fs cosθ、KE=½mv²、PE=mgh；能计算沿斜面运动时各力做的功；Ex 8A–8C 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
-章末复习 M1 Ch6 直线上的一般运动
-· 章末复习题 End-of-chapter review p.153
-· 限时完成并批改</t>
+术语与格式 M1 Ch9 功能原理与功率 §9.1、§9.2、§9.3、§9.4
+· 速览 §9.1 功能原理 p.186（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.2 保守力系统中的能量守恒 p.193（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.3 含非保守力系统的能量守恒 p.196（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.4 功率 p.201（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -3699,13 +4094,16 @@
           <t>1月10日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch6 ｜ Phy Ch5 ｜ M1 Ch6
+· 回顾：P1 Ch8 ｜ Phy Ch6 ｜ M1 Ch9
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch5 极坐标 §5.1、§5.2
-· §5.1 极坐标系 p.94
-· §5.2 极坐标的应用 p.103</t>
+格式训练 FM Ch6 向量（进阶）（§6.1、§6.2）
+· Ex 6A 题 全部（约 25 分钟，p.121）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6B 题 全部（约 25 分钟，p.125）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
     </row>
@@ -3715,9 +4113,12 @@
           <t>1月11日 周一
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch6 数列 §6.3、§6.4
-· §6.3 等差数列 p.166
-· §6.4 等比数列 p.171</t>
+格式训练 P1 Ch8 进阶微分（§8.3、§8.4）
+· Ex 8C 题 1–15（约 32 分钟，p.224）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8D 题 1–9（约 24 分钟，p.229）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -3725,9 +4126,12 @@
           <t>1月12日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch5 功、能与功率 §5.5、§5.6
-· §5.5 下降、上升、下降：能量变化
-· §5.6 能量转移</t>
+术语与格式 Phy Ch7 物质与材料 §7.1、§7.2、§7.3、§7.4
+· 速览 §7.1 密度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.2 压强（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.3 阿基米德原理（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.4 压力与张力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -3735,9 +4139,10 @@
           <t>1月13日 周三
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch6 数列（§6.3、§6.4）
-· 做 §6.3 课后练习并批改
-· 做 §6.4 课后练习并批改</t>
+术语与格式 P1 Ch8 进阶微分 §8.5
+· 速览 §8.5 相关变化率的实际应用 p.230（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -3745,9 +4150,12 @@
           <t>1月14日 周四
 ────────────
 21:00-22:15 物理
-练习 Phy Ch5 功、能与功率（§5.5、§5.6）
-· 做 §5.5 课后练习并批改
-· 做 §5.6 课后练习并批改</t>
+格式训练 Phy Ch7 物质与材料（§7.1、§7.2）
+· 节末 Questions 题 全部（约 25 分钟，p.195）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.196）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -3765,13 +4173,19 @@
           <t>1月16日 周六
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch7 动量 §7.1、§7.2
-· §7.1 动量 p.159
-· §7.2 碰撞与动量守恒 p.161
+格式训练 M1 Ch9 功能原理与功率（§9.1、§9.2）
+· Ex 9A 题 全部（约 25 分钟，p.188）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9B 题 全部（约 25 分钟，p.195）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-章末复习 M1 Ch7 动量
-· 章末复习题 End-of-chapter review p.167
-· 限时完成并批改</t>
+章末复习 M1 Ch9 功能原理与功率
+· 章末复习题 End-of-chapter review p.206，限时 30 分钟
+· 本章要会：功能原理、保守/非保守系统的能量守恒、功率
+· 过关自测：能列出「初动能+初势能+外力做功=末动能+末势能」；能算恒定力与瞬时功率；Ex 9A–9D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -3779,13 +4193,16 @@
           <t>1月17日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch6 ｜ Phy Ch5 ｜ M1 Ch7
+· 回顾：P1 Ch8 ｜ Phy Ch7 ｜ M1 Ch9
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch5 极坐标
-· 章末复习题 End-of-chapter review p.117
-· 限时完成并批改</t>
+章末复习 FM Ch6 向量（进阶）
+· 章末复习题 End-of-chapter review p.138，限时 30 分钟
+· 本章要会：能算向量积、写直线与平面的向量方程
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -3795,9 +4212,12 @@
           <t>1月18日 周一
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch6 数列 §6.5、§6.6
-· §6.5 无穷等比级数 p.175
-· §6.6 综合等差与等比数列 p.180</t>
+章末复习 P1 Ch8 进阶微分
+· 章末复习题 End-of-chapter review p.235，限时 30 分钟
+· 本章要会：链式法则、乘积/商法则、隐函数与参数方程求导
+· 过关自测：三类法则各能默写并各做 5 题全对；Ex 8A–8E 错题清零；能说清 dy/dx 里「谁是自变量」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -3805,9 +4225,12 @@
           <t>1月19日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch5 功、能与功率 §5.7
-· §5.7 功率
-· 精读课本+做例题，整理笔记</t>
+格式训练 Phy Ch7 物质与材料（§7.3、§7.4）
+· 节末 Questions 题 全部（约 25 分钟，p.200）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.201）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3815,10 +4238,14 @@
           <t>1月20日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P1 Ch6 数列
-· 章末复习题 End-of-chapter review p.183
-新课 P1 Ch7 微分 §7.1、§7.2
-· §7.1 导数与梯度函数 p.191</t>
+术语与格式 P1 Ch9 积分 §9.1、§9.2、§9.3、§9.4
+· 速览 §9.1 积分是微分的逆运算 p.239（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.2 求积分常数 p.244（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.3 (ax+b)^n 型函数的积分 p.247（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 P1 Ch9 积分（§9.1、§9.2）
+· Ex 9A 题 1–7（约 20 分钟，p.243）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9B 题 1–18（约 35 分钟，p.245）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -3826,10 +4253,14 @@
           <t>1月21日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch5 功、能与功率
-· 章末复习题 End-of-chapter review
-新课 Phy Ch6 动量 §6.1、§6.2
-· §6.1 动量的概念</t>
+术语与格式 Phy Ch7 物质与材料 §7.5、§7.6
+· 速览 §7.5 材料的拉伸（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.6 弹性势能（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+章末复习 Phy Ch7 物质与材料
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：材料力学性质、应力应变、杨氏模量、弹性形变
+· 过关自测：能画应力—应变图并标出弹性极限/屈服点；能算 Young 模量 E=Fl/Ax；Chapter 7 EXAM-STYLE QUESTIONS 限时做完并批改</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -3847,13 +4278,19 @@
           <t>1月23日 周六 ◆寒假
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch8 功与能 §8.1、§8.2
-· §8.1 力做的功 p.171
-· §8.2 动能 p.177
+术语与格式 S1 Ch1 数据的表示 §1.1、§1.2、§1.3、§1.4
+· 速览 §1.1 数据的类型 p.2（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.2 离散数据的表示：茎叶图 p.3（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.3 连续数据的表示：直方图 p.6（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.4 连续数据的表示：累积频率图 p.13（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 20:00-21:00 应用数学
-练习 M1 Ch8 功与能（§8.1、§8.2）
-· 做 §8.1 课后练习并批改
-· 做 §8.2 课后练习并批改</t>
+格式训练 S1 Ch1 数据的表示（§1.1、§1.2）
+· Ex 1A 题 1–9（约 24 分钟，p.4）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1B 题 1–13（约 30 分钟，p.10）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3864,9 +4301,11 @@
 ★ 寒假前测试：P1 Ch1-6｜物理 Ch1-5
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-新课 FM Ch6 向量（进阶） §6.1、§6.2
-· §6.1 向量积（叉积） p.119
-· §6.2 直线的向量方程 p.123</t>
+术语与格式 FM Ch7 数学归纳法 §7.1、§7.2
+· 速览 §7.1 归纳过程 p.140（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.2 整除性的归纳证明 p.146（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -3876,13 +4315,19 @@
           <t>1月25日 周一 ◆寒假
 ────────────
 14:00-15:00 纯数
-练习 P1 Ch7 微分（§7.1、§7.2）
-· 做 §7.1 课后练习并批改
-· 做 §7.2 课后练习并批改
+格式训练 P1 Ch9 积分（§9.3、§9.4）
+· Ex 9C 题 1–8（约 22 分钟，p.248）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9D 题 1–8（约 22 分钟，p.249）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 纯数
-新课 P1 Ch7 微分 §7.3、§7.4
-· §7.3 切线与法线 p.201
-· §7.4 二阶导数 p.205</t>
+术语与格式 P1 Ch9 积分 §9.5、§9.6、§9.7、§9.8
+· 速览 §9.5 定积分 p.250（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.6 曲线下的面积 p.253（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.7 曲线与直线/两曲线围成的面积 p.260（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.8 反常（广义）积分 p.264（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -3890,13 +4335,19 @@
           <t>1月26日 周二 ◆寒假
 ────────────
 14:00-15:00 物理
-练习 Phy Ch6 动量（§6.1、§6.2）
-· 做 §6.1 课后练习并批改
-· 做 §6.2 课后练习并批改
+术语与格式 Phy Ch8 电流 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 电路符号与电路图（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.2 电流（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.3 电流的公式（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.4 电压的含义（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 15:15-16:15 物理
-新课 Phy Ch6 动量 §6.3、§6.4
-· §6.3 理解碰撞
-· §6.4 爆炸与撞击</t>
+格式训练 Phy Ch8 电流（§8.1、§8.2）
+· 节末 Questions 题 全部（约 25 分钟，p.223）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.226）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3904,13 +4355,19 @@
           <t>1月27日 周三 ◆寒假
 ────────────
 14:00-15:00 纯数
-章末复习 P1 Ch7 微分
-· 章末复习题 End-of-chapter review p.209
-· 限时完成并批改
+格式训练 P1 Ch9 积分（§9.5、§9.6）
+· Ex 9E 题 1–9（约 24 分钟，p.252）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9F 题 1–14（约 31 分钟，p.256）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 纯数
-新课 P1 Ch8 进阶微分 §8.1、§8.2
-· §8.1 增函数与减函数 p.213
-· §8.2 驻点 p.216</t>
+格式训练 P1 Ch9 积分（§9.7、§9.8）
+· Ex 9G 题 1–10（约 25 分钟，p.262）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9H 题 1–4（约 16 分钟，p.267）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -3918,13 +4375,18 @@
           <t>1月28日 周四 ◆寒假
 ────────────
 14:00-15:00 物理
-练习 Phy Ch6 动量（§6.3、§6.4）
-· 做 §6.3 课后练习并批改
-· 做 §6.4 课后练习并批改
+格式训练 Phy Ch8 电流（§8.3、§8.4）
+· 节末 Questions 题 全部（约 25 分钟，p.228）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.233）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 物理
-新课 Phy Ch6 动量 §6.5、§6.6
-· §6.5 二维碰撞
-· §6.6 动量与牛顿定律</t>
+术语与格式 Phy Ch8 电流 §8.5、§8.6
+· 速览 §8.5 电阻（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.6 电功率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -3946,13 +4408,17 @@
           <t>1月30日 周六 ◆寒假
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch8 功与能 §8.3
-· §8.3 重力势能 p.179
-· 精读课本+做例题，整理笔记
+格式训练 S1 Ch1 数据的表示（§1.3、§1.4）
+· Ex 1C 题 1–11（约 26 分钟，p.16）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1D 题 1–9（约 24 分钟，p.21）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-章末复习 M1 Ch8 功与能
-· 章末复习题 End-of-chapter review p.183
-· 限时完成并批改</t>
+术语与格式 S1 Ch1 数据的表示 §1.5
+· 速览 §1.5 不同数据表示方法的比较 p.20（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3960,13 +4426,16 @@
           <t>1月31日 周日 ◆寒假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch8 ｜ Phy Ch6 ｜ M1 Ch8
+· 回顾：P1 Ch9 ｜ Phy Ch8 ｜ S1 Ch1
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-练习 FM Ch6 向量（进阶）（§6.1、§6.2）
-· 做 §6.1 课后练习并批改
-· 做 §6.2 课后练习并批改</t>
+章末复习 FM Ch7 数学归纳法
+· 章末复习题 End-of-chapter review p.151，限时 30 分钟
+· 本章要会：能写标准归纳法三步并证明整除性命题
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -4036,13 +4505,17 @@
           <t>2月1日 周一 ◆寒假
 ────────────
 14:00-15:00 纯数
-练习 P1 Ch8 进阶微分（§8.1、§8.2）
-· 做 §8.1 课后练习并批改
-· 做 §8.2 课后练习并批改
+术语与格式 P1 Ch9 积分 §9.9
+· 速览 §9.9 旋转体体积 p.268（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 纯数
-新课 P1 Ch8 进阶微分 §8.3、§8.4
-· §8.3 实际最大最小值问题 p.221
-· §8.4 变化率 p.227</t>
+章末复习 P1 Ch9 积分
+· 章末复习题 End-of-chapter review p.276，限时 30 分钟
+· 本章要会：不定积分与定积分、面积与体积、换元与分部积分
+· 过关自测：能默写 ∫xⁿ、∫sin、∫cos、∫eˣ 的积分表；Ex 9A–9I 错题清零；能用定积分求一条曲线与 x 轴围成的面积
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -4050,13 +4523,19 @@
           <t>2月2日 周二 ◆寒假
 ────────────
 14:00-15:00 物理
-练习 Phy Ch6 动量（§6.5、§6.6）
-· 做 §6.5 课后练习并批改
-· 做 §6.6 课后练习并批改
+章末复习 Phy Ch8 电流
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：电流、电荷守恒、基尔霍夫电流定律
+· 过关自测：能默写 I=Q/t；能在电路图中标出电流方向与大小；Chapter 8 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
-新课 Phy Ch6 动量 §6.7
-· §6.7 理解运动
-· 精读课本+做例题，整理笔记</t>
+术语与格式 Phy Ch9 基尔霍夫定律 §9.1、§9.2、§9.3、§9.4
+· 速览 §9.1 基尔霍夫第一定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.2 基尔霍夫第二定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.3 基尔霍夫定律的应用（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.4 电阻的组合（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4064,13 +4543,19 @@
           <t>2月3日 周三 ◆寒假
 ────────────
 14:00-15:00 纯数
-练习 P1 Ch8 进阶微分（§8.3、§8.4）
-· 做 §8.3 课后练习并批改
-· 做 §8.4 课后练习并批改
+术语与格式 P2/3 Ch1 代数 §1.1、§1.2、§1.3、§1.4
+· 速览 §1.1 绝对值函数 p.2（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.2 线性函数的绝对值图像 p.7（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.3 绝对值不等式 p.8（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.4 多项式的除法 p.11（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 15:15-16:15 纯数
-新课 P1 Ch8 进阶微分 §8.5
-· §8.5 相关变化率的实际应用 p.230
-· 精读课本+做例题，整理笔记</t>
+格式训练 P2/3 Ch1 代数（§1.1、§1.2）
+· Ex 1A 题 1–9（约 24 分钟，p.6）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1B 题 1–8（约 22 分钟，p.8）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -4078,13 +4563,19 @@
           <t>2月4日 周四 ◆寒假
 ────────────
 14:00-15:00 物理
-章末复习 Phy Ch6 动量
-· 章末复习题 End-of-chapter review
+格式训练 Phy Ch9 基尔霍夫定律（§9.1、§9.2）
+· 节末 Questions 题 全部（约 25 分钟，p.249）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.251）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+15:15-16:15 物理
+章末复习 Phy Ch9 基尔霍夫定律
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：基尔霍夫定律与电路求解、电动势与内阻
+· 过关自测：能对回路列 KVL；能算端电压 U=ε−Ir；Chapter 9 EXAM-STYLE QUESTIONS 限时做完并批改
 · 本章公式/术语卡入 Anki
-15:15-16:15 物理
-新课 Phy Ch7 物质与材料 §7.1、§7.2
-· §7.1 密度
-· §7.2 压强</t>
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -4102,9 +4593,12 @@
           <t>2月6日 周六 ◆寒假
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch9 功能原理与功率 §9.1、§9.2
-· §9.1 功能原理 p.186
-· §9.2 保守力系统中的能量守恒 p.193</t>
+章末复习 S1 Ch1 数据的表示
+· 章末复习题 End-of-chapter review p.24，限时 30 分钟
+· 本章要会：数据表示：stem-and-leaf、直方图、累积频数图、箱线图
+· 过关自测：能画 stem-and-leaf 并写 key；能从累积频数图读中位数与四分位数；Ex 1A–1D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -4112,7 +4606,7 @@
           <t>2月7日 周日 ◆寒假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch8 ｜ Phy Ch7 ｜ M1 Ch9
+· 回顾：P2/3 Ch1 ｜ Phy Ch9 ｜ S1 Ch1
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划</t>
         </is>
@@ -4124,9 +4618,12 @@
           <t>2月8日 周一 ◆寒假
 ────────────
 14:00-15:00 纯数
-章末复习 P1 Ch8 进阶微分
-· 章末复习题 End-of-chapter review p.235
-· 限时完成并批改</t>
+格式训练 P2/3 Ch1 代数（§1.3、§1.4）
+· Ex 1C 题 1–6（约 19 分钟，p.10）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1D 题 1–7（约 20 分钟，p.13）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -4134,9 +4631,12 @@
           <t>2月9日 周二 ◆寒假
 ────────────
 14:00-15:00 物理
-练习 Phy Ch7 物质与材料（§7.1、§7.2）
-· 做 §7.1 课后练习并批改
-· 做 §7.2 课后练习并批改</t>
+术语与格式 Phy Ch10 电阻与电阻率 §10.1、§10.2、§10.3、§10.4
+· 速览 §10.1 金属导体的 I–V 特性（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §10.2 欧姆定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §10.3 电阻与温度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §10.4 电阻率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4144,9 +4644,11 @@
           <t>2月10日 周三 ◆寒假
 ────────────
 14:00-15:00 纯数
-新课 P1 Ch9 积分 §9.1、§9.2
-· §9.1 积分是微分的逆运算 p.239
-· §9.2 求积分常数 p.244</t>
+术语与格式 P2/3 Ch1 代数 §1.5、§1.6
+· 速览 §1.5 因式定理 p.14（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §1.6 余数定理 p.18（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -4154,9 +4656,12 @@
           <t>2月11日 周四 ◆寒假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch7 物质与材料 §7.3、§7.4
-· §7.3 阿基米德原理
-· §7.4 压力与张力</t>
+格式训练 Phy Ch10 电阻与电阻率（§10.1、§10.2）
+· 节末 Questions 题 全部（约 25 分钟，p.271）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.273）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -4174,9 +4679,12 @@
           <t>2月13日 周六 ◆寒假
 ────────────
 14:00-15:00 应用数学
-练习 M1 Ch9 功能原理与功率（§9.1、§9.2）
-· 做 §9.1 课后练习并批改
-· 做 §9.2 课后练习并批改</t>
+术语与格式 S1 Ch2 集中趋势的度量 §2.1、§2.2、§2.3
+· 速览 §2.1 众数与众数类 p.28（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.2 平均数 p.30（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.3 中位数 p.42（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -4184,13 +4692,15 @@
           <t>2月14日 周日 ◆寒假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch9 ｜ Phy Ch7 ｜ M1 Ch9
+· 回顾：P2/3 Ch1 ｜ Phy Ch10 ｜ S1 Ch2
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch6 向量（进阶） §6.3
-· §6.3 平面 p.128
-· 精读课本+做例题，整理笔记</t>
+术语与格式 FM Ch13 抛体运动 §13.1、§13.2
+· 速览 §13.1 竖直平面内的运动 p.309（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §13.2 轨迹的直角坐标方程 p.314（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -4200,13 +4710,19 @@
           <t>2月15日 周一 ◆寒假
 ────────────
 14:00-15:00 纯数
-练习 P1 Ch9 积分（§9.1、§9.2）
-· 做 §9.1 课后练习并批改
-· 做 §9.2 课后练习并批改
+章末复习 P2/3 Ch1 代数
+· 章末复习题 End-of-chapter review p.22，限时 30 分钟
+· 本章要会：指数与对数运算法则、解指数/对数方程与不等式
+· 过关自测：默写 3 条对数法则；Ex 1A–1F 错题清零；能判断写出 log 时定义域的限制
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 纯数
-新课 P1 Ch9 积分 §9.3、§9.4
-· §9.3 (ax+b)^n 型函数的积分 p.247
-· §9.4 进一步的不定积分 p.249</t>
+术语与格式 P2/3 Ch2 对数与指数函数 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 以 10 为底的对数 p.26（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.2 以 a 为底的对数 p.30（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.3 对数的运算法则 p.33（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.4 解对数方程 p.35（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -4214,13 +4730,19 @@
           <t>2月16日 周二 ◆寒假
 ────────────
 14:00-15:00 物理
-练习 Phy Ch7 物质与材料（§7.3、§7.4）
-· 做 §7.3 课后练习并批改
-· 做 §7.4 课后练习并批改
+章末复习 Phy Ch10 电阻与电阻率
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：电阻、电阻率、温度对电阻的影响
+· 过关自测：能默写 R=ρl/A；能画 I–V 图并区分欧姆/非欧姆器件；Chapter 10 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
-新课 Phy Ch7 物质与材料 §7.5、§7.6
-· §7.5 材料的拉伸
-· §7.6 弹性势能</t>
+术语与格式 Phy Ch11 实用电路 §11.1、§11.2、§11.3、§11.4
+· 速览 §11.1 内阻（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §11.2 分压器（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §11.3 传感器（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §11.4 电位器电路（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -4228,13 +4750,19 @@
           <t>2月17日 周三 ◆寒假
 ────────────
 14:00-15:00 纯数
-练习 P1 Ch9 积分（§9.3、§9.4）
-· 做 §9.3 课后练习并批改
-· 做 §9.4 课后练习并批改
+格式训练 P2/3 Ch2 对数与指数函数（§2.1、§2.2）
+· Ex 2A 题 1–7（约 20 分钟，p.29）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 1–9（约 24 分钟，p.32）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 纯数
-新课 P1 Ch9 积分 §9.5、§9.6
-· §9.5 定积分 p.250
-· §9.6 曲线下的面积 p.253</t>
+格式训练 P2/3 Ch2 对数与指数函数（§2.3、§2.4）
+· Ex 2C 题 1–13（约 30 分钟，p.34）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2D 题 1–10（约 25 分钟，p.37）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -4242,13 +4770,19 @@
           <t>2月18日 周四 ◆寒假
 ────────────
 14:00-15:00 物理
-章末复习 Phy Ch7 物质与材料
-· 章末复习题 End-of-chapter review
+格式训练 Phy Ch11 实用电路（§11.1、§11.2）
+· 节末 Questions 题 全部（约 25 分钟，p.292）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.295）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+15:15-16:15 物理
+章末复习 Phy Ch11 实用电路
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：分压与分流、电位器、内阻影响
+· 过关自测：能设计分压电路；能算串联/并联等效电阻；Chapter 11 EXAM-STYLE QUESTIONS 限时做完并批改
 · 本章公式/术语卡入 Anki
-15:15-16:15 物理
-新课 Phy Ch8 电流 §8.1、§8.2
-· §8.1 电路符号与电路图
-· §8.2 电流</t>
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -4270,13 +4804,19 @@
           <t>2月20日 周六 ◆寒假
 ────────────
 14:00-15:00 应用数学
-新课 M1 Ch9 功能原理与功率 §9.3、§9.4
-· §9.3 含非保守力系统的能量守恒 p.196
-· §9.4 功率 p.201
+格式训练 S1 Ch2 集中趋势的度量（§2.1、§2.2）
+· Ex 2A 题 1–6（约 19 分钟，p.29）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 1–17（约 35 分钟，p.34）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-章末复习 M1 Ch9 功能原理与功率
-· 章末复习题 End-of-chapter review p.206
-· 限时完成并批改</t>
+章末复习 S1 Ch2 集中趋势的度量
+· 章末复习题 End-of-chapter review p.51，限时 30 分钟
+· 本章要会：均值、中位数、众数、分组数据的估计均值
+· 过关自测：能算分组数据的估计均值；能说明为什么估计均值有误差；Ex 2A–2E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -4284,13 +4824,16 @@
           <t>2月21日 周日 ◆寒假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch9 ｜ Phy Ch8 ｜ M1 Ch9
+· 回顾：P2/3 Ch2 ｜ Phy Ch11 ｜ S1 Ch2
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch6 向量（进阶）
-· 章末复习题 End-of-chapter review p.138
-· 限时完成并批改</t>
+章末复习 FM Ch13 抛体运动
+· 章末复习题 End-of-chapter review p.320，限时 30 分钟
+· 本章要会：能把抛体运动分解为水平匀速+竖直匀加速并求轨迹方程
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -4300,9 +4843,12 @@
           <t>2月22日 周一
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch9 积分（§9.5、§9.6）
-· 做 §9.5 课后练习并批改
-· 做 §9.6 课后练习并批改</t>
+术语与格式 P2/3 Ch2 对数与指数函数 §2.5、§2.6、§2.7、§2.8
+· 速览 §2.5 解指数方程 p.38（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.6 解指数不等式 p.40（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.7 自然对数 p.42（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §2.8 把关系式化为线性形式 p.44（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4310,9 +4856,12 @@
           <t>2月23日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch8 电流（§8.1、§8.2）
-· 做 §8.1 课后练习并批改
-· 做 §8.2 课后练习并批改</t>
+术语与格式 Phy Ch12 波 §12.1、§12.2、§12.3、§12.4
+· 速览 §12.1 描述波（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §12.2 横波与纵波（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §12.3 波的能量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §12.4 波速（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -4320,9 +4869,12 @@
           <t>2月24日 周三
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch9 积分 §9.7、§9.8
-· §9.7 曲线与直线/两曲线围成的面积 p.260
-· §9.8 反常（广义）积分 p.264</t>
+格式训练 P2/3 Ch2 对数与指数函数（§2.5、§2.6）
+· Ex 2E 题 1–13（约 30 分钟，p.39）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2F 题 1–7（约 20 分钟，p.41）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4330,9 +4882,12 @@
           <t>2月25日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch8 电流 §8.3、§8.4
-· §8.3 电流的公式
-· §8.4 电压的含义</t>
+格式训练 Phy Ch12 波（§12.1、§12.2）
+· 节末 Questions 题 全部（约 25 分钟，p.313）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.314）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -4342,8 +4897,10 @@
 21:00-22:15 学术英语
 EAP 31
 · 学术阅读③：长篇文献速读与结构化笔记
+· 词汇/术语入 Anki
 EAP 32
-· 学术写作⑧：批判性写作</t>
+· 学术写作⑧：批判性写作
+· 词汇/术语入 Anki</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -4351,13 +4908,19 @@
           <t>2月27日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch1 数据的表示 §1.1、§1.2
-· §1.1 数据的类型 p.2
-· §1.2 离散数据的表示：茎叶图 p.3
+术语与格式 S1 Ch3 离散程度的度量 §3.1、§3.2、§3.3
+· 速览 §3.1 极差 p.55（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.2 四分位距与百分位数 p.56（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.3 方差与标准差 p.65（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
-练习 S1 Ch1 数据的表示（§1.1、§1.2）
-· 做 §1.1 课后练习并批改
-· 做 §1.2 课后练习并批改</t>
+格式训练 S1 Ch3 离散程度的度量（§3.1、§3.2）
+· Ex 3A 题 1–13（约 30 分钟，p.61）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3B 题 1–12（约 28 分钟，p.69）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -4368,9 +4931,12 @@
 ★ 2月测试：P1 全部｜物理 Ch1-7｜M1 全书
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-新课 FM Ch7 数学归纳法 §7.1、§7.2
-· §7.1 归纳过程 p.140
-· §7.2 整除性的归纳证明 p.146</t>
+术语与格式 FM Ch14 刚体平衡 §14.1、§14.2、§14.3、§14.4
+· 速览 §14.1 力矩 p.322（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §14.2 杆与薄板的重心 p.326（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §14.3 立体的重心 p.336（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §14.4 物体的平衡 p.341（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
     </row>
@@ -4440,9 +5006,12 @@
           <t>3月1日 周一
 ────────────
 21:00-22:15 纯数
-练习 P1 Ch9 积分（§9.7、§9.8）
-· 做 §9.7 课后练习并批改
-· 做 §9.8 课后练习并批改</t>
+章末复习 P2/3 Ch2 对数与指数函数
+· 章末复习题 End-of-chapter review p.50，限时 30 分钟
+· 本章要会：eˣ 与 ln x 的图象与性质、把它们用于建模（增长/衰减）
+· 过关自测：能画 y=eˣ 与 y=ln x 并说出互为反函数；Ex 2A–2H 错题清零；能把「翻倍时间」问题列成指数方程
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -4450,9 +5019,12 @@
           <t>3月2日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch8 电流（§8.3、§8.4）
-· 做 §8.3 课后练习并批改
-· 做 §8.4 课后练习并批改</t>
+格式训练 Phy Ch12 波（§12.3、§12.4）
+· 节末 Questions 题 全部（约 25 分钟，p.316）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.319）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -4460,10 +5032,14 @@
           <t>3月3日 周三
 ────────────
 21:00-22:15 纯数
-新课 P1 Ch9 积分 §9.9
-· §9.9 旋转体体积 p.268
-章末复习 P1 Ch9 积分
-· 章末复习题 End-of-chapter review p.276</t>
+术语与格式 P2/3 Ch3 三角学 §3.1、§3.2、§3.3、§3.4
+· 速览 §3.1 cosec / sec / cot p.53（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.2 和角公式 p.58（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §3.3 倍角公式 p.61（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 P2/3 Ch3 三角学（§3.1、§3.2）
+· Ex 3A 题 1–14（约 31 分钟，p.56）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3B 题 1–17（约 35 分钟，p.60）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -4471,10 +5047,14 @@
           <t>3月4日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch8 电流 §8.5、§8.6
-· §8.5 电阻
-章末复习 Phy Ch8 电流
-· 章末复习题 End-of-chapter review</t>
+术语与格式 Phy Ch12 波 §12.5、§12.6、§12.7、§12.8
+· 速览 §12.5 声波的多普勒效应（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §12.6 电磁波（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §12.7 电磁辐射（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 Phy Ch12 波（§12.5、§12.6）
+· 节末 Questions 题 全部（约 25 分钟，p.320）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.323）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -4492,13 +5072,19 @@
           <t>3月6日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch1 数据的表示 §1.3、§1.4
-· §1.3 连续数据的表示：直方图 p.6
-· §1.4 连续数据的表示：累积频率图 p.13
+章末复习 S1 Ch3 离散程度的度量
+· 章末复习题 End-of-chapter review p.83，限时 30 分钟
+· 本章要会：极差/四分位距/方差/标准差、用编码简化计算
+· 过关自测：默写方差与标准差公式（原始与编码两种）；能对数据做编码 y=(x−a)/b 并还原；Ex 3A–3E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
-练习 S1 Ch1 数据的表示（§1.3、§1.4）
-· 做 §1.3 课后练习并批改
-· 做 §1.4 课后练习并批改</t>
+术语与格式 S1 Ch4 概率 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 试验、事件与结果 p.91（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.2 互斥事件与加法法则 p.94（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.3 独立事件与乘法法则 p.100（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.4 条件概率 p.108（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -4506,13 +5092,16 @@
           <t>3月7日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch9 ｜ Phy Ch8 ｜ S1 Ch1
+· 回顾：P2/3 Ch3 ｜ Phy Ch12 ｜ S1 Ch4
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch7 数学归纳法
-· 章末复习题 End-of-chapter review p.151
-· 限时完成并批改</t>
+格式训练 FM Ch14 刚体平衡（§14.1、§14.2）
+· Ex 14A 题 全部（约 25 分钟，p.324）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 14B 题 全部（约 25 分钟，p.328）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
     </row>
@@ -4522,9 +5111,12 @@
           <t>3月8日 周一
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch1 代数 §1.1、§1.2
-· §1.1 绝对值函数 p.2
-· §1.2 线性函数的绝对值图像 p.7</t>
+格式训练 P2/3 Ch3 三角学（§3.3、§3.4）
+· Ex 3C 题 1–19（约 35 分钟，p.64）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3D 题 1–6（约 19 分钟，p.67）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4532,9 +5124,12 @@
           <t>3月9日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch9 基尔霍夫定律 §9.1、§9.2
-· §9.1 基尔霍夫第一定律
-· §9.2 基尔霍夫第二定律</t>
+格式训练 Phy Ch12 波（§12.7、§12.8）
+· 节末 Questions 题 全部（约 25 分钟，p.325）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.326）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -4542,9 +5137,10 @@
           <t>3月10日 周三
 ────────────
 21:00-22:15 纯数
-练习 P2/3 Ch1 代数（§1.1、§1.2）
-· 做 §1.1 课后练习并批改
-· 做 §1.2 课后练习并批改</t>
+术语与格式 P2/3 Ch3 三角学 §3.5
+· 速览 §3.5 a sinθ + b cosθ 化为 R sin(θ±α) p.68（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -4552,9 +5148,11 @@
           <t>3月11日 周四
 ────────────
 21:00-22:15 物理
-练习 Phy Ch9 基尔霍夫定律（§9.1、§9.2）
-· 做 §9.1 课后练习并批改
-· 做 §9.2 课后练习并批改</t>
+术语与格式 Phy Ch12 波 §12.9、§12.10
+· 速览 §12.9 电磁波的本质（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §12.10 偏振（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -4572,13 +5170,19 @@
           <t>3月13日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch1 数据的表示 §1.5
-· §1.5 不同数据表示方法的比较 p.20
-· 精读课本+做例题，整理笔记
+格式训练 S1 Ch4 概率（§4.1、§4.2）
+· Ex 4A 题 1–8（约 22 分钟，p.93）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 1–15（约 32 分钟，p.98）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-章末复习 S1 Ch1 数据的表示
-· 章末复习题 End-of-chapter review p.24
-· 限时完成并批改</t>
+格式训练 S1 Ch4 概率（§4.3、§4.4）
+· Ex 4C 题 1–16（约 34 分钟，p.102）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4E 题 1–10（约 25 分钟，p.110）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -4586,13 +5190,16 @@
           <t>3月14日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch1 ｜ Phy Ch9 ｜ S1 Ch1
+· 回顾：P2/3 Ch3 ｜ Phy Ch12 ｜ S1 Ch4
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch13 抛体运动 §13.1、§13.2
-· §13.1 竖直平面内的运动 p.309
-· §13.2 轨迹的直角坐标方程 p.314</t>
+章末复习 FM Ch14 刚体平衡
+· 章末复习题 End-of-chapter review p.352，限时 30 分钟
+· 本章要会：能求杆/薄板/立体的重心并解刚体平衡
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -4602,9 +5209,12 @@
           <t>3月15日 周一
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch1 代数 §1.3、§1.4
-· §1.3 绝对值不等式 p.8
-· §1.4 多项式的除法 p.11</t>
+章末复习 P2/3 Ch3 三角学
+· 章末复习题 End-of-chapter review p.74，限时 30 分钟
+· 本章要会：反三角与小角度近似、R 形式求解、更复杂的三角方程
+· 过关自测：能默写 asin/acos/atan 的值域（这是考点）；Ex 3A–3E 错题清零；能把 a sinθ+b cosθ 化成 R sin(θ+α)
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -4612,9 +5222,12 @@
           <t>3月16日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch9 基尔霍夫定律 §9.3、§9.4
-· §9.3 基尔霍夫定律的应用
-· §9.4 电阻的组合</t>
+章末复习 Phy Ch12 波
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：波的基本性质：频率、波长、波速、横波纵波、电磁波
+· 过关自测：能默写 v=fλ；能区分横波纵波与偏振；能读示波器波形；Chapter 12 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -4622,10 +5235,14 @@
           <t>3月17日 周三
 ────────────
 21:00-22:15 纯数
-练习 P2/3 Ch1 代数（§1.3、§1.4）
-· 做 §1.3 课后练习并批改
-新课 P2/3 Ch1 代数 §1.5、§1.6
-· §1.5 因式定理 p.14</t>
+术语与格式 P2/3 Ch4 微分 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 乘积法则 p.81（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.2 商法则 p.84（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.3 指数函数的导数 p.87（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 P2/3 Ch4 微分（§4.1、§4.2）
+· Ex 4A 题 1–8（约 22 分钟，p.83）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 1–13（约 30 分钟，p.87）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -4633,10 +5250,14 @@
           <t>3月18日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch9 基尔霍夫定律
-· 章末复习题 End-of-chapter review
-新课 Phy Ch10 电阻与电阻率 §10.1、§10.2
-· §10.1 金属导体的 I–V 特性</t>
+术语与格式 Phy Ch13 波的叠加 §13.1、§13.2、§13.3、§13.4
+· 速览 §13.1 波的叠加原理（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §13.2 波的衍射（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §13.3 干涉（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 Phy Ch13 波的叠加（§13.1、§13.2）
+· 节末 Questions 题 全部（约 25 分钟，p.341）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.343）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -4654,13 +5275,17 @@
           <t>3月20日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch2 集中趋势的度量 §2.1、§2.2
-· §2.1 众数与众数类 p.28
-· §2.2 平均数 p.30
+术语与格式 S1 Ch4 概率 §4.5
+· 速览 §4.5 非独立事件与条件概率 p.112（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
-练习 S1 Ch2 集中趋势的度量（§2.1、§2.2）
-· 做 §2.1 课后练习并批改
-· 做 §2.2 课后练习并批改</t>
+章末复习 S1 Ch4 概率
+· 章末复习题 End-of-chapter review p.118，限时 30 分钟
+· 本章要会：概率公理、互斥与独立、条件概率、树形图与韦恩图
+· 过关自测：默写 P(A∪B)=P(A)+P(B)−P(A∩B) 与 P(A|B)=P(A∩B)/P(B)；能区分互斥与独立；Ex 4A–4F 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -4668,13 +5293,16 @@
           <t>3月21日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch1 ｜ Phy Ch10 ｜ S1 Ch2
+· 回顾：P2/3 Ch4 ｜ Phy Ch13 ｜ S1 Ch4
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch13 抛体运动
-· 章末复习题 End-of-chapter review p.320
-· 限时完成并批改</t>
+术语与格式 FM Ch15 圆周运动（进阶） §15.1、§15.2、§15.3
+· 速览 §15.1 水平圆 p.355（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.2 三维情形 p.360（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.3 竖直圆 p.365（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -4684,9 +5312,12 @@
           <t>3月22日 周一
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch1 代数
-· 章末复习题 End-of-chapter review p.25
-· 限时完成并批改</t>
+格式训练 P2/3 Ch4 微分（§4.3、§4.4）
+· Ex 4C 题 1–14（约 31 分钟，p.90）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4D 题 1–12（约 28 分钟，p.94）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4694,9 +5325,12 @@
           <t>3月23日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch10 电阻与电阻率（§10.1、§10.2）
-· 做 §10.1 课后练习并批改
-· 做 §10.2 课后练习并批改</t>
+格式训练 Phy Ch13 波的叠加（§13.3、§13.4）
+· 节末 Questions 题 全部（约 25 分钟，p.347）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.356）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -4704,9 +5338,12 @@
           <t>3月24日 周三
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch2 对数与指数函数 §2.1、§2.2
-· §2.1 以 10 为底的对数 p.26
-· §2.2 以 a 为底的对数 p.30</t>
+术语与格式 P2/3 Ch4 微分 §4.5、§4.6、§4.7
+· 速览 §4.5 三角函数的导数 p.95（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.6 隐函数求导 p.99（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §4.7 参数方程求导 p.103（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -4714,9 +5351,10 @@
           <t>3月25日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch10 电阻与电阻率 §10.3、§10.4
-· §10.3 电阻与温度
-· §10.4 电阻率</t>
+术语与格式 Phy Ch13 波的叠加 §13.5
+· 速览 §13.5 衍射光栅（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -4726,8 +5364,10 @@
 21:00-22:15 学术英语
 EAP 36
 · 学术写作⑩：EAP 真题 essay 题目精练
+· 词汇/术语入 Anki
 EAP 37
-· 综合复习：EAP 读听说写技能串联</t>
+· 综合复习：EAP 读听说写技能串联
+· 词汇/术语入 Anki</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -4735,13 +5375,19 @@
           <t>3月27日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch2 集中趋势的度量 §2.3
-· §2.3 中位数 p.33
-· 精读课本+做例题，整理笔记
+术语与格式 S1 Ch5 排列与组合 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 阶乘函数 p.124（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.2 排列 p.125（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.3 组合 p.135（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.4 排列组合的应用 p.138（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 20:00-21:00 应用数学
-章末复习 S1 Ch2 集中趋势的度量
-· 章末复习题 End-of-chapter review p.38
-· 限时完成并批改</t>
+格式训练 S1 Ch5 排列与组合（§5.1、§5.2）
+· Ex 5A 题 1–9（约 24 分钟，p.124）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5B 题 1–7（约 20 分钟，p.127）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -4752,9 +5398,12 @@
 ★ 3月测试：P2/3 Ch1｜物理 Ch1-9｜S1 Ch1-3
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-新课 FM Ch14 刚体平衡 §14.1、§14.2
-· §14.1 力矩 p.322
-· §14.2 杆与薄板的重心 p.326</t>
+格式训练 FM Ch15 圆周运动（进阶）（§15.1、§15.2）
+· Ex 15A 题 全部（约 25 分钟，p.357）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 15B 题 全部（约 25 分钟，p.362）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
     </row>
@@ -4764,9 +5413,12 @@
           <t>3月29日 周一
 ────────────
 21:00-22:15 纯数
-练习 P2/3 Ch2 对数与指数函数（§2.1、§2.2）
-· 做 §2.1 课后练习并批改
-· 做 §2.2 课后练习并批改</t>
+格式训练 P2/3 Ch4 微分（§4.5、§4.6）
+· Ex 4E 题 1–17（约 35 分钟，p.98）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4F 题 1–14（约 31 分钟，p.101）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -4774,9 +5426,12 @@
           <t>3月30日 周二
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch10 电阻与电阻率
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+章末复习 Phy Ch13 波的叠加
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：叠加与干涉、双缝、衍射光栅
+· 过关自测：能默写 λ=ax/D；能判断相干条件；能算条纹间距；Chapter 13 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4784,10 +5439,14 @@
           <t>3月31日 周三
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch2 对数与指数函数 §2.3、§2.4
-· §2.3 对数的运算法则 p.33
-练习 P2/3 Ch2 对数与指数函数（§2.3、§2.4）
-· 做 §2.3 课后练习并批改</t>
+章末复习 P2/3 Ch4 微分
+· 章末复习题 End-of-chapter review p.108，限时 30 分钟
+· 本章要会：乘积/商/链式法则的综合运用、隐函数与参数方程二阶导、导数用于变化率
+· 过关自测：参数方程求二阶导能独立做对；Ex 4A–4G 错题清零；能说清隐函数求导何时必须链式
+术语与格式 P2/3 Ch5 积分 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 指数函数的积分 p.112（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.2 1/(ax+b) 的积分 p.115（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §5.3 sin/cos/sec²(ax+b) 的积分 p.118（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
@@ -4864,10 +5523,14 @@
           <t>4月1日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch11 实用电路 §11.1、§11.2
-· §11.1 内阻
-练习 Phy Ch11 实用电路（§11.1、§11.2）
-· 做 §11.1 课后练习并批改</t>
+术语与格式 Phy Ch14 驻波 §14.1、§14.2、§14.3、§14.4
+· 速览 §14.1 从行波到驻波（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §14.2 波节与波腹（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §14.3 驻波的形成（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 Phy Ch14 驻波（§14.1、§14.2）
+· 节末 Questions 题 全部（约 25 分钟，p.369）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.370）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -4885,13 +5548,19 @@
           <t>4月3日 周六 ◆清明节假期
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch3 离散程度的度量 §3.1、§3.2
-· §3.1 极差 p.51
-· §3.2 四分位距与百分位数 p.54
+章末复习 S1 Ch5 排列与组合
+· 章末复习题 End-of-chapter review p.143，限时 30 分钟
+· 本章要会：排列与组合、含重复/相邻/限制条件的计数
+· 过关自测：能判断该用 P 还是 C；能处理「至少/至多」用补集；Ex 5A–5G 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
-练习 S1 Ch3 离散程度的度量（§3.1、§3.2）
-· 做 §3.1 课后练习并批改
-· 做 §3.2 课后练习并批改</t>
+术语与格式 S1 Ch6 概率分布 §6.1、§6.2、§6.3
+· 速览 §6.1 离散随机变量 p.150（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.2 概率分布 p.150（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.3 离散随机变量的期望与方差 p.156（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -4899,13 +5568,16 @@
           <t>4月4日 周日 ◆清明节假期
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch2 ｜ Phy Ch11 ｜ S1 Ch3
+· 回顾：P2/3 Ch5 ｜ Phy Ch14 ｜ S1 Ch6
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-练习 FM Ch14 刚体平衡（§14.1、§14.2）
-· 做 §14.1 课后练习并批改
-· 做 §14.2 课后练习并批改</t>
+章末复习 FM Ch15 圆周运动（进阶）
+· 章末复习题 End-of-chapter review p.378，限时 30 分钟
+· 本章要会：能对水平与竖直圆周运动列径向方程并用能量求速度
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -4915,13 +5587,19 @@
           <t>4月5日 周一 ◆清明节假期
 ────────────
 14:00-15:00 纯数
-新课 P2/3 Ch2 对数与指数函数 §2.5、§2.6
-· §2.5 解指数方程 p.38
-· §2.6 解指数不等式 p.40
+格式训练 P2/3 Ch5 积分（§5.1、§5.2）
+· Ex 5A 题 1–12（约 28 分钟，p.113）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5B 题 1–10（约 25 分钟，p.117）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 纯数
-练习 P2/3 Ch2 对数与指数函数（§2.5、§2.6）
-· 做 §2.5 课后练习并批改
-· 做 §2.6 课后练习并批改</t>
+格式训练 P2/3 Ch5 积分（§5.3、§5.4）
+· Ex 5C 题 1–10（约 25 分钟，p.120）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5D 题 1–12（约 28 分钟，p.125）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -4929,9 +5607,12 @@
           <t>4月6日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch11 实用电路 §11.3、§11.4
-· §11.3 传感器
-· §11.4 电位器电路</t>
+章末复习 Phy Ch14 驻波
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：驻波与共振、弦与气柱的基频与泛音
+· 过关自测：能画各阶驻波图；能算弦频率 f=(1/2L)√(T/μ)；Chapter 14 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4939,9 +5620,10 @@
           <t>4月7日 周三
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch2 对数与指数函数 §2.7、§2.8
-· §2.7 自然对数 p.42
-· §2.8 把关系式化为线性形式 p.44</t>
+术语与格式 P2/3 Ch5 积分 §5.5
+· 速览 §5.5 梯形法则 p.126（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -4949,9 +5631,12 @@
           <t>4月8日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch11 实用电路
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+术语与格式 Phy Ch15 原子结构 §15.1、§15.2、§15.3、§15.4
+· 速览 §15.1 观察原子内部（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.2 α 粒子散射与原子核（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.3 原子的简单模型（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.4 核子与电子（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -4969,13 +5654,19 @@
           <t>4月10日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch3 离散程度的度量 §3.3
-· §3.3 方差与标准差 p.56
-· 精读课本+做例题，整理笔记
+格式训练 S1 Ch6 概率分布（§6.1、§6.2）
+· Ex 6A 题 1–20（约 35 分钟，p.153）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6B 题 1–15（约 32 分钟，p.158）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 20:00-21:00 应用数学
-章末复习 S1 Ch3 离散程度的度量
-· 章末复习题 End-of-chapter review p.65
-· 限时完成并批改</t>
+章末复习 S1 Ch6 概率分布
+· 章末复习题 End-of-chapter review p.162，限时 30 分钟
+· 本章要会：离散随机变量、概率分布表、E(X) 与 Var(X)
+· 过关自测：能默写 E(X)=Σxp 与 Var(X)=E(X²)−μ²；能列出随机变量的所有取值；Ex 6A–6B 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -4983,13 +5674,16 @@
           <t>4月11日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch2 ｜ Phy Ch11 ｜ S1 Ch3
+· 回顾：P2/3 Ch5 ｜ Phy Ch15 ｜ S1 Ch6
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch14 刚体平衡 §14.3、§14.4
-· §14.3 立体的重心 p.336
-· §14.4 物体的平衡 p.341</t>
+术语与格式 FM Ch16 胡克定律 §16.1、§16.2、§16.3
+· 速览 §16.1 胡克定律 p.380（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §16.2 弹性势能 p.385（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §16.3 功能原理 p.389（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -4999,9 +5693,12 @@
           <t>4月12日 周一
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch2 对数与指数函数
-· 章末复习题 End-of-chapter review p.40
-· 限时完成并批改</t>
+章末复习 P2/3 Ch5 积分
+· 章末复习题 End-of-chapter review p.131，限时 30 分钟
+· 本章要会：分部积分、分式拆分法、定积分的换元、梯形法则数值积分
+· 过关自测：分部积分的 LIATE 顺序能默写；梯形法则能徒手算 4 条带；Ex 5A–5E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -5009,9 +5706,12 @@
           <t>4月13日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch12 波 §12.1、§12.2
-· §12.1 描述波
-· §12.2 横波与纵波</t>
+格式训练 Phy Ch15 原子结构（§15.1、§15.2）
+· 节末 Questions 题 全部（约 25 分钟，p.389）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.392）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5019,9 +5719,12 @@
           <t>4月14日 周三
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch3 三角学 §3.1、§3.2
-· §3.1 cosec / sec / cot p.53
-· §3.2 和角公式 p.58</t>
+术语与格式 P2/3 Ch6 方程的数值解法 §6.1、§6.2、§6.3
+· 速览 §6.1 寻找初始近似值 p.135（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.2 改进解的精度 p.140（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §6.3 迭代法的跨领域应用 p.149（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -5029,10 +5732,14 @@
           <t>4月15日 周四
 ────────────
 21:00-22:15 物理
-练习 Phy Ch12 波（§12.1、§12.2）
-· 做 §12.1 课后练习并批改
-新课 Phy Ch12 波 §12.3、§12.4
-· §12.3 波的能量</t>
+格式训练 Phy Ch15 原子结构（§15.3、§15.4）
+· 节末 Questions 题 全部（约 25 分钟，p.393）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.397）
+术语与格式 Phy Ch15 原子结构 §15.5、§15.6、§15.7、§15.8
+· 速览 §15.5 原子核内的力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.6 放射性的发现（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.7 放射性物质发出的射线（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -5050,13 +5757,18 @@
           <t>4月17日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch4 概率 §4.1、§4.2
-· §4.1 试验、事件与结果 p.86
-· §4.2 互斥事件与加法法则 p.90
+术语与格式 S1 Ch7 二项分布与几何分布 §7.1、§7.2
+· 速览 §7.1 二项分布 p.166（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.2 几何分布 p.175（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
-练习 S1 Ch4 概率（§4.1、§4.2）
-· 做 §4.1 课后练习并批改
-· 做 §4.2 课后练习并批改</t>
+章末复习 S1 Ch7 二项分布与几何分布
+· 章末复习题 End-of-chapter review p.185，限时 30 分钟
+· 本章要会：二项分布与几何分布、求概率与均值方差
+· 过关自测：能判断二项分布的 4 个条件；能默写 P(X=r)=ⁿCᵣpʳqⁿ⁻ʳ 与几何分布公式；Ex 7A–7D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -5064,13 +5776,16 @@
           <t>4月18日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch3 ｜ Phy Ch12 ｜ S1 Ch4
+· 回顾：P2/3 Ch6 ｜ Phy Ch15 ｜ S1 Ch7
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch14 刚体平衡
-· 章末复习题 End-of-chapter review p.352
-· 限时完成并批改</t>
+格式训练 FM Ch16 胡克定律（§16.1、§16.2）
+· Ex 16A 题 全部（约 25 分钟，p.382）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 16B 题 全部（约 25 分钟，p.387）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
     </row>
@@ -5080,10 +5795,14 @@
           <t>4月19日 周一
 ────────────
 21:00-22:15 纯数
-练习 P2/3 Ch3 三角学（§3.1、§3.2）
-· 做 §3.1 课后练习并批改
-新课 P2/3 Ch3 三角学 §3.3、§3.4
-· §3.3 倍角公式 p.61</t>
+格式训练 P2/3 Ch6 方程的数值解法（§6.1、§6.2）
+· Ex 6A 题 1–15（约 32 分钟，p.137）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6B 题 1–14（约 31 分钟，p.146）
+章末复习 P2/3 Ch6 方程的数值解法
+· 章末复习题 End-of-chapter review p.155，限时 30 分钟
+· 本章要会：用迭代法（不动点/牛顿—拉夫森）求方程近似解
+· 过关自测：能默写牛顿—拉夫森迭代式；能判断迭代是否收敛（|f'(x)|&lt;1）；Ex 6A–6C 错题清零</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -5091,9 +5810,12 @@
           <t>4月20日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch12 波（§12.3、§12.4）
-· 做 §12.3 课后练习并批改
-· 做 §12.4 课后练习并批改</t>
+格式训练 Phy Ch15 原子结构（§15.5、§15.6）
+· 节末 Questions 题 全部（约 25 分钟，p.400）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.401）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -5101,9 +5823,12 @@
           <t>4月21日 周三
 ────────────
 21:00-22:15 纯数
-练习 P2/3 Ch3 三角学（§3.3、§3.4）
-· 做 §3.3 课后练习并批改
-· 做 §3.4 课后练习并批改</t>
+术语与格式 P2/3 Ch7 进阶代数 §7.1、§7.2、§7.3、§7.4
+· 速览 §7.1 假分式 p.166（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.2 部分分式 p.168（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.3 二项式展开 (1+x)^n（n 非正整数） p.174（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §7.4 二项式展开 (a+x)^n（n 非正整数） p.177（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -5111,9 +5836,12 @@
           <t>4月22日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch12 波 §12.5、§12.6
-· §12.5 声波的多普勒效应
-· §12.6 电磁波</t>
+格式训练 Phy Ch15 原子结构（§15.7、§15.8）
+· 节末 Questions 题 全部（约 25 分钟，p.402）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.405）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -5123,8 +5851,10 @@
 21:00-22:15 学术英语
 EAP 强化 01
 · 限时 essay（40 分钟 / 450 词）并自评
+· 限时完成后复盘
 EAP 强化 02
-· 听力讲座 + 康奈尔笔记 + 口头复述</t>
+· 听力讲座 + 康奈尔笔记 + 口头复述
+· 限时完成后复盘</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -5132,13 +5862,19 @@
           <t>4月24日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch4 概率 §4.3、§4.4
-· §4.3 独立事件与乘法法则 p.91
-· §4.4 条件概率 p.94
+术语与格式 S1 Ch8 正态分布 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 连续随机变量 p.188（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.2 正态分布 p.193（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.3 用正态分布建模 p.205（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.4 二项分布的正态近似 p.208（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 20:00-21:00 应用数学
-练习 S1 Ch4 概率（§4.3、§4.4）
-· 做 §4.3 课后练习并批改
-· 做 §4.4 课后练习并批改</t>
+格式训练 S1 Ch8 正态分布（§8.1、§8.2）
+· Ex 8A 题 1–6（约 19 分钟，p.191）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 1–4（约 16 分钟，p.199）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -5149,9 +5885,12 @@
 ★ 期中测试：P2/3 Ch1-2｜物理 Ch1-11｜S1 Ch1-5
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-新课 FM Ch15 圆周运动（进阶） §15.1、§15.2
-· §15.1 水平圆 p.355
-· §15.2 三维情形 p.360</t>
+章末复习 FM Ch16 胡克定律
+· 章末复习题 End-of-chapter review p.396，限时 30 分钟
+· 本章要会：能用胡克定律与弹性势能解弹簧问题
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -5161,9 +5900,12 @@
           <t>4月26日 周一
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch3 三角学 §3.5
-· §3.5 a sinθ + b cosθ 化为 R sin(θ±α) p.66
-· 精读课本+做例题，整理笔记</t>
+格式训练 P2/3 Ch7 进阶代数（§7.1、§7.2）
+· Ex 7A 题 1–4（约 16 分钟，p.167）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 7B 题 1–10（约 25 分钟，p.173）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -5171,9 +5913,12 @@
           <t>4月27日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch12 波（§12.5、§12.6）
-· 做 §12.5 课后练习并批改
-· 做 §12.6 课后练习并批改</t>
+术语与格式 Phy Ch15 原子结构 §15.9、§15.10、§15.11、§15.12
+· 速览 §15.9 放射性衰变方程（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.10 基本粒子（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.11 粒子家族（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §15.12 再看 β 衰变（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -5181,9 +5926,12 @@
           <t>4月28日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch3 三角学
-· 章末复习题 End-of-chapter review p.58
-· 限时完成并批改</t>
+格式训练 P2/3 Ch7 进阶代数（§7.3、§7.4）
+· Ex 7C 题 1–11（约 26 分钟，p.176）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 7D 题 1–8（约 22 分钟，p.178）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -5191,10 +5939,14 @@
           <t>4月29日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch12 波 §12.7、§12.8
-· §12.7 电磁辐射
-练习 Phy Ch12 波（§12.7、§12.8）
-· 做 §12.7 课后练习并批改</t>
+格式训练 Phy Ch15 原子结构（§15.9、§15.10）
+· 节末 Questions 题 全部（约 25 分钟，p.406）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.407）
+格式训练 Phy Ch15 原子结构（§15.11、§15.12）
+· 节末 Questions 题 全部（约 25 分钟，p.409）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.410）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -5281,13 +6033,17 @@
           <t>5月1日 周六 ◆劳动节假期
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch4 概率 §4.5
-· §4.5 非独立事件与条件概率 p.100
-· 精读课本+做例题，整理笔记
+章末复习 S1 Ch8 正态分布
+· 章末复习题 End-of-chapter review p.215，限时 30 分钟
+· 本章要会：正态分布、标准化、逆正态求分位点、近似二项分布
+· 过关自测：能默写 z=(x−μ)/σ 并查表；能做逆查表；能判断何时用连续性修正；Ex 8A–8E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
-章末复习 S1 Ch4 概率
-· 章末复习题 End-of-chapter review p.108
-· 限时完成并批改</t>
+真题精练 9709 M1 2019 Paper 4
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -5295,13 +6051,15 @@
           <t>5月2日 周日 ◆劳动节假期
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch3 ｜ Phy Ch12 ｜ S1 Ch4
+· 回顾：P2/3 Ch7 ｜ Phy Ch15 ｜ S1 Ch8
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-练习 FM Ch15 圆周运动（进阶）（§15.1、§15.2）
-· 做 §15.1 课后练习并批改
-· 做 §15.2 课后练习并批改</t>
+术语与格式 FM Ch17 变力作用下的直线运动 §17.1、§17.2
+· 速览 §17.1 加速度关于时间 p.398（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §17.2 加速度关于位移 p.403（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -5311,13 +6069,17 @@
           <t>5月3日 周一 ◆劳动节假期
 ────────────
 14:00-15:00 纯数
-新课 P2/3 Ch4 微分 §4.1、§4.2
-· §4.1 乘积法则 p.81
-· §4.2 商法则 p.84
+术语与格式 P2/3 Ch7 进阶代数 §7.5
+· 速览 §7.5 部分分式与二项式展开 p.179（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 纯数
-练习 P2/3 Ch4 微分（§4.1、§4.2）
-· 做 §4.1 课后练习并批改
-· 做 §4.2 课后练习并批改</t>
+章末复习 P2/3 Ch7 进阶代数
+· 章末复习题 End-of-chapter review p.182，限时 30 分钟
+· 本章要会：部分分式、除法算式与余数定理、代数式的组合运算
+· 过关自测：能把真分式拆成部分分式；能处理假分式（先做除法）；Ex 7A–7E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -5325,13 +6087,17 @@
           <t>5月4日 周二 ◆劳动节假期
 ────────────
 14:00-15:00 物理
-新课 Phy Ch12 波 §12.9、§12.10
-· §12.9 电磁波的本质
-· §12.10 偏振
+术语与格式 Phy Ch15 原子结构 §15.13
+· 速览 §15.13 另一种核力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 物理
-章末复习 Phy Ch12 波
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+章末复习 Phy Ch15 原子结构
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：原子结构、光电效应、能级与光谱、波粒二象性
+· 过关自测：能默写 E=hf 与 hf=Φ+KE_max；能解释「存在红限频率」；Chapter 15 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -5339,13 +6105,19 @@
           <t>5月5日 周三 ◆劳动节假期
 ────────────
 14:00-15:00 纯数
-新课 P2/3 Ch4 微分 §4.3、§4.4
-· §4.3 指数函数的导数 p.87
-· §4.4 自然对数函数的导数 p.91
+术语与格式 P2/3 Ch8 进阶微积分 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 tan⁻¹x 的导数 p.186（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.2 1/(x²+a²) 的积分 p.187（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.3 k f′(x)/f(x) 的积分 p.189（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.4 换元积分法 p.191（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 15:15-16:15 纯数
-练习 P2/3 Ch4 微分（§4.3、§4.4）
-· 做 §4.3 课后练习并批改
-· 做 §4.4 课后练习并批改</t>
+格式训练 P2/3 Ch8 进阶微积分（§8.1、§8.2）
+· Ex 8A 题 1–5（约 18 分钟，p.187）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 1–6（约 19 分钟，p.188）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -5353,9 +6125,11 @@
           <t>5月6日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch13 波的叠加 §13.1、§13.2
-· §13.1 波的叠加原理
-· §13.2 波的衍射</t>
+术语与格式 Phy P1 实验技能 §P1.1–P1.5、§P1.6–P1.11
+· 速览 §P1.1–P1.5 实验操作与不确定度（一）（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §P1.6–P1.11 数据处理与误差合成（二）（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -5383,13 +6157,16 @@
           <t>5月9日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch4 ｜ Phy Ch13
+· 回顾：P2/3 Ch8 ｜ Phy Ch15
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch15 圆周运动（进阶） §15.3
-· §15.3 竖直圆 p.365
-· 精读课本+做例题，整理笔记</t>
+章末复习 FM Ch17 变力作用下的直线运动
+· 章末复习题 End-of-chapter review p.409，限时 30 分钟
+· 本章要会：能用 a=dv/dt 与 a=v dv/dx 解变力直线运动
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -5399,10 +6176,14 @@
           <t>5月10日 周一
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch4 微分 §4.5、§4.6
-· §4.5 三角函数的导数 p.95
-练习 P2/3 Ch4 微分（§4.5、§4.6）
-· 做 §4.5 课后练习并批改</t>
+格式训练 P2/3 Ch8 进阶微积分（§8.3、§8.4）
+· Ex 8C 题 1–5（约 18 分钟，p.190）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8D 题 1–9（约 24 分钟，p.193）
+术语与格式 P2/3 Ch8 进阶微积分 §8.5、§8.6、§8.7
+· 速览 §8.5 部分分式在积分中的应用 p.194（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.6 分部积分法 p.197（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.7 进阶积分技巧 p.201（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -5410,9 +6191,12 @@
           <t>5月11日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch13 波的叠加（§13.1、§13.2）
-· 做 §13.1 课后练习并批改
-· 做 §13.2 课后练习并批改</t>
+章末复习 Phy P1 实验技能
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：测量不确定度、作图求斜率、误差分析、实验设计
+· 过关自测：能给结果配上绝对/相对不确定度；能画最佳拟合直线并求斜率；能识别系统误差与随机误差；P1.1–P1.11 全部读一遍并做笔记
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -5420,9 +6204,12 @@
           <t>5月12日 周三
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch4 微分 §4.7
-· §4.7 参数方程求导 p.103
-· 精读课本+做例题，整理笔记</t>
+格式训练 P2/3 Ch8 进阶微积分（§8.5、§8.6）
+· Ex 8E 题 1–6（约 19 分钟，p.196）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8F 题 1–27（约 35 分钟，p.200）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -5430,9 +6217,12 @@
           <t>5月13日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch13 波的叠加 §13.3、§13.4
-· §13.3 干涉
-· §13.4 杨氏双缝实验</t>
+术语与格式 Phy Ch16 圆周运动 §16.1、§16.2、§16.3、§16.4
+· 速览 §16.1 描述圆周运动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §16.2 弧度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §16.3 恒定速率、变化速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §16.4 角速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -5442,8 +6232,10 @@
 21:00-22:15 学术英语
 EAP 强化 06
 · EAP 真题套卷（读+写）限时
+· 限时完成后复盘
 EAP 强化 07
-· EAP 真题套卷（听+说）限时</t>
+· EAP 真题套卷（听+说）限时
+· 限时完成后复盘</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -5451,13 +6243,15 @@
           <t>5月15日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch5 排列与组合 §5.1、§5.2
-· §5.1 阶乘函数 p.118
-· §5.2 排列 p.122
+真题精练 9709 S1 2019 Paper 6
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 20:00-21:00 应用数学
-练习 S1 Ch5 排列与组合（§5.1、§5.2）
-· 做 §5.1 课后练习并批改
-· 做 §5.2 课后练习并批改</t>
+真题精练 9709 M1 2020 Paper 4
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -5465,13 +6259,15 @@
           <t>5月16日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch4 ｜ Phy Ch13 ｜ S1 Ch5
+· 回顾：P2/3 Ch8 ｜ Phy Ch16
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch15 圆周运动（进阶）
-· 章末复习题 End-of-chapter review p.378
-· 限时完成并批改</t>
+术语与格式 FM Ch18 动量（进阶） §18.1、§18.2
+· 速览 §18.1 冲量与动量守恒 p.411（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §18.2 斜碰撞及其他例子 p.417（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -5481,9 +6277,12 @@
           <t>5月17日 周一
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch4 微分
-· 章末复习题 End-of-chapter review p.108
-· 限时完成并批改</t>
+章末复习 P2/3 Ch8 进阶微积分
+· 章末复习题 End-of-chapter review p.203，限时 30 分钟
+· 本章要会：用导数画曲线（驻点/拐点/渐近线）、参数方程与隐函数的积分
+· 过关自测：能列「画曲线 6 步」清单并照做；Ex 8A–8G 错题清零；能说清拐点与二阶导为零的关系
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -5491,10 +6290,14 @@
           <t>5月18日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch13 波的叠加（§13.3、§13.4）
-· 做 §13.3 课后练习并批改
-新课 Phy Ch13 波的叠加 §13.5
-· §13.5 衍射光栅</t>
+格式训练 Phy Ch16 圆周运动（§16.1、§16.2）
+· 节末 Questions 题 全部（约 25 分钟，p.454）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.455）
+格式训练 Phy Ch16 圆周运动（§16.3、§16.4）
+· 节末 Questions 题 全部（约 25 分钟，p.457）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.458）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5502,9 +6305,12 @@
           <t>5月19日 周三
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch5 积分 §5.1、§5.2
-· §5.1 指数函数的积分 p.112
-· §5.2 1/(ax+b) 的积分 p.115</t>
+术语与格式 P2/3 Ch9 向量 §9.1、§9.2、§9.3、§9.4
+· 速览 §9.1 位移（平移）向量 p.211（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.2 位置向量 p.220（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.3 数量积 p.225（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.4 直线的向量方程 p.231（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -5512,9 +6318,12 @@
           <t>5月20日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch13 波的叠加
-· 章末复习题 End-of-chapter review
-· 本章公式/术语卡入 Anki</t>
+术语与格式 Phy Ch16 圆周运动 §16.5、§16.6、§16.7
+· 速览 §16.5 向心力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §16.6 计算加速度与力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §16.7 向心力的来源（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -5532,13 +6341,15 @@
           <t>5月22日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch5 排列与组合 §5.3、§5.4
-· §5.3 组合 p.135
-· §5.4 排列组合的应用 p.138
+真题精练 9709 S1 2020 Paper 6
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 20:00-21:00 应用数学
-章末复习 S1 Ch5 排列与组合
-· 章末复习题 End-of-chapter review p.143
-· 限时完成并批改</t>
+真题精练 9709 M1 2021 Paper 4
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -5546,13 +6357,16 @@
           <t>5月23日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch5 ｜ Phy Ch13 ｜ S1 Ch5
+· 回顾：P2/3 Ch9 ｜ Phy Ch16
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch16 胡克定律 §16.1、§16.2
-· §16.1 胡克定律 p.380
-· §16.2 弹性势能 p.385</t>
+章末复习 FM Ch18 动量（进阶）
+· 章末复习题 End-of-chapter review p.429，限时 30 分钟
+· 本章要会：能处理一维与二维碰撞的动量与能量问题
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -5562,10 +6376,14 @@
           <t>5月24日 周一
 ────────────
 21:00-22:15 纯数
-练习 P2/3 Ch5 积分（§5.1、§5.2）
-· 做 §5.1 课后练习并批改
-新课 P2/3 Ch5 积分 §5.3、§5.4
-· §5.3 sin/cos/sec²(ax+b) 的积分 p.118</t>
+格式训练 P2/3 Ch9 向量（§9.1、§9.2）
+· Ex 9A 题 1–7（约 20 分钟，p.218）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9B 题 1–13（约 30 分钟，p.223）
+格式训练 P2/3 Ch9 向量（§9.3、§9.4）
+· Ex 9C 题 1–10（约 25 分钟，p.230）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9D 题 1–13（约 30 分钟，p.235）</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -5573,9 +6391,12 @@
           <t>5月25日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch14 驻波 §14.1、§14.2
-· §14.1 从行波到驻波
-· §14.2 波节与波腹</t>
+格式训练 Phy Ch16 圆周运动（§16.5、§16.6）
+· 节末 Questions 题 全部（约 25 分钟，p.461）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.464）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -5583,9 +6404,10 @@
           <t>5月26日 周三
 ────────────
 21:00-22:15 纯数
-练习 P2/3 Ch5 积分（§5.3、§5.4）
-· 做 §5.3 课后练习并批改
-· 做 §5.4 课后练习并批改</t>
+术语与格式 P2/3 Ch9 向量 §9.5
+· 速览 §9.5 两直线的交点 p.236（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -5593,9 +6415,12 @@
           <t>5月27日 周四
 ────────────
 21:00-22:15 物理
-练习 Phy Ch14 驻波（§14.1、§14.2）
-· 做 §14.1 课后练习并批改
-· 做 §14.2 课后练习并批改</t>
+章末复习 Phy Ch16 圆周运动
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：圆周运动、向心加速度、转动惯量概念
+· 过关自测：能默写 a=v²/r 与 F=mv²/r；能分析竖直圆周运动的临界点；Chapter 16 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -5613,13 +6438,15 @@
           <t>5月29日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch6 概率分布 §6.1、§6.2
-· §6.1 离散随机变量 p.150
-· §6.2 概率分布 p.150
+真题精练 9709 S1 2021 Paper 6
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 20:00-21:00 应用数学
-练习 S1 Ch6 概率分布（§6.1、§6.2）
-· 做 §6.1 课后练习并批改
-· 做 §6.2 课后练习并批改</t>
+真题精练 9709 M1 2022 Paper 4
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -5630,9 +6457,12 @@
 ★ 5月测试：P2/3 Ch1-4｜物理 Ch1-12｜S1 全书
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-练习 FM Ch16 胡克定律（§16.1、§16.2）
-· 做 §16.1 课后练习并批改
-· 做 §16.2 课后练习并批改</t>
+术语与格式 FM Ch8 连续随机变量 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 概率密度函数 p.155（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.2 累积分布函数 p.161（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.3 计算连续随机变量的 E(g(X)) p.174（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §8.4 由 Y=g(X) 求 pdf 与 cdf p.178（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
     </row>
@@ -5642,9 +6472,12 @@
           <t>5月31日 周一
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch5 积分 §5.5
-· §5.5 梯形法则 p.121
-· 精读课本+做例题，整理笔记</t>
+章末复习 P2/3 Ch9 向量
+· 章末复习题 End-of-chapter review p.240，限时 30 分钟
+· 本章要会：三维向量运算、数量积、直线与平面的向量方程、夹角与交点
+· 过关自测：能默写直线与平面的向量方程；能求两直线夹角与交点；Ex 9A–9E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -5721,10 +6554,14 @@
           <t>6月1日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch14 驻波 §14.3、§14.4
-· §14.3 驻波的形成
-章末复习 Phy Ch14 驻波
-· 章末复习题 End-of-chapter review</t>
+术语与格式 Phy Ch17 引力场 §17.1、§17.2、§17.3、§17.4
+· 速览 §17.1 表示引力场（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §17.2 重力场强度 g（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §17.3 引力场中的能量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 Phy Ch17 引力场（§17.1、§17.2）
+· 节末 Questions 题 全部（约 25 分钟，p.480）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.482）</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -5732,9 +6569,11 @@
           <t>6月2日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch5 积分
-· 章末复习题 End-of-chapter review p.131
-· 限时完成并批改</t>
+术语与格式 P2/3 Ch10 微分方程 §10.1、§10.2
+· 速览 §10.1 分离变量法 p.245（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §10.2 由实际问题建立微分方程 p.252（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -5742,9 +6581,12 @@
           <t>6月3日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch15 原子结构 §15.1、§15.2
-· §15.1 观察原子内部
-· §15.2 α 粒子散射与原子核</t>
+格式训练 Phy Ch17 引力场（§17.3、§17.4）
+· 节末 Questions 题 全部（约 25 分钟，p.484）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.486）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -5762,13 +6604,17 @@
           <t>6月5日 周六
 ────────────
 14:00-15:00 应用数学
-新课 S1 Ch6 概率分布 §6.3
-· §6.3 离散随机变量的期望与方差 p.156
-· 精读课本+做例题，整理笔记
-20:00-21:00 应用数学
-章末复习 S1 Ch6 概率分布
-· 章末复习题 End-of-chapter review p.162
-· 限时完成并批改</t>
+真题精练 9709 S1 2022 Paper 6
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+20:00-21:00 进阶数学
+格式训练 FM Ch8 连续随机变量（§8.1、§8.2）
+· Ex 8A 题 全部（约 25 分钟，p.157）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 全部（约 25 分钟，p.163）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -5776,13 +6622,16 @@
           <t>6月6日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch5 ｜ Phy Ch15 ｜ S1 Ch6
+· 回顾：P2/3 Ch10 ｜ Phy Ch17 ｜ FM Ch8
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-新课 FM Ch16 胡克定律 §16.3
-· §16.3 功能原理 p.389
-· 精读课本+做例题，整理笔记</t>
+章末复习 FM Ch8 连续随机变量
+· 章末复习题 End-of-chapter review p.188，限时 30 分钟
+· 本章要会：能从 pdf 求概率、均值、方差，并求 Y=g(X) 的分布
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -5792,10 +6641,14 @@
           <t>6月7日 周一
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch6 方程的数值解法 §6.1、§6.2
-· §6.1 寻找初始近似值 p.135
-练习 P2/3 Ch6 方程的数值解法（§6.1、§6.2）
-· 做 §6.1 课后练习并批改</t>
+章末复习 P2/3 Ch10 微分方程
+· 章末复习题 End-of-chapter review p.262，限时 30 分钟
+· 本章要会：识别并求解一阶可分离变量微分方程、用初始条件定常数
+· 过关自测：能判断方程是否可分离变量；Ex 10A–10B 错题清零；能完整写出「分离→积分→代初值→写解」四步
+术语与格式 P2/3 Ch11 复数 §11.1、§11.2、§11.3、§11.4
+· 速览 §11.1 虚数 p.267（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §11.2 复数 p.269（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §11.3 复平面 p.273（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -5803,9 +6656,12 @@
           <t>6月8日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch15 原子结构（§15.1、§15.2）
-· 做 §15.1 课后练习并批改
-· 做 §15.2 课后练习并批改</t>
+术语与格式 Phy Ch17 引力场 §17.5、§17.6、§17.7
+· 速览 §17.5 在引力下运行（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §17.6 轨道周期（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §17.7 绕地球运行（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5813,13 +6669,19 @@
           <t>6月9日 周三 ◆端午节假期
 ────────────
 14:00-15:00 纯数
-新课 P2/3 Ch6 方程的数值解法 §6.3
-· §6.3 迭代法的跨领域应用 p.140
-· 精读课本+做例题，整理笔记
+格式训练 P2/3 Ch11 复数（§11.1、§11.2）
+· Ex 11A 题 1–6（约 19 分钟，p.269）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11B 题 1–10（约 25 分钟，p.272）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 纯数
-章末复习 P2/3 Ch6 方程的数值解法
-· 章末复习题 End-of-chapter review p.155
-· 限时完成并批改</t>
+格式训练 P2/3 Ch11 复数（§11.3、§11.4）
+· Ex 11C 题 1–12（约 28 分钟，p.282）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11D 题 1–10（约 25 分钟，p.288）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -5827,9 +6689,12 @@
           <t>6月10日 周四
 ────────────
 21:00-22:15 物理
-新课 Phy Ch15 原子结构 §15.3、§15.4
-· §15.3 原子的简单模型
-· §15.4 核子与电子</t>
+格式训练 Phy Ch17 引力场（§17.5、§17.6）
+· 节末 Questions 题 全部（约 25 分钟，p.488）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.490）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -5837,24 +6702,32 @@
           <t>6月11日 周五
 ────────────
 21:00-22:15 进阶数学
-章末复习 FM Ch16 胡克定律
-· 章末复习题 End-of-chapter review p.396
-新课 FM Ch17 变力作用下的直线运动 §17.1、§17.2
-· §17.1 加速度关于时间 p.398</t>
+术语与格式 FM Ch9 推断统计 §9.1、§9.2、§9.3、§9.4
+· 速览 §9.1 t 分布 p.190（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.2 两均值之差的假设检验 p.197（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.3 配对 t 检验 p.203（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+格式训练 FM Ch9 推断统计（§9.1、§9.2）
+· Ex 9A 题 全部（约 25 分钟，p.192）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9B 题 全部（约 25 分钟，p.199）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>6月12日 周六
 ────────────
-14:00-15:00 应用数学
-新课 S1 Ch7 二项分布与几何分布 §7.1、§7.2
-· §7.1 二项分布 p.166
-· §7.2 几何分布 p.175
-20:00-21:00 应用数学
-章末复习 S1 Ch7 二项分布与几何分布
-· 章末复习题 End-of-chapter review p.185
-· 限时完成并批改</t>
+14:00-15:00 进阶数学
+格式训练 FM Ch9 推断统计（§9.3、§9.4）
+· Ex 9C 题 全部（约 25 分钟，p.205）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9D 题 全部（约 25 分钟，p.209）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+20:00-21:00 进阶数学
+术语与格式 FM Ch9 推断统计 §9.5
+· 速览 §9.5 均值之差的置信区间 p.210（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -5862,13 +6735,16 @@
           <t>6月13日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch6 ｜ Phy Ch15 ｜ S1 Ch7 ｜ FM Ch17
+· 回顾：P2/3 Ch11 ｜ Phy Ch17 ｜ FM Ch9
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch17 变力作用下的直线运动
-· 章末复习题 End-of-chapter review p.409
-· 限时完成并批改</t>
+章末复习 FM Ch9 推断统计
+· 章末复习题 End-of-chapter review p.219，限时 30 分钟
+· 本章要会：能用 t 分布做单/双样本假设检验与置信区间
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -5878,9 +6754,10 @@
           <t>6月14日 周一
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch7 进阶代数 §7.1、§7.2
-· §7.1 假分式 p.166
-· §7.2 部分分式 p.168</t>
+术语与格式 P2/3 Ch11 复数 §11.5
+· 速览 §11.5 轨迹 p.288（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -5888,10 +6765,14 @@
           <t>6月15日 周二
 ────────────
 21:00-22:15 物理
-练习 Phy Ch15 原子结构（§15.3、§15.4）
-· 做 §15.3 课后练习并批改
-新课 Phy Ch15 原子结构 §15.5、§15.6
-· §15.5 原子核内的力</t>
+章末复习 Phy Ch17 引力场
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：引力场、场强、引力势与轨道运动
+· 过关自测：能默写 F=GMm/r² 与 g=GM/r²；能区分场强与势；Chapter 17 EXAM-STYLE QUESTIONS 限时做完并批改
+术语与格式 Phy Ch18 振动 §18.1、§18.2、§18.3、§18.4
+· 速览 §18.1 自由振动与受迫振动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §18.2 观察振动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §18.3 描述振动（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5899,9 +6780,12 @@
           <t>6月16日 周三
 ────────────
 21:00-22:15 纯数
-练习 P2/3 Ch7 进阶代数（§7.1、§7.2）
-· 做 §7.1 课后练习并批改
-· 做 §7.2 课后练习并批改</t>
+章末复习 P2/3 Ch11 复数
+· 章末复习题 End-of-chapter review p.297，限时 30 分钟
+· 本章要会：复数四则运算、模与辐角、Argand 图、复数方程与几何意义
+· 过关自测：能默写 i²=−1、模与辐角定义；能把复数在 Argand 图上表示；Ex 11A–11E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -5909,9 +6793,12 @@
           <t>6月17日 周四
 ────────────
 21:00-22:15 物理
-练习 Phy Ch15 原子结构（§15.5、§15.6）
-· 做 §15.5 课后练习并批改
-· 做 §15.6 课后练习并批改</t>
+格式训练 Phy Ch18 振动（§18.1、§18.2）
+· 节末 Questions 题 全部（约 25 分钟，p.502）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.504）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -5919,23 +6806,32 @@
           <t>6月18日 周五
 ────────────
 21:00-22:15 进阶数学
-新课 FM Ch18 动量（进阶） §18.1、§18.2
-· §18.1 冲量与动量守恒 p.411
-· §18.2 斜碰撞及其他例子 p.417</t>
+术语与格式 FM Ch10 卡方检验 §10.1、§10.2、§10.3、§10.4
+· 速览 §10.1 建立假设 p.221（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §10.2 离散分布的拟合优度 p.227（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §10.3 连续分布的拟合优度 p.231（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §10.4 列联表检验相关性 p.237（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>6月19日 周六
 ────────────
-14:00-15:00 应用数学
-新课 S1 Ch8 正态分布 §8.1、§8.2
-· §8.1 连续随机变量 p.188
-· §8.2 正态分布 p.193
-20:00-21:00 应用数学
-练习 S1 Ch8 正态分布（§8.1、§8.2）
-· 做 §8.1 课后练习并批改
-· 做 §8.2 课后练习并批改</t>
+14:00-15:00 进阶数学
+格式训练 FM Ch10 卡方检验（§10.1、§10.2）
+· Ex 10A 题 全部（约 25 分钟，p.223）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 10B 题 全部（约 25 分钟，p.229）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+20:00-21:00 进阶数学
+章末复习 FM Ch10 卡方检验
+· 章末复习题 End-of-chapter review p.248，限时 30 分钟
+· 本章要会：能做离散/连续拟合优度检验与列联表关联检验
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -5943,13 +6839,16 @@
           <t>6月20日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch7 ｜ Phy Ch15 ｜ S1 Ch8 ｜ FM Ch18
+· 回顾：P2/3 Ch11 ｜ Phy Ch18 ｜ FM Ch10
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch18 动量（进阶）
-· 章末复习题 End-of-chapter review p.429
-· 限时完成并批改</t>
+术语与格式 FM Ch11 非参数检验 §11.1、§11.2、§11.3、§11.4
+· 速览 §11.1 非参数检验概述 p.250（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §11.2 单样本符号检验 p.251（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §11.3 单样本 Wilcoxon 符号秩检验 p.254（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §11.4 配对样本符号检验 p.260（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
     </row>
@@ -5959,9 +6858,10 @@
           <t>6月21日 周一
 ────────────
 21:00-22:15 纯数
-新课 P2/3 Ch7 进阶代数 §7.3、§7.4
-· §7.3 二项式展开 (1+x)^n（n 非正整数） p.174
-· §7.4 二项式展开 (a+x)^n（n 非正整数） p.177</t>
+真题精练 9709 P1 2019 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -5969,9 +6869,12 @@
           <t>6月22日 周二
 ────────────
 21:00-22:15 物理
-新课 Phy Ch15 原子结构 §15.7、§15.8
-· §15.7 放射性物质发出的射线
-· §15.8 α 与 β 衰变中的能量</t>
+格式训练 Phy Ch18 振动（§18.3、§18.4）
+· 节末 Questions 题 全部（约 25 分钟，p.506）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.510）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -5979,10 +6882,14 @@
           <t>6月23日 周三
 ────────────
 21:00-22:15 纯数
-练习 P2/3 Ch7 进阶代数（§7.3、§7.4）
-· 做 §7.3 课后练习并批改
-新课 P2/3 Ch7 进阶代数 §7.5
-· §7.5 部分分式与二项式展开 p.179</t>
+真题精练 9709 P3 2019 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+真题精练 9709 P1 2020 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -5990,9 +6897,12 @@
           <t>6月24日 周四
 ────────────
 21:00-22:15 物理
-练习 Phy Ch15 原子结构（§15.7、§15.8）
-· 做 §15.7 课后练习并批改
-· 做 §15.8 课后练习并批改</t>
+术语与格式 Phy Ch18 振动 §18.5、§18.6、§18.7、§18.8
+· 速览 §18.5 简谐运动的图像表示（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §18.6 频率与角频率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §18.7 简谐运动方程（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §18.8 简谐运动中的能量变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -6000,23 +6910,31 @@
           <t>6月25日 周五
 ────────────
 21:00-22:15 进阶数学
-新课 FM Ch8 连续随机变量 §8.1、§8.2
-· §8.1 概率密度函数 p.155
-· §8.2 累积分布函数 p.161</t>
+格式训练 FM Ch11 非参数检验（§11.1、§11.2）
+· Ex 11A 题 全部（约 25 分钟，p.250）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11B 题 全部（约 25 分钟，p.253）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>6月26日 周六
 ────────────
-14:00-15:00 应用数学
-新课 S1 Ch8 正态分布 §8.3、§8.4
-· §8.3 用正态分布建模 p.205
-· §8.4 二项分布的正态近似 p.208
-20:00-21:00 应用数学
-章末复习 S1 Ch8 正态分布
-· 章末复习题 End-of-chapter review p.215
-· 限时完成并批改</t>
+14:00-15:00 进阶数学
+格式训练 FM Ch11 非参数检验（§11.3、§11.4）
+· Ex 11C 题 全部（约 25 分钟，p.256）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11D 题 全部（约 25 分钟，p.262）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+20:00-21:00 进阶数学
+术语与格式 FM Ch11 非参数检验 §11.5、§11.6
+· 速览 §11.5 Wilcoxon 配对符号秩检验 p.263（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §11.6 Wilcoxon 秩和检验 p.266（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -6027,9 +6945,12 @@
 ★ 学年末 AS 全科模拟（真题限时）
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-练习 FM Ch8 连续随机变量（§8.1、§8.2）
-· 做 §8.1 课后练习并批改
-· 做 §8.2 课后练习并批改</t>
+章末复习 FM Ch11 非参数检验
+· 章末复习题 End-of-chapter review p.277，限时 30 分钟
+· 本章要会：能判断何时该用非参数检验并正确查临界值
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
     </row>
@@ -6039,13 +6960,15 @@
           <t>6月28日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-章末复习 P2/3 Ch7 进阶代数
-· 章末复习题 End-of-chapter review p.182
-· 限时完成并批改
+真题精练 9709 P3 2020 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 15:15-16:15 纯数
-新课 P2/3 Ch8 进阶微积分 §8.1、§8.2
-· §8.1 tan⁻¹x 的导数 p.186
-· §8.2 1/(x²+a²) 的积分 p.187</t>
+真题精练 9709 P1 2021 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6053,13 +6976,19 @@
           <t>6月29日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-新课 Phy Ch15 原子结构 §15.9、§15.10
-· §15.9 放射性衰变方程
-· §15.10 基本粒子
+格式训练 Phy Ch18 振动（§18.5、§18.6）
+· 节末 Questions 题 全部（约 25 分钟，p.511）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.514）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 15:15-16:15 物理
-练习 Phy Ch15 原子结构（§15.9、§15.10）
-· 做 §15.9 课后练习并批改
-· 做 §15.10 课后练习并批改</t>
+格式训练 Phy Ch18 振动（§18.7、§18.8）
+· 节末 Questions 题 全部（约 25 分钟，p.516）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.522）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -6067,13 +6996,15 @@
           <t>6月30日 周三 ◆暑假
 ────────────
 14:00-15:00 纯数
-练习 P2/3 Ch8 进阶微积分（§8.1、§8.2）
-· 做 §8.1 课后练习并批改
-· 做 §8.2 课后练习并批改
+真题精练 9709 P3 2021 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
 15:15-16:15 纯数
-新课 P2/3 Ch8 进阶微积分 §8.3、§8.4
-· §8.3 k f′(x)/f(x) 的积分 p.189
-· §8.4 换元积分法 p.191</t>
+真题精练 9709 P1 2022 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>

--- a/StudyCompanionAndroid/assets/Schedule.xlsx
+++ b/StudyCompanionAndroid/assets/Schedule.xlsx
@@ -592,151 +592,157 @@
         <is>
           <t>10月1日 周四 ◆国庆假期
 ────────────
-14:00-15:00 物理
+（国庆假期，不排课）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>10月2日 周五 ◆国庆假期
+────────────
+（国庆假期，不排课）</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>10月3日 周六 ◆国庆假期
+────────────
+（国庆假期，不排课）</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>10月4日 周日 ◆国庆假期
+────────────
+（国庆假期，不排课）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>10月5日 周一 ◆国庆假期
+────────────
+（国庆假期，不排课）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>10月6日 周二 ◆国庆假期
+────────────
+（国庆假期，不排课）</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>10月7日 周三 ◆国庆假期
+────────────
+（国庆假期，不排课）</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>10月8日 周四
+────────────
+21:00-22:15 物理
 术语与格式 Phy Ch1 运动学 §1.1、§1.2、§1.3、§1.4
-· 速览 §1.1 速率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.2 距离与位移、标量与矢量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.3 速率与速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.4 位移-时间图像（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-15:15-16:15 物理
-格式训练 Phy Ch1 运动学（§1.1、§1.2）
-· 节末 Questions 题 全部（约 25 分钟，p.17）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.20）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>10月2日 周五 ◆国庆假期
-────────────
-14:00-15:00 学术英语
+· 速览 §1.1 速率、§1.2 距离与位移、标量与矢量、§1.3 速率与速度、§1.4 位移-时间图像（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>10月9日 周五
+────────────
+21:00-22:15 学术英语
 EAP 01
 · EAP 导论：学术英语与日常英语的差异
-· 词汇/术语入 Anki
-15:15-16:15 学术英语
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>10月10日 周六
+────────────
+21:00-22:15 学术英语
 EAP 02
 · 学术阅读①：略读与扫读（skimming）
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>10月3日 周六 ◆国庆假期
-────────────
-14:00-15:00 应用数学
-术语与格式 M1 Ch1 速度与加速度 §1.1、§1.2、§1.3、§1.4
-· 速览 §1.1 位移与速度 p.2（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.2 加速度 p.9（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.3 匀加速运动方程 p.11（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.4 位移-时间图像与多阶段问题 p.15（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-20:00-21:00 应用数学
-格式训练 M1 Ch1 速度与加速度（§1.1、§1.2）
-· Ex 1A 题 全部（约 25 分钟，p.4）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 1B 题 全部（约 25 分钟，p.10）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>10月4日 周日 ◆国庆假期
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>10月11日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：Phy Ch1 ｜ M1 Ch1
+· 回顾：Phy Ch1
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
 术语与格式 FM Ch1 多项式方程的根 §1.1、§1.2、§1.3、§1.4
-· 速览 §1.1 二次方程 p.2（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.2 三次方程 p.5（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.3 四次方程 p.8（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.4 代换法 p.10（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>10月5日 周一 ◆国庆假期
-────────────
-14:00-15:00 纯数
+· 速览 §1.1 二次方程、§1.2 三次方程、§1.3 四次方程、§1.4 代换法（p.2、p.5、p.8、p.10，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>10月12日 周一
+────────────
+21:00-22:15 纯数
 术语与格式 P1 Ch1 二次方程 §1.1、§1.2、§1.3、§1.4
-· 速览 §1.1 因式分解法解二次方程 p.3（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.2 配方法 p.6（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.3 求根公式 p.10（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.4 联立方程（一个线性一个二次） p.11（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-15:15-16:15 纯数
+· 速览 §1.1 因式分解法解二次方程、§1.2 配方法、§1.3 求根公式、§1.4 联立方程（一个线性一个二次）（p.3、p.6、p.10、p.11，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>10月13日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch1 运动学（§1.1、§1.2）
+· 节末 Questions 题 全部（约 25 分钟，p.17）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.20）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>10月14日 周三
+────────────
+21:00-22:15 纯数
 格式训练 P1 Ch1 二次方程（§1.1、§1.2）
 · Ex 1A 题 1–7（约 20 分钟，p.6）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 1B 题 1–12（约 28 分钟，p.9）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>10月6日 周二 ◆国庆假期
-────────────
-14:00-15:00 物理
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>10月15日 周四
+────────────
+21:00-22:15 物理
 格式训练 Phy Ch1 运动学（§1.3、§1.4）
 · 节末 Questions 题 全部（约 25 分钟，p.23）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.25）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 物理
-术语与格式 Phy Ch1 运动学 §1.5、§1.6、§1.7、§1.8
-· 速览 §1.5 位移的合成（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.6 速度的合成（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.7 矢量的减法（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.8 其他标量与矢量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>10月7日 周三 ◆国庆假期
-────────────
-14:00-15:00 纯数
-格式训练 P1 Ch1 二次方程（§1.3、§1.4）
-· Ex 1C 题 1–5（约 18 分钟，p.11）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 1D 题 1–14（约 31 分钟，p.13）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 纯数
-术语与格式 P1 Ch1 二次方程 §1.5、§1.6、§1.7、§1.8
-· 速览 §1.5 更复杂的二次方程 p.15（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.6 二次函数的最大值与最小值 p.17（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.7 二次不等式 p.21（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.8 二次方程根的个数（判别式） p.24（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>10月8日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch1 运动学（§1.5、§1.6）
-· 节末 Questions 题 全部（约 25 分钟，p.28）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.30）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>10月9日 周五
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>10月16日 周五
 ────────────
 21:00-22:15 学术英语
 EAP 03
@@ -744,22 +750,31 @@
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>10月10日 周六
-────────────
-21:00-22:15 学术英语
-EAP 04
-· 段落写作：主题句/支撑句/结论句
-· 词汇/术语入 Anki</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>10月11日 周日
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>10月17日 周六
+────────────
+14:00-15:00 应用数学
+术语与格式 M1 Ch1 速度与加速度 §1.1、§1.2、§1.3、§1.4
+· 速览 §1.1 位移与速度、§1.2 加速度、§1.3 匀加速运动方程、§1.4 位移-时间图像与多阶段问题（p.2、p.9、p.11、p.15，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+20:00-21:00 应用数学
+格式训练 M1 Ch1 速度与加速度（§1.1、§1.2）
+· Ex 1A 题 全部（约 25 分钟，p.4）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1B 题 全部（约 25 分钟，p.10）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>10月18日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch1 ｜ Phy Ch1
+· 回顾：P1 Ch1 ｜ Phy Ch1 ｜ M1 Ch1
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -768,16 +783,52 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 1B 题 全部（约 25 分钟，p.7）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>10月19日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P1 Ch1 二次方程（§1.3、§1.4）
+· Ex 1C 题 1–5（约 18 分钟，p.11）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1D 题 1–14（约 31 分钟，p.13）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>10月20日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch1 运动学 §1.5、§1.6、§1.7、§1.8
+· 速览 §1.5 位移的合成、§1.6 速度的合成、§1.7 矢量的减法、§1.8 其他标量与矢量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+格式训练 Phy Ch1 运动学（§1.5、§1.6）
+· 节末 Questions 题 全部（约 25 分钟，p.28）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.30）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>10月12日 周一
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>10月21日 周三
 ────────────
 21:00-22:15 纯数
+术语与格式 P1 Ch1 二次方程 §1.5、§1.6、§1.7、§1.8
+· 速览 §1.5 更复杂的二次方程、§1.6 二次函数的最大值与最小值、§1.7 二次不等式、§1.8 二次方程根的个数（判别式）（p.15、p.17、p.21、p.24，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 格式训练 P1 Ch1 二次方程（§1.5、§1.6）
 · Ex 1E 题 1–5（约 18 分钟，p.16）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -786,9 +837,9 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>10月13日 周二
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>10月22日 周四
 ────────────
 21:00-22:15 物理
 章末复习 Phy Ch1 运动学
@@ -799,45 +850,22 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>10月14日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch1 二次方程（§1.7、§1.8）
-· Ex 1G 题 1–7（约 20 分钟，p.23）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 1H 题 1–12（约 28 分钟，p.26）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>10月15日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch2 加速运动 §2.1、§2.2、§2.3、§2.4
-· 速览 §2.1 加速度的含义（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.2 计算加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.3 加速度的单位（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.4 推导加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>10月16日 周五
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>10月23日 周五
 ────────────
 21:00-22:15 学术英语
+EAP 04
+· 段落写作：主题句/支撑句/结论句
+· 词汇/术语入 Anki
 EAP 05
 · 学术阅读②：识别论点、论据与论证结构
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>10月17日 周六
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>10月24日 周六
 ────────────
 14:00-15:00 应用数学
 格式训练 M1 Ch1 速度与加速度（§1.3、§1.4）
@@ -846,22 +874,21 @@
 · Ex 1D 题 全部（约 25 分钟，p.17）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 应用数学
 术语与格式 M1 Ch1 速度与加速度 §1.5、§1.6
-· 速览 §1.5 速度-时间图像与多阶段问题 p.22（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.6 不连续图像 p.27（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>10月18日 周日
+· 速览 §1.5 速度-时间图像与多阶段问题、§1.6 不连续图像（p.22、p.27，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>10月25日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch1 ｜ Phy Ch2 ｜ M1 Ch1
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
+★ 10月测试：P1 Ch1｜物理 Ch1-2
+· 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
 章末复习 FM Ch1 多项式方程的根
 · 章末复习题 End-of-chapter review p.15，限时 30 分钟
@@ -872,77 +899,70 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>10月19日 周一
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>10月26日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P1 Ch1 二次方程（§1.7、§1.8）
+· Ex 1G 题 1–7（约 20 分钟，p.23）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1H 题 1–12（约 28 分钟，p.26）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>10月27日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch2 加速运动 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 加速度的含义、§2.2 计算加速度、§2.3 加速度的单位、§2.4 推导加速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>10月28日 周三
 ────────────
 21:00-22:15 纯数
 术语与格式 P1 Ch1 二次方程 §1.9
-· 速览 §1.9 直线与二次曲线的交点 p.27（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>10月20日 周二
+· 速览 §1.9 直线与二次曲线的交点（p.27，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>10月29日 周四
 ────────────
 21:00-22:15 物理
 格式训练 Phy Ch2 加速运动（§2.1、§2.2）
 · 节末 Questions 题 全部（约 25 分钟，p.41）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.42）
-格式训练 Phy Ch2 加速运动（§2.3、§2.4）
-· 节末 Questions 题 全部（约 25 分钟，p.43）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.45）</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>10月21日 周三
-────────────
-21:00-22:15 纯数
-章末复习 P1 Ch1 二次方程
-· 章末复习题 End-of-chapter review p.31，限时 30 分钟
-· 本章要会：把任意二次式配方、用判别式判断根的个数、解二次不等式与「一个线性一个二次」的联立方程
-· 过关自测：Ex 1A–1I 各做过一遍且错题清零；能对 xx²+bx+c 在 20 秒内写出配方形式；能口述判别式三种情况
-术语与格式 P1 Ch2 函数 §2.1、§2.2、§2.3、§2.4
-· 速览 §2.1 函数的定义 p.34（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.2 复合函数 p.39（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.3 反函数 p.43（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>10月22日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch2 加速运动 §2.5、§2.6、§2.7、§2.8
-· 速览 §2.5 推导位移（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.6 测量速度与加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.7 实验室中测定速度与加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.8 运动方程（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>10月23日 周五
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>10月30日 周五
 ────────────
 21:00-22:15 学术英语
 EAP 06
 · 学术词汇②：AWL Sublist 3-4
-· 词汇/术语入 Anki
-EAP 07
-· 摘要写作：压缩与转述学术文本（paraphrase）
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>10月24日 周六
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>10月31日 周六
 ────────────
 14:00-15:00 应用数学
 章末复习 M1 Ch1 速度与加速度
@@ -953,111 +973,9 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
 术语与格式 M1 Ch2 一维力与运动 §2.1、§2.2、§2.3、§2.4
-· 速览 §2.1 牛顿第一定律及力与加速度的关系 p.36（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.2 力的合成 p.39（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.3 重力与重力加速度 p.42（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.4 接触力与竖直方向运动 p.47（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>10月25日 周日
-────────────
-14:00-15:00 复习/测试
-★ 10月测试：P1 Ch1｜物理 Ch1-2
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-术语与格式 FM Ch2 有理函数 §2.1、§2.2、§2.3、§2.4
-· 速览 §2.1 竖直渐近线 p.17（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.2 斜渐近线 p.24（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.3 不等式 p.29（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.4 曲线之间的关系 p.34（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>10月26日 周一
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch2 函数（§2.1、§2.2）
-· Ex 2A 题 1–16（约 34 分钟，p.37）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2B 题 1–19（约 35 分钟，p.41）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>10月27日 周二
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch2 加速运动（§2.5、§2.6）
-· 节末 Questions 题 全部（约 25 分钟，p.47）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.49）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>10月28日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch2 函数（§2.3、§2.4）
-· Ex 2C 题 1–16（约 34 分钟，p.46）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2D 题 1–6（约 19 分钟，p.50）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>10月29日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch2 加速运动（§2.7、§2.8）
-· 节末 Questions 题 全部（约 25 分钟，p.51）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.56）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>10月30日 周五
-────────────
-21:00-22:15 学术英语
-EAP 08
-· 引用规范：Harvard 格式入门与学术诚信
-· 词汇/术语入 Anki</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>10月31日 周六
-────────────
-14:00-15:00 应用数学
-格式训练 M1 Ch2 一维力与运动（§2.1、§2.2）
-· Ex 2A 题 全部（约 25 分钟，p.38）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2B 题 全部（约 25 分钟，p.41）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-20:00-21:00 应用数学
-章末复习 M1 Ch2 一维力与运动
-· 章末复习题 End-of-chapter review p.51，限时 30 分钟
-· 本章要会：牛顿第二定律 F=ma 在一维的应用、重量与法向力
-· 过关自测：能画一维受力图（free-body diagram）；能处理竖直方向运动；Ex 2A–2D 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+· 速览 §2.1 牛顿第一定律及力与加速度的关系、§2.2 力的合成、§2.3 重力与重力加速度、§2.4 接触力与竖直方向运动（p.36、p.39、p.42、p.47，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
@@ -1131,10 +1049,139 @@
           <t>7月1日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
+格式训练 Phy Ch18 振动（§18.3、§18.4）
+· 节末 Questions 题 全部（约 25 分钟，p.506）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.510）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+术语与格式 Phy Ch18 振动 §18.5、§18.6、§18.7、§18.8
+· 速览 §18.5 简谐运动的图像表示、§18.6 频率与角频率、§18.7 简谐运动方程、§18.8 简谐运动中的能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>7月2日 周五 ◆暑假
+────────────
+14:00-15:00 进阶数学
+术语与格式 FM Ch11 非参数检验 §11.1、§11.2、§11.3、§11.4
+· 速览 §11.1 非参数检验概述、§11.2 单样本符号检验、§11.3 单样本 Wilcoxon 符号秩检验、§11.4 配对样本符号检验（p.250、p.251、p.254、p.260，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 进阶数学
+格式训练 FM Ch11 非参数检验（§11.1、§11.2）
+· Ex 11A 题 全部（约 25 分钟，p.250）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11B 题 全部（约 25 分钟，p.253）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>7月3日 周六 ◆暑假
+────────────
+14:00-15:00 进阶数学
+格式训练 FM Ch11 非参数检验（§11.3、§11.4）
+· Ex 11C 题 全部（约 25 分钟，p.256）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11D 题 全部（约 25 分钟，p.262）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+20:00-21:00 进阶数学
+术语与格式 FM Ch11 非参数检验 §11.5、§11.6
+· 速览 §11.5 Wilcoxon 配对符号秩检验、§11.6 Wilcoxon 秩和检验（p.263、p.266，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>7月4日 周日 ◆暑假
+────────────
+14:00-15:00 复习/测试
+· 回顾：P2/3 Ch11 ｜ Phy Ch18 ｜ FM Ch11
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+章末复习 FM Ch11 非参数检验
+· 章末复习题 End-of-chapter review p.277，限时 30 分钟
+· 本章要会：能判断何时该用非参数检验并正确查临界值
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>7月5日 周一 ◆暑假
+────────────
+14:00-15:00 纯数
+真题精练 9709 P3 2020 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 纯数
+真题精练 9709 P1 2021 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>7月6日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch18 振动（§18.5、§18.6）
+· 节末 Questions 题 全部（约 25 分钟，p.511）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.514）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+格式训练 Phy Ch18 振动（§18.7、§18.8）
+· 节末 Questions 题 全部（约 25 分钟，p.516）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.522）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>7月7日 周三 ◆暑假
+────────────
+14:00-15:00 纯数
+真题精练 9709 P3 2021 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 纯数
+真题精练 9709 P1 2022 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>7月8日 周四 ◆暑假
+────────────
+14:00-15:00 物理
 术语与格式 Phy Ch18 振动 §18.9、§18.10
-· 速览 §18.9 阻尼振动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §18.10 共振（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §18.9 阻尼振动、§18.10 共振（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 物理
 章末复习 Phy Ch18 振动
@@ -1145,29 +1192,28 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>7月2日 周五 ◆暑假
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>7月9日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 术语与格式 FM Ch12 概率母函数 §12.1、§12.2、§12.3、§12.4
-· 速览 §12.1 概率母函数 p.280（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §12.2 用 pgf 求 E(X) 与 Var(X) p.287（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §12.3 独立随机变量之和 p.292（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §12.4 三个及以上随机变量 p.298（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §12.1 概率母函数、§12.2 用 pgf 求 E(X) 与 Var(X)、§12.3 独立随机变量之和、§12.4 三个及以上随机变量（p.280、p.287、p.292、p.298，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 进阶数学
 格式训练 FM Ch12 概率母函数（§12.1、§12.2）
 · Ex 12A 题 全部（约 25 分钟，p.282）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 12B 题 全部（约 25 分钟，p.289）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>7月3日 周六 ◆暑假
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>7月10日 周六 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 章末复习 FM Ch12 概率母函数
@@ -1178,16 +1224,14 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 进阶数学
 术语与格式 FM Ch19 双曲函数 §19.1、§19.2、§19.3、§19.4
-· 速览 §19.1 双曲函数的指数形式 p.432（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §19.2 双曲恒等式 p.438（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §19.3 反双曲函数 p.440（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §19.4 反双曲函数的对数形式 p.442（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>7月4日 周日 ◆暑假
+· 速览 §19.1 双曲函数的指数形式、§19.2 双曲恒等式、§19.3 反双曲函数、§19.4 反双曲函数的对数形式（p.432、p.438、p.440、p.442，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>7月11日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
 · 回顾：Phy Ch18 ｜ FM Ch19
@@ -1199,14 +1243,15 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 19B 题 全部（约 25 分钟，p.439）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>7月5日 周一 ◆暑假
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>7月12日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
 真题精练 9709 P3 2022 Paper 3
@@ -1222,49 +1267,47 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>7月6日 周二 ◆暑假
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>7月13日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
 术语与格式 Phy Ch19 热物理 §19.1、§19.2、§19.3、§19.4
-· 速览 §19.1 物态变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §19.2 能量变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §19.3 内能（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §19.4 温度的含义（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §19.1 物态变化、§19.2 能量变化、§19.3 内能、§19.4 温度的含义（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 物理
 格式训练 Phy Ch19 热物理（§19.1、§19.2）
 · 节末 Questions 题 全部（约 25 分钟，p.543）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.544）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>7月7日 周三 ◆暑假
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>7月14日 周三 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 术语与格式 FM Ch20 矩阵 2 §20.1、§20.2、§20.3、§20.4
-· 速览 §20.1 特征值与特征向量 p.448（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §20.2 矩阵代数 p.451（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §20.3 对角化 p.461（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §20.4 方程组 p.465（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §20.1 特征值与特征向量、§20.2 矩阵代数、§20.3 对角化、§20.4 方程组（p.448、p.451、p.461、p.465，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 进阶数学
 格式训练 FM Ch20 矩阵 2（§20.1、§20.2）
 · Ex 20A 题 全部（约 25 分钟，p.450）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 20B 题 全部（约 25 分钟，p.453）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>7月8日 周四 ◆暑假
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>7月15日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
 格式训练 Phy Ch19 热物理（§19.3、§19.4）
@@ -1273,17 +1316,17 @@
 · 节末 Questions 题 全部（约 25 分钟，p.552）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 物理
 术语与格式 Phy Ch19 热物理 §19.5、§19.6
-· 速览 §19.5 温度计（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §19.6 计算能量变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>7月9日 周五 ◆暑假
+· 速览 §19.5 温度计、§19.6 计算能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>7月16日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 章末复习 FM Ch20 矩阵 2
@@ -1294,16 +1337,14 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 进阶数学
 术语与格式 FM Ch21 微分（进阶） §21.1、§21.2、§21.3、§21.4
-· 速览 §21.1 隐函数 p.473（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §21.2 参数方程 p.478（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §21.3 双曲函数与反函数 p.481（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §21.4 麦克劳林级数 p.488（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>7月10日 周六 ◆暑假
+· 速览 §21.1 隐函数、§21.2 参数方程、§21.3 双曲函数与反函数、§21.4 麦克劳林级数（p.473、p.478、p.481、p.488，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>7月17日 周六 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 格式训练 FM Ch21 微分（进阶）（§21.1、§21.2）
@@ -1312,6 +1353,7 @@
 · Ex 21B 题 全部（约 25 分钟，p.480）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 进阶数学
 章末复习 FM Ch21 微分（进阶）
 · 章末复习题 End-of-chapter review p.496，限时 30 分钟
@@ -1321,9 +1363,9 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>7月11日 周日 ◆暑假
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>7月18日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
 · 回顾：Phy Ch19 ｜ FM Ch21
@@ -1331,18 +1373,16 @@
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
 术语与格式 FM Ch22 积分（进阶） §22.1、§22.2、§22.3、§22.4
-· 速览 §22.1 积分技巧 p.498（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §22.2 递推公式 p.503（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §22.3 弧长与表面积 p.509（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §22.4 面积的极限 p.515（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>7月12日 周一 ◆暑假
+· 速览 §22.1 积分技巧、§22.2 递推公式、§22.3 弧长与表面积、§22.4 面积的极限（p.498、p.503、p.509、p.515，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>7月19日 周一 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 格式训练 FM Ch22 积分（进阶）（§22.1、§22.2）
@@ -1351,6 +1391,7 @@
 · Ex 22B 题 全部（约 25 分钟，p.505）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 进阶数学
 章末复习 FM Ch22 积分（进阶）
 · 章末复习题 End-of-chapter review p.523，限时 30 分钟
@@ -1360,9 +1401,9 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>7月13日 周二 ◆暑假
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>7月20日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
 章末复习 Phy Ch19 热物理
@@ -1373,36 +1414,33 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
 术语与格式 Phy Ch20 理想气体 §20.1、§20.2、§20.3、§20.4
-· 速览 §20.1 气体的粒子模型（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §20.2 解释压强（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §20.3 测量气体（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §20.4 玻意耳定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>7月14日 周三 ◆暑假
+· 速览 §20.1 气体的粒子模型、§20.2 解释压强、§20.3 测量气体、§20.4 玻意耳定律（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>7月21日 周三 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 术语与格式 FM Ch23 复数（进阶） §23.1、§23.2、§23.3、§23.4
-· 速览 §23.1 棣莫弗定理 p.525（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §23.2 正弦与余弦的幂 p.529（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §23.3 单位根 p.532（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §23.4 复数求和 p.537（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §23.1 棣莫弗定理、§23.2 正弦与余弦的幂、§23.3 单位根、§23.4 复数求和（p.525、p.529、p.532、p.537，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 进阶数学
 格式训练 FM Ch23 复数（进阶）（§23.1、§23.2）
 · Ex 23A 题 全部（约 25 分钟，p.527）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 23B 题 全部（约 25 分钟，p.531）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>7月15日 周四 ◆暑假
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>7月22日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
 格式训练 Phy Ch20 理想气体（§20.1、§20.2）
@@ -1411,18 +1449,20 @@
 · 节末 Questions 题 全部（约 25 分钟，p.572）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 物理
 格式训练 Phy Ch20 理想气体（§20.3、§20.4）
 · 节末 Questions 题 全部（约 25 分钟，p.574）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.575）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>7月16日 周五 ◆暑假
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>7月23日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 章末复习 FM Ch23 复数（进阶）
@@ -1433,16 +1473,14 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 进阶数学
 术语与格式 FM Ch24 微分方程（进阶） §24.1、§24.2、§24.3、§24.4
-· 速览 §24.1 一阶微分方程 p.545（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §24.2 二阶微分方程：齐次情形 p.550（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §24.3 二阶微分方程：非齐次情形 p.557（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §24.4 微分方程的代换法 p.565（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>7月17日 周六 ◆暑假
+· 速览 §24.1 一阶微分方程、§24.2 二阶微分方程：齐次情形、§24.3 二阶微分方程：非齐次情形、§24.4 微分方程的代换法（p.545、p.550、p.557、p.565，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>7月24日 周六 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 格式训练 FM Ch24 微分方程（进阶）（§24.1、§24.2）
@@ -1451,6 +1489,7 @@
 · Ex 24B 题 全部（约 25 分钟，p.552）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 进阶数学
 章末复习 FM Ch24 微分方程（进阶）
 · 章末复习题 End-of-chapter review p.575，限时 30 分钟
@@ -1460,14 +1499,13 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>7月18日 周日 ◆暑假
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>7月25日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：Phy Ch20 ｜ FM Ch24
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
+★ 暑期测试：P2/3 Ch6-8｜物理 Ch13-16
+· 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
 真题精练 9231 FP1 2019 Paper 1
 · 进阶数学真题卷
@@ -1476,10 +1514,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>7月19日 周一 ◆暑假
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>7月26日 周一 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 真题精练 9231 FP2 2019 Paper 2
@@ -1493,29 +1531,28 @@
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>7月20日 周二 ◆暑假
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>7月27日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
 术语与格式 Phy Ch20 理想气体 §20.5、§20.6、§20.7、§20.8
-· 速览 §20.5 温度变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §20.6 理想气体方程（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §20.7 气体建模：动力学模型（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §20.8 温度与分子能量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §20.5 温度变化、§20.6 理想气体方程、§20.7 气体建模：动力学模型、§20.8 温度与分子能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 物理
 格式训练 Phy Ch20 理想气体（§20.5、§20.6）
 · 节末 Questions 题 全部（约 25 分钟，p.577）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.580）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>7月21日 周三 ◆暑假
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>7月28日 周三 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 真题精练 9231 FM 2019 Paper 4
@@ -1529,9 +1566,9 @@
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>7月22日 周四 ◆暑假
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>7月29日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
 章末复习 Phy Ch20 理想气体
@@ -1542,16 +1579,14 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
 术语与格式 Phy Ch21 匀强电场 §21.1、§21.2、§21.3、§21.4
-· 速览 §21.1 吸引与排斥（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §21.2 电场概念（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §21.3 电场强度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §21.4 电荷受到的力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>7月23日 周五 ◆暑假
+· 速览 §21.1 吸引与排斥、§21.2 电场概念、§21.3 电场强度、§21.4 电荷受到的力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>7月30日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 真题精练 9231 FP2 2020 Paper 2
@@ -1565,113 +1600,15 @@
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>7月24日 周六 ◆暑假
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>7月31日 周六 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 真题精练 9231 FM 2020 Paper 4
 · 进阶数学真题卷
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题
-20:00-21:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>7月25日 周日 ◆暑假
-────────────
-14:00-15:00 复习/测试
-★ 暑期测试：P2/3 Ch6-8｜物理 Ch13-16
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>7月26日 周一 ◆暑假
-────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>7月27日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch21 匀强电场（§21.1、§21.2）
-· 节末 Questions 题 全部（约 25 分钟，p.595）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.597）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 物理
-章末复习 Phy Ch21 匀强电场
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：匀强电场、电势与电容器
-· 过关自测：能默写 E=V/d 与 F=qE；能算电容器储能 W=½QV；Chapter 21 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>7月28日 周三 ◆暑假
-────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>7月29日 周四 ◆暑假
-────────────
-14:00-15:00 物理
-真题精练 9702 AS 2019 Paper 1
-· 物理 AS 真题（选择题/结构题）
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-15:15-16:15 物理
-真题精练 9702 AS 2019 Paper 2
-· 物理 AS 真题（选择题/结构题）
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>7月30日 周五 ◆暑假
-────────────
-14:00-15:00 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>7月31日 周六 ◆暑假
-────────────
-14:00-15:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
 20:00-21:00 应用数学
 本阶段内容已全部完成
 · 自由复习 / 自主拓展</t>
@@ -1778,6 +1715,106 @@
           <t>8月3日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
+格式训练 Phy Ch21 匀强电场（§21.1、§21.2）
+· 节末 Questions 题 全部（约 25 分钟，p.595）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.597）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+章末复习 Phy Ch21 匀强电场
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：匀强电场、电势与电容器
+· 过关自测：能默写 E=V/d 与 F=qE；能算电容器储能 W=½QV；Chapter 21 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>8月4日 周三 ◆暑假
+────────────
+14:00-15:00 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>8月5日 周四 ◆暑假
+────────────
+14:00-15:00 物理
+真题精练 9702 AS 2019 Paper 1
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 物理
+真题精练 9702 AS 2019 Paper 2
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>8月6日 周五 ◆暑假
+────────────
+14:00-15:00 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>8月7日 周六 ◆暑假
+────────────
+14:00-15:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+20:00-21:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>8月8日 周日 ◆暑假
+────────────
+14:00-15:00 复习/测试
+· 回顾：Phy Ch21
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>8月9日 周一 ◆暑假
+────────────
+14:00-15:00 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>8月10日 周二 ◆暑假
+────────────
+14:00-15:00 物理
 真题精练 9702 AS 2020 Paper 1
 · 物理 AS 真题（选择题/结构题）
 · 限时 55 分钟作答 + 即时对答案
@@ -1789,9 +1826,9 @@
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>8月4日 周三 ◆暑假
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>8月11日 周三 ◆暑假
 ────────────
 14:00-15:00 纯数
 本阶段内容已全部完成
@@ -1801,9 +1838,9 @@
 · 自由复习 / 自主拓展</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>8月5日 周四 ◆暑假
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>8月12日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
 真题精练 9702 AS 2021 Paper 1
@@ -1817,9 +1854,9 @@
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>8月6日 周五 ◆暑假
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>8月13日 周五 ◆暑假
 ────────────
 14:00-15:00 学术英语
 本阶段内容已全部完成
@@ -1829,9 +1866,9 @@
 · 自由复习 / 自主拓展</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>8月7日 周六 ◆暑假
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>8月14日 周六 ◆暑假
 ────────────
 14:00-15:00 应用数学
 本阶段内容已全部完成
@@ -1841,9 +1878,9 @@
 · 自由复习 / 自主拓展</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>8月8日 周日 ◆暑假
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>8月15日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
 · 回顾：整理本周笔记
@@ -1855,10 +1892,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>8月9日 周一 ◆暑假
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>8月16日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
 本阶段内容已全部完成
@@ -1868,9 +1905,9 @@
 · 自由复习 / 自主拓展</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>8月10日 周二 ◆暑假
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>8月17日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
 真题精练 9702 AS 2022 Paper 1
@@ -1882,93 +1919,6 @@
 · 物理 AS 真题（选择题/结构题）
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>8月11日 周三 ◆暑假
-────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>8月12日 周四 ◆暑假
-────────────
-14:00-15:00 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>8月13日 周五 ◆暑假
-────────────
-14:00-15:00 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>8月14日 周六 ◆暑假
-────────────
-14:00-15:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-20:00-21:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>8月15日 周日 ◆暑假
-────────────
-14:00-15:00 复习/测试
-· 回顾：整理本周笔记
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>8月16日 周一 ◆暑假
-────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>8月17日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -2324,7 +2274,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -2334,7 +2284,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>543.25</v>
+        <v>529.25</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2384,7 +2334,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch2 ｜ 物理 Phy Ch2 ｜ 应用数学 M1 Ch2 ｜ 进阶数学 FM Ch2</t>
+          <t>纯数 P1 Ch1 ｜ 物理 Phy Ch1 ｜ 应用数学 M1 Ch1 ｜ 进阶数学 FM Ch1</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2351,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch4 ｜ 物理 Phy Ch3 ｜ 应用数学 M1 Ch4 ｜ 进阶数学 FM Ch4</t>
+          <t>纯数 P1 Ch3 ｜ 物理 Phy Ch3 ｜ 应用数学 M1 Ch4 ｜ 进阶数学 FM Ch3</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2368,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch6 ｜ 物理 Phy Ch5 ｜ 应用数学 M1 Ch7 ｜ 进阶数学 FM Ch5</t>
+          <t>纯数 P1 Ch5 ｜ 物理 Phy Ch5 ｜ 应用数学 M1 Ch6 ｜ 进阶数学 FM Ch5</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch9 ｜ 物理 Phy Ch7 ｜ 应用数学 S1 Ch1 ｜ 进阶数学 FM Ch7</t>
+          <t>纯数 P1 Ch8 ｜ 物理 Phy Ch7 ｜ 应用数学 M1 Ch9 ｜ 进阶数学 FM Ch6</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2402,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch2 ｜ 物理 Phy Ch12 ｜ 应用数学 S1 Ch3 ｜ 进阶数学 FM Ch14</t>
+          <t>纯数 P2/3 Ch2 ｜ 物理 Phy Ch11 ｜ 应用数学 S1 Ch2 ｜ 进阶数学 FM Ch13</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch4 ｜ 物理 Phy Ch13 ｜ 应用数学 S1 Ch5 ｜ 进阶数学 FM Ch15</t>
+          <t>纯数 P2/3 Ch3 ｜ 物理 Phy Ch12 ｜ 应用数学 S1 Ch4 ｜ 进阶数学 FM Ch15</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch7 ｜ 物理 Phy Ch15 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch16</t>
+          <t>纯数 P2/3 Ch5 ｜ 物理 Phy Ch15 ｜ 应用数学 S1 Ch7 ｜ 进阶数学 FM Ch16</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch9 ｜ 物理 Phy Ch16 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch8</t>
+          <t>纯数 P2/3 Ch8 ｜ 物理 Phy Ch16 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch18</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch18 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch11</t>
+          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch17 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch10</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2487,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch21 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch24</t>
+          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch20 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch24</t>
         </is>
       </c>
     </row>
@@ -2888,6 +2838,115 @@
           <t>11月1日 周日
 ────────────
 14:00-15:00 复习/测试
+· 回顾：P1 Ch1 ｜ Phy Ch2 ｜ M1 Ch2
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+术语与格式 FM Ch2 有理函数 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 竖直渐近线、§2.2 斜渐近线、§2.3 不等式、§2.4 曲线之间的关系（p.17、p.24、p.29、p.34，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>11月2日 周一
+────────────
+21:00-22:15 纯数
+章末复习 P1 Ch1 二次方程
+· 章末复习题 End-of-chapter review p.31，限时 30 分钟
+· 本章要会：把任意二次式配方、用判别式判断根的个数、解二次不等式与「一个线性一个二次」的联立方程
+· 过关自测：Ex 1A–1I 各做过一遍且错题清零；能对 xx²+bx+c 在 20 秒内写出配方形式；能口述判别式三种情况
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>11月3日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch2 加速运动（§2.3、§2.4）
+· 节末 Questions 题 全部（约 25 分钟，p.43）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.45）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+术语与格式 Phy Ch2 加速运动 §2.5、§2.6、§2.7、§2.8
+· 速览 §2.5 推导位移、§2.6 测量速度与加速度、§2.7 实验室中测定速度与加速度、§2.8 运动方程（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>11月4日 周三
+────────────
+21:00-22:15 纯数
+术语与格式 P1 Ch2 函数 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 函数的定义、§2.2 复合函数、§2.3 反函数、§2.4 函数与其反函数的图像（p.34、p.39、p.43、p.48，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+格式训练 P1 Ch2 函数（§2.1、§2.2）
+· Ex 2A 题 1–16（约 34 分钟，p.37）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 1–19（约 35 分钟，p.41）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>11月5日 周四
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch2 加速运动（§2.5、§2.6）
+· 节末 Questions 题 全部（约 25 分钟，p.47）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.49）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>11月6日 周五
+────────────
+21:00-22:15 学术英语
+EAP 07
+· 摘要写作：压缩与转述学术文本（paraphrase）
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>11月7日 周六
+────────────
+14:00-15:00 应用数学
+格式训练 M1 Ch2 一维力与运动（§2.1、§2.2）
+· Ex 2A 题 全部（约 25 分钟，p.38）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 全部（约 25 分钟，p.41）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+20:00-21:00 应用数学
+章末复习 M1 Ch2 一维力与运动
+· 章末复习题 End-of-chapter review p.51，限时 30 分钟
+· 本章要会：牛顿第二定律 F=ma 在一维的应用、重量与法向力
+· 过关自测：能画一维受力图（free-body diagram）；能处理竖直方向运动；Ex 2A–2D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>11月8日 周日
+────────────
+14:00-15:00 复习/测试
 · 回顾：P1 Ch2 ｜ Phy Ch2 ｜ M1 Ch2
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
@@ -2897,100 +2956,94 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 2B 题 全部（约 25 分钟，p.26）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>11月2日 周一
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>11月9日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P1 Ch2 函数（§2.3、§2.4）
+· Ex 2C 题 1–16（约 34 分钟，p.46）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2D 题 1–6（约 19 分钟，p.50）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>11月10日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch2 加速运动（§2.7、§2.8）
+· 节末 Questions 题 全部（约 25 分钟，p.51）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.56）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>11月11日 周三
 ────────────
 21:00-22:15 纯数
 术语与格式 P1 Ch2 函数 §2.5、§2.6、§2.7、§2.8
-· 速览 §2.5 函数的图像变换 p.51（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.6 反射变换 p.55（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.7 伸缩变换 p.57（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.8 复合变换 p.59（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>11月3日 周二
+· 速览 §2.5 函数的图像变换、§2.6 反射变换、§2.7 伸缩变换、§2.8 复合变换（p.51、p.55、p.57、p.59，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>11月12日 周四
 ────────────
 21:00-22:15 物理
 术语与格式 Phy Ch2 加速运动 §2.9、§2.10、§2.11、§2.12
-· 速览 §2.9 运动方程的推导（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.10 匀变速与非匀变速（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.11 重力加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 Phy Ch2 加速运动（§2.9、§2.10）
-· 节末 Questions 题 全部（约 25 分钟，p.59）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.60）</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>11月4日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch2 函数（§2.5、§2.6）
-· Ex 2E 题 1–7（约 20 分钟，p.54）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2F 题 1–4（约 16 分钟，p.56）
-章末复习 P1 Ch2 函数
-· 章末复习题 End-of-chapter review p.67，限时 30 分钟
-· 本章要会：判断映射是否为一对一、求反函数与复合函数、画 y=f(x) 的图象变换
-· 过关自测：能不看笔记写出 4 种图象变换（平移/拉伸/反射）的规则；Ex 2A–2H 错题清零；能解释「定义域限制」从哪来</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>11月5日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch2 加速运动（§2.11、§2.12）
-· 节末 Questions 题 全部（约 25 分钟，p.62）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.67）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>11月6日 周五
+· 速览 §2.9 运动方程的推导、§2.10 匀变速与非匀变速、§2.11 重力加速度、§2.12 测定 g（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>11月13日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 09
-· 学术听力①：康奈尔笔记法与讲座笔记符号
+EAP 08
+· 引用规范：Harvard 格式入门与学术诚信
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>11月7日 周六
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>11月14日 周六
 ────────────
 14:00-15:00 应用数学
 术语与格式 M1 Ch3 二维力 §3.1、§3.2、§3.3、§3.4
-· 速览 §3.1 平衡问题中力的水平/竖直分解 p.54（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.2 其他角度平衡问题中的力的分解 p.59（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.3 力的三角形与拉密定理 p.62（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.4 斜面上的非平衡问题 p.66（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §3.1 平衡问题中力的水平/竖直分解、§3.2 其他角度平衡问题中的力的分解、§3.3 力的三角形与拉密定理、§3.4 斜面上的非平衡问题（p.54、p.59、p.62、p.66，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
 格式训练 M1 Ch3 二维力（§3.1、§3.2）
 · Ex 3A 题 全部（约 25 分钟，p.56）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 3B 题 全部（约 25 分钟，p.61）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>11月8日 周日
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>11月15日 周日
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P1 Ch2 ｜ Phy Ch2 ｜ M1 Ch3
@@ -3006,71 +3059,84 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>11月9日 周一
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>11月16日 周一
 ────────────
 21:00-22:15 纯数
+格式训练 P1 Ch2 函数（§2.5、§2.6）
+· Ex 2E 题 1–7（约 20 分钟，p.54）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2F 题 1–4（约 16 分钟，p.56）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>11月17日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch2 加速运动（§2.9、§2.10）
+· 节末 Questions 题 全部（约 25 分钟，p.59）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.60）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+格式训练 Phy Ch2 加速运动（§2.11、§2.12）
+· 节末 Questions 题 全部（约 25 分钟，p.62）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.67）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>11月18日 周三
+────────────
+21:00-22:15 纯数
+章末复习 P1 Ch2 函数
+· 章末复习题 End-of-chapter review p.67，限时 30 分钟
+· 本章要会：判断映射是否为一对一、求反函数与复合函数、画 y=f(x) 的图象变换
+· 过关自测：能不看笔记写出 4 种图象变换（平移/拉伸/反射）的规则；Ex 2A–2H 错题清零；能解释「定义域限制」从哪来
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 术语与格式 P1 Ch3 坐标几何 §3.1、§3.2、§3.3、§3.4
-· 速览 §3.1 线段长度与中点 p.72（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.2 平行与垂直 p.75（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.3 直线的方程 p.78（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.4 圆的方程 p.82（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>11月10日 周二
+· 速览 §3.1 线段长度与中点、§3.2 平行与垂直、§3.3 直线的方程、§3.4 圆的方程（p.72、p.75、p.78、p.82，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>11月19日 周四
 ────────────
 21:00-22:15 物理
 术语与格式 Phy Ch2 加速运动 §2.13、§2.14
-· 速览 §2.13 二维运动：抛体（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.14 理解抛体运动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>11月11日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch3 坐标几何（§3.1、§3.2）
-· Ex 3A 题 1–12（约 28 分钟，p.74）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 3B 题 1–11（约 26 分钟，p.77）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>11月12日 周四
-────────────
-21:00-22:15 物理
-章末复习 Phy Ch2 加速运动
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：用四个匀加速公式与图象解多阶段运动
-· 过关自测：四个公式默写全对；能从 v–t 图求位移；能处理自由落体与抛体；Chapter 2 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>11月13日 周五
+· 速览 §2.13 二维运动：抛体、§2.14 理解抛体运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>11月20日 周五
 ────────────
 21:00-22:15 学术英语
+EAP 09
+· 学术听力①：康奈尔笔记法与讲座笔记符号
+· 词汇/术语入 Anki
 EAP 10
 · 学术写作①：说明文（explanatory essay）结构
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>11月14日 周六
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>11月21日 周六
 ────────────
 14:00-15:00 应用数学
 格式训练 M1 Ch3 二维力（§3.3、§3.4）
@@ -3079,16 +3145,17 @@
 · Ex 3D 题 全部（约 25 分钟，p.68）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 应用数学
 术语与格式 M1 Ch3 二维力 §3.5
-· 速览 §3.5 求合力与加速度方向 p.71（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>11月15日 周日
+· 速览 §3.5 求合力与加速度方向（p.71，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>11月22日 周日
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P1 Ch3 ｜ Phy Ch2 ｜ M1 Ch3
@@ -3096,17 +3163,43 @@
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
 术语与格式 FM Ch3 级数求和 §3.1、§3.2
-· 速览 §3.1 Σr、Σr²、Σr³ 求和公式 p.46（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.2 收敛级数 p.51（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>11月16日 周一
+· 速览 §3.1 Σr、Σr²、Σr³ 求和公式、§3.2 收敛级数（p.46、p.51，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>11月23日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P1 Ch3 坐标几何（§3.1、§3.2）
+· Ex 3A 题 1–12（约 28 分钟，p.74）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3B 题 1–11（约 26 分钟，p.77）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>11月24日 周二
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch2 加速运动
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：用四个匀加速公式与图象解多阶段运动
+· 过关自测：四个公式默写全对；能从 v–t 图求位移；能处理自由落体与抛体；Chapter 2 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>11月25日 周三
 ────────────
 21:00-22:15 纯数
 格式训练 P1 Ch3 坐标几何（§3.3、§3.4）
@@ -3114,68 +3207,34 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 3D 题 1–17（约 35 分钟，p.87）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>11月17日 周二
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>11月26日 周四
 ────────────
 21:00-22:15 物理
 术语与格式 Phy Ch3 动力学 §3.1、§3.2、§3.3、§3.4
-· 速览 §3.1 力、质量与加速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.2 识别力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.3 重力、摩擦与引力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 Phy Ch3 动力学（§3.1、§3.2）
-· 节末 Questions 题 全部（约 25 分钟，p.87）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.88）</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>11月18日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P1 Ch3 坐标几何 §3.5
-· 速览 §3.5 直线与圆的交点问题 p.88（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-章末复习 P1 Ch3 坐标几何
-· 章末复习题 End-of-chapter review p.92，限时 30 分钟
-· 本章要会：求两点间距离与中点、直线方程、直线交点与垂直/平行条件
-· 过关自测：能把「两点式/斜截式/一般式」互相转换；Ex 3A–3E 错题清零；圆与直线关系的 3 种情况能画图说明</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>11月19日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch3 动力学（§3.3、§3.4）
-· 节末 Questions 题 全部（约 25 分钟，p.89）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.94）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>11月20日 周五
+· 速览 §3.1 力、质量与加速度、§3.2 识别力、§3.3 重力、摩擦与引力、§3.4 质量与惯性（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>11月27日 周五
 ────────────
 21:00-22:15 学术英语
 EAP 11
 · 学术词汇③：AWL Sublist 5-6
-· 词汇/术语入 Anki
-EAP 12
-· 图表描述：数据、趋势与比较（Task 1）
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>11月21日 周六
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>11月28日 周六
 ────────────
 14:00-15:00 应用数学
 章末复习 M1 Ch3 二维力
@@ -3186,21 +3245,18 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
 术语与格式 M1 Ch4 摩擦力 §4.1、§4.2、§4.3、§4.4
-· 速览 §4.1 摩擦力作为接触力的一部分 p.83（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.2 摩擦极限 p.90（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.3 运动不同阶段摩擦方向的变化 p.95（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.4 摩擦角 p.100（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>11月22日 周日
+· 速览 §4.1 摩擦力作为接触力的一部分、§4.2 摩擦极限、§4.3 运动不同阶段摩擦方向的变化、§4.4 摩擦角（p.83、p.90、p.95、p.100，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>11月29日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch3 ｜ Phy Ch3 ｜ M1 Ch4
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
+★ 11月测试：P1 Ch1-3｜物理 Ch1-2
+· 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
 章末复习 FM Ch3 级数求和
 · 章末复习题 End-of-chapter review p.57，限时 30 分钟
@@ -3211,118 +3267,16 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>11月23日 周一
-────────────
-21:00-22:15 纯数
-术语与格式 P1 Ch4 弧度制 §4.1、§4.2、§4.3
-· 速览 §4.1 弧度 p.101（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.2 弧长 p.104（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.3 扇形面积 p.107（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>11月24日 周二
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch3 动力学 §3.5、§3.6、§3.7
-· 速览 §3.5 在流体中运动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.6 牛顿第三定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.7 理解 SI 单位（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>11月25日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch4 弧度制（§4.1、§4.2）
-· Ex 4A 题 1–9（约 24 分钟，p.102）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 4B 题 1–10（约 25 分钟，p.105）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>11月26日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch3 动力学（§3.5、§3.6）
-· 节末 Questions 题 全部（约 25 分钟，p.98）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.101）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>11月27日 周五
-────────────
-21:00-22:15 学术英语
-EAP 13
-· 学术听力②：TED-Ed / BBC 学术播客精听
-· 词汇/术语入 Anki</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>11月28日 周六
-────────────
-14:00-15:00 应用数学
-格式训练 M1 Ch4 摩擦力（§4.1、§4.2）
-· Ex 4A 题 全部（约 25 分钟，p.85）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 4B 题 全部（约 25 分钟，p.92）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-20:00-21:00 应用数学
-章末复习 M1 Ch4 摩擦力
-· 章末复习题 End-of-chapter review p.105，限时 30 分钟
-· 本章要会：摩擦作为接触力、极限摩擦 F=μN、摩擦方向随运动变化
-· 过关自测：能判断摩擦方向（与相对运动/趋势相反）；能区分「静止」与「滑动」两种方程；Ex 4A–4D 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>11月29日 周日
-────────────
-14:00-15:00 复习/测试
-★ 11月测试：P1 Ch1-3｜物理 Ch1-2
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-术语与格式 FM Ch4 矩阵 1 §4.1、§4.2、§4.3、§4.4
-· 速览 §4.1 矩阵运算 p.59（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.2 逆矩阵 p.65（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.3 行列式 p.72（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.4 矩阵变换 p.76（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-    </row>
     <row r="7" ht="178" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>11月30日 周一
 ────────────
 21:00-22:15 纯数
-章末复习 P1 Ch4 弧度制
-· 章末复习题 End-of-chapter review p.112，限时 30 分钟
-· 本章要会：弧度制、扇形弧长与面积、弧度下的三角比
-· 过关自测：弧长 s=rθ 与面积 A=½r²θ 能默写；Ex 4A–4C 错题清零；能在 30 秒内把 60°/90°/180° 换成弧度
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 P1 Ch3 坐标几何 §3.5
+· 速览 §3.5 直线与圆的交点问题（p.88，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -3399,80 +3353,185 @@
           <t>12月1日 周二
 ────────────
 21:00-22:15 物理
+格式训练 Phy Ch3 动力学（§3.1、§3.2）
+· 节末 Questions 题 全部（约 25 分钟，p.87）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.88）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+格式训练 Phy Ch3 动力学（§3.3、§3.4）
+· 节末 Questions 题 全部（约 25 分钟，p.89）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.94）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>12月2日 周三
+────────────
+21:00-22:15 纯数
+章末复习 P1 Ch3 坐标几何
+· 章末复习题 End-of-chapter review p.92，限时 30 分钟
+· 本章要会：求两点间距离与中点、直线方程、直线交点与垂直/平行条件
+· 过关自测：能把「两点式/斜截式/一般式」互相转换；Ex 3A–3E 错题清零；圆与直线关系的 3 种情况能画图说明
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+术语与格式 P1 Ch4 弧度制 §4.1、§4.2、§4.3
+· 速览 §4.1 弧度、§4.2 弧长、§4.3 扇形面积（p.101、p.104、p.107，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>12月3日 周四
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch3 动力学 §3.5、§3.6、§3.7
+· 速览 §3.5 在流体中运动、§3.6 牛顿第三定律、§3.7 理解 SI 单位（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>12月4日 周五
+────────────
+21:00-22:15 学术英语
+EAP 12
+· 图表描述：数据、趋势与比较（Task 1）
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>12月5日 周六
+────────────
+14:00-15:00 应用数学
+格式训练 M1 Ch4 摩擦力（§4.1、§4.2）
+· Ex 4A 题 全部（约 25 分钟，p.85）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 全部（约 25 分钟，p.92）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+20:00-21:00 应用数学
+章末复习 M1 Ch4 摩擦力
+· 章末复习题 End-of-chapter review p.105，限时 30 分钟
+· 本章要会：摩擦作为接触力、极限摩擦 F=μN、摩擦方向随运动变化
+· 过关自测：能判断摩擦方向（与相对运动/趋势相反）；能区分「静止」与「滑动」两种方程；Ex 4A–4D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>12月6日 周日
+────────────
+14:00-15:00 复习/测试
+· 回顾：P1 Ch4 ｜ Phy Ch3 ｜ M1 Ch4
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+术语与格式 FM Ch4 矩阵 1 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 矩阵运算、§4.2 逆矩阵、§4.3 行列式、§4.4 矩阵变换（p.59、p.65、p.72、p.76，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>12月7日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P1 Ch4 弧度制（§4.1、§4.2）
+· Ex 4A 题 1–9（约 24 分钟，p.102）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 1–10（约 25 分钟，p.105）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>12月8日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch3 动力学（§3.5、§3.6）
+· 节末 Questions 题 全部（约 25 分钟，p.98）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.101）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>12月9日 周三
+────────────
+21:00-22:15 纯数
+章末复习 P1 Ch4 弧度制
+· 章末复习题 End-of-chapter review p.112，限时 30 分钟
+· 本章要会：弧度制、扇形弧长与面积、弧度下的三角比
+· 过关自测：弧长 s=rθ 与面积 A=½r²θ 能默写；Ex 4A–4C 错题清零；能在 30 秒内把 60°/90°/180° 换成弧度
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>12月10日 周四
+────────────
+21:00-22:15 物理
 章末复习 Phy Ch3 动力学
 · 章末复习题 End-of-chapter review，限时 30 分钟
 · 本章要会：牛顿三定律、动量与冲量、平衡与合力
 · 过关自测：能画受力图；能区分质量与重量；能解连接体问题；Chapter 3 EXAM-STYLE QUESTIONS 限时做完并批改
-术语与格式 Phy Ch4 力 §4.1、§4.2、§4.3、§4.4
-· 速览 §4.1 力的合成（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.2 矢量的分量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.3 重心（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>12月2日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P1 Ch5 三角学 §5.1、§5.2、§5.3、§5.4
-· 速览 §5.1 0°–90° 之间的角 p.118（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.2 角的一般定义 p.121（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.3 任意角的三角比 p.123（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 P1 Ch5 三角学（§5.1、§5.2）
-· Ex 5A 题 1–6（约 19 分钟，p.120）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 5B 题 1–9（约 24 分钟，p.122）</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>12月3日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch4 力（§4.1、§4.2）
-· 节末 Questions 题 全部（约 25 分钟，p.116）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.120）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>12月4日 周五
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>12月11日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 14
-· 学术写作②：议论文与反驳段
+EAP 13
+· 学术听力②：TED-Ed / BBC 学术播客精听
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>12月5日 周六
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>12月12日 周六
 ────────────
 14:00-15:00 应用数学
 术语与格式 M1 Ch5 连接体 §5.1、§5.2、§5.3、§5.4
-· 速览 §5.1 牛顿第三定律 p.109（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.2 杆连接的物体 p.110（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.3 绳连接的物体 p.114（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.4 电梯中的物体 p.121（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §5.1 牛顿第三定律、§5.2 杆连接的物体、§5.3 绳连接的物体、§5.4 电梯中的物体（p.109、p.110、p.114、p.121，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
 格式训练 M1 Ch5 连接体（§5.1、§5.2）
 · Ex 5A 题 全部（约 25 分钟，p.109）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 5B 题 全部（约 25 分钟，p.112）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>12月6日 周日
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>12月13日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch5 ｜ Phy Ch4 ｜ M1 Ch5
+· 回顾：P1 Ch4 ｜ Phy Ch3 ｜ M1 Ch5
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -3481,16 +3540,51 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 4B 题 全部（约 25 分钟，p.67）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>12月14日 周一
+────────────
+21:00-22:15 纯数
+术语与格式 P1 Ch5 三角学 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 0°–90° 之间的角、§5.2 角的一般定义、§5.3 任意角的三角比、§5.4 三角函数的图像（p.118、p.121、p.123、p.127，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>12月15日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch4 力 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 力的合成、§4.2 矢量的分量、§4.3 重心、§4.4 力的转动效应（力矩）（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+格式训练 Phy Ch4 力（§4.1、§4.2）
+· 节末 Questions 题 全部（约 25 分钟，p.116）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.120）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>12月7日 周一
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>12月16日 周三
 ────────────
 21:00-22:15 纯数
+格式训练 P1 Ch5 三角学（§5.1、§5.2）
+· Ex 5A 题 1–6（约 19 分钟，p.120）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5B 题 1–9（约 24 分钟，p.122）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 格式训练 P1 Ch5 三角学（§5.3、§5.4）
 · Ex 5C 题 1–13（约 30 分钟，p.126）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -3499,9 +3593,9 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>12月8日 周二
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>12月17日 周四
 ────────────
 21:00-22:15 物理
 格式训练 Phy Ch4 力（§4.3、§4.4）
@@ -3509,46 +3603,26 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.127）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>12月9日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P1 Ch5 三角学 §5.5、§5.6、§5.7、§5.8
-· 速览 §5.5 反三角函数 p.136（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.6 三角方程 p.140（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.7 三角恒等式 p.145（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.8 更复杂的三角方程 p.149（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>12月10日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch4 力 §4.5
-· 速览 §4.5 力偶的力矩（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>12月11日 周五
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>12月18日 周五
 ────────────
 21:00-22:15 学术英语
+EAP 14
+· 学术写作②：议论文与反驳段
+· 词汇/术语入 Anki
 EAP 15
 · 学术词汇④：AWL Sublist 7-10
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>12月12日 周六
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>12月19日 周六
 ────────────
 14:00-15:00 应用数学
 章末复习 M1 Ch5 连接体
@@ -3559,16 +3633,14 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
 术语与格式 M1 Ch6 直线上的一般运动 §6.1、§6.2、§6.3、§6.4
-· 速览 §6.1 速度作为位移对时间的导数 p.130（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.2 加速度作为速度对时间的导数 p.134（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.3 位移作为速度对时间的积分 p.139（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.4 速度作为加速度对时间的积分 p.148（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>12月13日 周日
+· 速览 §6.1 速度作为位移对时间的导数、§6.2 加速度作为速度对时间的导数、§6.3 位移作为速度对时间的积分、§6.4 速度作为加速度对时间的积分（p.130、p.134、p.139、p.148，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>12月20日 周日
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P1 Ch5 ｜ Phy Ch4 ｜ M1 Ch6
@@ -3584,10 +3656,32 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>12月14日 周一
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>12月21日 周一
+────────────
+21:00-22:15 纯数
+术语与格式 P1 Ch5 三角学 §5.5、§5.6、§5.7、§5.8
+· 速览 §5.5 反三角函数、§5.6 三角方程、§5.7 三角恒等式、§5.8 更复杂的三角方程（p.136、p.140、p.145、p.149，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>12月22日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch4 力 §4.5
+· 速览 §4.5 力偶的力矩（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>12月23日 周三
 ────────────
 21:00-22:15 纯数
 格式训练 P1 Ch5 三角学（§5.5、§5.6）
@@ -3595,68 +3689,45 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 5F 题 1–11（约 26 分钟，p.144）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>12月15日 周二
-────────────
-21:00-22:15 物理
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>12月24日 周四 ◆圣诞·元旦假期
+────────────
+14:00-15:00 物理
 章末复习 Phy Ch4 力
 · 章末复习题 End-of-chapter review，限时 30 分钟
 · 本章要会：力矩、平衡、重心、压强与密度
 · 过关自测：能对悬空/靠墙物体列力矩方程；能把力分解到任意方向；Chapter 4 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 物理
 术语与格式 Phy Ch5 功、能与功率 §5.1、§5.2、§5.3、§5.4
-· 速览 §5.1 做功与能量转移（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.2 重力势能（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.3 动能（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>12月16日 周三
-────────────
-21:00-22:15 纯数
-章末复习 P1 Ch5 三角学
-· 章末复习题 End-of-chapter review p.153，限时 30 分钟
-· 本章要会：六个三角函数的图象与恒等式、解三角方程、和角公式与 R sin(θ±α)
-· 过关自测：能默写 sin²+cos²=1 及两个变形、和角公式、倍角公式；Ex 5A–5H 错题清零；能口述「为什么解三角方程要注意区间」
-术语与格式 P1 Ch6 数列 §6.1、§6.2、§6.3、§6.4
-· 速览 §6.1 (a+b)^n 的二项式展开 p.156（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.2 二项式系数 p.160（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.3 等差数列 p.166（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>12月17日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch5 功、能与功率（§5.1、§5.2）
-· 节末 Questions 题 全部（约 25 分钟，p.142）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.146）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>12月18日 周五
-────────────
-21:00-22:15 学术英语
+· 速览 §5.1 做功与能量转移、§5.2 重力势能、§5.3 动能、§5.4 重力势能→动能转化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>12月25日 周五 ◆圣诞·元旦假期
+────────────
+14:00-15:00 学术英语
 EAP 16
 · 学术讨论：seminar 发言、提问与回应
 · 词汇/术语入 Anki
+15:15-16:15 学术英语
 EAP 17
 · 学术写作③：报告与实验报告结构
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>12月19日 周六
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>12月26日 周六 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 应用数学
 格式训练 M1 Ch6 直线上的一般运动（§6.1、§6.2）
@@ -3665,6 +3736,7 @@
 · Ex 6B 题 全部（约 25 分钟，p.136）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 应用数学
 章末复习 M1 Ch6 直线上的一般运动
 · 章末复习题 End-of-chapter review p.153，限时 30 分钟
@@ -3674,73 +3746,92 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>12月20日 周日
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>12月27日 周日 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch6 ｜ Phy Ch5 ｜ M1 Ch6
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
+★ 12月测试：P1 Ch1-5｜物理 Ch1-4
+· 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
 术语与格式 FM Ch5 极坐标 §5.1、§5.2
-· 速览 §5.1 极坐标系 p.94（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.2 极坐标的应用 p.103（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>12月21日 周一
-────────────
-21:00-22:15 纯数
+· 速览 §5.1 极坐标系、§5.2 极坐标的应用（p.94、p.103，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>12月28日 周一 ◆圣诞·元旦假期
+────────────
+14:00-15:00 纯数
+章末复习 P1 Ch5 三角学
+· 章末复习题 End-of-chapter review p.153，限时 30 分钟
+· 本章要会：六个三角函数的图象与恒等式、解三角方程、和角公式与 R sin(θ±α)
+· 过关自测：能默写 sin²+cos²=1 及两个变形、和角公式、倍角公式；Ex 5A–5H 错题清零；能口述「为什么解三角方程要注意区间」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 纯数
+术语与格式 P1 Ch6 数列 §6.1、§6.2、§6.3、§6.4
+· 速览 §6.1 (a+b)^n 的二项式展开、§6.2 二项式系数、§6.3 等差数列、§6.4 等比数列（p.156、p.160、p.166、p.171，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>12月29日 周二 ◆圣诞·元旦假期
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch5 功、能与功率（§5.1、§5.2）
+· 节末 Questions 题 全部（约 25 分钟，p.142）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.146）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+格式训练 Phy Ch5 功、能与功率（§5.3、§5.4）
+· 节末 Questions 题 全部（约 25 分钟，p.148）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.149）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>12月30日 周三 ◆圣诞·元旦假期
+────────────
+14:00-15:00 纯数
 格式训练 P1 Ch6 数列（§6.1、§6.2）
 · Ex 6A 题 1–16（约 34 分钟，p.158）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 6B 题 1–15（约 32 分钟，p.165）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>12月22日 周二
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch5 功、能与功率（§5.3、§5.4）
-· 节末 Questions 题 全部（约 25 分钟，p.148）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.149）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>12月23日 周三
-────────────
-21:00-22:15 纯数
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
 格式训练 P1 Ch6 数列（§6.3、§6.4）
 · Ex 6C 题 1–20（约 35 分钟，p.170）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 6D 题 1–16（约 34 分钟，p.174）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>12月24日 周四 ◆圣诞·元旦假期
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>12月31日 周四 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 物理
 术语与格式 Phy Ch5 功、能与功率 §5.5、§5.6、§5.7
-· 速览 §5.5 下降、上升、下降：能量变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.6 能量转移（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.7 功率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §5.5 下降、上升、下降：能量变化、§5.6 能量转移、§5.7 功率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 物理
 格式训练 Phy Ch5 功、能与功率（§5.5、§5.6）
@@ -3748,137 +3839,8 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.153）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>12月25日 周五 ◆圣诞·元旦假期
-────────────
-14:00-15:00 学术英语
-EAP 18
-· 学术听力③：大学公开课精听（MIT OCW）
-· 词汇/术语入 Anki
-15:15-16:15 学术英语
-EAP 19
-· 学术写作④：essay 自我修改与同伴互评
-· 词汇/术语入 Anki</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>12月26日 周六 ◆圣诞·元旦假期
-────────────
-14:00-15:00 应用数学
-术语与格式 M1 Ch7 动量 §7.1、§7.2
-· 速览 §7.1 动量 p.159（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.2 碰撞与动量守恒 p.161（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-20:00-21:00 应用数学
-章末复习 M1 Ch7 动量
-· 章末复习题 End-of-chapter review p.167，限时 30 分钟
-· 本章要会：动量与动量守恒、碰撞问题
-· 过关自测：能判断动量守恒适用于哪个方向；能处理粘连与反弹两类碰撞；Ex 7A–7B 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>12月27日 周日 ◆圣诞·元旦假期
-────────────
-14:00-15:00 复习/测试
-★ 12月测试：P1 Ch1-5｜物理 Ch1-4
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-章末复习 FM Ch5 极坐标
-· 章末复习题 End-of-chapter review p.117，限时 30 分钟
-· 本章要会：能把曲线在直角坐标与极坐标间转换并求交面积
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>12月28日 周一 ◆圣诞·元旦假期
-────────────
-14:00-15:00 纯数
-术语与格式 P1 Ch6 数列 §6.5、§6.6
-· 速览 §6.5 无穷等比级数 p.175（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.6 综合等差与等比数列 p.180（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-15:15-16:15 纯数
-章末复习 P1 Ch6 数列
-· 章末复习题 End-of-chapter review p.183，限时 30 分钟
-· 本章要会：等差/等比数列通项与求和、无穷等比级数收敛条件
-· 过关自测：默写等差/等比通项与求和公式；能判断 |r|&lt;1；Ex 6A–6F 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>12月29日 周二 ◆圣诞·元旦假期
-────────────
-14:00-15:00 物理
-章末复习 Phy Ch5 功、能与功率
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：功、功率、效率、动能与势能转换
-· 过关自测：能算 W=Fs cosθ 与 P=W/t、P=Fv；能列能量守恒式；Chapter 5 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 物理
-术语与格式 Phy Ch6 动量 §6.1、§6.2、§6.3、§6.4
-· 速览 §6.1 动量的概念（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.2 碰撞建模（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.3 理解碰撞（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.4 爆炸与撞击（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>12月30日 周三 ◆圣诞·元旦假期
-────────────
-14:00-15:00 纯数
-术语与格式 P1 Ch7 微分 §7.1、§7.2、§7.3、§7.4
-· 速览 §7.1 导数与梯度函数 p.191（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.2 链式法则 p.198（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.3 切线与法线 p.201（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.4 二阶导数 p.205（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-15:15-16:15 纯数
-格式训练 P1 Ch7 微分（§7.1、§7.2）
-· Ex 7A 题 1–19（约 35 分钟，p.197）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 7B 题 1–8（约 22 分钟，p.201）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>12月31日 周四 ◆圣诞·元旦假期
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch6 动量（§6.1、§6.2）
-· 节末 Questions 题 全部（约 25 分钟，p.167）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.170）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 物理
-格式训练 Phy Ch6 动量（§6.3、§6.4）
-· 节末 Questions 题 全部（约 25 分钟，p.175）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.178）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E6" s="3" t="n"/>
@@ -3955,25 +3917,128 @@
           <t>1月1日 周五 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 学术英语
+EAP 18
+· 学术听力③：大学公开课精听（MIT OCW）
+· 词汇/术语入 Anki
+15:15-16:15 学术英语
+EAP 19
+· 学术写作④：essay 自我修改与同伴互评
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1月2日 周六 ◆圣诞·元旦假期
+────────────
+14:00-15:00 应用数学
+术语与格式 M1 Ch7 动量 §7.1、§7.2
+· 速览 §7.1 动量、§7.2 碰撞与动量守恒（p.159、p.161，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+20:00-21:00 应用数学
+章末复习 M1 Ch7 动量
+· 章末复习题 End-of-chapter review p.167，限时 30 分钟
+· 本章要会：动量与动量守恒、碰撞问题
+· 过关自测：能判断动量守恒适用于哪个方向；能处理粘连与反弹两类碰撞；Ex 7A–7B 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>1月3日 周日 ◆圣诞·元旦假期
+────────────
+14:00-15:00 复习/测试
+· 回顾：P1 Ch6 ｜ Phy Ch5 ｜ M1 Ch7
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+章末复习 FM Ch5 极坐标
+· 章末复习题 End-of-chapter review p.117，限时 30 分钟
+· 本章要会：能把曲线在直角坐标与极坐标间转换并求交面积
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>1月4日 周一
+────────────
+21:00-22:15 纯数
+术语与格式 P1 Ch6 数列 §6.5、§6.6
+· 速览 §6.5 无穷等比级数、§6.6 综合等差与等比数列（p.175、p.180，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>1月5日 周二
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch5 功、能与功率
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：功、功率、效率、动能与势能转换
+· 过关自测：能算 W=Fs cosθ 与 P=W/t、P=Fv；能列能量守恒式；Chapter 5 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>1月6日 周三
+────────────
+21:00-22:15 纯数
+章末复习 P1 Ch6 数列
+· 章末复习题 End-of-chapter review p.183，限时 30 分钟
+· 本章要会：等差/等比数列通项与求和、无穷等比级数收敛条件
+· 过关自测：默写等差/等比通项与求和公式；能判断 |r|&lt;1；Ex 6A–6F 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+术语与格式 P1 Ch7 微分 §7.1、§7.2、§7.3、§7.4
+· 速览 §7.1 导数与梯度函数、§7.2 链式法则、§7.3 切线与法线、§7.4 二阶导数（p.191、p.198、p.201、p.205，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>1月7日 周四
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch6 动量 §6.1、§6.2、§6.3、§6.4
+· 速览 §6.1 动量的概念、§6.2 碰撞建模、§6.3 理解碰撞、§6.4 爆炸与撞击（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+格式训练 Phy Ch6 动量（§6.1、§6.2）
+· 节末 Questions 题 全部（约 25 分钟，p.167）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.170）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>1月8日 周五
+────────────
+21:00-22:15 学术英语
 EAP 20
 · 扩展论文：选题、文献检索与提纲
-· 词汇/术语入 Anki
-15:15-16:15 学术英语
-EAP 21
-· 学术写作⑤：引言与结论的写法
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>1月2日 周六 ◆圣诞·元旦假期
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1月9日 周六
 ────────────
 14:00-15:00 应用数学
 术语与格式 M1 Ch8 功与能 §8.1、§8.2、§8.3
-· 速览 §8.1 力做的功 p.171（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.2 动能 p.177（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.3 重力势能 p.179（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §8.1 力做的功、§8.2 动能、§8.3 重力势能（p.171、p.177、p.179，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
 格式训练 M1 Ch8 功与能（§8.1、§8.2）
@@ -3981,12 +4046,13 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 8B 题 全部（约 25 分钟，p.178）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>1月3日 周日 ◆圣诞·元旦假期
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>1月10日 周日
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P1 Ch7 ｜ Phy Ch6 ｜ M1 Ch8
@@ -3994,18 +4060,44 @@
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
 术语与格式 FM Ch6 向量（进阶） §6.1、§6.2、§6.3
-· 速览 §6.1 向量积（叉积） p.119（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.2 直线的向量方程 p.123（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.3 平面 p.128（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>1月4日 周一
+· 速览 §6.1 向量积（叉积）、§6.2 直线的向量方程、§6.3 平面（p.119、p.123、p.128，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>1月11日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P1 Ch7 微分（§7.1、§7.2）
+· Ex 7A 题 1–19（约 35 分钟，p.197）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 7B 题 1–8（约 22 分钟，p.201）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>1月12日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch6 动量（§6.3、§6.4）
+· 节末 Questions 题 全部（约 25 分钟，p.175）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.178）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>1月13日 周三
 ────────────
 21:00-22:15 纯数
 章末复习 P1 Ch7 微分
@@ -4016,62 +4108,30 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>1月5日 周二
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>1月14日 周四
 ────────────
 21:00-22:15 物理
 术语与格式 Phy Ch6 动量 §6.5、§6.6、§6.7
-· 速览 §6.5 二维碰撞（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.6 动量与牛顿定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.7 理解运动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>1月6日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P1 Ch8 进阶微分 §8.1、§8.2、§8.3、§8.4
-· 速览 §8.1 增函数与减函数 p.213（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.2 驻点 p.216（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.3 实际最大最小值问题 p.221（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 P1 Ch8 进阶微分（§8.1、§8.2）
-· Ex 8A 题 1–9（约 24 分钟，p.215）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 8B 题 1–13（约 30 分钟，p.220）</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>1月7日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch6 动量（§6.5、§6.6）
-· 节末 Questions 题 全部（约 25 分钟，p.181）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.183）
-章末复习 Phy Ch6 动量
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：动量守恒与碰撞（含弹性/非弹性）
-· 过关自测：能判断动量守恒的方向；能用动能计算判断碰撞类型；Chapter 6 EXAM-STYLE QUESTIONS 限时做完并批改</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>1月8日 周五
+· 速览 §6.5 二维碰撞、§6.6 动量与牛顿定律、§6.7 理解运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>1月15日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 22
-· 数据与公式的英文表达（数理语境）
+EAP 21
+· 学术写作⑤：引言与结论的写法
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>1月9日 周六
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1月16日 周六
 ────────────
 14:00-15:00 应用数学
 章末复习 M1 Ch8 功与能
@@ -4082,19 +4142,17 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
 术语与格式 M1 Ch9 功能原理与功率 §9.1、§9.2、§9.3、§9.4
-· 速览 §9.1 功能原理 p.186（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.2 保守力系统中的能量守恒 p.193（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.3 含非保守力系统的能量守恒 p.196（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.4 功率 p.201（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>1月10日 周日
+· 速览 §9.1 功能原理、§9.2 保守力系统中的能量守恒、§9.3 含非保守力系统的能量守恒、§9.4 功率（p.186、p.193、p.196、p.201，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>1月17日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch8 ｜ Phy Ch6 ｜ M1 Ch9
+· 回顾：P1 Ch7 ｜ Phy Ch6 ｜ M1 Ch9
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -4103,16 +4161,48 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 6B 题 全部（约 25 分钟，p.125）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>1月11日 周一
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1月18日 周一
 ────────────
 21:00-22:15 纯数
+术语与格式 P1 Ch8 进阶微分 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 增函数与减函数、§8.2 驻点、§8.3 实际最大最小值问题、§8.4 变化率（p.213、p.216、p.221、p.227，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>1月19日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch6 动量（§6.5、§6.6）
+· 节末 Questions 题 全部（约 25 分钟，p.181）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.183）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>1月20日 周三
+────────────
+21:00-22:15 纯数
+格式训练 P1 Ch8 进阶微分（§8.1、§8.2）
+· Ex 8A 题 1–9（约 24 分钟，p.215）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 1–13（约 30 分钟，p.220）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 格式训练 P1 Ch8 进阶微分（§8.3、§8.4）
 · Ex 8C 题 1–15（约 32 分钟，p.224）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -4121,56 +4211,36 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>1月12日 周二
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>1月21日 周四
 ────────────
 21:00-22:15 物理
+章末复习 Phy Ch6 动量
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：动量守恒与碰撞（含弹性/非弹性）
+· 过关自测：能判断动量守恒的方向；能用动能计算判断碰撞类型；Chapter 6 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 术语与格式 Phy Ch7 物质与材料 §7.1、§7.2、§7.3、§7.4
-· 速览 §7.1 密度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.2 压强（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.3 阿基米德原理（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.4 压力与张力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>1月13日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P1 Ch8 进阶微分 §8.5
-· 速览 §8.5 相关变化率的实际应用 p.230（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>1月14日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch7 物质与材料（§7.1、§7.2）
-· 节末 Questions 题 全部（约 25 分钟，p.195）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.196）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>1月15日 周五
+· 速览 §7.1 密度、§7.2 压强、§7.3 阿基米德原理、§7.4 压力与张力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>1月22日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 23
-· 学术演讲①：presentation 结构与开场
+EAP 22
+· 数据与公式的英文表达（数理语境）
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1月16日 周六
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1月23日 周六 ◆寒假
 ────────────
 14:00-15:00 应用数学
 格式训练 M1 Ch9 功能原理与功率（§9.1、§9.2）
@@ -4179,6 +4249,7 @@
 · Ex 9B 题 全部（约 25 分钟，p.195）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 应用数学
 章末复习 M1 Ch9 功能原理与功率
 · 章末复习题 End-of-chapter review p.206，限时 30 分钟
@@ -4188,14 +4259,13 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>1月17日 周日
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>1月24日 周日 ◆寒假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch8 ｜ Phy Ch7 ｜ M1 Ch9
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
+★ 寒假前测试：P1 Ch1-6｜物理 Ch1-5
+· 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
 章末复习 FM Ch6 向量（进阶）
 · 章末复习题 End-of-chapter review p.138，限时 30 分钟
@@ -4206,12 +4276,17 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>1月18日 周一
-────────────
-21:00-22:15 纯数
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1月25日 周一 ◆寒假
+────────────
+14:00-15:00 纯数
+术语与格式 P1 Ch8 进阶微分 §8.5
+· 速览 §8.5 相关变化率的实际应用（p.230，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 纯数
 章末复习 P1 Ch8 进阶微分
 · 章末复习题 End-of-chapter review p.235，限时 30 分钟
 · 本章要会：链式法则、乘积/商法则、隐函数与参数方程求导
@@ -4220,222 +4295,111 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>1月19日 周二
-────────────
-21:00-22:15 物理
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>1月26日 周二 ◆寒假
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch7 物质与材料（§7.1、§7.2）
+· 节末 Questions 题 全部（约 25 分钟，p.195）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.196）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
 格式训练 Phy Ch7 物质与材料（§7.3、§7.4）
 · 节末 Questions 题 全部（约 25 分钟，p.200）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.201）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>1月20日 周三
-────────────
-21:00-22:15 纯数
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>1月27日 周三 ◆寒假
+────────────
+14:00-15:00 纯数
 术语与格式 P1 Ch9 积分 §9.1、§9.2、§9.3、§9.4
-· 速览 §9.1 积分是微分的逆运算 p.239（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.2 求积分常数 p.244（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.3 (ax+b)^n 型函数的积分 p.247（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.1 积分是微分的逆运算、§9.2 求积分常数、§9.3 (ax+b)^n 型函数的积分、§9.4 进一步的不定积分（p.239、p.244、p.247、p.249，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 纯数
 格式训练 P1 Ch9 积分（§9.1、§9.2）
 · Ex 9A 题 1–7（约 20 分钟，p.243）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9B 题 1–18（约 35 分钟，p.245）</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>1月21日 周四
-────────────
-21:00-22:15 物理
+· Ex 9B 题 1–18（约 35 分钟，p.245）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>1月28日 周四 ◆寒假
+────────────
+14:00-15:00 物理
 术语与格式 Phy Ch7 物质与材料 §7.5、§7.6
-· 速览 §7.5 材料的拉伸（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.6 弹性势能（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §7.5 材料的拉伸、§7.6 弹性势能（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 物理
 章末复习 Phy Ch7 物质与材料
 · 章末复习题 End-of-chapter review，限时 30 分钟
 · 本章要会：材料力学性质、应力应变、杨氏模量、弹性形变
-· 过关自测：能画应力—应变图并标出弹性极限/屈服点；能算 Young 模量 E=Fl/Ax；Chapter 7 EXAM-STYLE QUESTIONS 限时做完并批改</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>1月22日 周五
-────────────
-21:00-22:15 学术英语
+· 过关自测：能画应力—应变图并标出弹性极限/屈服点；能算 Young 模量 E=Fl/Ax；Chapter 7 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>1月29日 周五 ◆寒假
+────────────
+14:00-15:00 学术英语
+EAP 23
+· 学术演讲①：presentation 结构与开场
+· 词汇/术语入 Anki
+15:15-16:15 学术英语
 EAP 24
 · 学术演讲②：幻灯片设计与视觉辅助
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1月23日 周六 ◆寒假
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1月30日 周六 ◆寒假
 ────────────
 14:00-15:00 应用数学
 术语与格式 S1 Ch1 数据的表示 §1.1、§1.2、§1.3、§1.4
-· 速览 §1.1 数据的类型 p.2（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.2 离散数据的表示：茎叶图 p.3（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.3 连续数据的表示：直方图 p.6（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.4 连续数据的表示：累积频率图 p.13（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §1.1 数据的类型、§1.2 离散数据的表示：茎叶图、§1.3 连续数据的表示：直方图、§1.4 连续数据的表示：累积频率图（p.2、p.3、p.6、p.13，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
 格式训练 S1 Ch1 数据的表示（§1.1、§1.2）
 · Ex 1A 题 1–9（约 24 分钟，p.4）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 1B 题 1–13（约 30 分钟，p.10）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>1月24日 周日 ◆寒假
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>1月31日 周日 ◆寒假
 ────────────
 14:00-15:00 复习/测试
-★ 寒假前测试：P1 Ch1-6｜物理 Ch1-5
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-术语与格式 FM Ch7 数学归纳法 §7.1、§7.2
-· 速览 §7.1 归纳过程 p.140（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.2 整除性的归纳证明 p.146（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>1月25日 周一 ◆寒假
-────────────
-14:00-15:00 纯数
-格式训练 P1 Ch9 积分（§9.3、§9.4）
-· Ex 9C 题 1–8（约 22 分钟，p.248）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9D 题 1–8（约 22 分钟，p.249）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 纯数
-术语与格式 P1 Ch9 积分 §9.5、§9.6、§9.7、§9.8
-· 速览 §9.5 定积分 p.250（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.6 曲线下的面积 p.253（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.7 曲线与直线/两曲线围成的面积 p.260（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.8 反常（广义）积分 p.264（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>1月26日 周二 ◆寒假
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch8 电流 §8.1、§8.2、§8.3、§8.4
-· 速览 §8.1 电路符号与电路图（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.2 电流（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.3 电流的公式（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.4 电压的含义（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-15:15-16:15 物理
-格式训练 Phy Ch8 电流（§8.1、§8.2）
-· 节末 Questions 题 全部（约 25 分钟，p.223）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.226）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>1月27日 周三 ◆寒假
-────────────
-14:00-15:00 纯数
-格式训练 P1 Ch9 积分（§9.5、§9.6）
-· Ex 9E 题 1–9（约 24 分钟，p.252）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9F 题 1–14（约 31 分钟，p.256）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 纯数
-格式训练 P1 Ch9 积分（§9.7、§9.8）
-· Ex 9G 题 1–10（约 25 分钟，p.262）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9H 题 1–4（约 16 分钟，p.267）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>1月28日 周四 ◆寒假
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch8 电流（§8.3、§8.4）
-· 节末 Questions 题 全部（约 25 分钟，p.228）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.233）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 物理
-术语与格式 Phy Ch8 电流 §8.5、§8.6
-· 速览 §8.5 电阻（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.6 电功率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>1月29日 周五 ◆寒假
-────────────
-14:00-15:00 学术英语
-EAP 25
-· 数学与物理术语英汉对照复习（配 Anki）
-· 词汇/术语入 Anki
-15:15-16:15 学术英语
-EAP 26
-· 学术写作⑥：因果链与逻辑连接词
-· 词汇/术语入 Anki</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1月30日 周六 ◆寒假
-────────────
-14:00-15:00 应用数学
-格式训练 S1 Ch1 数据的表示（§1.3、§1.4）
-· Ex 1C 题 1–11（约 26 分钟，p.16）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 1D 题 1–9（约 24 分钟，p.21）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-20:00-21:00 应用数学
-术语与格式 S1 Ch1 数据的表示 §1.5
-· 速览 §1.5 不同数据表示方法的比较 p.20（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>1月31日 周日 ◆寒假
-────────────
-14:00-15:00 复习/测试
-· 回顾：P1 Ch9 ｜ Phy Ch8 ｜ S1 Ch1
+· 回顾：P1 Ch9 ｜ Phy Ch7 ｜ S1 Ch1
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch7 数学归纳法
-· 章末复习题 End-of-chapter review p.151，限时 30 分钟
-· 本章要会：能写标准归纳法三步并证明整除性命题
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 FM Ch7 数学归纳法 §7.1、§7.2
+· 速览 §7.1 归纳过程、§7.2 整除性的归纳证明（p.140、p.146，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -4505,22 +4469,130 @@
           <t>2月1日 周一 ◆寒假
 ────────────
 14:00-15:00 纯数
+格式训练 P1 Ch9 积分（§9.3、§9.4）
+· Ex 9C 题 1–8（约 22 分钟，p.248）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9D 题 1–8（约 22 分钟，p.249）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
+术语与格式 P1 Ch9 积分 §9.5、§9.6、§9.7、§9.8
+· 速览 §9.5 定积分、§9.6 曲线下的面积、§9.7 曲线与直线/两曲线围成的面积、§9.8 反常（广义）积分（p.250、p.253、p.260、p.264，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2月2日 周二 ◆寒假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch8 电流 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 电路符号与电路图、§8.2 电流、§8.3 电流的公式、§8.4 电压的含义（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 物理
+格式训练 Phy Ch8 电流（§8.1、§8.2）
+· 节末 Questions 题 全部（约 25 分钟，p.223）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.226）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>2月3日 周三 ◆寒假
+────────────
+14:00-15:00 纯数
+格式训练 P1 Ch9 积分（§9.5、§9.6）
+· Ex 9E 题 1–9（约 24 分钟，p.252）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9F 题 1–14（约 31 分钟，p.256）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
+格式训练 P1 Ch9 积分（§9.7、§9.8）
+· Ex 9G 题 1–10（约 25 分钟，p.262）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9H 题 1–4（约 16 分钟，p.267）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>2月4日 周四 ◆寒假
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch8 电流（§8.3、§8.4）
+· 节末 Questions 题 全部（约 25 分钟，p.228）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.233）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+术语与格式 Phy Ch8 电流 §8.5、§8.6
+· 速览 §8.5 电阻、§8.6 电功率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>2月5日 周五 ◆寒假
+────────────
+14:00-15:00 学术英语
+EAP 25
+· 数学与物理术语英汉对照复习（配 Anki）
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>2月6日 周六 ◆寒假
+────────────
+14:00-15:00 应用数学
+格式训练 S1 Ch1 数据的表示（§1.3、§1.4）
+· Ex 1C 题 1–11（约 26 分钟，p.16）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1D 题 1–9（约 24 分钟，p.21）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>2月7日 周日 ◆寒假
+────────────
+14:00-15:00 复习/测试
+· 回顾：P1 Ch9 ｜ Phy Ch8 ｜ S1 Ch1
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2月8日 周一 ◆寒假
+────────────
+14:00-15:00 纯数
 术语与格式 P1 Ch9 积分 §9.9
-· 速览 §9.9 旋转体体积 p.268（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-15:15-16:15 纯数
-章末复习 P1 Ch9 积分
-· 章末复习题 End-of-chapter review p.276，限时 30 分钟
-· 本章要会：不定积分与定积分、面积与体积、换元与分部积分
-· 过关自测：能默写 ∫xⁿ、∫sin、∫cos、∫eˣ 的积分表；Ex 9A–9I 错题清零；能用定积分求一条曲线与 x 轴围成的面积
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2月2日 周二 ◆寒假
+· 速览 §9.9 旋转体体积（p.268，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2月9日 周二 ◆寒假
 ────────────
 14:00-15:00 物理
 章末复习 Phy Ch8 电流
@@ -4528,39 +4600,95 @@
 · 本章要会：电流、电荷守恒、基尔霍夫电流定律
 · 过关自测：能默写 I=Q/t；能在电路图中标出电流方向与大小；Chapter 8 EXAM-STYLE QUESTIONS 限时做完并批改
 · 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 物理
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>2月10日 周三 ◆寒假
+────────────
+14:00-15:00 纯数
+章末复习 P1 Ch9 积分
+· 章末复习题 End-of-chapter review p.276，限时 30 分钟
+· 本章要会：不定积分与定积分、面积与体积、换元与分部积分
+· 过关自测：能默写 ∫xⁿ、∫sin、∫cos、∫eˣ 的积分表；Ex 9A–9I 错题清零；能用定积分求一条曲线与 x 轴围成的面积
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>2月11日 周四 ◆寒假
+────────────
+14:00-15:00 物理
 术语与格式 Phy Ch9 基尔霍夫定律 §9.1、§9.2、§9.3、§9.4
-· 速览 §9.1 基尔霍夫第一定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.2 基尔霍夫第二定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.3 基尔霍夫定律的应用（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.4 电阻的组合（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>2月3日 周三 ◆寒假
+· 速览 §9.1 基尔霍夫第一定律、§9.2 基尔霍夫第二定律、§9.3 基尔霍夫定律的应用、§9.4 电阻的组合（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2月12日 周五 ◆寒假
+────────────
+14:00-15:00 学术英语
+EAP 26
+· 学术写作⑥：因果链与逻辑连接词
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>2月13日 周六 ◆寒假
+────────────
+14:00-15:00 应用数学
+术语与格式 S1 Ch1 数据的表示 §1.5
+· 速览 §1.5 不同数据表示方法的比较（p.20，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>2月14日 周日 ◆寒假
+────────────
+14:00-15:00 复习/测试
+· 回顾：P1 Ch9 ｜ Phy Ch9 ｜ S1 Ch1
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+章末复习 FM Ch7 数学归纳法
+· 章末复习题 End-of-chapter review p.151，限时 30 分钟
+· 本章要会：能写标准归纳法三步并证明整除性命题
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2月15日 周一 ◆寒假
 ────────────
 14:00-15:00 纯数
 术语与格式 P2/3 Ch1 代数 §1.1、§1.2、§1.3、§1.4
-· 速览 §1.1 绝对值函数 p.2（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.2 线性函数的绝对值图像 p.7（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.3 绝对值不等式 p.8（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.4 多项式的除法 p.11（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §1.1 绝对值函数、§1.2 线性函数的绝对值图像、§1.3 绝对值不等式、§1.4 多项式的除法（p.2、p.7、p.8、p.11，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 15:15-16:15 纯数
 格式训练 P2/3 Ch1 代数（§1.1、§1.2）
 · Ex 1A 题 1–9（约 24 分钟，p.6）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 1B 题 1–8（约 22 分钟，p.8）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>2月4日 周四 ◆寒假
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2月16日 周二 ◆寒假
 ────────────
 14:00-15:00 物理
 格式训练 Phy Ch9 基尔霍夫定律（§9.1、§9.2）
@@ -4569,6 +4697,7 @@
 · 节末 Questions 题 全部（约 25 分钟，p.251）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 物理
 章末复习 Phy Ch9 基尔霍夫定律
 · 章末复习题 End-of-chapter review，限时 30 分钟
@@ -4578,19 +4707,61 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2月5日 周五 ◆寒假
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2月17日 周三 ◆寒假
+────────────
+14:00-15:00 纯数
+格式训练 P2/3 Ch1 代数（§1.3、§1.4）
+· Ex 1C 题 1–6（约 19 分钟，p.10）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1D 题 1–7（约 20 分钟，p.13）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
+术语与格式 P2/3 Ch1 代数 §1.5、§1.6
+· 速览 §1.5 因式定理、§1.6 余数定理（p.14、p.18，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2月18日 周四 ◆寒假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch10 电阻与电阻率 §10.1、§10.2、§10.3、§10.4
+· 速览 §10.1 金属导体的 I–V 特性、§10.2 欧姆定律、§10.3 电阻与温度、§10.4 电阻率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 物理
+格式训练 Phy Ch10 电阻与电阻率（§10.1、§10.2）
+· 节末 Questions 题 全部（约 25 分钟，p.271）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.273）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2月19日 周五 ◆寒假
 ────────────
 14:00-15:00 学术英语
 EAP 27
 · 学术听力④：英音/美音/多口音训练
+· 词汇/术语入 Anki
+15:15-16:15 学术英语
+EAP 28
+· 学术写作⑦：定义、分类与举例
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>2月6日 周六 ◆寒假
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>2月20日 周六 ◆寒假
 ────────────
 14:00-15:00 应用数学
 章末复习 S1 Ch1 数据的表示
@@ -4598,98 +4769,17 @@
 · 本章要会：数据表示：stem-and-leaf、直方图、累积频数图、箱线图
 · 过关自测：能画 stem-and-leaf 并写 key；能从累积频数图读中位数与四分位数；Ex 1A–1D 错题清零
 · 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>2月7日 周日 ◆寒假
-────────────
-14:00-15:00 复习/测试
-· 回顾：P2/3 Ch1 ｜ Phy Ch9 ｜ S1 Ch1
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2月8日 周一 ◆寒假
-────────────
-14:00-15:00 纯数
-格式训练 P2/3 Ch1 代数（§1.3、§1.4）
-· Ex 1C 题 1–6（约 19 分钟，p.10）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 1D 题 1–7（约 20 分钟，p.13）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2月9日 周二 ◆寒假
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch10 电阻与电阻率 §10.1、§10.2、§10.3、§10.4
-· 速览 §10.1 金属导体的 I–V 特性（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §10.2 欧姆定律（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §10.3 电阻与温度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §10.4 电阻率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>2月10日 周三 ◆寒假
-────────────
-14:00-15:00 纯数
-术语与格式 P2/3 Ch1 代数 §1.5、§1.6
-· 速览 §1.5 因式定理 p.14（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §1.6 余数定理 p.18（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>2月11日 周四 ◆寒假
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch10 电阻与电阻率（§10.1、§10.2）
-· 节末 Questions 题 全部（约 25 分钟，p.271）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.273）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2月12日 周五 ◆寒假
-────────────
-14:00-15:00 学术英语
-EAP 28
-· 学术写作⑦：定义、分类与举例
-· 词汇/术语入 Anki</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2月13日 周六 ◆寒假
-────────────
-14:00-15:00 应用数学
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+20:00-21:00 应用数学
 术语与格式 S1 Ch2 集中趋势的度量 §2.1、§2.2、§2.3
-· 速览 §2.1 众数与众数类 p.28（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.2 平均数 p.30（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.3 中位数 p.42（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>2月14日 周日 ◆寒假
+· 速览 §2.1 众数与众数类、§2.2 平均数、§2.3 中位数（p.28、p.30、p.42，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2月21日 周日 ◆寒假
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P2/3 Ch1 ｜ Phy Ch10 ｜ S1 Ch2
@@ -4697,111 +4787,77 @@
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
 术语与格式 FM Ch13 抛体运动 §13.1、§13.2
-· 速览 §13.1 竖直平面内的运动 p.309（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §13.2 轨迹的直角坐标方程 p.314（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2月15日 周一 ◆寒假
-────────────
-14:00-15:00 纯数
+· 速览 §13.1 竖直平面内的运动、§13.2 轨迹的直角坐标方程（p.309、p.314，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2月22日 周一
+────────────
+21:00-22:15 纯数
 章末复习 P2/3 Ch1 代数
 · 章末复习题 End-of-chapter review p.22，限时 30 分钟
 · 本章要会：指数与对数运算法则、解指数/对数方程与不等式
 · 过关自测：默写 3 条对数法则；Ex 1A–1F 错题清零；能判断写出 log 时定义域的限制
 · 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 纯数
-术语与格式 P2/3 Ch2 对数与指数函数 §2.1、§2.2、§2.3、§2.4
-· 速览 §2.1 以 10 为底的对数 p.26（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.2 以 a 为底的对数 p.30（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.3 对数的运算法则 p.33（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.4 解对数方程 p.35（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2月16日 周二 ◆寒假
-────────────
-14:00-15:00 物理
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2月23日 周二
+────────────
+21:00-22:15 物理
 章末复习 Phy Ch10 电阻与电阻率
 · 章末复习题 End-of-chapter review，限时 30 分钟
 · 本章要会：电阻、电阻率、温度对电阻的影响
 · 过关自测：能默写 R=ρl/A；能画 I–V 图并区分欧姆/非欧姆器件；Chapter 10 EXAM-STYLE QUESTIONS 限时做完并批改
 · 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 物理
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2月24日 周三
+────────────
+21:00-22:15 纯数
+术语与格式 P2/3 Ch2 对数与指数函数 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 以 10 为底的对数、§2.2 以 a 为底的对数、§2.3 对数的运算法则、§2.4 解对数方程（p.26、p.30、p.33、p.35，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2月25日 周四
+────────────
+21:00-22:15 物理
 术语与格式 Phy Ch11 实用电路 §11.1、§11.2、§11.3、§11.4
-· 速览 §11.1 内阻（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §11.2 分压器（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §11.3 传感器（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §11.4 电位器电路（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2月17日 周三 ◆寒假
-────────────
-14:00-15:00 纯数
-格式训练 P2/3 Ch2 对数与指数函数（§2.1、§2.2）
-· Ex 2A 题 1–7（约 20 分钟，p.29）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2B 题 1–9（约 24 分钟，p.32）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 纯数
-格式训练 P2/3 Ch2 对数与指数函数（§2.3、§2.4）
-· Ex 2C 题 1–13（约 30 分钟，p.34）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2D 题 1–10（约 25 分钟，p.37）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2月18日 周四 ◆寒假
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch11 实用电路（§11.1、§11.2）
-· 节末 Questions 题 全部（约 25 分钟，p.292）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.295）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 物理
-章末复习 Phy Ch11 实用电路
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：分压与分流、电位器、内阻影响
-· 过关自测：能设计分压电路；能算串联/并联等效电阻；Chapter 11 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2月19日 周五 ◆寒假
-────────────
-14:00-15:00 学术英语
+· 速览 §11.1 内阻、§11.2 分压器、§11.3 传感器、§11.4 电位器电路（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2月26日 周五
+────────────
+21:00-22:15 学术英语
 EAP 29
 · 学术演讲③：presentation 演练与录像复盘
 · 词汇/术语入 Anki
-15:15-16:15 学术英语
 EAP 30
 · EAP 模拟①：限时 essay（40 分钟 / 400 词）
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2月20日 周六 ◆寒假
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2月27日 周六
 ────────────
 14:00-15:00 应用数学
 格式训练 S1 Ch2 集中趋势的度量（§2.1、§2.2）
@@ -4810,6 +4866,7 @@
 · Ex 2B 题 1–17（约 35 分钟，p.34）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 应用数学
 章末复习 S1 Ch2 集中趋势的度量
 · 章末复习题 End-of-chapter review p.51，限时 30 分钟
@@ -4819,14 +4876,13 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>2月21日 周日 ◆寒假
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2月28日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch2 ｜ Phy Ch11 ｜ S1 Ch2
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
+★ 2月测试：P1 全部｜物理 Ch1-7｜M1 全书
+· 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
 章末复习 FM Ch13 抛体运动
 · 章末复习题 End-of-chapter review p.320，限时 30 分钟
@@ -4834,109 +4890,6 @@
 · 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2月22日 周一
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch2 对数与指数函数 §2.5、§2.6、§2.7、§2.8
-· 速览 §2.5 解指数方程 p.38（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.6 解指数不等式 p.40（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.7 自然对数 p.42（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §2.8 把关系式化为线性形式 p.44（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2月23日 周二
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch12 波 §12.1、§12.2、§12.3、§12.4
-· 速览 §12.1 描述波（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §12.2 横波与纵波（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §12.3 波的能量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §12.4 波速（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>2月24日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P2/3 Ch2 对数与指数函数（§2.5、§2.6）
-· Ex 2E 题 1–13（约 30 分钟，p.39）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2F 题 1–7（约 20 分钟，p.41）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2月25日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch12 波（§12.1、§12.2）
-· 节末 Questions 题 全部（约 25 分钟，p.313）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.314）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2月26日 周五
-────────────
-21:00-22:15 学术英语
-EAP 31
-· 学术阅读③：长篇文献速读与结构化笔记
-· 词汇/术语入 Anki
-EAP 32
-· 学术写作⑧：批判性写作
-· 词汇/术语入 Anki</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>2月27日 周六
-────────────
-14:00-15:00 应用数学
-术语与格式 S1 Ch3 离散程度的度量 §3.1、§3.2、§3.3
-· 速览 §3.1 极差 p.55（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.2 四分位距与百分位数 p.56（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.3 方差与标准差 p.65（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-20:00-21:00 应用数学
-格式训练 S1 Ch3 离散程度的度量（§3.1、§3.2）
-· Ex 3A 题 1–13（约 30 分钟，p.61）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 3B 题 1–12（约 28 分钟，p.69）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>2月28日 周日
-────────────
-14:00-15:00 复习/测试
-★ 2月测试：P1 全部｜物理 Ch1-7｜M1 全书
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-术语与格式 FM Ch14 刚体平衡 §14.1、§14.2、§14.3、§14.4
-· 速览 §14.1 力矩 p.322（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §14.2 杆与薄板的重心 p.326（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §14.3 立体的重心 p.336（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §14.4 物体的平衡 p.341（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
         </is>
       </c>
     </row>
@@ -5006,6 +4959,142 @@
           <t>3月1日 周一
 ────────────
 21:00-22:15 纯数
+格式训练 P2/3 Ch2 对数与指数函数（§2.1、§2.2）
+· Ex 2A 题 1–7（约 20 分钟，p.29）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 1–9（约 24 分钟，p.32）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>3月2日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch11 实用电路（§11.1、§11.2）
+· 节末 Questions 题 全部（约 25 分钟，p.292）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.295）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>3月3日 周三
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch2 对数与指数函数（§2.3、§2.4）
+· Ex 2C 题 1–13（约 30 分钟，p.34）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2D 题 1–10（约 25 分钟，p.37）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+术语与格式 P2/3 Ch2 对数与指数函数 §2.5、§2.6、§2.7、§2.8
+· 速览 §2.5 解指数方程、§2.6 解指数不等式、§2.7 自然对数、§2.8 把关系式化为线性形式（p.38、p.40、p.42、p.44，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>3月4日 周四
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch11 实用电路
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：分压与分流、电位器、内阻影响
+· 过关自测：能设计分压电路；能算串联/并联等效电阻；Chapter 11 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+术语与格式 Phy Ch12 波 §12.1、§12.2、§12.3、§12.4
+· 速览 §12.1 描述波、§12.2 横波与纵波、§12.3 波的能量、§12.4 波速（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>3月5日 周五
+────────────
+21:00-22:15 学术英语
+EAP 31
+· 学术阅读③：长篇文献速读与结构化笔记
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>3月6日 周六
+────────────
+14:00-15:00 应用数学
+术语与格式 S1 Ch3 离散程度的度量 §3.1、§3.2、§3.3
+· 速览 §3.1 极差、§3.2 四分位距与百分位数、§3.3 方差与标准差（p.55、p.56、p.65，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+20:00-21:00 应用数学
+格式训练 S1 Ch3 离散程度的度量（§3.1、§3.2）
+· Ex 3A 题 1–13（约 30 分钟，p.61）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3B 题 1–12（约 28 分钟，p.69）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>3月7日 周日
+────────────
+14:00-15:00 复习/测试
+· 回顾：P2/3 Ch2 ｜ Phy Ch12 ｜ S1 Ch3
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+术语与格式 FM Ch14 刚体平衡 §14.1、§14.2、§14.3、§14.4
+· 速览 §14.1 力矩、§14.2 杆与薄板的重心、§14.3 立体的重心、§14.4 物体的平衡（p.322、p.326、p.336、p.341，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>3月8日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch2 对数与指数函数（§2.5、§2.6）
+· Ex 2E 题 1–13（约 30 分钟，p.39）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2F 题 1–7（约 20 分钟，p.41）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>3月9日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch12 波（§12.1、§12.2）
+· 节末 Questions 题 全部（约 25 分钟，p.313）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.314）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>3月10日 周三
+────────────
+21:00-22:15 纯数
 章末复习 P2/3 Ch2 对数与指数函数
 · 章末复习题 End-of-chapter review p.50，限时 30 分钟
 · 本章要会：eˣ 与 ln x 的图象与性质、把它们用于建模（增长/衰减）
@@ -5014,9 +5103,9 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>3月2日 周二
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>3月11日 周四
 ────────────
 21:00-22:15 物理
 格式训练 Phy Ch12 波（§12.3、§12.4）
@@ -5024,52 +5113,23 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.319）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>3月3日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch3 三角学 §3.1、§3.2、§3.3、§3.4
-· 速览 §3.1 cosec / sec / cot p.53（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.2 和角公式 p.58（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §3.3 倍角公式 p.61（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 P2/3 Ch3 三角学（§3.1、§3.2）
-· Ex 3A 题 1–14（约 31 分钟，p.56）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 3B 题 1–17（约 35 分钟，p.60）</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>3月4日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch12 波 §12.5、§12.6、§12.7、§12.8
-· 速览 §12.5 声波的多普勒效应（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §12.6 电磁波（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §12.7 电磁辐射（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 Phy Ch12 波（§12.5、§12.6）
-· 节末 Questions 题 全部（约 25 分钟，p.320）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.323）</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>3月5日 周五
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>3月12日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 33
-· EAP 模拟②：听力 + 笔记 + 口头复述
+EAP 32
+· 学术写作⑧：批判性写作
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>3月6日 周六
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>3月13日 周六
 ────────────
 14:00-15:00 应用数学
 章末复习 S1 Ch3 离散程度的度量
@@ -5080,19 +5140,17 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
 术语与格式 S1 Ch4 概率 §4.1、§4.2、§4.3、§4.4
-· 速览 §4.1 试验、事件与结果 p.91（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.2 互斥事件与加法法则 p.94（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.3 独立事件与乘法法则 p.100（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.4 条件概率 p.108（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>3月7日 周日
+· 速览 §4.1 试验、事件与结果、§4.2 互斥事件与加法法则、§4.3 独立事件与乘法法则、§4.4 条件概率（p.91、p.94、p.100、p.108，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>3月14日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch3 ｜ Phy Ch12 ｜ S1 Ch4
+· 回顾：P2/3 Ch2 ｜ Phy Ch12 ｜ S1 Ch4
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -5101,16 +5159,45 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 14B 题 全部（约 25 分钟，p.328）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>3月8日 周一
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>3月15日 周一
 ────────────
 21:00-22:15 纯数
+术语与格式 P2/3 Ch3 三角学 §3.1、§3.2、§3.3、§3.4
+· 速览 §3.1 cosec / sec / cot、§3.2 和角公式、§3.3 倍角公式、§3.4 进阶三角恒等式（p.53、p.58、p.61、p.66，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>3月16日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch12 波 §12.5、§12.6、§12.7、§12.8
+· 速览 §12.5 声波的多普勒效应、§12.6 电磁波、§12.7 电磁辐射、§12.8 数量级（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>3月17日 周三
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch3 三角学（§3.1、§3.2）
+· Ex 3A 题 1–14（约 31 分钟，p.56）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3B 题 1–17（约 35 分钟，p.60）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 格式训练 P2/3 Ch3 三角学（§3.3、§3.4）
 · Ex 3C 题 1–19（约 35 分钟，p.64）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -5119,11 +5206,17 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>3月9日 周二
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>3月18日 周四
 ────────────
 21:00-22:15 物理
+格式训练 Phy Ch12 波（§12.5、§12.6）
+· 节末 Questions 题 全部（约 25 分钟，p.320）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.323）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 格式训练 Phy Ch12 波（§12.7、§12.8）
 · 节末 Questions 题 全部（约 25 分钟，p.325）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -5132,42 +5225,19 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>3月10日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch3 三角学 §3.5
-· 速览 §3.5 a sinθ + b cosθ 化为 R sin(θ±α) p.68（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>3月11日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch12 波 §12.9、§12.10
-· 速览 §12.9 电磁波的本质（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §12.10 偏振（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>3月12日 周五
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>3月19日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 34
-· 学术写作⑨：中式英语错误与学术语域
+EAP 33
+· EAP 模拟②：听力 + 笔记 + 口头复述
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>3月13日 周六
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>3月20日 周六
 ────────────
 14:00-15:00 应用数学
 格式训练 S1 Ch4 概率（§4.1、§4.2）
@@ -5176,18 +5246,20 @@
 · Ex 4B 题 1–15（约 32 分钟，p.98）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 应用数学
 格式训练 S1 Ch4 概率（§4.3、§4.4）
 · Ex 4C 题 1–16（约 34 分钟，p.102）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 4E 题 1–10（约 25 分钟，p.110）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>3月14日 周日
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>3月21日 周日
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P2/3 Ch3 ｜ Phy Ch12 ｜ S1 Ch4
@@ -5203,10 +5275,32 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>3月15日 周一
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>3月22日 周一
+────────────
+21:00-22:15 纯数
+术语与格式 P2/3 Ch3 三角学 §3.5
+· 速览 §3.5 a sinθ + b cosθ 化为 R sin(θ±α)（p.68，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>3月23日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch12 波 §12.9、§12.10
+· 速览 §12.9 电磁波的本质、§12.10 偏振（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>3月24日 周三
 ────────────
 21:00-22:15 纯数
 章末复习 P2/3 Ch3 三角学
@@ -5217,9 +5311,9 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>3月16日 周二
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>3月25日 周四
 ────────────
 21:00-22:15 物理
 章末复习 Phy Ch12 波
@@ -5230,54 +5324,27 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>3月17日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch4 微分 §4.1、§4.2、§4.3、§4.4
-· 速览 §4.1 乘积法则 p.81（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.2 商法则 p.84（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.3 指数函数的导数 p.87（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 P2/3 Ch4 微分（§4.1、§4.2）
-· Ex 4A 题 1–8（约 22 分钟，p.83）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 4B 题 1–13（约 30 分钟，p.87）</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>3月18日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch13 波的叠加 §13.1、§13.2、§13.3、§13.4
-· 速览 §13.1 波的叠加原理（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §13.2 波的衍射（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §13.3 干涉（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 Phy Ch13 波的叠加（§13.1、§13.2）
-· 节末 Questions 题 全部（约 25 分钟，p.341）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.343）</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>3月19日 周五
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>3月26日 周五
 ────────────
 21:00-22:15 学术英语
+EAP 34
+· 学术写作⑨：中式英语错误与学术语域
+· 词汇/术语入 Anki
 EAP 35
 · EAP 模拟③：小组讨论与口头答辩
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>3月20日 周六
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>3月27日 周六
 ────────────
 14:00-15:00 应用数学
 术语与格式 S1 Ch4 概率 §4.5
-· 速览 §4.5 非独立事件与条件概率 p.112（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §4.5 非独立事件与条件概率（p.112，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
 章末复习 S1 Ch4 概率
@@ -5288,108 +5355,6 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>3月21日 周日
-────────────
-14:00-15:00 复习/测试
-· 回顾：P2/3 Ch4 ｜ Phy Ch13 ｜ S1 Ch4
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-术语与格式 FM Ch15 圆周运动（进阶） §15.1、§15.2、§15.3
-· 速览 §15.1 水平圆 p.355（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.2 三维情形 p.360（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.3 竖直圆 p.365（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>3月22日 周一
-────────────
-21:00-22:15 纯数
-格式训练 P2/3 Ch4 微分（§4.3、§4.4）
-· Ex 4C 题 1–14（约 31 分钟，p.90）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 4D 题 1–12（约 28 分钟，p.94）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>3月23日 周二
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch13 波的叠加（§13.3、§13.4）
-· 节末 Questions 题 全部（约 25 分钟，p.347）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.356）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>3月24日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch4 微分 §4.5、§4.6、§4.7
-· 速览 §4.5 三角函数的导数 p.95（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.6 隐函数求导 p.99（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §4.7 参数方程求导 p.103（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>3月25日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch13 波的叠加 §13.5
-· 速览 §13.5 衍射光栅（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>3月26日 周五
-────────────
-21:00-22:15 学术英语
-EAP 36
-· 学术写作⑩：EAP 真题 essay 题目精练
-· 词汇/术语入 Anki
-EAP 37
-· 综合复习：EAP 读听说写技能串联
-· 词汇/术语入 Anki</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>3月27日 周六
-────────────
-14:00-15:00 应用数学
-术语与格式 S1 Ch5 排列与组合 §5.1、§5.2、§5.3、§5.4
-· 速览 §5.1 阶乘函数 p.124（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.2 排列 p.125（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.3 组合 p.135（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.4 排列组合的应用 p.138（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-20:00-21:00 应用数学
-格式训练 S1 Ch5 排列与组合（§5.1、§5.2）
-· Ex 5A 题 1–9（约 24 分钟，p.124）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 5B 题 1–7（约 20 分钟，p.127）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>3月28日 周日
@@ -5398,12 +5363,10 @@
 ★ 3月测试：P2/3 Ch1｜物理 Ch1-9｜S1 Ch1-3
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-格式训练 FM Ch15 圆周运动（进阶）（§15.1、§15.2）
-· Ex 15A 题 全部（约 25 分钟，p.357）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 15B 题 全部（约 25 分钟，p.362）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+术语与格式 FM Ch15 圆周运动（进阶） §15.1、§15.2、§15.3
+· 速览 §15.1 水平圆、§15.2 三维情形、§15.3 竖直圆（p.355、p.360、p.365，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -5413,40 +5376,40 @@
           <t>3月29日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch4 微分（§4.5、§4.6）
-· Ex 4E 题 1–17（约 35 分钟，p.98）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 4F 题 1–14（约 31 分钟，p.101）
+术语与格式 P2/3 Ch4 微分 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 乘积法则、§4.2 商法则、§4.3 指数函数的导数、§4.4 自然对数函数的导数（p.81、p.84、p.87、p.91，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>3月30日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch13 波的叠加 §13.1、§13.2、§13.3、§13.4
+· 速览 §13.1 波的叠加原理、§13.2 波的衍射、§13.3 干涉、§13.4 杨氏双缝实验（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>3月31日 周三
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch4 微分（§4.1、§4.2）
+· Ex 4A 题 1–8（约 22 分钟，p.83）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 1–13（约 30 分钟，p.87）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+格式训练 P2/3 Ch4 微分（§4.3、§4.4）
+· Ex 4C 题 1–14（约 31 分钟，p.90）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4D 题 1–12（约 28 分钟，p.94）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>3月30日 周二
-────────────
-21:00-22:15 物理
-章末复习 Phy Ch13 波的叠加
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：叠加与干涉、双缝、衍射光栅
-· 过关自测：能默写 λ=ax/D；能判断相干条件；能算条纹间距；Chapter 13 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>3月31日 周三
-────────────
-21:00-22:15 纯数
-章末复习 P2/3 Ch4 微分
-· 章末复习题 End-of-chapter review p.108，限时 30 分钟
-· 本章要会：乘积/商/链式法则的综合运用、隐函数与参数方程二阶导、导数用于变化率
-· 过关自测：参数方程求二阶导能独立做对；Ex 4A–4G 错题清零；能说清隐函数求导何时必须链式
-术语与格式 P2/3 Ch5 积分 §5.1、§5.2、§5.3、§5.4
-· 速览 §5.1 指数函数的积分 p.112（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.2 1/(ax+b) 的积分 p.115（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §5.3 sin/cos/sec²(ax+b) 的积分 p.118（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
@@ -5523,14 +5486,18 @@
           <t>4月1日 周四
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch14 驻波 §14.1、§14.2、§14.3、§14.4
-· 速览 §14.1 从行波到驻波（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §14.2 波节与波腹（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §14.3 驻波的形成（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 Phy Ch14 驻波（§14.1、§14.2）
-· 节末 Questions 题 全部（约 25 分钟，p.369）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.370）</t>
+格式训练 Phy Ch13 波的叠加（§13.1、§13.2）
+· 节末 Questions 题 全部（约 25 分钟，p.341）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.343）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+格式训练 Phy Ch13 波的叠加（§13.3、§13.4）
+· 节末 Questions 题 全部（约 25 分钟，p.347）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.356）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -5538,14 +5505,119 @@
           <t>4月2日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 38
-· EAP 模拟④：读写综合限时任务
+EAP 36
+· 学术写作⑩：EAP 真题 essay 题目精练
 · 词汇/术语入 Anki</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
           <t>4月3日 周六 ◆清明节假期
+────────────
+14:00-15:00 应用数学
+术语与格式 S1 Ch5 排列与组合 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 阶乘函数、§5.2 排列、§5.3 组合、§5.4 排列组合的应用（p.124、p.125、p.135、p.138，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+20:00-21:00 应用数学
+格式训练 S1 Ch5 排列与组合（§5.1、§5.2）
+· Ex 5A 题 1–9（约 24 分钟，p.124）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5B 题 1–7（约 20 分钟，p.127）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>4月4日 周日 ◆清明节假期
+────────────
+14:00-15:00 复习/测试
+· 回顾：P2/3 Ch4 ｜ Phy Ch13 ｜ S1 Ch5
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+格式训练 FM Ch15 圆周运动（进阶）（§15.1、§15.2）
+· Ex 15A 题 全部（约 25 分钟，p.357）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 15B 题 全部（约 25 分钟，p.362）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>4月5日 周一 ◆清明节假期
+────────────
+14:00-15:00 纯数
+术语与格式 P2/3 Ch4 微分 §4.5、§4.6、§4.7
+· 速览 §4.5 三角函数的导数、§4.6 隐函数求导、§4.7 参数方程求导（p.95、p.99、p.103，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 纯数
+格式训练 P2/3 Ch4 微分（§4.5、§4.6）
+· Ex 4E 题 1–17（约 35 分钟，p.98）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4F 题 1–14（约 31 分钟，p.101）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>4月6日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch13 波的叠加 §13.5
+· 速览 §13.5 衍射光栅（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>4月7日 周三
+────────────
+21:00-22:15 纯数
+章末复习 P2/3 Ch4 微分
+· 章末复习题 End-of-chapter review p.108，限时 30 分钟
+· 本章要会：乘积/商/链式法则的综合运用、隐函数与参数方程二阶导、导数用于变化率
+· 过关自测：参数方程求二阶导能独立做对；Ex 4A–4G 错题清零；能说清隐函数求导何时必须链式
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>4月8日 周四
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch13 波的叠加
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：叠加与干涉、双缝、衍射光栅
+· 过关自测：能默写 λ=ax/D；能判断相干条件；能算条纹间距；Chapter 13 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>4月9日 周五
+────────────
+21:00-22:15 学术英语
+EAP 37
+· 综合复习：EAP 读听说写技能串联
+· 词汇/术语入 Anki</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>4月10日 周六
 ────────────
 14:00-15:00 应用数学
 章末复习 S1 Ch5 排列与组合
@@ -5556,19 +5628,17 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 应用数学
 术语与格式 S1 Ch6 概率分布 §6.1、§6.2、§6.3
-· 速览 §6.1 离散随机变量 p.150（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.2 概率分布 p.150（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.3 离散随机变量的期望与方差 p.156（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>4月4日 周日 ◆清明节假期
+· 速览 §6.1 离散随机变量、§6.2 概率分布、§6.3 离散随机变量的期望与方差（p.150、p.150、p.156，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>4月11日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch5 ｜ Phy Ch14 ｜ S1 Ch6
+· 回顾：P2/3 Ch4 ｜ Phy Ch13 ｜ S1 Ch6
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -5581,32 +5651,54 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>4月5日 周一 ◆清明节假期
-────────────
-14:00-15:00 纯数
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>4月12日 周一
+────────────
+21:00-22:15 纯数
+术语与格式 P2/3 Ch5 积分 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 指数函数的积分、§5.2 1/(ax+b) 的积分、§5.3 sin/cos/sec²(ax+b) 的积分、§5.4 进一步的三角函数积分（p.112、p.115、p.118、p.121，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>4月13日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch14 驻波 §14.1、§14.2、§14.3、§14.4
+· 速览 §14.1 从行波到驻波、§14.2 波节与波腹、§14.3 驻波的形成、§14.4 测定声波的波长与速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>4月14日 周三
+────────────
+21:00-22:15 纯数
 格式训练 P2/3 Ch5 积分（§5.1、§5.2）
 · Ex 5A 题 1–12（约 28 分钟，p.113）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 5B 题 1–10（约 25 分钟，p.117）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 纯数
-格式训练 P2/3 Ch5 积分（§5.3、§5.4）
-· Ex 5C 题 1–10（约 25 分钟，p.120）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 5D 题 1–12（约 28 分钟，p.125）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>4月6日 周二
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>4月15日 周四
 ────────────
 21:00-22:15 物理
+格式训练 Phy Ch14 驻波（§14.1、§14.2）
+· 节末 Questions 题 全部（约 25 分钟，p.369）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.370）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 章末复习 Phy Ch14 驻波
 · 章末复习题 End-of-chapter review，限时 30 分钟
 · 本章要会：驻波与共振、弦与气柱的基频与泛音
@@ -5615,43 +5707,19 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>4月7日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch5 积分 §5.5
-· 速览 §5.5 梯形法则 p.126（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>4月8日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch15 原子结构 §15.1、§15.2、§15.3、§15.4
-· 速览 §15.1 观察原子内部（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.2 α 粒子散射与原子核（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.3 原子的简单模型（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.4 核子与电子（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>4月9日 周五
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>4月16日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 39
-· 个人陈述①：素材梳理与初稿
+EAP 38
+· EAP 模拟④：读写综合限时任务
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>4月10日 周六
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>4月17日 周六
 ────────────
 14:00-15:00 应用数学
 格式训练 S1 Ch6 概率分布（§6.1、§6.2）
@@ -5660,6 +5728,7 @@
 · Ex 6B 题 1–15（约 32 分钟，p.158）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 应用数学
 章末复习 S1 Ch6 概率分布
 · 章末复习题 End-of-chapter review p.162，限时 30 分钟
@@ -5669,28 +5738,54 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>4月11日 周日
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>4月18日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch5 ｜ Phy Ch15 ｜ S1 Ch6
+· 回顾：P2/3 Ch5 ｜ Phy Ch14 ｜ S1 Ch6
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
 术语与格式 FM Ch16 胡克定律 §16.1、§16.2、§16.3
-· 速览 §16.1 胡克定律 p.380（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §16.2 弹性势能 p.385（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §16.3 功能原理 p.389（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>4月12日 周一
+· 速览 §16.1 胡克定律、§16.2 弹性势能、§16.3 功能原理（p.380、p.385、p.389，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>4月19日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch5 积分（§5.3、§5.4）
+· Ex 5C 题 1–10（约 25 分钟，p.120）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5D 题 1–12（约 28 分钟，p.125）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+术语与格式 P2/3 Ch5 积分 §5.5
+· 速览 §5.5 梯形法则（p.126，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>4月20日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch15 原子结构 §15.1、§15.2、§15.3、§15.4
+· 速览 §15.1 观察原子内部、§15.2 α 粒子散射与原子核、§15.3 原子的简单模型、§15.4 核子与电子（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>4月21日 周三
 ────────────
 21:00-22:15 纯数
 章末复习 P2/3 Ch5 积分
@@ -5701,9 +5796,9 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>4月13日 周二
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>4月22日 周四
 ────────────
 21:00-22:15 物理
 格式训练 Phy Ch15 原子结构（§15.1、§15.2）
@@ -5711,56 +5806,31 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.392）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>4月14日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch6 方程的数值解法 §6.1、§6.2、§6.3
-· 速览 §6.1 寻找初始近似值 p.135（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.2 改进解的精度 p.140（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §6.3 迭代法的跨领域应用 p.149（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>4月15日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch15 原子结构（§15.3、§15.4）
-· 节末 Questions 题 全部（约 25 分钟，p.393）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.397）
-术语与格式 Phy Ch15 原子结构 §15.5、§15.6、§15.7、§15.8
-· 速览 §15.5 原子核内的力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.6 放射性的发现（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.7 放射性物质发出的射线（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>4月16日 周五
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>4月23日 周五
 ────────────
 21:00-22:15 学术英语
+EAP 39
+· 个人陈述①：素材梳理与初稿
+· 词汇/术语入 Anki
 EAP 40
 · 个人陈述②：修改、润色与定稿
 · 词汇/术语入 Anki</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>4月17日 周六
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>4月24日 周六
 ────────────
 14:00-15:00 应用数学
 术语与格式 S1 Ch7 二项分布与几何分布 §7.1、§7.2
-· 速览 §7.1 二项分布 p.166（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.2 几何分布 p.175（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 速览 §7.1 二项分布、§7.2 几何分布（p.166、p.175，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 20:00-21:00 应用数学
 章末复习 S1 Ch7 二项分布与几何分布
@@ -5771,112 +5841,6 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>4月18日 周日
-────────────
-14:00-15:00 复习/测试
-· 回顾：P2/3 Ch6 ｜ Phy Ch15 ｜ S1 Ch7
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-格式训练 FM Ch16 胡克定律（§16.1、§16.2）
-· Ex 16A 题 全部（约 25 分钟，p.382）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 16B 题 全部（约 25 分钟，p.387）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>4月19日 周一
-────────────
-21:00-22:15 纯数
-格式训练 P2/3 Ch6 方程的数值解法（§6.1、§6.2）
-· Ex 6A 题 1–15（约 32 分钟，p.137）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 6B 题 1–14（约 31 分钟，p.146）
-章末复习 P2/3 Ch6 方程的数值解法
-· 章末复习题 End-of-chapter review p.155，限时 30 分钟
-· 本章要会：用迭代法（不动点/牛顿—拉夫森）求方程近似解
-· 过关自测：能默写牛顿—拉夫森迭代式；能判断迭代是否收敛（|f'(x)|&lt;1）；Ex 6A–6C 错题清零</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>4月20日 周二
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch15 原子结构（§15.5、§15.6）
-· 节末 Questions 题 全部（约 25 分钟，p.400）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.401）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>4月21日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch7 进阶代数 §7.1、§7.2、§7.3、§7.4
-· 速览 §7.1 假分式 p.166（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.2 部分分式 p.168（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.3 二项式展开 (1+x)^n（n 非正整数） p.174（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §7.4 二项式展开 (a+x)^n（n 非正整数） p.177（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>4月22日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch15 原子结构（§15.7、§15.8）
-· 节末 Questions 题 全部（约 25 分钟，p.402）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.405）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>4月23日 周五
-────────────
-21:00-22:15 学术英语
-EAP 强化 01
-· 限时 essay（40 分钟 / 450 词）并自评
-· 限时完成后复盘
-EAP 强化 02
-· 听力讲座 + 康奈尔笔记 + 口头复述
-· 限时完成后复盘</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>4月24日 周六
-────────────
-14:00-15:00 应用数学
-术语与格式 S1 Ch8 正态分布 §8.1、§8.2、§8.3、§8.4
-· 速览 §8.1 连续随机变量 p.188（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.2 正态分布 p.193（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.3 用正态分布建模 p.205（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.4 二项分布的正态近似 p.208（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-20:00-21:00 应用数学
-格式训练 S1 Ch8 正态分布（§8.1、§8.2）
-· Ex 8A 题 1–6（约 19 分钟，p.191）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 8B 题 1–4（约 16 分钟，p.199）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>4月25日 周日
@@ -5885,12 +5849,13 @@
 ★ 期中测试：P2/3 Ch1-2｜物理 Ch1-11｜S1 Ch1-5
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-章末复习 FM Ch16 胡克定律
-· 章末复习题 End-of-chapter review p.396，限时 30 分钟
-· 本章要会：能用胡克定律与弹性势能解弹簧问题
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 FM Ch16 胡克定律（§16.1、§16.2）
+· Ex 16A 题 全部（约 25 分钟，p.382）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 16B 题 全部（约 25 分钟，p.387）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
     </row>
@@ -5900,62 +5865,64 @@
           <t>4月26日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch7 进阶代数（§7.1、§7.2）
-· Ex 7A 题 1–4（约 16 分钟，p.167）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 7B 题 1–10（约 25 分钟，p.173）
+术语与格式 P2/3 Ch6 方程的数值解法 §6.1、§6.2、§6.3
+· 速览 §6.1 寻找初始近似值、§6.2 改进解的精度、§6.3 迭代法的跨领域应用（p.135、p.140、p.149，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>4月27日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch15 原子结构（§15.3、§15.4）
+· 节末 Questions 题 全部（约 25 分钟，p.393）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.397）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>4月28日 周三
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch6 方程的数值解法（§6.1、§6.2）
+· Ex 6A 题 1–15（约 32 分钟，p.137）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6B 题 1–14（约 31 分钟，p.146）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>4月29日 周四
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch15 原子结构 §15.5、§15.6、§15.7、§15.8
+· 速览 §15.5 原子核内的力、§15.6 放射性的发现、§15.7 放射性物质发出的射线、§15.8 α 与 β 衰变中的能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+格式训练 Phy Ch15 原子结构（§15.5、§15.6）
+· 节末 Questions 题 全部（约 25 分钟，p.400）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.401）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>4月27日 周二
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch15 原子结构 §15.9、§15.10、§15.11、§15.12
-· 速览 §15.9 放射性衰变方程（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.10 基本粒子（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.11 粒子家族（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §15.12 再看 β 衰变（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>4月28日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P2/3 Ch7 进阶代数（§7.3、§7.4）
-· Ex 7C 题 1–11（约 26 分钟，p.176）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 7D 题 1–8（约 22 分钟，p.178）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>4月29日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch15 原子结构（§15.9、§15.10）
-· 节末 Questions 题 全部（约 25 分钟，p.406）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.407）
-格式训练 Phy Ch15 原子结构（§15.11、§15.12）
-· 节末 Questions 题 全部（约 25 分钟，p.409）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.410）</t>
-        </is>
-      </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>4月30日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 强化 03
-· 学术阅读长文速读 + 摘要写作
+EAP 强化 01
+· 限时 essay（40 分钟 / 450 词）并自评
 · 限时完成后复盘</t>
         </is>
       </c>
@@ -6033,6 +6000,220 @@
           <t>5月1日 周六 ◆劳动节假期
 ────────────
 14:00-15:00 应用数学
+术语与格式 S1 Ch8 正态分布 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 连续随机变量、§8.2 正态分布、§8.3 用正态分布建模、§8.4 二项分布的正态近似（p.188、p.193、p.205、p.208，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+20:00-21:00 应用数学
+格式训练 S1 Ch8 正态分布（§8.1、§8.2）
+· Ex 8A 题 1–6（约 19 分钟，p.191）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 1–4（约 16 分钟，p.199）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>5月2日 周日 ◆劳动节假期
+────────────
+14:00-15:00 复习/测试
+· 回顾：P2/3 Ch6 ｜ Phy Ch15 ｜ S1 Ch8
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+章末复习 FM Ch16 胡克定律
+· 章末复习题 End-of-chapter review p.396，限时 30 分钟
+· 本章要会：能用胡克定律与弹性势能解弹簧问题
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>5月3日 周一 ◆劳动节假期
+────────────
+14:00-15:00 纯数
+章末复习 P2/3 Ch6 方程的数值解法
+· 章末复习题 End-of-chapter review p.155，限时 30 分钟
+· 本章要会：用迭代法（不动点/牛顿—拉夫森）求方程近似解
+· 过关自测：能默写牛顿—拉夫森迭代式；能判断迭代是否收敛（|f'(x)|&lt;1）；Ex 6A–6C 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 纯数
+术语与格式 P2/3 Ch7 进阶代数 §7.1、§7.2、§7.3、§7.4
+· 速览 §7.1 假分式、§7.2 部分分式、§7.3 二项式展开 (1+x)^n（n 非正整数）、§7.4 二项式展开 (a+x)^n（n 非正整数）（p.166、p.168、p.174、p.177，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>5月4日 周二 ◆劳动节假期
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch15 原子结构（§15.7、§15.8）
+· 节末 Questions 题 全部（约 25 分钟，p.402）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.405）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+术语与格式 Phy Ch15 原子结构 §15.9、§15.10、§15.11、§15.12
+· 速览 §15.9 放射性衰变方程、§15.10 基本粒子、§15.11 粒子家族、§15.12 再看 β 衰变（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>5月5日 周三 ◆劳动节假期
+────────────
+14:00-15:00 纯数
+格式训练 P2/3 Ch7 进阶代数（§7.1、§7.2）
+· Ex 7A 题 1–4（约 16 分钟，p.167）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 7B 题 1–10（约 25 分钟，p.173）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
+格式训练 P2/3 Ch7 进阶代数（§7.3、§7.4）
+· Ex 7C 题 1–11（约 26 分钟，p.176）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 7D 题 1–8（约 22 分钟，p.178）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>5月6日 周四
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch15 原子结构（§15.9、§15.10）
+· 节末 Questions 题 全部（约 25 分钟，p.406）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.407）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>5月7日 周五
+────────────
+21:00-22:15 学术英语
+EAP 强化 02
+· 听力讲座 + 康奈尔笔记 + 口头复述
+· 限时完成后复盘</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>5月8日 周六
+────────────
+21:00-22:15 学术英语
+EAP 强化 03
+· 学术阅读长文速读 + 摘要写作
+· 限时完成后复盘</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>5月9日 周日
+────────────
+14:00-15:00 复习/测试
+· 回顾：P2/3 Ch7 ｜ Phy Ch15
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+术语与格式 FM Ch17 变力作用下的直线运动 §17.1、§17.2
+· 速览 §17.1 加速度关于时间、§17.2 加速度关于位移（p.398、p.403，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>5月10日 周一
+────────────
+21:00-22:15 纯数
+术语与格式 P2/3 Ch7 进阶代数 §7.5
+· 速览 §7.5 部分分式与二项式展开（p.179，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+章末复习 P2/3 Ch7 进阶代数
+· 章末复习题 End-of-chapter review p.182，限时 30 分钟
+· 本章要会：部分分式、除法算式与余数定理、代数式的组合运算
+· 过关自测：能把真分式拆成部分分式；能处理假分式（先做除法）；Ex 7A–7E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>5月11日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch15 原子结构（§15.11、§15.12）
+· 节末 Questions 题 全部（约 25 分钟，p.409）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.410）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>5月12日 周三
+────────────
+21:00-22:15 纯数
+术语与格式 P2/3 Ch8 进阶微积分 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 tan⁻¹x 的导数、§8.2 1/(x²+a²) 的积分、§8.3 k f′(x)/f(x) 的积分、§8.4 换元积分法（p.186、p.187、p.189、p.191，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>5月13日 周四
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch15 原子结构 §15.13
+· 速览 §15.13 另一种核力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>5月14日 周五
+────────────
+21:00-22:15 学术英语
+EAP 强化 04
+· seminar 讨论录音复盘（流利度/学术语域）
+· 限时完成后复盘
+EAP 强化 05
+· presentation 限时演练与同伴反馈
+· 限时完成后复盘</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>5月15日 周六
+────────────
+14:00-15:00 应用数学
 章末复习 S1 Ch8 正态分布
 · 章末复习题 End-of-chapter review p.215，限时 30 分钟
 · 本章要会：正态分布、标准化、逆正态求分位点、近似二项分布
@@ -6046,118 +6227,12 @@
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>5月2日 周日 ◆劳动节假期
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>5月16日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch7 ｜ Phy Ch15 ｜ S1 Ch8
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-术语与格式 FM Ch17 变力作用下的直线运动 §17.1、§17.2
-· 速览 §17.1 加速度关于时间 p.398（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §17.2 加速度关于位移 p.403（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>5月3日 周一 ◆劳动节假期
-────────────
-14:00-15:00 纯数
-术语与格式 P2/3 Ch7 进阶代数 §7.5
-· 速览 §7.5 部分分式与二项式展开 p.179（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-15:15-16:15 纯数
-章末复习 P2/3 Ch7 进阶代数
-· 章末复习题 End-of-chapter review p.182，限时 30 分钟
-· 本章要会：部分分式、除法算式与余数定理、代数式的组合运算
-· 过关自测：能把真分式拆成部分分式；能处理假分式（先做除法）；Ex 7A–7E 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>5月4日 周二 ◆劳动节假期
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch15 原子结构 §15.13
-· 速览 §15.13 另一种核力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-15:15-16:15 物理
-章末复习 Phy Ch15 原子结构
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：原子结构、光电效应、能级与光谱、波粒二象性
-· 过关自测：能默写 E=hf 与 hf=Φ+KE_max；能解释「存在红限频率」；Chapter 15 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>5月5日 周三 ◆劳动节假期
-────────────
-14:00-15:00 纯数
-术语与格式 P2/3 Ch8 进阶微积分 §8.1、§8.2、§8.3、§8.4
-· 速览 §8.1 tan⁻¹x 的导数 p.186（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.2 1/(x²+a²) 的积分 p.187（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.3 k f′(x)/f(x) 的积分 p.189（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.4 换元积分法 p.191（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-15:15-16:15 纯数
-格式训练 P2/3 Ch8 进阶微积分（§8.1、§8.2）
-· Ex 8A 题 1–5（约 18 分钟，p.187）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 8B 题 1–6（约 19 分钟，p.188）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>5月6日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy P1 实验技能 §P1.1–P1.5、§P1.6–P1.11
-· 速览 §P1.1–P1.5 实验操作与不确定度（一）（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §P1.6–P1.11 数据处理与误差合成（二）（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>5月7日 周五
-────────────
-21:00-22:15 学术英语
-EAP 强化 04
-· seminar 讨论录音复盘（流利度/学术语域）
-· 限时完成后复盘</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>5月8日 周六
-────────────
-21:00-22:15 学术英语
-EAP 强化 05
-· presentation 限时演练与同伴反馈
-· 限时完成后复盘</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>5月9日 周日
-────────────
-14:00-15:00 复习/测试
-· 回顾：P2/3 Ch8 ｜ Phy Ch15
+· 回顾：P2/3 Ch8 ｜ Phy Ch15 ｜ S1 Ch8
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -6170,25 +6245,55 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>5月10日 周一
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>5月17日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch8 进阶微积分（§8.1、§8.2）
+· Ex 8A 题 1–5（约 18 分钟，p.187）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 1–6（约 19 分钟，p.188）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>5月18日 周二
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch15 原子结构
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：原子结构、光电效应、能级与光谱、波粒二象性
+· 过关自测：能默写 E=hf 与 hf=Φ+KE_max；能解释「存在红限频率」；Chapter 15 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+术语与格式 Phy P1 实验技能 §P1.1–P1.5、§P1.6–P1.11
+· 速览 §P1.1–P1.5 实验操作与不确定度（一）、§P1.6–P1.11 数据处理与误差合成（二）（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>5月19日 周三
 ────────────
 21:00-22:15 纯数
 格式训练 P2/3 Ch8 进阶微积分（§8.3、§8.4）
 · Ex 8C 题 1–5（约 18 分钟，p.190）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 8D 题 1–9（约 24 分钟，p.193）
-术语与格式 P2/3 Ch8 进阶微积分 §8.5、§8.6、§8.7
-· 速览 §8.5 部分分式在积分中的应用 p.194（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.6 分部积分法 p.197（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.7 进阶积分技巧 p.201（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>5月11日 周二
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>5月20日 周四
 ────────────
 21:00-22:15 物理
 章末复习 Phy P1 实验技能
@@ -6199,48 +6304,19 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>5月12日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P2/3 Ch8 进阶微积分（§8.5、§8.6）
-· Ex 8E 题 1–6（约 19 分钟，p.196）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 8F 题 1–27（约 35 分钟，p.200）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>5月13日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch16 圆周运动 §16.1、§16.2、§16.3、§16.4
-· 速览 §16.1 描述圆周运动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §16.2 弧度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §16.3 恒定速率、变化速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §16.4 角速度（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>5月14日 周五
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>5月21日 周五
 ────────────
 21:00-22:15 学术英语
 EAP 强化 06
 · EAP 真题套卷（读+写）限时
-· 限时完成后复盘
-EAP 强化 07
-· EAP 真题套卷（听+说）限时
 · 限时完成后复盘</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>5月15日 周六
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>5月22日 周六
 ────────────
 14:00-15:00 应用数学
 真题精练 9709 S1 2019 Paper 6
@@ -6254,27 +6330,54 @@
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>5月16日 周日
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>5月23日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch8 ｜ Phy Ch16
+· 回顾：P2/3 Ch8 ｜ Phy Ch15
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
 术语与格式 FM Ch18 动量（进阶） §18.1、§18.2
-· 速览 §18.1 冲量与动量守恒 p.411（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §18.2 斜碰撞及其他例子 p.417（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>5月17日 周一
+· 速览 §18.1 冲量与动量守恒、§18.2 斜碰撞及其他例子（p.411、p.417，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>5月24日 周一
+────────────
+21:00-22:15 纯数
+术语与格式 P2/3 Ch8 进阶微积分 §8.5、§8.6、§8.7
+· 速览 §8.5 部分分式在积分中的应用、§8.6 分部积分法、§8.7 进阶积分技巧（p.194、p.197、p.201，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+格式训练 P2/3 Ch8 进阶微积分（§8.5、§8.6）
+· Ex 8E 题 1–6（约 19 分钟，p.196）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8F 题 1–27（约 35 分钟，p.200）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>5月25日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch16 圆周运动 §16.1、§16.2、§16.3、§16.4
+· 速览 §16.1 描述圆周运动、§16.2 弧度、§16.3 恒定速率、变化速度、§16.4 角速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>5月26日 周三
 ────────────
 21:00-22:15 纯数
 章末复习 P2/3 Ch8 进阶微积分
@@ -6285,60 +6388,33 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>5月18日 周二
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>5月27日 周四
 ────────────
 21:00-22:15 物理
 格式训练 Phy Ch16 圆周运动（§16.1、§16.2）
 · 节末 Questions 题 全部（约 25 分钟，p.454）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.455）
-格式训练 Phy Ch16 圆周运动（§16.3、§16.4）
-· 节末 Questions 题 全部（约 25 分钟，p.457）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.458）</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>5月19日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch9 向量 §9.1、§9.2、§9.3、§9.4
-· 速览 §9.1 位移（平移）向量 p.211（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.2 位置向量 p.220（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.3 数量积 p.225（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.4 直线的向量方程 p.231（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>5月20日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch16 圆周运动 §16.5、§16.6、§16.7
-· 速览 §16.5 向心力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §16.6 计算加速度与力（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §16.7 向心力的来源（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>5月21日 周五
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>5月28日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 强化 08
-· 学术词汇综合自测（AWL 全表）
+EAP 强化 07
+· EAP 真题套卷（听+说）限时
 · 限时完成后复盘</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>5月22日 周六
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>5月29日 周六
 ────────────
 14:00-15:00 应用数学
 真题精练 9709 S1 2020 Paper 6
@@ -6352,14 +6428,13 @@
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>5月23日 周日
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>5月30日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch9 ｜ Phy Ch16
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
+★ 5月测试：P2/3 Ch1-4｜物理 Ch1-12｜S1 全书
+· 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
 章末复习 FM Ch18 动量（进阶）
 · 章末复习题 End-of-chapter review p.429，限时 30 分钟
@@ -6370,114 +6445,16 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>5月24日 周一
-────────────
-21:00-22:15 纯数
-格式训练 P2/3 Ch9 向量（§9.1、§9.2）
-· Ex 9A 题 1–7（约 20 分钟，p.218）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9B 题 1–13（约 30 分钟，p.223）
-格式训练 P2/3 Ch9 向量（§9.3、§9.4）
-· Ex 9C 题 1–10（约 25 分钟，p.230）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9D 题 1–13（约 30 分钟，p.235）</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>5月25日 周二
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch16 圆周运动（§16.5、§16.6）
-· 节末 Questions 题 全部（约 25 分钟，p.461）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.464）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>5月26日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch9 向量 §9.5
-· 速览 §9.5 两直线的交点 p.236（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>5月27日 周四
-────────────
-21:00-22:15 物理
-章末复习 Phy Ch16 圆周运动
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：圆周运动、向心加速度、转动惯量概念
-· 过关自测：能默写 a=v²/r 与 F=mv²/r；能分析竖直圆周运动的临界点；Chapter 16 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>5月28日 周五
-────────────
-21:00-22:15 学术英语
-EAP 强化 09
-· 个人陈述 + 面试问答演练
-· 限时完成后复盘</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>5月29日 周六
-────────────
-14:00-15:00 应用数学
-真题精练 9709 S1 2021 Paper 6
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-20:00-21:00 应用数学
-真题精练 9709 M1 2022 Paper 4
-· 力学/概率统计真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>5月30日 周日
-────────────
-14:00-15:00 复习/测试
-★ 5月测试：P2/3 Ch1-4｜物理 Ch1-12｜S1 全书
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-术语与格式 FM Ch8 连续随机变量 §8.1、§8.2、§8.3、§8.4
-· 速览 §8.1 概率密度函数 p.155（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.2 累积分布函数 p.161（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.3 计算连续随机变量的 E(g(X)) p.174（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §8.4 由 Y=g(X) 求 pdf 与 cdf p.178（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-    </row>
     <row r="7" ht="178" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>5月31日 周一
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch9 向量
-· 章末复习题 End-of-chapter review p.240，限时 30 分钟
-· 本章要会：三维向量运算、数量积、直线与平面的向量方程、夹角与交点
-· 过关自测：能默写直线与平面的向量方程；能求两直线夹角与交点；Ex 9A–9E 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 P2/3 Ch9 向量 §9.1、§9.2、§9.3、§9.4
+· 速览 §9.1 位移（平移）向量、§9.2 位置向量、§9.3 数量积、§9.4 直线的向量方程（p.211、p.220、p.225、p.231，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -6554,54 +6531,164 @@
           <t>6月1日 周二
 ────────────
 21:00-22:15 物理
+格式训练 Phy Ch16 圆周运动（§16.3、§16.4）
+· 节末 Questions 题 全部（约 25 分钟，p.457）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.458）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+术语与格式 Phy Ch16 圆周运动 §16.5、§16.6、§16.7
+· 速览 §16.5 向心力、§16.6 计算加速度与力、§16.7 向心力的来源（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>6月2日 周三
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch9 向量（§9.1、§9.2）
+· Ex 9A 题 1–7（约 20 分钟，p.218）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9B 题 1–13（约 30 分钟，p.223）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>6月3日 周四
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch16 圆周运动（§16.5、§16.6）
+· 节末 Questions 题 全部（约 25 分钟，p.461）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.464）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>6月4日 周五
+────────────
+21:00-22:15 学术英语
+EAP 强化 08
+· 学术词汇综合自测（AWL 全表）
+· 限时完成后复盘</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>6月5日 周六
+────────────
+14:00-15:00 应用数学
+真题精练 9709 S1 2021 Paper 6
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+20:00-21:00 应用数学
+真题精练 9709 M1 2022 Paper 4
+· 力学/概率统计真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>6月6日 周日
+────────────
+14:00-15:00 复习/测试
+· 回顾：P2/3 Ch9 ｜ Phy Ch16
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+术语与格式 FM Ch8 连续随机变量 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 概率密度函数、§8.2 累积分布函数、§8.3 计算连续随机变量的 E(g(X))、§8.4 由 Y=g(X) 求 pdf 与 cdf（p.155、p.161、p.174、p.178，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>6月7日 周一
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch9 向量（§9.3、§9.4）
+· Ex 9C 题 1–10（约 25 分钟，p.230）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9D 题 1–13（约 30 分钟，p.235）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+术语与格式 P2/3 Ch9 向量 §9.5
+· 速览 §9.5 两直线的交点（p.236，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>6月8日 周二
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch16 圆周运动
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：圆周运动、向心加速度、转动惯量概念
+· 过关自测：能默写 a=v²/r 与 F=mv²/r；能分析竖直圆周运动的临界点；Chapter 16 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>6月9日 周三 ◆端午节假期
+────────────
+14:00-15:00 纯数
+章末复习 P2/3 Ch9 向量
+· 章末复习题 End-of-chapter review p.240，限时 30 分钟
+· 本章要会：三维向量运算、数量积、直线与平面的向量方程、夹角与交点
+· 过关自测：能默写直线与平面的向量方程；能求两直线夹角与交点；Ex 9A–9E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 纯数
+术语与格式 P2/3 Ch10 微分方程 §10.1、§10.2
+· 速览 §10.1 分离变量法、§10.2 由实际问题建立微分方程（p.245、p.252，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>6月10日 周四
+────────────
+21:00-22:15 物理
 术语与格式 Phy Ch17 引力场 §17.1、§17.2、§17.3、§17.4
-· 速览 §17.1 表示引力场（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §17.2 重力场强度 g（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §17.3 引力场中的能量（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-格式训练 Phy Ch17 引力场（§17.1、§17.2）
-· 节末 Questions 题 全部（约 25 分钟，p.480）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.482）</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>6月2日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch10 微分方程 §10.1、§10.2
-· 速览 §10.1 分离变量法 p.245（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §10.2 由实际问题建立微分方程 p.252（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>6月3日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch17 引力场（§17.3、§17.4）
-· 节末 Questions 题 全部（约 25 分钟，p.484）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.486）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>6月4日 周五
+· 速览 §17.1 表示引力场、§17.2 重力场强度 g、§17.3 引力场中的能量、§17.4 引力势（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>6月11日 周五
 ────────────
 21:00-22:15 学术英语
+EAP 强化 09
+· 个人陈述 + 面试问答演练
+· 限时完成后复盘
 EAP 强化 10
 · 学年总结：错题/弱项清单与下阶段目标
 · 限时完成后复盘</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>6月5日 周六
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>6月12日 周六
 ────────────
 14:00-15:00 应用数学
 真题精练 9709 S1 2022 Paper 6
@@ -6614,12 +6701,13 @@
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 8B 题 全部（约 25 分钟，p.163）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>6月6日 周日
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>6月13日 周日
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P2/3 Ch10 ｜ Phy Ch17 ｜ FM Ch8
@@ -6635,196 +6723,208 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>6月7日 周一
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>6月14日 周一
 ────────────
 21:00-22:15 纯数
 章末复习 P2/3 Ch10 微分方程
 · 章末复习题 End-of-chapter review p.262，限时 30 分钟
 · 本章要会：识别并求解一阶可分离变量微分方程、用初始条件定常数
 · 过关自测：能判断方程是否可分离变量；Ex 10A–10B 错题清零；能完整写出「分离→积分→代初值→写解」四步
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>6月15日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch17 引力场（§17.1、§17.2）
+· 节末 Questions 题 全部（约 25 分钟，p.480）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.482）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+格式训练 Phy Ch17 引力场（§17.3、§17.4）
+· 节末 Questions 题 全部（约 25 分钟，p.484）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.486）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>6月16日 周三
+────────────
+21:00-22:15 纯数
 术语与格式 P2/3 Ch11 复数 §11.1、§11.2、§11.3、§11.4
-· 速览 §11.1 虚数 p.267（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §11.2 复数 p.269（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §11.3 复平面 p.273（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>6月8日 周二
+· 速览 §11.1 虚数、§11.2 复数、§11.3 复平面、§11.4 解方程（p.267、p.269、p.273、p.283，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>6月17日 周四
 ────────────
 21:00-22:15 物理
 术语与格式 Phy Ch17 引力场 §17.5、§17.6、§17.7
-· 速览 §17.5 在引力下运行（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §17.6 轨道周期（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §17.7 绕地球运行（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>6月9日 周三 ◆端午节假期
-────────────
-14:00-15:00 纯数
-格式训练 P2/3 Ch11 复数（§11.1、§11.2）
-· Ex 11A 题 1–6（约 19 分钟，p.269）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 11B 题 1–10（约 25 分钟，p.272）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 纯数
-格式训练 P2/3 Ch11 复数（§11.3、§11.4）
-· Ex 11C 题 1–12（约 28 分钟，p.282）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 11D 题 1–10（约 25 分钟，p.288）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>6月10日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch17 引力场（§17.5、§17.6）
-· 节末 Questions 题 全部（约 25 分钟，p.488）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.490）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>6月11日 周五
+· 速览 §17.5 在引力下运行、§17.6 轨道周期、§17.7 绕地球运行（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>6月18日 周五
 ────────────
 21:00-22:15 进阶数学
 术语与格式 FM Ch9 推断统计 §9.1、§9.2、§9.3、§9.4
-· 速览 §9.1 t 分布 p.190（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.2 两均值之差的假设检验 p.197（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §9.3 配对 t 检验 p.203（5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 速览 §9.1 t 分布、§9.2 两均值之差的假设检验、§9.3 配对 t 检验、§9.4 小样本均值的置信区间（p.190、p.197、p.203、p.207，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>6月19日 周六
+────────────
+14:00-15:00 进阶数学
 格式训练 FM Ch9 推断统计（§9.1、§9.2）
 · Ex 9A 题 全部（约 25 分钟，p.192）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9B 题 全部（约 25 分钟，p.199）</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>6月12日 周六
-────────────
-14:00-15:00 进阶数学
+· Ex 9B 题 全部（约 25 分钟，p.199）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+20:00-21:00 进阶数学
 格式训练 FM Ch9 推断统计（§9.3、§9.4）
 · Ex 9C 题 全部（约 25 分钟，p.205）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 9D 题 全部（约 25 分钟，p.209）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-20:00-21:00 进阶数学
-术语与格式 FM Ch9 推断统计 §9.5
-· 速览 §9.5 均值之差的置信区间 p.210（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>6月13日 周日
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>6月20日 周日
 ────────────
 14:00-15:00 复习/测试
 · 回顾：P2/3 Ch11 ｜ Phy Ch17 ｜ FM Ch9
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch9 推断统计
-· 章末复习题 End-of-chapter review p.219，限时 30 分钟
-· 本章要会：能用 t 分布做单/双样本假设检验与置信区间
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>6月14日 周一
+术语与格式 FM Ch9 推断统计 §9.5
+· 速览 §9.5 均值之差的置信区间（p.210，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>6月21日 周一
 ────────────
 21:00-22:15 纯数
+格式训练 P2/3 Ch11 复数（§11.1、§11.2）
+· Ex 11A 题 1–6（约 19 分钟，p.269）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11B 题 1–10（约 25 分钟，p.272）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>6月22日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch17 引力场（§17.5、§17.6）
+· 节末 Questions 题 全部（约 25 分钟，p.488）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.490）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>6月23日 周三
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch11 复数（§11.3、§11.4）
+· Ex 11C 题 1–12（约 28 分钟，p.282）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11D 题 1–10（约 25 分钟，p.288）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 术语与格式 P2/3 Ch11 复数 §11.5
-· 速览 §11.5 轨迹 p.288（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>6月15日 周二
+· 速览 §11.5 轨迹（p.288，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>6月24日 周四
 ────────────
 21:00-22:15 物理
 章末复习 Phy Ch17 引力场
 · 章末复习题 End-of-chapter review，限时 30 分钟
 · 本章要会：引力场、场强、引力势与轨道运动
 · 过关自测：能默写 F=GMm/r² 与 g=GM/r²；能区分场强与势；Chapter 17 EXAM-STYLE QUESTIONS 限时做完并批改
-术语与格式 Phy Ch18 振动 §18.1、§18.2、§18.3、§18.4
-· 速览 §18.1 自由振动与受迫振动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §18.2 观察振动（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §18.3 描述振动（5 分钟）：只看定义、符号、单位与例题的写法，不做题</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>6月16日 周三
-────────────
-21:00-22:15 纯数
-章末复习 P2/3 Ch11 复数
-· 章末复习题 End-of-chapter review p.297，限时 30 分钟
-· 本章要会：复数四则运算、模与辐角、Argand 图、复数方程与几何意义
-· 过关自测：能默写 i²=−1、模与辐角定义；能把复数在 Argand 图上表示；Ex 11A–11E 错题清零
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>6月17日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch18 振动（§18.1、§18.2）
-· 节末 Questions 题 全部（约 25 分钟，p.502）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.504）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>6月18日 周五
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>6月25日 周五
 ────────────
 21:00-22:15 进阶数学
+章末复习 FM Ch9 推断统计
+· 章末复习题 End-of-chapter review p.219，限时 30 分钟
+· 本章要会：能用 t 分布做单/双样本假设检验与置信区间
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>6月26日 周六
+────────────
+14:00-15:00 进阶数学
 术语与格式 FM Ch10 卡方检验 §10.1、§10.2、§10.3、§10.4
-· 速览 §10.1 建立假设 p.221（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §10.2 离散分布的拟合优度 p.227（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §10.3 连续分布的拟合优度 p.231（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §10.4 列联表检验相关性 p.237（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>6月19日 周六
-────────────
-14:00-15:00 进阶数学
+· 速览 §10.1 建立假设、§10.2 离散分布的拟合优度、§10.3 连续分布的拟合优度、§10.4 列联表检验相关性（p.221、p.227、p.231、p.237，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+20:00-21:00 进阶数学
 格式训练 FM Ch10 卡方检验（§10.1、§10.2）
 · Ex 10A 题 全部（约 25 分钟，p.223）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 10B 题 全部（约 25 分钟，p.229）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>6月27日 周日
+────────────
+14:00-15:00 复习/测试
+★ 学年末 AS 全科模拟（真题限时）
+· 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
 章末复习 FM Ch10 卡方检验
 · 章末复习题 End-of-chapter review p.248，限时 30 分钟
@@ -6834,179 +6934,61 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>6月20日 周日
-────────────
-14:00-15:00 复习/测试
-· 回顾：P2/3 Ch11 ｜ Phy Ch18 ｜ FM Ch10
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-术语与格式 FM Ch11 非参数检验 §11.1、§11.2、§11.3、§11.4
-· 速览 §11.1 非参数检验概述 p.250（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §11.2 单样本符号检验 p.251（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §11.3 单样本 Wilcoxon 符号秩检验 p.254（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §11.4 配对样本符号检验 p.260（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>6月21日 周一
-────────────
-21:00-22:15 纯数
+    </row>
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>6月28日 周一 ◆暑假
+────────────
+14:00-15:00 纯数
+章末复习 P2/3 Ch11 复数
+· 章末复习题 End-of-chapter review p.297，限时 30 分钟
+· 本章要会：复数四则运算、模与辐角、Argand 图、复数方程与几何意义
+· 过关自测：能默写 i²=−1、模与辐角定义；能把复数在 Argand 图上表示；Ex 11A–11E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 纯数
 真题精练 9709 P1 2019 Paper 1
 · 纯数真题卷，限时 1 小时 50 分
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>6月22日 周二
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch18 振动（§18.3、§18.4）
-· 节末 Questions 题 全部（约 25 分钟，p.506）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.510）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>6月23日 周三
-────────────
-21:00-22:15 纯数
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>6月29日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch18 振动 §18.1、§18.2、§18.3、§18.4
+· 速览 §18.1 自由振动与受迫振动、§18.2 观察振动、§18.3 描述振动、§18.4 简谐运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 物理
+格式训练 Phy Ch18 振动（§18.1、§18.2）
+· 节末 Questions 题 全部（约 25 分钟，p.502）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.504）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>6月30日 周三 ◆暑假
+────────────
+14:00-15:00 纯数
 真题精练 9709 P3 2019 Paper 3
 · 纯数真题卷，限时 1 小时 50 分
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题
+15:15-16:15 纯数
 真题精练 9709 P1 2020 Paper 1
 · 纯数真题卷，限时 1 小时 50 分
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>6月24日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch18 振动 §18.5、§18.6、§18.7、§18.8
-· 速览 §18.5 简谐运动的图像表示（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §18.6 频率与角频率（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §18.7 简谐运动方程（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §18.8 简谐运动中的能量变化（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>6月25日 周五
-────────────
-21:00-22:15 进阶数学
-格式训练 FM Ch11 非参数检验（§11.1、§11.2）
-· Ex 11A 题 全部（约 25 分钟，p.250）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 11B 题 全部（约 25 分钟，p.253）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>6月26日 周六
-────────────
-14:00-15:00 进阶数学
-格式训练 FM Ch11 非参数检验（§11.3、§11.4）
-· Ex 11C 题 全部（约 25 分钟，p.256）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 11D 题 全部（约 25 分钟，p.262）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-20:00-21:00 进阶数学
-术语与格式 FM Ch11 非参数检验 §11.5、§11.6
-· 速览 §11.5 Wilcoxon 配对符号秩检验 p.263（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 速览 §11.6 Wilcoxon 秩和检验 p.266（5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下本节术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>6月27日 周日
-────────────
-14:00-15:00 复习/测试
-★ 学年末 AS 全科模拟（真题限时）
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-章末复习 FM Ch11 非参数检验
-· 章末复习题 End-of-chapter review p.277，限时 30 分钟
-· 本章要会：能判断何时该用非参数检验并正确查临界值
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>6月28日 周一 ◆暑假
-────────────
-14:00-15:00 纯数
-真题精练 9709 P3 2020 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-15:15-16:15 纯数
-真题精练 9709 P1 2021 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>6月29日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch18 振动（§18.5、§18.6）
-· 节末 Questions 题 全部（约 25 分钟，p.511）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.514）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-15:15-16:15 物理
-格式训练 Phy Ch18 振动（§18.7、§18.8）
-· 节末 Questions 题 全部（约 25 分钟，p.516）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.522）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>6月30日 周三 ◆暑假
-────────────
-14:00-15:00 纯数
-真题精练 9709 P3 2021 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-15:15-16:15 纯数
-真题精练 9709 P1 2022 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>

--- a/StudyCompanionAndroid/assets/Schedule.xlsx
+++ b/StudyCompanionAndroid/assets/Schedule.xlsx
@@ -655,9 +655,13 @@
           <t>10月9日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 01
-· EAP 导论：学术英语与日常英语的差异
-· 词汇/术语入 Anki</t>
+EAP 01 学术英语与日常英语的差异
+· ① 回收：无（第一节）——这 10 分钟并入下面的输入
+· ② 输入（25 分钟）：EAP Foundation 写作区首页 + Academic Writing 入门页（https://www.eapfoundation.com/writing/）——只读这两页，读完立刻关掉；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：同一件事写两个版本：① 日常英语 80 词「我昨天做了什么」② 学术英语 80 词「本次实验的目的与方法」；再列 5 条差异（用词／缩写／人称／句长）
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-01 学术英语与日常英语的差异」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：两个版本都在；5 条差异里至少 3 条能举出具体例子（不许写「学术英语更正式」这种空话）
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -665,9 +669,13 @@
           <t>10月10日 周六
 ────────────
 21:00-22:15 学术英语
-EAP 02
-· 学术阅读①：略读与扫读（skimming）
-· 词汇/术语入 Anki</t>
+EAP 02 学术阅读①：略读与扫读（skimming）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：剑桥雅思真题 15 的 Reading Passage 1（真题书或 PDF）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：同一篇文章做两遍：第一遍 90 秒略读，只写一句「这段在讲什么」；第二遍扫读定位，挑 3 道题写出每题的定位词 + 出现在第几段
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-02 学术阅读①：略读与扫读（skimming）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：90 秒后能说出全文主题；3 道题的定位词都标对（答案对不对不重要，定位对才重要）
+· 本类（阅读类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -745,9 +753,13 @@
           <t>10月16日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 03
-· 学术词汇①：AWL Sublist 1-2 + Anki 制卡
-· 词汇/术语入 Anki</t>
+EAP 03 学术词汇①：AWL Sublist 1-2
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Anki 牌组「英语词汇::AWL」的 Sublist 1-2（180 张已建好，见 EAP\02_词汇与Anki.md）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：开 15–20 张新卡（20 分钟封顶，不要整节刷卡），然后用当天 10 个新词写一段 120 词学术段落（主题：为什么要用统计方法验证实验结论）
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-03 学术词汇①：AWL Sublist 1-2」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：10 个新词里至少主动用出 6 个；段落发我批改 TR / CC / LR / GRA
+· 本类（词汇类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -855,12 +867,13 @@
           <t>10月23日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 04
-· 段落写作：主题句/支撑句/结论句
-· 词汇/术语入 Anki
-EAP 05
-· 学术阅读②：识别论点、论据与论证结构
-· 词汇/术语入 Anki</t>
+EAP 04 段落写作：主题句／支撑句／结论句
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP Foundation 写作区 Paragraphs 页——只看这一页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：写一段 120 词：1 个主题句 + 3 个支撑句 + 1 个结论句；每个支撑句后面用括号标出它在支撑主题句的哪一半
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-04 段落写作：主题句／支撑句／结论句」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：主题句能一句话概括全段；3 个支撑句各带一条具体证据（数字、例子或引用）
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -955,9 +968,13 @@
           <t>10月30日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 06
-· 学术词汇②：AWL Sublist 3-4
-· 词汇/术语入 Anki</t>
+EAP 05 学术阅读②：识别论点、论据与论证结构
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：一篇 600–800 词学术短文，或剑桥雅思阅读 Passage 2；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：一页纸三块：① 论点一句话（用自己的英文）② 论据列表 ③ 「题干用词 ↔ 原文用词」同义替换表
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-05 学术阅读②：识别论点、论据与论证结构」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：论点能不看原文用自己的英文说出；同义替换至少 8 对
+· 本类（阅读类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -1067,38 +1084,43 @@
         <is>
           <t>7月2日 周五 ◆暑假
 ────────────
+14:00-15:00 学术英语
+EAP 强化 05 presentation 限时演练与同伴反馈
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自己 EAP 24 的 5 张幻灯片（或重做一版）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：3 分钟完整讲一遍 + 录像 + 写 3 条反馈
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-45 presentation 限时演练与同伴反馈」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：3 条反馈具体可执行（能直接改下一次的动作）
+· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
+15:15-16:15 学术英语
+EAP 强化 06 EAP 真题套卷（读 + 写）限时
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：剑桥雅思真题 15–20 里的一整套（Reading + Writing）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：严格限时 60 分钟阅读 + 60 分钟写作，做完统计正确率与四项自评
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-46 EAP 真题套卷（读 + 写）限时」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：记录阅读正确数 / 40、作文四项分；错题归因到「定位错 / 词不懂 / 时间不够」三类
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>7月3日 周六 ◆暑假
+────────────
 14:00-15:00 进阶数学
-术语与格式 FM Ch11 非参数检验 §11.1、§11.2、§11.3、§11.4
-· 速览 §11.1 非参数检验概述、§11.2 单样本符号检验、§11.3 单样本 Wilcoxon 符号秩检验、§11.4 配对样本符号检验（p.250、p.251、p.254、p.260，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-15:15-16:15 进阶数学
-格式训练 FM Ch11 非参数检验（§11.1、§11.2）
-· Ex 11A 题 全部（约 25 分钟，p.250）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 11B 题 全部（约 25 分钟，p.253）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>7月3日 周六 ◆暑假
-────────────
-14:00-15:00 进阶数学
-格式训练 FM Ch11 非参数检验（§11.3、§11.4）
-· Ex 11C 题 全部（约 25 分钟，p.256）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 11D 题 全部（约 25 分钟，p.262）
+格式训练 FM Ch10 卡方检验（§10.1、§10.2）
+· Ex 10A 题 全部（约 25 分钟，p.223）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 10B 题 全部（约 25 分钟，p.229）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
 20:00-21:00 进阶数学
-术语与格式 FM Ch11 非参数检验 §11.5、§11.6
-· 速览 §11.5 Wilcoxon 配对符号秩检验、§11.6 Wilcoxon 秩和检验（p.263、p.266，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+章末复习 FM Ch10 卡方检验
+· 章末复习题 End-of-chapter review p.248，限时 30 分钟
+· 本章要会：能做离散/连续拟合优度检验与列联表关联检验
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1106,16 +1128,14 @@
           <t>7月4日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch11 ｜ Phy Ch18 ｜ FM Ch11
+· 回顾：P2/3 Ch11 ｜ Phy Ch18 ｜ FM Ch10
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-章末复习 FM Ch11 非参数检验
-· 章末复习题 End-of-chapter review p.277，限时 30 分钟
-· 本章要会：能判断何时该用非参数检验并正确查临界值
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 FM Ch11 非参数检验 §11.1、§11.2、§11.3、§11.4
+· 速览 §11.1 非参数检验概述、§11.2 单样本符号检验、§11.3 单样本 Wilcoxon 符号秩检验、§11.4 配对样本符号检验（p.250、p.251、p.254、p.260，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -1196,37 +1216,44 @@
         <is>
           <t>7月9日 周五 ◆暑假
 ────────────
+14:00-15:00 学术英语
+EAP 强化 07 EAP 真题套卷（听 + 说）限时
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：剑桥雅思真题一整套（Listening + Speaking）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：40 分钟听力 + 完整口语三部分录音
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-47 EAP 真题套卷（听 + 说）限时」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：记录听力正确数与口语停顿次数；听力错题同样归因分类
+· 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
+15:15-16:15 学术英语
+EAP 强化 08 学术词汇综合自测（AWL 全表）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Anki 里 AWL 全部牌组（关掉提示，纯默写）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：不看书，写出 AWL 全表里你能**主动用出**的词（目标 ≥120 个），不能主动用的标记出来
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-48 学术词汇综合自测（AWL 全表）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：≥120 个；标记出来的词全部入 Anki 并写出各自的搭配（哪个介词、哪个动词）
+· 本类（词汇类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>7月10日 周六 ◆暑假
+────────────
 14:00-15:00 进阶数学
-术语与格式 FM Ch12 概率母函数 §12.1、§12.2、§12.3、§12.4
-· 速览 §12.1 概率母函数、§12.2 用 pgf 求 E(X) 与 Var(X)、§12.3 独立随机变量之和、§12.4 三个及以上随机变量（p.280、p.287、p.292、p.298，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-15:15-16:15 进阶数学
-格式训练 FM Ch12 概率母函数（§12.1、§12.2）
-· Ex 12A 题 全部（约 25 分钟，p.282）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 12B 题 全部（约 25 分钟，p.289）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>7月10日 周六 ◆暑假
-────────────
-14:00-15:00 进阶数学
-章末复习 FM Ch12 概率母函数
-· 章末复习题 End-of-chapter review p.304，限时 30 分钟
-· 本章要会：能用 pgf 求均值、方差与独立和
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+格式训练 FM Ch11 非参数检验（§11.1、§11.2）
+· Ex 11A 题 全部（约 25 分钟，p.250）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11B 题 全部（约 25 分钟，p.253）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 20:00-21:00 进阶数学
-术语与格式 FM Ch19 双曲函数 §19.1、§19.2、§19.3、§19.4
-· 速览 §19.1 双曲函数的指数形式、§19.2 双曲恒等式、§19.3 反双曲函数、§19.4 反双曲函数的对数形式（p.432、p.438、p.440、p.442，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+格式训练 FM Ch11 非参数检验（§11.3、§11.4）
+· Ex 11C 题 全部（约 25 分钟，p.256）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11D 题 全部（约 25 分钟，p.262）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1234,17 +1261,14 @@
           <t>7月11日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：Phy Ch18 ｜ FM Ch19
+· 回顾：Phy Ch18 ｜ FM Ch11
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-格式训练 FM Ch19 双曲函数（§19.1、§19.2）
-· Ex 19A 题 全部（约 25 分钟，p.434）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 19B 题 全部（约 25 分钟，p.439）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 FM Ch11 非参数检验 §11.5、§11.6
+· 速览 §11.5 Wilcoxon 配对符号秩检验、§11.6 Wilcoxon 秩和检验（p.263、p.266，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>
@@ -1259,146 +1283,147 @@
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题
 15:15-16:15 进阶数学
+章末复习 FM Ch11 非参数检验
+· 章末复习题 End-of-chapter review p.277，限时 30 分钟
+· 本章要会：能判断何时该用非参数检验并正确查临界值
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>7月13日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch19 热物理 §19.1、§19.2、§19.3、§19.4
+· 速览 §19.1 物态变化、§19.2 能量变化、§19.3 内能、§19.4 温度的含义（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 物理
+格式训练 Phy Ch19 热物理（§19.1、§19.2）
+· 节末 Questions 题 全部（约 25 分钟，p.543）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.544）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>7月14日 周三 ◆暑假
+────────────
+14:00-15:00 进阶数学
+术语与格式 FM Ch12 概率母函数 §12.1、§12.2、§12.3、§12.4
+· 速览 §12.1 概率母函数、§12.2 用 pgf 求 E(X) 与 Var(X)、§12.3 独立随机变量之和、§12.4 三个及以上随机变量（p.280、p.287、p.292、p.298，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 进阶数学
+格式训练 FM Ch12 概率母函数（§12.1、§12.2）
+· Ex 12A 题 全部（约 25 分钟，p.282）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 12B 题 全部（约 25 分钟，p.289）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>7月15日 周四 ◆暑假
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch19 热物理（§19.3、§19.4）
+· 节末 Questions 题 全部（约 25 分钟，p.551）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.552）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+术语与格式 Phy Ch19 热物理 §19.5、§19.6
+· 速览 §19.5 温度计、§19.6 计算能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>7月16日 周五 ◆暑假
+────────────
+14:00-15:00 学术英语
+EAP 强化 09 个人陈述 + 面试问答演练
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP 40 定稿的 PS；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：用英文把 PS 讲成 2 分钟自我介绍录音 + 模拟面试 5 个问题（为什么这个专业 / 为什么这个学校 / 你的弱点 / 一个失败经历 / 未来规划）
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-49 个人陈述 + 面试问答演练」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：2 分钟能讲完；5 个问题都能答满 30 秒且不跑题
+· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
+15:15-16:15 学术英语
+EAP 强化 10 学年总结：错题 / 弱项清单与下阶段目标
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：全年错题本 + EAP 全部笔记 + 雅思模考曲线；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：写 10 条弱项清单，每条配一个下阶段动作（做什么、多久一次、怎么检查）
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-50 学年总结：错题 / 弱项清单与下阶段目标」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：10 条都具体可执行；每条都能回答「下周怎么验证它进步了」
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>7月17日 周六 ◆暑假
+────────────
+14:00-15:00 进阶数学
+章末复习 FM Ch12 概率母函数
+· 章末复习题 End-of-chapter review p.304，限时 30 分钟
+· 本章要会：能用 pgf 求均值、方差与独立和
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+20:00-21:00 进阶数学
+术语与格式 FM Ch19 双曲函数 §19.1、§19.2、§19.3、§19.4
+· 速览 §19.1 双曲函数的指数形式、§19.2 双曲恒等式、§19.3 反双曲函数、§19.4 反双曲函数的对数形式（p.432、p.438、p.440、p.442，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>7月18日 周日 ◆暑假
+────────────
+14:00-15:00 复习/测试
+· 回顾：Phy Ch19 ｜ FM Ch19
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+格式训练 FM Ch19 双曲函数（§19.1、§19.2）
+· Ex 19A 题 全部（约 25 分钟，p.434）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 19B 题 全部（约 25 分钟，p.439）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>7月19日 周一 ◆暑假
+────────────
+14:00-15:00 进阶数学
 章末复习 FM Ch19 双曲函数
 · 章末复习题 End-of-chapter review p.446，限时 30 分钟
 · 本章要会：能默写双曲函数的指数定义与恒等式、反双曲函数对数形式
 · 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
 · 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>7月13日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch19 热物理 §19.1、§19.2、§19.3、§19.4
-· 速览 §19.1 物态变化、§19.2 能量变化、§19.3 内能、§19.4 温度的含义（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-15:15-16:15 物理
-格式训练 Phy Ch19 热物理（§19.1、§19.2）
-· 节末 Questions 题 全部（约 25 分钟，p.543）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.544）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>7月14日 周三 ◆暑假
-────────────
-14:00-15:00 进阶数学
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 进阶数学
 术语与格式 FM Ch20 矩阵 2 §20.1、§20.2、§20.3、§20.4
 · 速览 §20.1 特征值与特征向量、§20.2 矩阵代数、§20.3 对角化、§20.4 方程组（p.448、p.451、p.461、p.465，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-15:15-16:15 进阶数学
-格式训练 FM Ch20 矩阵 2（§20.1、§20.2）
-· Ex 20A 题 全部（约 25 分钟，p.450）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 20B 题 全部（约 25 分钟，p.453）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>7月15日 周四 ◆暑假
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch19 热物理（§19.3、§19.4）
-· 节末 Questions 题 全部（约 25 分钟，p.551）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.552）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-15:15-16:15 物理
-术语与格式 Phy Ch19 热物理 §19.5、§19.6
-· 速览 §19.5 温度计、§19.6 计算能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>7月16日 周五 ◆暑假
-────────────
-14:00-15:00 进阶数学
-章末复习 FM Ch20 矩阵 2
-· 章末复习题 End-of-chapter review p.471，限时 30 分钟
-· 本章要会：能求特征值与特征向量、对角化并解方程组
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 进阶数学
-术语与格式 FM Ch21 微分（进阶） §21.1、§21.2、§21.3、§21.4
-· 速览 §21.1 隐函数、§21.2 参数方程、§21.3 双曲函数与反函数、§21.4 麦克劳林级数（p.473、p.478、p.481、p.488，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>7月17日 周六 ◆暑假
-────────────
-14:00-15:00 进阶数学
-格式训练 FM Ch21 微分（进阶）（§21.1、§21.2）
-· Ex 21A 题 全部（约 25 分钟，p.475）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 21B 题 全部（约 25 分钟，p.480）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-20:00-21:00 进阶数学
-章末复习 FM Ch21 微分（进阶）
-· 章末复习题 End-of-chapter review p.496，限时 30 分钟
-· 本章要会：能用隐函数/参数方程求导并写出 Maclaurin 展开
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>7月18日 周日 ◆暑假
-────────────
-14:00-15:00 复习/测试
-· 回顾：Phy Ch19 ｜ FM Ch21
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-术语与格式 FM Ch22 积分（进阶） §22.1、§22.2、§22.3、§22.4
-· 速览 §22.1 积分技巧、§22.2 递推公式、§22.3 弧长与表面积、§22.4 面积的极限（p.498、p.503、p.509、p.515，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>7月19日 周一 ◆暑假
-────────────
-14:00-15:00 进阶数学
-格式训练 FM Ch22 积分（进阶）（§22.1、§22.2）
-· Ex 22A 题 全部（约 25 分钟，p.500）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 22B 题 全部（约 25 分钟，p.505）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-15:15-16:15 进阶数学
-章末复习 FM Ch22 积分（进阶）
-· 章末复习题 End-of-chapter review p.523，限时 30 分钟
-· 本章要会：能选对积分技巧、用递推公式、求弧长与旋转面面积
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1424,18 +1449,20 @@
           <t>7月21日 周三 ◆暑假
 ────────────
 14:00-15:00 进阶数学
-术语与格式 FM Ch23 复数（进阶） §23.1、§23.2、§23.3、§23.4
-· 速览 §23.1 棣莫弗定理、§23.2 正弦与余弦的幂、§23.3 单位根、§23.4 复数求和（p.525、p.529、p.532、p.537，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+格式训练 FM Ch20 矩阵 2（§20.1、§20.2）
+· Ex 20A 题 全部（约 25 分钟，p.450）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 20B 题 全部（约 25 分钟，p.453）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 进阶数学
-格式训练 FM Ch23 复数（进阶）（§23.1、§23.2）
-· Ex 23A 题 全部（约 25 分钟，p.527）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 23B 题 全部（约 25 分钟，p.531）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+章末复习 FM Ch20 矩阵 2
+· 章末复习题 End-of-chapter review p.471，限时 30 分钟
+· 本章要会：能求特征值与特征向量、对角化并解方程组
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1465,153 +1492,168 @@
           <t>7月23日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
+术语与格式 FM Ch21 微分（进阶） §21.1、§21.2、§21.3、§21.4
+· 速览 §21.1 隐函数、§21.2 参数方程、§21.3 双曲函数与反函数、§21.4 麦克劳林级数（p.473、p.478、p.481、p.488，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 进阶数学
+格式训练 FM Ch21 微分（进阶）（§21.1、§21.2）
+· Ex 21A 题 全部（约 25 分钟，p.475）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 21B 题 全部（约 25 分钟，p.480）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>7月24日 周六 ◆暑假
+────────────
+14:00-15:00 进阶数学
+章末复习 FM Ch21 微分（进阶）
+· 章末复习题 End-of-chapter review p.496，限时 30 分钟
+· 本章要会：能用隐函数/参数方程求导并写出 Maclaurin 展开
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+20:00-21:00 进阶数学
+术语与格式 FM Ch22 积分（进阶） §22.1、§22.2、§22.3、§22.4
+· 速览 §22.1 积分技巧、§22.2 递推公式、§22.3 弧长与表面积、§22.4 面积的极限（p.498、p.503、p.509、p.515，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>7月25日 周日 ◆暑假
+────────────
+14:00-15:00 复习/测试
+★ 暑期测试：P2/3 Ch6-8｜物理 Ch13-16
+· 限时作答后逐题订正，记录失分点
+20:00-21:00 进阶数学
+格式训练 FM Ch22 积分（进阶）（§22.1、§22.2）
+· Ex 22A 题 全部（约 25 分钟，p.500）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 22B 题 全部（约 25 分钟，p.505）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>7月26日 周一 ◆暑假
+────────────
+14:00-15:00 进阶数学
+章末复习 FM Ch22 积分（进阶）
+· 章末复习题 End-of-chapter review p.523，限时 30 分钟
+· 本章要会：能选对积分技巧、用递推公式、求弧长与旋转面面积
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 进阶数学
+术语与格式 FM Ch23 复数（进阶） §23.1、§23.2、§23.3、§23.4
+· 速览 §23.1 棣莫弗定理、§23.2 正弦与余弦的幂、§23.3 单位根、§23.4 复数求和（p.525、p.529、p.532、p.537，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>7月27日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch20 理想气体 §20.5、§20.6、§20.7、§20.8
+· 速览 §20.5 温度变化、§20.6 理想气体方程、§20.7 气体建模：动力学模型、§20.8 温度与分子能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 物理
+格式训练 Phy Ch20 理想气体（§20.5、§20.6）
+· 节末 Questions 题 全部（约 25 分钟，p.577）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.580）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>7月28日 周三 ◆暑假
+────────────
+14:00-15:00 进阶数学
+格式训练 FM Ch23 复数（进阶）（§23.1、§23.2）
+· Ex 23A 题 全部（约 25 分钟，p.527）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 23B 题 全部（约 25 分钟，p.531）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 进阶数学
 章末复习 FM Ch23 复数（进阶）
 · 章末复习题 End-of-chapter review p.543，限时 30 分钟
 · 本章要会：能用 de Moivre 定理求幂、根与复数和
 · 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
 · 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>7月29日 周四 ◆暑假
+────────────
+14:00-15:00 物理
+章末复习 Phy Ch20 理想气体
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：理想气体状态方程与分子运动论
+· 过关自测：能默写 pV=nRT 与 pV=NkT；能解释压强与温度的微观意义；Chapter 20 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 进阶数学
+15:15-16:15 物理
+术语与格式 Phy Ch21 匀强电场 §21.1、§21.2、§21.3、§21.4
+· 速览 §21.1 吸引与排斥、§21.2 电场概念、§21.3 电场强度、§21.4 电荷受到的力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>7月30日 周五 ◆暑假
+────────────
+14:00-15:00 进阶数学
 术语与格式 FM Ch24 微分方程（进阶） §24.1、§24.2、§24.3、§24.4
 · 速览 §24.1 一阶微分方程、§24.2 二阶微分方程：齐次情形、§24.3 二阶微分方程：非齐次情形、§24.4 微分方程的代换法（p.545、p.550、p.557、p.565，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>7月24日 周六 ◆暑假
-────────────
-14:00-15:00 进阶数学
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+15:15-16:15 进阶数学
 格式训练 FM Ch24 微分方程（进阶）（§24.1、§24.2）
 · Ex 24A 题 全部（约 25 分钟，p.547）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 24B 题 全部（约 25 分钟，p.552）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-20:00-21:00 进阶数学
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>7月31日 周六 ◆暑假
+────────────
+14:00-15:00 进阶数学
 章末复习 FM Ch24 微分方程（进阶）
 · 章末复习题 End-of-chapter review p.575，限时 30 分钟
 · 本章要会：能解一阶与二阶（齐次/非齐次）微分方程
 · 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
 · 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>7月25日 周日 ◆暑假
-────────────
-14:00-15:00 复习/测试
-★ 暑期测试：P2/3 Ch6-8｜物理 Ch13-16
-· 限时作答后逐题订正，记录失分点
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 20:00-21:00 进阶数学
 真题精练 9231 FP1 2019 Paper 1
 · 进阶数学真题卷
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>7月26日 周一 ◆暑假
-────────────
-14:00-15:00 进阶数学
-真题精练 9231 FP2 2019 Paper 2
-· 进阶数学真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-15:15-16:15 进阶数学
-真题精练 9231 FS 2019 Paper 3
-· 进阶数学真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>7月27日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch20 理想气体 §20.5、§20.6、§20.7、§20.8
-· 速览 §20.5 温度变化、§20.6 理想气体方程、§20.7 气体建模：动力学模型、§20.8 温度与分子能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-15:15-16:15 物理
-格式训练 Phy Ch20 理想气体（§20.5、§20.6）
-· 节末 Questions 题 全部（约 25 分钟，p.577）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.580）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>7月28日 周三 ◆暑假
-────────────
-14:00-15:00 进阶数学
-真题精练 9231 FM 2019 Paper 4
-· 进阶数学真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-15:15-16:15 进阶数学
-真题精练 9231 FP1 2020 Paper 1
-· 进阶数学真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>7月29日 周四 ◆暑假
-────────────
-14:00-15:00 物理
-章末复习 Phy Ch20 理想气体
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：理想气体状态方程与分子运动论
-· 过关自测：能默写 pV=nRT 与 pV=NkT；能解释压强与温度的微观意义；Chapter 20 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 物理
-术语与格式 Phy Ch21 匀强电场 §21.1、§21.2、§21.3、§21.4
-· 速览 §21.1 吸引与排斥、§21.2 电场概念、§21.3 电场强度、§21.4 电荷受到的力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>7月30日 周五 ◆暑假
-────────────
-14:00-15:00 进阶数学
-真题精练 9231 FP2 2020 Paper 2
-· 进阶数学真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-15:15-16:15 进阶数学
-真题精练 9231 FS 2020 Paper 3
-· 进阶数学真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>7月31日 周六 ◆暑假
-────────────
-14:00-15:00 进阶数学
-真题精练 9231 FM 2020 Paper 4
-· 进阶数学真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-20:00-21:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
@@ -1688,12 +1730,14 @@
           <t>8月1日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：Phy Ch21
+· 回顾：Phy Ch21 ｜ FM Ch24
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
+真题精练 9231 FP2 2019 Paper 2
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1746,16 @@
         <is>
           <t>8月2日 周一 ◆暑假
 ────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
+14:00-15:00 进阶数学
+真题精练 9231 FS 2019 Paper 3
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 进阶数学
+真题精练 9231 FM 2019 Paper 4
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1735,12 +1783,16 @@
         <is>
           <t>8月4日 周三 ◆暑假
 ────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
+14:00-15:00 进阶数学
+真题精练 9231 FP1 2020 Paper 1
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 进阶数学
+真题精练 9231 FP2 2020 Paper 2
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1763,12 +1815,16 @@
         <is>
           <t>8月6日 周五 ◆暑假
 ────────────
-14:00-15:00 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
+14:00-15:00 进阶数学
+真题精练 9231 FS 2020 Paper 3
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 进阶数学
+真题精练 9231 FM 2020 Paper 4
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -2487,7 +2543,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch20 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch24</t>
+          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch20 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch22</t>
         </is>
       </c>
     </row>
@@ -2916,9 +2972,13 @@
           <t>11月6日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 07
-· 摘要写作：压缩与转述学术文本（paraphrase）
-· 词汇/术语入 Anki</t>
+EAP 06 学术词汇②：AWL Sublist 3-4
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Anki 牌组「英语词汇::AWL」的 Sublist 3-4；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：开 15–20 张新卡（20 分钟封顶）+ 用当天 10 个新词写 120 词学术段落
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-06 学术词汇②：AWL Sublist 3-4」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：10 个新词主动用出 ≥6 个；段落四项自检各指出 1 处不足
+· 本类（词汇类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -3017,9 +3077,13 @@
           <t>11月13日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 08
-· 引用规范：Harvard 格式入门与学术诚信
-· 词汇/术语入 Anki</t>
+EAP 07 摘要写作：压缩与转述（paraphrase）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP Foundation 写作区 Paraphrasing 页 + 一篇 300 词左右的学术文本；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：把 300 词压成 80 词摘要，**不许出现原文连续 5 个词**；另写 2 句纯 paraphrase 练习（换词性、换语序）
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-07 摘要写作：压缩与转述（paraphrase）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：逐句核对无连续 5 词重合；摘要包含原文全部主论点，且没有加入自己的观点
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -3126,12 +3190,13 @@
           <t>11月20日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 09
-· 学术听力①：康奈尔笔记法与讲座笔记符号
-· 词汇/术语入 Anki
-EAP 10
-· 学术写作①：说明文（explanatory essay）结构
-· 词汇/术语入 Anki</t>
+EAP 08 引用规范：Harvard 格式入门与学术诚信
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Purdue OWL（https://owl.purdue.edu/owl/research_and_citation/resources.html）+ EAP Foundation 的 Citation 页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：对 2 条真实来源（课本/论文/网页）各做出：1 条文内引用 + 1 条参考文献条目，逐字符核对标点
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-08 引用规范：Harvard 格式入门与学术诚信」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：与 OWL 样例逐字符一致（含斜体、逗号、句号位置）；存进 EAP-08 笔记，以后每次写作业直接复制这份样例
+· 本类（引用类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3227,9 +3292,13 @@
           <t>11月27日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 11
-· 学术词汇③：AWL Sublist 5-6
-· 词汇/术语入 Anki</t>
+EAP 09 学术听力①：康奈尔笔记法与讲座笔记符号
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP Foundation 听力区「讲座信号词 / 笔记符号」一节（https://www.eapfoundation.com/listening/lectures/；大陆镜像 http://i.youku.com/eapfoundation）——看完教程立刻关掉；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：关掉教程，直接听一段 5–8 分钟真讲座做康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）+ 2 分钟口头复述录音
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-09 学术听力①：康奈尔笔记法与讲座笔记符号」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：复述能连续讲满 2 分钟且停顿 &lt;5 次；笔记不看原文也能支撑复述
+· 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -3400,9 +3469,13 @@
           <t>12月4日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 12
-· 图表描述：数据、趋势与比较（Task 1）
-· 词汇/术语入 Anki</t>
+EAP 10 学术写作①：说明文（explanatory essay）结构
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP Foundation 写作区 Essay types → Explanatory——只看这一页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：先写 3 段提纲，再写 250 词说明文一篇
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-10 学术写作①：说明文（explanatory essay）结构」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：每段一个主题句；TR / CC / LR / GRA 四项各指出 1 处**具体**不足（「不够好」不算）
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -3502,9 +3575,13 @@
           <t>12月11日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 13
-· 学术听力②：TED-Ed / BBC 学术播客精听
-· 词汇/术语入 Anki</t>
+EAP 11 学术词汇③：AWL Sublist 5-6
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Anki 牌组「英语词汇::AWL」的 Sublist 5-6；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：开 15–20 张新卡 + 用当天 10 个新词写 120 词学术段落
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-11 学术词汇③：AWL Sublist 5-6」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：10 个新词主动用出 ≥6 个
+· 本类（词汇类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -3612,12 +3689,13 @@
           <t>12月18日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 14
-· 学术写作②：议论文与反驳段
-· 词汇/术语入 Anki
-EAP 15
-· 学术词汇④：AWL Sublist 7-10
-· 词汇/术语入 Anki</t>
+EAP 12 图表描述：数据、趋势与比较（Task 1）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：IELTS Liz 的 Task 1 band descriptor（https://ieltsliz.com/）+ 剑桥雅思真题里任一套 Task 1 图表；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：20 分钟写 150 词 Task 1（含 overview 句 + 3 个具体数据点）；写完对照范文标出 3 处差距
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-12 图表描述：数据、趋势与比较（Task 1）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：有独立 overview 句；数据引用与图表一致；3 处差距写到具体句子上
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -3716,13 +3794,21 @@
           <t>12月25日 周五 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 学术英语
-EAP 16
-· 学术讨论：seminar 发言、提问与回应
-· 词汇/术语入 Anki
+EAP 13 学术听力②：TED-Ed / BBC 学术播客精听
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：TED-Ed 一段（≤8 分钟），先开英文字幕看一遍，再关字幕听一遍；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：康奈尔笔记 + 2 分钟复述录音；把听不出的连读弱读标出来
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-13 学术听力②：TED-Ed / BBC 学术播客精听」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：复述停顿 &lt;5 次；标出的连读弱读 ≥5 处
+· 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
 15:15-16:15 学术英语
-EAP 17
-· 学术写作③：报告与实验报告结构
-· 词汇/术语入 Anki</t>
+EAP 14 学术写作②：议论文与反驳段
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Manchester Academic Phrasebank（https://www.phrasebank.manchester.ac.uk/）的 Comparing ideas / Referring to sources——只借结构，不整句背；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：250 词议论文一篇，必须包含一个反驳段
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-14 学术写作②：议论文与反驳段」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：反驳段有「让步 + 转折」两步（先承认对方在什么条件下成立，再指出它的边界）
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -3917,13 +4003,21 @@
           <t>1月1日 周五 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 学术英语
-EAP 18
-· 学术听力③：大学公开课精听（MIT OCW）
-· 词汇/术语入 Anki
+EAP 15 学术词汇④：AWL Sublist 7-10
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Anki 牌组「英语词汇::AWL」的 Sublist 7-10；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：开 15–20 张新卡 + 用当天 10 个新词写 120 词学术段落
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-15 学术词汇④：AWL Sublist 7-10」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：10 个新词主动用出 ≥6 个；AWL 全表累计主动词 ≥100
+· 本类（词汇类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
 15:15-16:15 学术英语
-EAP 19
-· 学术写作④：essay 自我修改与同伴互评
-· 词汇/术语入 Anki</t>
+EAP 16 学术讨论：seminar 发言、提问与回应
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自问自答材料：从本周课本里挑一个可争论的问题（如「实验误差应该归因于仪器还是方法」）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：3 分钟 seminar 发言录音 + 提 2 个问题 + 回应 2 次；把用到的学术用语列一份清单
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-16 学术讨论：seminar 发言、提问与回应」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：录音回放能听出 3 个该改的地方；发言里没有「I think it's very good」这类空话
+· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -4026,9 +4120,13 @@
           <t>1月8日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 20
-· 扩展论文：选题、文献检索与提纲
-· 词汇/术语入 Anki</t>
+EAP 17 学术写作③：报告与实验报告结构
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP Foundation 写作区 Reports——只看这一页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：写一份 300 词实验报告：目的 / 方法 / 结果 / 讨论 四节
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-17 学术写作③：报告与实验报告结构」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：四节齐全；结果与讨论严格分开（结果只写数据，解释放讨论）
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -4124,9 +4222,13 @@
           <t>1月15日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 21
-· 学术写作⑤：引言与结论的写法
-· 词汇/术语入 Anki</t>
+EAP 18 学术听力③：大学公开课精听（MIT OCW）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：MIT OCW 一节入门课（https://ocw.mit.edu/），一次只听 8–10 分钟；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：康奈尔笔记 + 2–3 分钟复述录音
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-18 学术听力③：大学公开课精听（MIT OCW）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：复述能说出讲座的三个要点；笔记里有 ≥3 个学科术语
+· 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -4233,9 +4335,13 @@
           <t>1月22日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 22
-· 数据与公式的英文表达（数理语境）
-· 词汇/术语入 Anki</t>
+EAP 19 学术写作④：essay 自我修改与同伴互评
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自己 EAP 10 或 EAP 14 写过的 essay；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：把旧作**重写一遍**（不是改标点）：对照 TR / CC / LR / GRA 四项，每项至少改 1 处结构（改段落顺序、换主题句、加过渡句、改句长节奏）
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-19 学术写作④：essay 自我修改与同伴互评」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：四项都能指出「改了什么、为什么改」，不许只说「读起来更顺了」
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -4359,13 +4465,21 @@
           <t>1月29日 周五 ◆寒假
 ────────────
 14:00-15:00 学术英语
-EAP 23
-· 学术演讲①：presentation 结构与开场
-· 词汇/术语入 Anki
+EAP 20 扩展论文：选题、文献检索与提纲
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Google Scholar + Phrasebank 的 Introduction 页（只用来学结构）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：写 1 张论文提纲：题目 + 3 个分论点 + 每个分论点 2 条可能来源（作者/年份/标题/链接）
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-20 扩展论文：选题、文献检索与提纲」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：3 个分论点互不重叠；来源信息完整到能再次找到
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
 15:15-16:15 学术英语
-EAP 24
-· 学术演讲②：幻灯片设计与视觉辅助
-· 词汇/术语入 Anki</t>
+EAP 21 学术写作⑤：引言与结论的写法
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Phrasebank 的 Introduction / Conclusions 两页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：给 EAP 20 的提纲写 150 词引言 + 100 词结论
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-21 学术写作⑤：引言与结论的写法」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：引言末句写明立场；结论不引入任何新论据
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -4548,9 +4662,13 @@
           <t>2月5日 周五 ◆寒假
 ────────────
 14:00-15:00 学术英语
-EAP 25
-· 数学与物理术语英汉对照复习（配 Anki）
-· 词汇/术语入 Anki</t>
+EAP 22 数据与公式的英文表达（数理语境）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自己的物理/数学课本里的英文段落（就用课本原文，一举两得）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：从课本抄 10 个含数据的英文句子，每个改写成三种说法（如 increase by 20% / a 20% increase / rises 20 per cent），再把术语入 Anki
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-22 数据与公式的英文表达（数理语境）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：10 句改写全部语法正确；入 Anki 的术语卡 ≥10 张
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -4632,9 +4750,13 @@
           <t>2月12日 周五 ◆寒假
 ────────────
 14:00-15:00 学术英语
-EAP 26
-· 学术写作⑥：因果链与逻辑连接词
-· 词汇/术语入 Anki</t>
+EAP 23 学术演讲①：presentation 结构与开场
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP Foundation 口语 / Presentation 区——只看结构那一页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：选题（如「为什么我要学 EEE」），写 1 页大纲（hook → 3 个点 → 收尾），录 2 分钟
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-23 学术演讲①：presentation 结构与开场」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：录音回放能听出 3 个该改的地方；开场没有「Hello everyone, today I will talk about」这种套话
+· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -4750,13 +4872,21 @@
           <t>2月19日 周五 ◆寒假
 ────────────
 14:00-15:00 学术英语
-EAP 27
-· 学术听力④：英音/美音/多口音训练
-· 词汇/术语入 Anki
+EAP 24 学术演讲②：幻灯片设计与视觉辅助
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自己 EAP 23 写的大纲；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：做 5 张幻灯片：每张 ≤6 个词 + 1 张图，然后照着讲一遍录音
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-24 学术演讲②：幻灯片设计与视觉辅助」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：每张幻灯片上没有一个完整句子（幻灯片不是提词器）
+· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
 15:15-16:15 学术英语
-EAP 28
-· 学术写作⑦：定义、分类与举例
-· 词汇/术语入 Anki</t>
+EAP 25 数学与物理术语英汉对照复习（配 Anki）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Anki 里的数理术语牌组 + 本书 EAP 文件夹；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：把本学期物理/数学的术语列成中英对照表（≥30 条），不认识的补进 Anki
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-25 数学与物理术语英汉对照复习（配 Anki）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：30 条里能不看笔记说出英文的 ≥25 条
+· 本类（词汇类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -4847,12 +4977,13 @@
           <t>2月26日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 29
-· 学术演讲③：presentation 演练与录像复盘
-· 词汇/术语入 Anki
-EAP 30
-· EAP 模拟①：限时 essay（40 分钟 / 400 词）
-· 词汇/术语入 Anki</t>
+EAP 26 学术写作⑥：因果链与逻辑连接词
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Phrasebank 的 Cause and effect / Signalling transition 两页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：写 150 词段落，要求用出 5 个**不同**的因果连接（because of / due to / consequently / hence / thereby 之类）
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-26 学术写作⑥：因果链与逻辑连接词」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：5 个连接用法都正确且不重复；没有把 because 当万能连接词用满全段
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -5021,9 +5152,13 @@
           <t>3月5日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 31
-· 学术阅读③：长篇文献速读与结构化笔记
-· 词汇/术语入 Anki</t>
+EAP 27 学术听力④：英音／美音／多口音训练
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：三段真实材料：BBC（英音）+ CNN 或 NPR（美音）+ 一段非英美口音（印度／澳洲，YouTube 或 BBC World Service）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：每段 3 分钟逐句听写，统计三段的错因分布（① 不认识 ② 连读弱读 ③ 拼写 ④ 走神）
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-27 学术听力④：英音／美音／多口音训练」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：三段的错因分类都写出来了；②类最多的那段找 1 个连读弱读专项练习
+· 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -5122,9 +5257,13 @@
           <t>3月12日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 32
-· 学术写作⑧：批判性写作
-· 词汇/术语入 Anki</t>
+EAP 28 学术写作⑦：定义、分类与举例
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Phrasebank 的 Defining terms / Giving examples 两页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：给「工程」或「算法」下一个学术定义（1 句）+ 按层级举 3 个例子
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-28 学术写作⑦：定义、分类与举例」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：定义句含限定条件、不含 very / a lot of；3 个例子分属不同层级（属 → 种 → 个体）
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -5230,9 +5369,13 @@
           <t>3月19日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 33
-· EAP 模拟②：听力 + 笔记 + 口头复述
-· 词汇/术语入 Anki</t>
+EAP 29 学术演讲③：presentation 演练与录像复盘
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自己 EAP 24 做的 5 张幻灯片；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：完整讲一遍（3 分钟）并录像；回放时记下 3 处要改的
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-29 学术演讲③：presentation 演练与录像复盘」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：回放能说出 3 个**具体**要改的地方（哪个词、哪个停顿、哪张幻灯片）
+· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -5329,12 +5472,13 @@
           <t>3月26日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 34
-· 学术写作⑨：中式英语错误与学术语域
-· 词汇/术语入 Anki
-EAP 35
-· EAP 模拟③：小组讨论与口头答辩
-· 词汇/术语入 Anki</t>
+EAP 30 EAP 模拟①：限时 essay（40 分钟 / 400 词）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：剑桥雅思 Task 2 题库里任选一题（不要用模拟题）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：40 分钟写 400 词，写完立刻用 TR / CC / LR / GRA 自评并各打一个分
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-30 EAP 模拟①：限时 essay（40 分钟 / 400 词）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：40 分钟内写满 400 词；四项各写 1 条改进，改完把第一段重写一遍
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -5505,9 +5649,13 @@
           <t>4月2日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 36
-· 学术写作⑩：EAP 真题 essay 题目精练
-· 词汇/术语入 Anki</t>
+EAP 31 学术阅读③：长篇文献速读与结构化笔记
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：一份 1500 词以上的学术长文（或剑桥雅思三篇连做）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：15 分钟读完，做结构化笔记（标题层级 + 每段一句话）+ 8 对同义替换
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-31 学术阅读③：长篇文献速读与结构化笔记」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：笔记的层级与原文结构一致；同义替换 ≥8 对
+· 本类（阅读类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -5610,9 +5758,13 @@
           <t>4月9日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 37
-· 综合复习：EAP 读听说写技能串联
-· 词汇/术语入 Anki</t>
+EAP 32 学术写作⑧：批判性写作
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Phrasebank 的 Being critical 页 + 一篇你有不同意见的短文；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：250 词，必须包含「某观点有道理但不完整 + 我的补充」
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-32 学术写作⑧：批判性写作」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：至少 1 处明确让步 + 1 处明确反驳；反驳有证据不是情绪
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -5712,9 +5864,13 @@
           <t>4月16日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 38
-· EAP 模拟④：读写综合限时任务
-· 词汇/术语入 Anki</t>
+EAP 33 EAP 模拟②：听力 + 笔记 + 口头复述
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：一段 8 分钟真实讲座（MIT OCW 或 EAP Foundation 材料库）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：康奈尔笔记 + 3 分钟复述录音 + 3 个学科术语入 Anki
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-33 EAP 模拟②：听力 + 笔记 + 口头复述」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：复述停顿 &lt;5 次；笔记能不看原文独立支撑复述
+· 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -5815,12 +5971,13 @@
           <t>4月23日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 39
-· 个人陈述①：素材梳理与初稿
-· 词汇/术语入 Anki
-EAP 40
-· 个人陈述②：修改、润色与定稿
-· 词汇/术语入 Anki</t>
+EAP 34 学术写作⑨：中式英语错误与学术语域
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自己写过的 2 篇旧作（EAP 30 和另一篇都行）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：逐句找错，覆盖六类：冠词、主谓一致、时态、可数/不可数（information / research / evidence / advice）、run-on sentence、口语词
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-34 学术写作⑨：中式英语错误与学术语域」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：错误清单 ≥10 条，每条写「错在哪 + 改成什么」
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -5921,9 +6078,13 @@
           <t>4月30日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 强化 01
-· 限时 essay（40 分钟 / 450 词）并自评
-· 限时完成后复盘</t>
+EAP 35 EAP 模拟③：小组讨论与口头答辩
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自设辩题（如「AI 会不会取代工程师」）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：3 分钟陈述 + 模拟提问 2 个 + 逐个回应，全程录音
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-35 EAP 模拟③：小组讨论与口头答辩」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：回应里有具体理由，不出现「I think it's very good」这类空话
+· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F6" s="3" t="n"/>
@@ -6111,9 +6272,13 @@
           <t>5月7日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 强化 02
-· 听力讲座 + 康奈尔笔记 + 口头复述
-· 限时完成后复盘</t>
+EAP 36 学术写作⑩：EAP 真题 essay 题目精练
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP 真题 essay 题（若还没拿到真题，用雅思 Task 2 学术类替代）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：40 分钟写 400 词 + 四项自评 + 把第一段重写一遍
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-36 学术写作⑩：EAP 真题 essay 题目精练」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：重写后的第一段比初稿立场更明确（立场句位置提前）
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -6121,9 +6286,13 @@
           <t>5月8日 周六
 ────────────
 21:00-22:15 学术英语
-EAP 强化 03
-· 学术阅读长文速读 + 摘要写作
-· 限时完成后复盘</t>
+EAP 37 综合复习：EAP 读听说写技能串联
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：本学期全部 EAP 专题笔记（EAP-01 到 EAP-36）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：用英文写 150 词「我这学期学会了哪些学术技能」，并列出 3 个仍然弱的点
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-37 综合复习：EAP 读听说写技能串联」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：3 个弱点都对应到具体节次（如「EAP 12 图表描述还不熟」），不许写「写作还要提高」
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -6201,12 +6370,13 @@
           <t>5月14日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 强化 04
-· seminar 讨论录音复盘（流利度/学术语域）
-· 限时完成后复盘
-EAP 强化 05
-· presentation 限时演练与同伴反馈
-· 限时完成后复盘</t>
+EAP 38 EAP 模拟④：读写综合限时任务
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：一篇 800 词学术文本（雅思阅读 Passage 3 或论文摘要页）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：限时 60 分钟：20 分钟读 + 写 200 词摘要 + 150 词评论
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-38 EAP 模拟④：读写综合限时任务」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：摘要无原文连续 5 词；评论有自己的明确立场
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -6309,9 +6479,13 @@
           <t>5月21日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 强化 06
-· EAP 真题套卷（读+写）限时
-· 限时完成后复盘</t>
+EAP 39 个人陈述①：素材梳理与初稿
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自己的简历 / 项目清单 / 获奖记录（没有就现列）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：列出 6 个可写素材（学术、竞赛、社团、实习、志愿者、一次挫折），每个写 3 行：做了什么 / 遇到什么 / 学到什么
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-39 个人陈述①：素材梳理与初稿」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：6 个素材各能用一句话说清「我做了什么、学到什么」；没有一条是「参加了 XX 活动」这种空壳
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -6407,9 +6581,13 @@
           <t>5月28日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 强化 07
-· EAP 真题套卷（听+说）限时
-· 限时完成后复盘</t>
+EAP 40 个人陈述②：修改、润色与定稿
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP 39 的 6 个素材；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：写 500 词 PS 初稿 → 按「每段一个主题句」改一遍 → 定稿
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-40 个人陈述②：修改、润色与定稿」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：PS 里没有一句空话；每段都能被追问「证据是什么」而不心虚
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -6576,9 +6754,13 @@
           <t>6月4日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 强化 08
-· 学术词汇综合自测（AWL 全表）
-· 限时完成后复盘</t>
+EAP 强化 01 限时 essay（40 分钟 / 450 词）并自评
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：剑桥雅思 Task 2 题库（换一道没写过的）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：40 分钟写 450 词 + TR / CC / LR / GRA 四项自评打分
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-41 限时 essay（40 分钟 / 450 词）并自评」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：按时写完 450 词；四项各 1 条改进，改在哪要具体到句子
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -6678,12 +6860,13 @@
           <t>6月11日 周五
 ────────────
 21:00-22:15 学术英语
-EAP 强化 09
-· 个人陈述 + 面试问答演练
-· 限时完成后复盘
-EAP 强化 10
-· 学年总结：错题/弱项清单与下阶段目标
-· 限时完成后复盘</t>
+EAP 强化 02 听力讲座 + 康奈尔笔记 + 口头复述
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：一段 8 分钟讲座（与 EAP 33 不同的材料）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：康奈尔笔记 + 3 分钟复述录音
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-42 听力讲座 + 康奈尔笔记 + 口头复述」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：复述停顿 &lt;5 次；能说出讲座的论证走向（不只是罗列细节）
+· 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -6782,30 +6965,30 @@
         <is>
           <t>6月18日 周五
 ────────────
-21:00-22:15 进阶数学
+21:00-22:15 学术英语
+EAP 强化 03 学术阅读长文速读 + 摘要写作
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：一份 1500 词以上学术长文；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：15 分钟速读笔记 + 200 词摘要
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-43 学术阅读长文速读 + 摘要写作」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：摘要无原文连续 5 词；速读笔记能在不翻原文的情况下复述全文骨架
+· 本类（阅读类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>6月19日 周六
+────────────
+14:00-15:00 进阶数学
 术语与格式 FM Ch9 推断统计 §9.1、§9.2、§9.3、§9.4
 · 速览 §9.1 t 分布、§9.2 两均值之差的假设检验、§9.3 配对 t 检验、§9.4 小样本均值的置信区间（p.190、p.197、p.203、p.207，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>6月19日 周六
-────────────
-14:00-15:00 进阶数学
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+20:00-21:00 进阶数学
 格式训练 FM Ch9 推断统计（§9.1、§9.2）
 · Ex 9A 题 全部（约 25 分钟，p.192）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 9B 题 全部（约 25 分钟，p.199）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-20:00-21:00 进阶数学
-格式训练 FM Ch9 推断统计（§9.3、§9.4）
-· Ex 9C 题 全部（约 25 分钟，p.205）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9D 题 全部（约 25 分钟，p.209）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -6820,10 +7003,13 @@
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
-术语与格式 FM Ch9 推断统计 §9.5
-· 速览 §9.5 均值之差的置信区间（p.210，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+格式训练 FM Ch9 推断统计（§9.3、§9.4）
+· Ex 9C 题 全部（约 25 分钟，p.205）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9D 题 全部（约 25 分钟，p.209）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
     </row>
@@ -6890,7 +7076,26 @@
         <is>
           <t>6月25日 周五
 ────────────
-21:00-22:15 进阶数学
+21:00-22:15 学术英语
+EAP 强化 04 seminar 讨论录音复盘（流利度 / 学术语域）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自己 EAP 35 的讨论录音；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：重听旧录音，列出 5 条流利度 / 语域问题，然后针对同一话题重讲一遍
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-44 seminar 讨论录音复盘（流利度 / 学术语域）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：5 条问题都具体；第二遍停顿次数比第一遍少
+· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>6月26日 周六
+────────────
+14:00-15:00 进阶数学
+术语与格式 FM Ch9 推断统计 §9.5
+· 速览 §9.5 均值之差的置信区间（p.210，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+20:00-21:00 进阶数学
 章末复习 FM Ch9 推断统计
 · 章末复习题 End-of-chapter review p.219，限时 30 分钟
 · 本章要会：能用 t 分布做单/双样本假设检验与置信区间
@@ -6899,25 +7104,6 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>6月26日 周六
-────────────
-14:00-15:00 进阶数学
-术语与格式 FM Ch10 卡方检验 §10.1、§10.2、§10.3、§10.4
-· 速览 §10.1 建立假设、§10.2 离散分布的拟合优度、§10.3 连续分布的拟合优度、§10.4 列联表检验相关性（p.221、p.227、p.231、p.237，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-20:00-21:00 进阶数学
-格式训练 FM Ch10 卡方检验（§10.1、§10.2）
-· Ex 10A 题 全部（约 25 分钟，p.223）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 10B 题 全部（约 25 分钟，p.229）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>6月27日 周日
@@ -6926,12 +7112,10 @@
 ★ 学年末 AS 全科模拟（真题限时）
 · 限时作答后逐题订正，记录失分点
 20:00-21:00 进阶数学
-章末复习 FM Ch10 卡方检验
-· 章末复习题 End-of-chapter review p.248，限时 30 分钟
-· 本章要会：能做离散/连续拟合优度检验与列联表关联检验
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 FM Ch10 卡方检验 §10.1、§10.2、§10.3、§10.4
+· 速览 §10.1 建立假设、§10.2 离散分布的拟合优度、§10.3 连续分布的拟合优度、§10.4 列联表检验相关性（p.221、p.227、p.231、p.237，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
         </is>
       </c>
     </row>

--- a/StudyCompanionAndroid/assets/Schedule.xlsx
+++ b/StudyCompanionAndroid/assets/Schedule.xlsx
@@ -646,8 +646,21 @@
 21:00-22:15 物理
 术语与格式 Phy Ch1 运动学 §1.1、§1.2、§1.3、§1.4
 · 速览 §1.1 速率、§1.2 距离与位移、标量与矢量、§1.3 速率与速度、§1.4 位移-时间图像（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. scalar = 标量
+· 2. vector = 矢量
+· 3. distance = 路程
+· 4. displacement = 位移
+· 5. speed = 速率
+· 6. velocity = 速度
+· 7. average speed = 平均速率
+· 8. magnitude = 大小
+· 9. resultant = 合矢量
+· 10. relative velocity = 相对速度
+· 11. component = 分量
+· 12. parallelogram rule = 平行四边形法则
+· 全部抄完后回看一遍：[[06_物理#Ch1 Kinematics 运动学]]（本章共 12 条）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -689,8 +702,14 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch1 多项式方程的根 §1.1、§1.2、§1.3、§1.4
 · 速览 §1.1 二次方程、§1.2 三次方程、§1.3 四次方程、§1.4 代换法（p.2、p.5、p.8、p.10，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. roots of a polynomial equation = 多项式方程的根
+· 2. relations between roots and coefficients = 韦达定理 / 根与系数关系
+· 3. symmetric function = 对称函数
+· 4. substitution = 代换
+· 5. reciprocal of the roots = 根的倒数
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch1 Roots of polynomial equations 多项式方程的根（9231 §1.1，Paper 1；只在 FM 考）]]（本章共 5 条）</t>
         </is>
       </c>
     </row>
@@ -702,8 +721,23 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch1 二次方程 §1.1、§1.2、§1.3、§1.4
 · 速览 §1.1 因式分解法解二次方程、§1.2 配方法、§1.3 求根公式、§1.4 联立方程（一个线性一个二次）（p.3、p.6、p.10、p.11，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. completing the square = 配方法
+· 2. discriminant = 判别式
+· 3. quadratic formula = 求根公式
+· 4. parabola = 抛物线
+· 5. vertex = 顶点
+· 6. line of symmetry / axis of symmetry = 对称轴
+· 7. distinct real roots = 两个不同实根
+· 8. equal real roots / repeated root = 相等实根 / 重根
+· 9. no real roots = 无实根
+· 10. tangent = 切线
+· 11. point of intersection = 交点
+· 12. stationary point / turning point = 驻点 / 极值点
+· 13. critical values = 临界值
+· 14. surd form = 根式形式
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch1 Quadratics 二次方程]]（本章共 14 条）</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -769,8 +803,23 @@
 14:00-15:00 应用数学
 术语与格式 M1 Ch1 速度与加速度 §1.1、§1.2、§1.3、§1.4
 · 速览 §1.1 位移与速度、§1.2 加速度、§1.3 匀加速运动方程、§1.4 位移-时间图像与多阶段问题（p.2、p.9、p.11、p.15，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. displacement = 位移
+· 2. distance = 路程
+· 3. velocity / speed = 速度 / 速率
+· 4. acceleration = 加速度
+· 5. deceleration / retardation = 减速度
+· 6. uniform (constant) acceleration = 匀加速
+· 7. starts from rest = 从静止开始
+· 8. instantaneous / instantaneously at rest = 瞬时静止
+· 9. displacement–time graph = 位移—时间图
+· 10. velocity–time graph = 速度—时间图
+· 11. gradient = 斜率
+· 12. intercept = 截距
+· 13. to 3 significant figures = 保留三位有效数字
+· 14. multi-stage problem = 多阶段运动
+· 全部抄完后回看一遍：[[03_力学 M1#Ch1 Velocity and acceleration 速度与加速度]]（本章共 14 条）
 20:00-21:00 应用数学
 格式训练 M1 Ch1 速度与加速度（§1.1、§1.2）
 · Ex 1A 题 全部（约 25 分钟，p.4）
@@ -822,8 +871,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch1 运动学 §1.5、§1.6、§1.7、§1.8
 · 速览 §1.5 位移的合成、§1.6 速度的合成、§1.7 矢量的减法、§1.8 其他标量与矢量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch1 Kinematics 运动学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 格式训练 Phy Ch1 运动学（§1.5、§1.6）
 · 节末 Questions 题 全部（约 25 分钟，p.28）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -839,8 +888,8 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch1 二次方程 §1.5、§1.6、§1.7、§1.8
 · 速览 §1.5 更复杂的二次方程、§1.6 二次函数的最大值与最小值、§1.7 二次不等式、§1.8 二次方程根的个数（判别式）（p.15、p.17、p.21、p.24，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch1 Quadratics 二次方程]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 格式训练 P1 Ch1 二次方程（§1.5、§1.6）
 · Ex 1E 题 1–5（约 18 分钟，p.16）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -891,8 +940,8 @@
 20:00-21:00 应用数学
 术语与格式 M1 Ch1 速度与加速度 §1.5、§1.6
 · 速览 §1.5 速度-时间图像与多阶段问题、§1.6 不连续图像（p.22、p.27，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[03_力学 M1#Ch1 Velocity and acceleration 速度与加速度]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -934,8 +983,21 @@
 21:00-22:15 物理
 术语与格式 Phy Ch2 加速运动 §2.1、§2.2、§2.3、§2.4
 · 速览 §2.1 加速度的含义、§2.2 计算加速度、§2.3 加速度的单位、§2.4 推导加速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. acceleration = 加速度
+· 2. uniform acceleration = 匀变速
+· 3. deceleration = 减速
+· 4. velocity–time graph = 速度-时间图像
+· 5. equations of motion = 运动方程
+· 6. free fall = 自由落体
+· 7. acceleration of free fall = 重力加速度
+· 8. projectile = 抛体
+· 9. trajectory = 轨迹
+· 10. light gate = 光电门
+· 11. time of flight = 飞行时间
+· 12. horizontal component = 水平分量
+· 全部抄完后回看一遍：[[06_物理#Ch2 Accelerated motion 加速运动]]（本章共 12 条）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -945,8 +1007,8 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch1 二次方程 §1.9
 · 速览 §1.9 直线与二次曲线的交点（p.27，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch1 Quadratics 二次方程]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -991,8 +1053,24 @@
 20:00-21:00 应用数学
 术语与格式 M1 Ch2 一维力与运动 §2.1、§2.2、§2.3、§2.4
 · 速览 §2.1 牛顿第一定律及力与加速度的关系、§2.2 力的合成、§2.3 重力与重力加速度、§2.4 接触力与竖直方向运动（p.36、p.39、p.42、p.47，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 15 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. Newton's first law = 牛顿第一定律
+· 2. Newton's second law = 牛顿第二定律
+· 3. resultant force = 合力
+· 4. mass / weight = 质量 / 重力
+· 5. driving force = 牵引力
+· 6. resistance (to motion) = 阻力
+· 7. thrust = 推力
+· 8. normal contact force / reaction = 法向接触力/支持力
+· 9. upthrust = 浮力
+· 10. force diagram = 受力图
+· 11. at rest / in equilibrium = 静止 / 平衡
+· 12. constant speed = 匀速
+· 13. apparent weight = 视重
+· 14. smooth surface = 光滑表面
+· 15. centre of mass = 质心
+· 全部抄完后回看一遍：[[03_力学 M1#Ch2 Force and motion in one dimension 一维力与运动]]（本章共 15 条）</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
@@ -1076,8 +1154,8 @@
 15:15-16:15 物理
 术语与格式 Phy Ch18 振动 §18.5、§18.6、§18.7、§18.8
 · 速览 §18.5 简谐运动的图像表示、§18.6 频率与角频率、§18.7 简谐运动方程、§18.8 简谐运动中的能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch18 Oscillations 振动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -1134,8 +1212,16 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch11 非参数检验 §11.1、§11.2、§11.3、§11.4
 · 速览 §11.1 非参数检验概述、§11.2 单样本符号检验、§11.3 单样本 Wilcoxon 符号秩检验、§11.4 配对样本符号检验（p.250、p.251、p.254、p.260，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. non-parametric test = 非参数检验
+· 2. sign test = 符号检验
+· 3. Wilcoxon signed-rank test = Wilcoxon 符号秩检验
+· 4. Wilcoxon rank-sum test = Wilcoxon 秩和检验
+· 5. median = 中位数
+· 6. tied ranks = 并列秩
+· 7. normal approximation = 正态近似
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch11 Non-parametric tests 非参数检验（9231 §4.4，Paper 4；只在 FM 考）]]（本章共 7 条）</t>
         </is>
       </c>
     </row>
@@ -1201,8 +1287,8 @@
 14:00-15:00 物理
 术语与格式 Phy Ch18 振动 §18.9、§18.10
 · 速览 §18.9 阻尼振动、§18.10 共振（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch18 Oscillations 振动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 15:15-16:15 物理
 章末复习 Phy Ch18 振动
 · 章末复习题 End-of-chapter review，限时 30 分钟
@@ -1267,8 +1353,8 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch11 非参数检验 §11.5、§11.6
 · 速览 §11.5 Wilcoxon 配对符号秩检验、§11.6 Wilcoxon 秩和检验（p.263、p.266，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 7 条）：[[05_进阶数学 FM#Ch11 Non-parametric tests 非参数检验（9231 §4.4，Paper 4；只在 FM 考）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
     </row>
@@ -1298,8 +1384,23 @@
 14:00-15:00 物理
 术语与格式 Phy Ch19 热物理 §19.1、§19.2、§19.3、§19.4
 · 速览 §19.1 物态变化、§19.2 能量变化、§19.3 内能、§19.4 温度的含义（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. internal energy = 内能
+· 2. temperature = 温度
+· 3. thermal equilibrium = 热平衡
+· 4. absolute zero = 绝对零度
+· 5. Kelvin scale = 开尔文温标
+· 6. specific heat capacity = 比热容
+· 7. specific latent heat = 比潜热
+· 8. latent heat of fusion = 熔化潜热
+· 9. latent heat of vaporisation = 汽化潜热
+· 10. sublimation = 升华
+· 11. evaporation = 蒸发
+· 12. thermometer = 温度计
+· 13. thermocouple = 热电偶
+· 14. work done by a gas = 气体做功
+· 全部抄完后回看一遍：[[06_物理#Ch19 Thermal physics 热物理]]（本章共 14 条）
 15:15-16:15 物理
 格式训练 Phy Ch19 热物理（§19.1、§19.2）
 · 节末 Questions 题 全部（约 25 分钟，p.543）
@@ -1317,8 +1418,14 @@
 14:00-15:00 进阶数学
 术语与格式 FM Ch12 概率母函数 §12.1、§12.2、§12.3、§12.4
 · 速览 §12.1 概率母函数、§12.2 用 pgf 求 E(X) 与 Var(X)、§12.3 独立随机变量之和、§12.4 三个及以上随机变量（p.280、p.287、p.292、p.298，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. probability generating function (PGF) = 概率母函数
+· 2. discrete uniform distribution = 离散均匀分布
+· 3. geometric distribution = 几何分布
+· 4. Poisson distribution = 泊松分布
+· 5. independent random variables = 独立随机变量
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch12 Probability generating functions 概率母函数（9231 §4.5，Paper 4；只在 FM 考）]]（本章共 5 条）
 15:15-16:15 进阶数学
 格式训练 FM Ch12 概率母函数（§12.1、§12.2）
 · Ex 12A 题 全部（约 25 分钟，p.282）
@@ -1344,8 +1451,8 @@
 15:15-16:15 物理
 术语与格式 Phy Ch19 热物理 §19.5、§19.6
 · 速览 §19.5 温度计、§19.6 计算能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch19 Thermal physics 热物理]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1384,8 +1491,14 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch19 双曲函数 §19.1、§19.2、§19.3、§19.4
 · 速览 §19.1 双曲函数的指数形式、§19.2 双曲恒等式、§19.3 反双曲函数、§19.4 反双曲函数的对数形式（p.432、p.438、p.440、p.442，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. hyperbolic functions = 双曲函数
+· 2. inverse hyperbolic functions = 反双曲函数
+· 3. logarithmic form = 对数形式
+· 4. identity = 恒等式
+· 5. even / odd function = 偶函数 / 奇函数
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch19 Hyperbolic functions 双曲函数（9231 §2.1，Paper 2；只在 FM 考）]]（本章共 5 条）</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1422,8 +1535,16 @@
 15:15-16:15 进阶数学
 术语与格式 FM Ch20 矩阵 2 §20.1、§20.2、§20.3、§20.4
 · 速览 §20.1 特征值与特征向量、§20.2 矩阵代数、§20.3 对角化、§20.4 方程组（p.448、p.451、p.461、p.465，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. characteristic equation = 特征方程
+· 2. eigenvalue = 特征值
+· 3. eigenvector = 特征向量
+· 4. diagonalisation = 对角化
+· 5. Cayley–Hamilton theorem = 凯莱–哈密顿定理
+· 6. consistent / inconsistent = 相容的 / 不相容的
+· 7. singularity = 奇异性
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch20 Matrices 2 矩阵 2（9231 §2.2，Paper 2；只在 FM 考）]]（本章共 7 条）</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1440,8 +1561,23 @@
 15:15-16:15 物理
 术语与格式 Phy Ch20 理想气体 §20.1、§20.2、§20.3、§20.4
 · 速览 §20.1 气体的粒子模型、§20.2 解释压强、§20.3 测量气体、§20.4 玻意耳定律（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. ideal gas = 理想气体
+· 2. kinetic theory = 分子动理论
+· 3. mole = 摩尔
+· 4. Avogadro constant = 阿伏伽德罗常数
+· 5. molar gas constant = 摩尔气体常量
+· 6. Boltzmann constant = 玻尔兹曼常量
+· 7. equation of state = 状态方程
+· 8. Boyle's law = 玻意耳定律
+· 9. pressure law = 压强定律
+· 10. Charles's law = 查理定律
+· 11. root-mean-square speed = 均方根速率
+· 12. mean translational kinetic energy = 平均平动动能
+· 13. number density = 数密度
+· 14. elastic collision = 弹性碰撞
+· 全部抄完后回看一遍：[[06_物理#Ch20 Ideal gases 理想气体]]（本章共 14 条）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1494,8 +1630,13 @@
 14:00-15:00 进阶数学
 术语与格式 FM Ch21 微分（进阶） §21.1、§21.2、§21.3、§21.4
 · 速览 §21.1 隐函数、§21.2 参数方程、§21.3 双曲函数与反函数、§21.4 麦克劳林级数（p.473、p.478、p.481、p.488，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 4 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. implicit differentiation = 隐函数求导
+· 2. parametric differentiation = 参数方程求导
+· 3. Maclaurin's series = 麦克劳林级数
+· 4. second derivative = 二阶导数
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch21 Differentiation 微分（进阶）（9231 §2.3，Paper 2；只在 FM 考）]]（本章共 4 条）
 15:15-16:15 进阶数学
 格式训练 FM Ch21 微分（进阶）（§21.1、§21.2）
 · Ex 21A 题 全部（约 25 分钟，p.475）
@@ -1520,8 +1661,15 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch22 积分（进阶） §22.1、§22.2、§22.3、§22.4
 · 速览 §22.1 积分技巧、§22.2 递推公式、§22.3 弧长与表面积、§22.4 面积的极限（p.498、p.503、p.509、p.515，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. reduction formula = 递推公式
+· 2. completing the square = 配方
+· 3. arc length = 弧长
+· 4. surface area of revolution = 旋转曲面面积
+· 5. integration by parts = 分部积分
+· 6. substitution = 换元
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch22 Integration 积分（进阶）（9231 §2.4，Paper 2；只在 FM 考）]]（本章共 6 条）</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1557,8 +1705,16 @@
 15:15-16:15 进阶数学
 术语与格式 FM Ch23 复数（进阶） §23.1、§23.2、§23.3、§23.4
 · 速览 §23.1 棣莫弗定理、§23.2 正弦与余弦的幂、§23.3 单位根、§23.4 复数求和（p.525、p.529、p.532、p.537，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. de Moivre's theorem = 棣莫弗定理
+· 2. modulus–argument form = 模–辐角形式
+· 3. argument (principal value) = 辐角（主值）
+· 4. $n$th roots of unity = $n$ 次单位根
+· 5. conjugate = 共轭
+· 6. multiple angle = 多倍角
+· 7. $\mathrm{C}+iS$ method = $C+iS$ 求和法
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch23 Complex numbers 复数（进阶）（9231 §2.5，Paper 2；只在 FM 考）]]（本章共 7 条）</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1568,8 +1724,8 @@
 14:00-15:00 物理
 术语与格式 Phy Ch20 理想气体 §20.5、§20.6、§20.7、§20.8
 · 速览 §20.5 温度变化、§20.6 理想气体方程、§20.7 气体建模：动力学模型、§20.8 温度与分子能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch20 Ideal gases 理想气体]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 15:15-16:15 物理
 格式训练 Phy Ch20 理想气体（§20.5、§20.6）
 · 节末 Questions 题 全部（约 25 分钟，p.577）
@@ -1615,8 +1771,23 @@
 15:15-16:15 物理
 术语与格式 Phy Ch21 匀强电场 §21.1、§21.2、§21.3、§21.4
 · 速览 §21.1 吸引与排斥、§21.2 电场概念、§21.3 电场强度、§21.4 电荷受到的力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. electric field = 电场
+· 2. electric field line = 电场线
+· 3. electric field strength = 电场强度
+· 4. uniform field = 匀强电场
+· 5. test charge = 试探电荷
+· 6. force on a charge = 电荷受力
+· 7. potential difference = 电势差
+· 8. N C⁻¹ = 牛每库仑
+· 9. V m⁻¹ = 伏每米
+· 10. parabolic path = 抛物线轨迹
+· 11. Coulomb's law = 库仑定律
+· 12. permittivity of free space = 真空介电常数
+· 13. electric potential = 电势
+· 14. electric potential energy = 电势能
+· 全部抄完后回看一遍：[[06_物理#Ch21 Uniform electric fields 匀强电场]]（本章共 14 条）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1626,8 +1797,15 @@
 14:00-15:00 进阶数学
 术语与格式 FM Ch24 微分方程（进阶） §24.1、§24.2、§24.3、§24.4
 · 速览 §24.1 一阶微分方程、§24.2 二阶微分方程：齐次情形、§24.3 二阶微分方程：非齐次情形、§24.4 微分方程的代换法（p.545、p.550、p.557、p.565，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. integrating factor = 积分因子
+· 2. complementary function (CF) = 余函数 / 互补函数
+· 3. particular integral (PI) = 特解 / 特积分
+· 4. auxiliary equation = 辅助方程
+· 5. general solution / particular solution = 通解 / 特解
+· 6. initial condition = 初始条件
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch24 Differential equations 微分方程（进阶）（9231 §2.6，Paper 2；只在 FM 考）]]（本章共 6 条）
 15:15-16:15 进阶数学
 格式训练 FM Ch24 微分方程（进阶）（§24.1、§24.2）
 · Ex 24A 题 全部（约 25 分钟，p.547）
@@ -2900,8 +3078,14 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch2 有理函数 §2.1、§2.2、§2.3、§2.4
 · 速览 §2.1 竖直渐近线、§2.2 斜渐近线、§2.3 不等式、§2.4 曲线之间的关系（p.17、p.24、p.29、p.34，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. rational function = 有理函数
+· 2. vertical asymptote = 竖直渐近线
+· 3. oblique (slant) asymptote = 斜渐近线
+· 4. set of values of a function = 函数的值域
+· 5. intersection with the axes = 与坐标轴的交点
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch2 Rational functions 有理函数（9231 §1.2，Paper 1；含 9709 未深入的部分）]]（本章共 5 条）</t>
         </is>
       </c>
     </row>
@@ -2932,8 +3116,8 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 术语与格式 Phy Ch2 加速运动 §2.5、§2.6、§2.7、§2.8
 · 速览 §2.5 推导位移、§2.6 测量速度与加速度、§2.7 实验室中测定速度与加速度、§2.8 运动方程（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch2 Accelerated motion 加速运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -2943,8 +3127,23 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch2 函数 §2.1、§2.2、§2.3、§2.4
 · 速览 §2.1 函数的定义、§2.2 复合函数、§2.3 反函数、§2.4 函数与其反函数的图像（p.34、p.39、p.43、p.48，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. one-one function = 一对一函数（单射）
+· 2. many-one function = 多对一函数
+· 3. domain = 定义域
+· 4. range (codomain / image set) = 值域（陪域／像集合）
+· 5. mapping = 映射
+· 6. composite function = 复合函数
+· 7. inverse function = 反函数
+· 8. self-inverse function = 自反函数
+· 9. translation = 平移
+· 10. reflection = 反射（翻折）
+· 11. stretch = 拉伸
+· 12. stretch factor = 伸缩因子
+· 13. invariant = 不变的（固定线）
+· 14. order of operations = 运算顺序
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch2 Functions 函数]]（本章共 14 条）
 格式训练 P1 Ch2 函数（§2.1、§2.2）
 · Ex 2A 题 1–16（约 34 分钟，p.37）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -3057,8 +3256,8 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch2 函数 §2.5、§2.6、§2.7、§2.8
 · 速览 §2.5 函数的图像变换、§2.6 反射变换、§2.7 伸缩变换、§2.8 复合变换（p.51、p.55、p.57、p.59，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch2 Functions 函数]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -3068,8 +3267,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch2 加速运动 §2.9、§2.10、§2.11、§2.12
 · 速览 §2.9 运动方程的推导、§2.10 匀变速与非匀变速、§2.11 重力加速度、§2.12 测定 g（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch2 Accelerated motion 加速运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -3093,8 +3292,23 @@
 14:00-15:00 应用数学
 术语与格式 M1 Ch3 二维力 §3.1、§3.2、§3.3、§3.4
 · 速览 §3.1 平衡问题中力的水平/竖直分解、§3.2 其他角度平衡问题中的力的分解、§3.3 力的三角形与拉密定理、§3.4 斜面上的非平衡问题（p.54、p.59、p.62、p.66，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. resolve a force = 分解力
+· 2. component = 分量
+· 3. resultant = 合力
+· 4. equilibrium = 平衡
+· 5. inclined plane / slope = 斜面
+· 6. perpendicular / parallel = 垂直 / 平行
+· 7. horizontal / vertical = 水平 / 竖直
+· 8. magnitude = 大小
+· 9. direction = 方向
+· 10. bearing = 方位角
+· 11. triangle of forces = 力的三角形
+· 12. Lami's theorem = 拉密定理
+· 13. concurrent forces = 共点力
+· 14. up/down the plane = 沿斜面向上/向下
+· 全部抄完后回看一遍：[[03_力学 M1#Ch3 Forces in two dimensions 二维力]]（本章共 14 条）
 20:00-21:00 应用数学
 格式训练 M1 Ch3 二维力（§3.1、§3.2）
 · Ex 3A 题 全部（约 25 分钟，p.56）
@@ -3170,8 +3384,23 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 术语与格式 P1 Ch3 坐标几何 §3.1、§3.2、§3.3、§3.4
 · 速览 §3.1 线段长度与中点、§3.2 平行与垂直、§3.3 直线的方程、§3.4 圆的方程（p.72、p.75、p.78、p.82，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. coordinate geometry = 坐标几何
+· 2. line segment = 线段
+· 3. midpoint = 中点
+· 4. gradient = 斜率
+· 5. collinear = 共线的
+· 6. perpendicular bisector = 垂直平分线
+· 7. $x$-intercept / $y$-intercept = $x$ 截距 / $y$ 截距
+· 8. locus = 轨迹
+· 9. completed square form = 配方法形式
+· 10. chord = 弦
+· 11. diameter = 直径
+· 12. angle in a semicircle = 半圆所对的圆周角
+· 13. tangent = 切线
+· 14. repeated root = 重根
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch3 Coordinate geometry 坐标几何]]（本章共 14 条）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -3181,8 +3410,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch2 加速运动 §2.13、§2.14
 · 速览 §2.13 二维运动：抛体、§2.14 理解抛体运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch2 Accelerated motion 加速运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -3214,8 +3443,8 @@
 20:00-21:00 应用数学
 术语与格式 M1 Ch3 二维力 §3.5
 · 速览 §3.5 求合力与加速度方向（p.71，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[03_力学 M1#Ch3 Forces in two dimensions 二维力]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3229,8 +3458,14 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch3 级数求和 §3.1、§3.2
 · 速览 §3.1 Σr、Σr²、Σr³ 求和公式、§3.2 收敛级数（p.46、p.51，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. summation of series = 级数求和
+· 2. method of differences = 差分法 / 逐项相消
+· 3. sum to infinity = 无穷和
+· 4. convergent / divergent = 收敛的 / 发散的
+· 5. partial fractions = 部分分式
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch3 Summation of series 级数求和（9231 §1.3，Paper 1；只在 FM 考）]]（本章共 5 条）</t>
         </is>
       </c>
     </row>
@@ -3283,8 +3518,25 @@
 21:00-22:15 物理
 术语与格式 Phy Ch3 动力学 §3.1、§3.2、§3.3、§3.4
 · 速览 §3.1 力、质量与加速度、§3.2 识别力、§3.3 重力、摩擦与引力、§3.4 质量与惯性（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 16 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. resultant force = 合力
+· 2. free-body diagram = 受力图
+· 3. Newton's first law = 牛顿第一定律
+· 4. Newton's second law = 牛顿第二定律
+· 5. Newton's third law = 牛顿第三定律
+· 6. weight = 重力
+· 7. mass = 质量
+· 8. inertia = 惯性
+· 9. friction = 摩擦力
+· 10. drag = 阻力
+· 11. terminal velocity = 终端速度
+· 12. normal contact force = 法向接触力
+· 13. tension = 张力
+· 14. upthrust = 浮力
+· 15. base unit = 基本单位
+· 16. derived unit = 导出单位
+· 全部抄完后回看一遍：[[06_物理#Ch3 Dynamics 动力学]]（本章共 16 条）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -3315,8 +3567,23 @@
 20:00-21:00 应用数学
 术语与格式 M1 Ch4 摩擦力 §4.1、§4.2、§4.3、§4.4
 · 速览 §4.1 摩擦力作为接触力的一部分、§4.2 摩擦极限、§4.3 运动不同阶段摩擦方向的变化、§4.4 摩擦角（p.83、p.90、p.95、p.100，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. friction = 摩擦力
+· 2. limiting friction = 极限摩擦
+· 3. limiting equilibrium = 极限平衡
+· 4. coefficient of friction = 摩擦系数
+· 5. smooth / rough = 光滑 / 粗糙
+· 6. contact force = 接触力
+· 7. normal contact force $R$ = 法向力
+· 8. on the point of sliding = 临界滑动
+· 9. impending motion = 即将发生的运动
+· 10. opposes motion = 阻碍运动
+· 11. angle of friction = 摩擦角
+· 12. resultant of two perpendicular forces = 互相垂直两力的合力
+· 13. rough surface = 粗糙面
+· 14. threshold / least value = 临界值 / 最小值
+· 全部抄完后回看一遍：[[03_力学 M1#Ch4 Friction 摩擦力]]（本章共 14 条）</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3344,8 +3611,8 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch3 坐标几何 §3.5
 · 速览 §3.5 直线与圆的交点问题（p.88，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch3 Coordinate geometry 坐标几何]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -3449,8 +3716,22 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 术语与格式 P1 Ch4 弧度制 §4.1、§4.2、§4.3
 · 速览 §4.1 弧度、§4.2 弧长、§4.3 扇形面积（p.101、p.104、p.107，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. radian = 弧度
+· 2. arc length = 弧长
+· 3. sector = 扇形
+· 4. minor sector / major sector = 小扇形 / 大扇形
+· 5. segment = 弓形
+· 6. minor arc / major arc = 劣弧 / 优弧
+· 7. chord = 弦
+· 8. subtend = 对（弧对圆心角）
+· 9. circumference = 圆周（周长）
+· 10. perimeter = 周长
+· 11. sine rule / cosine rule = 正弦定理 / 余弦定理
+· 12. significant figures = 有效数字
+· 13. inscribed circle = 内切圆
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch4 Circular measure 弧度制]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -3460,8 +3741,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch3 动力学 §3.5、§3.6、§3.7
 · 速览 §3.5 在流体中运动、§3.6 牛顿第三定律、§3.7 理解 SI 单位（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 16 条）：[[06_物理#Ch3 Dynamics 动力学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -3510,8 +3791,16 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch4 矩阵 1 §4.1、§4.2、§4.3、§4.4
 · 速览 §4.1 矩阵运算、§4.2 逆矩阵、§4.3 行列式、§4.4 矩阵变换（p.59、p.65、p.72、p.76，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. singular / non-singular = 奇异的 / 非奇异的
+· 2. determinant = 行列式
+· 3. inverse matrix = 逆矩阵
+· 4. area scale factor = 面积伸缩因子
+· 5. invariant point / invariant line = 不动点 / 不变直线
+· 6. shear = 剪切
+· 7. enlargement = 放大
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch4 Matrices 1 矩阵 1（9231 §1.4，Paper 1；只在 FM 考）]]（本章共 7 条）</t>
         </is>
       </c>
     </row>
@@ -3591,8 +3880,24 @@
 14:00-15:00 应用数学
 术语与格式 M1 Ch5 连接体 §5.1、§5.2、§5.3、§5.4
 · 速览 §5.1 牛顿第三定律、§5.2 杆连接的物体、§5.3 绳连接的物体、§5.4 电梯中的物体（p.109、p.110、p.114、p.121，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 15 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. Newton's third law = 牛顿第三定律
+· 2. connected particles = 连接体
+· 3. tension = 张力
+· 4. thrust = 推力
+· 5. inextensible string = 不可伸长绳
+· 6. light string / light rod = 轻绳 / 轻杆
+· 7. smooth pulley / peg = 光滑滑轮/光滑钉
+· 8. taut = 绷紧
+· 9. common acceleration = 共同加速度
+· 10. to eliminate $T$ = 消去张力
+· 11. coupling = 车钩/连接杆
+· 12. apparent weight = 视重
+· 13. free fall = 自由落体
+· 14. whole system = 整体
+· 15. modelling assumption = 建模假设
+· 全部抄完后回看一遍：[[03_力学 M1#Ch5 Connected particles 连接体]]（本章共 15 条）
 20:00-21:00 应用数学
 格式训练 M1 Ch5 连接体（§5.1、§5.2）
 · Ex 5A 题 全部（约 25 分钟，p.109）
@@ -3630,8 +3935,22 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch5 三角学 §5.1、§5.2、§5.3、§5.4
 · 速览 §5.1 0°–90° 之间的角、§5.2 角的一般定义、§5.3 任意角的三角比、§5.4 三角函数的图像（p.118、p.121、p.123、p.127，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. basic angle (reference angle) = 基准角（参考角）
+· 2. general definition of an angle = 角的通用定义
+· 3. quadrant = 象限
+· 4. period / periodic function = 周期 / 周期函数
+· 5. amplitude = 振幅
+· 6. principal axis = 中轴
+· 7. asymptote = 渐近线
+· 8. stretch factor = 伸缩因子
+· 9. inverse trigonometric function = 反三角函数
+· 10. principal angle (principal value) = 主值角
+· 11. one-one function = 一对一函数
+· 12. identity = 恒等式
+· 13. LHS / RHS = 左边 / 右边
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch5 Trigonometry 三角学]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -3641,8 +3960,21 @@
 21:00-22:15 物理
 术语与格式 Phy Ch4 力 §4.1、§4.2、§4.3、§4.4
 · 速览 §4.1 力的合成、§4.2 矢量的分量、§4.3 重心、§4.4 力的转动效应（力矩）（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. moment = 力矩
+· 2. torque of a couple = 力偶矩
+· 3. couple = 力偶
+· 4. pivot = 支点
+· 5. perpendicular distance = 垂直距离
+· 6. principle of moments = 力矩平衡原理
+· 7. centre of gravity = 重心
+· 8. equilibrium = 平衡
+· 9. resolving = 分解
+· 10. component = 分量
+· 11. lamina = 薄片
+· 12. plumb line = 铅垂线
+· 全部抄完后回看一遍：[[06_物理#Ch4 Forces 力]]（本章共 12 条）
 格式训练 Phy Ch4 力（§4.1、§4.2）
 · 节末 Questions 题 全部（约 25 分钟，p.116）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -3712,8 +4044,23 @@
 20:00-21:00 应用数学
 术语与格式 M1 Ch6 直线上的一般运动 §6.1、§6.2、§6.3、§6.4
 · 速览 §6.1 速度作为位移对时间的导数、§6.2 加速度作为速度对时间的导数、§6.3 位移作为速度对时间的积分、§6.4 速度作为加速度对时间的积分（p.130、p.134、p.139、p.148，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. differentiation / differentiate = 求导 / 求导数
+· 2. integration / integrate = 积分
+· 3. with respect to time = 对时间
+· 4. constant of integration = 积分常数
+· 5. initial condition = 初始条件
+· 6. stationary / instantaneously at rest = 静止 / 瞬时静止
+· 7. turning point = 转向点
+· 8. total distance travelled = 总路程
+· 9. displacement = 位移
+· 10. deceleration = 减速度
+· 11. datum / initial position = 基准 / 初始位置
+· 12. expand the brackets = 展开括号
+· 13. substitute = 代入
+· 14. maximum displacement = 最大位移
+· 全部抄完后回看一遍：[[03_力学 M1#Ch6 General motion in a straight line 直线上的一般运动]]（本章共 14 条）</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -3742,8 +4089,8 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch5 三角学 §5.5、§5.6、§5.7、§5.8
 · 速览 §5.5 反三角函数、§5.6 三角方程、§5.7 三角恒等式、§5.8 更复杂的三角方程（p.136、p.140、p.145、p.149，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[01_纯数学 P1#Ch5 Trigonometry 三角学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3753,8 +4100,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch4 力 §4.5
 · 速览 §4.5 力偶的力矩（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch4 Forces 力]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -3785,8 +4132,20 @@
 15:15-16:15 物理
 术语与格式 Phy Ch5 功、能与功率 §5.1、§5.2、§5.3、§5.4
 · 速览 §5.1 做功与能量转移、§5.2 重力势能、§5.3 动能、§5.4 重力势能→动能转化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. work done = 做功
+· 2. joule = 焦耳
+· 3. gravitational potential energy = 重力势能
+· 4. kinetic energy = 动能
+· 5. conservation of energy = 能量守恒
+· 6. efficiency = 效率
+· 7. power = 功率
+· 8. watt = 瓦特
+· 9. Sankey diagram = 能流图
+· 10. dissipate = 耗散
+· 11. transformation = 能量转化
+· 全部抄完后回看一遍：[[06_物理#Ch5 Work, energy and power 功、能与功率]]（本章共 11 条）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -3842,8 +4201,14 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch5 极坐标 §5.1、§5.2
 · 速览 §5.1 极坐标系、§5.2 极坐标的应用（p.94、p.103，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. polar coordinates = 极坐标
+· 2. initial line = 初始线 / 极轴
+· 3. pole = 极点
+· 4. area of a sector = 扇形面积
+· 5. symmetry of a polar curve = 极坐标曲线的对称性
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch5 Polar coordinates 极坐标（9231 §1.5，Paper 1；只在 FM 考）]]（本章共 5 条）</t>
         </is>
       </c>
     </row>
@@ -3862,8 +4227,22 @@
 15:15-16:15 纯数
 术语与格式 P1 Ch6 数列 §6.1、§6.2、§6.3、§6.4
 · 速览 §6.1 (a+b)^n 的二项式展开、§6.2 二项式系数、§6.3 等差数列、§6.4 等比数列（p.156、p.160、p.166、p.171，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. binomial expansion = 二项式展开
+· 2. binomial coefficient = 二项式系数
+· 3. Pascal's triangle = 杨辉三角
+· 4. factorial = 阶乘
+· 5. sequence = 数列
+· 6. series = 级数
+· 7. arithmetic progression = 等差数列
+· 8. common difference = 公差
+· 9. geometric progression = 等比数列
+· 10. common ratio = 公比
+· 11. convergent series = 收敛级数
+· 12. sum to infinity = 无穷和
+· 13. term = 项
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch6 Series 数列]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -3917,8 +4296,8 @@
 14:00-15:00 物理
 术语与格式 Phy Ch5 功、能与功率 §5.5、§5.6、§5.7
 · 速览 §5.5 下降、上升、下降：能量变化、§5.6 能量转移、§5.7 功率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 11 条）：[[06_物理#Ch5 Work, energy and power 功、能与功率]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 15:15-16:15 物理
 格式训练 Phy Ch5 功、能与功率（§5.5、§5.6）
 · 节末 Questions 题 全部（约 25 分钟，p.152）
@@ -4027,8 +4406,23 @@
 14:00-15:00 应用数学
 术语与格式 M1 Ch7 动量 §7.1、§7.2
 · 速览 §7.1 动量、§7.2 碰撞与动量守恒（p.159、p.161，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. momentum = 动量
+· 2. impulse = 冲量
+· 3. impulse–momentum relation = 冲量—动量关系
+· 4. conservation of momentum = 动量守恒
+· 5. direct impact = 正碰（一维碰撞）
+· 6. coalesce = 合并（粘在一起）
+· 7. rebound = 反弹
+· 8. before / after impact = 碰撞前 / 后
+· 9. positive direction = 正方向
+· 10. momentum is a vector quantity = 动量是矢量
+· 11. magnitude of momentum = 动量大小
+· 12. combined mass = 总质量
+· 13. external impulse = 外力冲量
+· 14. N s (newton second) = 牛顿秒
+· 全部抄完后回看一遍：[[03_力学 M1#Ch7 Momentum 动量]]（本章共 14 条）
 20:00-21:00 应用数学
 章末复习 M1 Ch7 动量
 · 章末复习题 End-of-chapter review p.167，限时 30 分钟
@@ -4064,8 +4458,8 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch6 数列 §6.5、§6.6
 · 速览 §6.5 无穷等比级数、§6.6 综合等差与等比数列（p.175、p.180，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[01_纯数学 P1#Ch6 Series 数列]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4094,8 +4488,20 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 术语与格式 P1 Ch7 微分 §7.1、§7.2、§7.3、§7.4
 · 速览 §7.1 导数与梯度函数、§7.2 链式法则、§7.3 切线与法线、§7.4 二阶导数（p.191、p.198、p.201、p.205，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. derivative = 导数
+· 2. differentiation = 微分（求导）
+· 3. differentiation from first principles = 用定义求导
+· 4. gradient function = 梯度函数
+· 5. chain rule = 链式法则
+· 6. composite function = 复合函数
+· 7. tangent = 切线
+· 8. normal = 法线
+· 9. second derivative = 二阶导数
+· 10. scalar multiple rule = 常数倍法则
+· 11. small increment = 微小增量
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch7 Differentiation 微分]]（本章共 11 条）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -4105,8 +4511,19 @@
 21:00-22:15 物理
 术语与格式 Phy Ch6 动量 §6.1、§6.2、§6.3、§6.4
 · 速览 §6.1 动量的概念、§6.2 碰撞建模、§6.3 理解碰撞、§6.4 爆炸与撞击（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. momentum = 动量
+· 2. linear momentum = 线动量
+· 3. closed system = 封闭系统
+· 4. conservation of momentum = 动量守恒
+· 5. elastic collision = 弹性碰撞
+· 6. inelastic collision = 非弹性碰撞
+· 7. impulse = 冲量
+· 8. explosion = 爆炸
+· 9. resultant external force = 合外力
+· 10. crumple zone = 溃缩区
+· 全部抄完后回看一遍：[[06_物理#Ch6 Momentum 动量]]（本章共 10 条）
 格式训练 Phy Ch6 动量（§6.1、§6.2）
 · 节末 Questions 题 全部（约 25 分钟，p.167）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -4136,8 +4553,24 @@
 14:00-15:00 应用数学
 术语与格式 M1 Ch8 功与能 §8.1、§8.2、§8.3
 · 速览 §8.1 力做的功、§8.2 动能、§8.3 重力势能（p.171、p.177、p.179，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 15 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. work done = 做功
+· 2. joule (J) = 焦耳
+· 3. kinetic energy = 动能
+· 4. gravitational potential energy = 重力势能
+· 5. datum / zero level = 基准面
+· 6. change in KE / GPE = 动能/势能的变化量
+· 7. work done against friction = 克服摩擦做功
+· 8. work done by weight = 重力做功
+· 9. perpendicular to the motion = 与运动垂直
+· 10. in the direction of the force = 沿力的方向
+· 11. component of the force = 力的分量
+· 12. conservative force = 保守力
+· 13. dissipate (as heat) = 耗散（发热）
+· 14. mechanical energy = 机械能
+· 15. convert units = 换算单位
+· 全部抄完后回看一遍：[[03_力学 M1#Ch8 Work and energy 功与能]]（本章共 15 条）
 20:00-21:00 应用数学
 格式训练 M1 Ch8 功与能（§8.1、§8.2）
 · Ex 8A 题 全部（约 25 分钟，p.173）
@@ -4159,8 +4592,16 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch6 向量（进阶） §6.1、§6.2、§6.3
 · 速览 §6.1 向量积（叉积）、§6.2 直线的向量方程、§6.3 平面（p.119、p.123、p.128，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. vector product (cross product) = 向量积 / 叉积
+· 2. scalar product = 标量积 / 点积
+· 3. equation of a plane = 平面方程
+· 4. foot of the perpendicular = 垂足
+· 5. skew lines = 异面直线
+· 6. common perpendicular = 公垂线
+· 7. line of intersection = 交线
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch6 Vectors 向量（进阶）（9231 §1.6，Paper 1；含 9709 未深化的向量积与平面）]]（本章共 7 条）</t>
         </is>
       </c>
     </row>
@@ -4213,8 +4654,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch6 动量 §6.5、§6.6、§6.7
 · 速览 §6.5 二维碰撞、§6.6 动量与牛顿定律、§6.7 理解运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 10 条）：[[06_物理#Ch6 Momentum 动量]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -4245,8 +4686,24 @@
 20:00-21:00 应用数学
 术语与格式 M1 Ch9 功能原理与功率 §9.1、§9.2、§9.3、§9.4
 · 速览 §9.1 功能原理、§9.2 保守力系统中的能量守恒、§9.3 含非保守力系统的能量守恒、§9.4 功率（p.186、p.193、p.196、p.201，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 15 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. work–energy principle = 功能原理
+· 2. increase in mechanical energy = 机械能增加量
+· 3. conservation of energy = 能量守恒
+· 4. conservative / non-conservative force = 保守力 / 非保守力
+· 5. dissipated as heat = 以热的形式耗散
+· 6. resistance = 阻力
+· 7. driving force = 牵引力
+· 8. power = 功率
+· 9. watt (W) = 瓦特
+· 10. rate of doing work = 做功的速率
+· 11. maximum speed = 最大速度
+· 12. tractive force = 牵引力
+· 13. efficiency = 效率
+· 14. rate of fuel consumption = 燃料消耗率
+· 15. the mass cancels = 质量约去
+· 全部抄完后回看一遍：[[03_力学 M1#Ch9 The work–energy principle and power 功能原理与功率]]（本章共 15 条）</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -4276,8 +4733,21 @@
 21:00-22:15 纯数
 术语与格式 P1 Ch8 进阶微分 §8.1、§8.2、§8.3、§8.4
 · 速览 §8.1 增函数与减函数、§8.2 驻点、§8.3 实际最大最小值问题、§8.4 变化率（p.213、p.216、p.221、p.227，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. increasing function = 增函数
+· 2. decreasing function = 减函数
+· 3. stationary point = 驻点
+· 4. turning point = 极值点
+· 5. maximum point = 极大值点
+· 6. minimum point = 极小值点
+· 7. point of inflexion = 拐点
+· 8. first derivative test = 一阶导数检验
+· 9. second derivative test = 二阶导数检验
+· 10. rate of change = 变化率
+· 11. connected rates of change = 相关变化率
+· 12. nature of a stationary point = 驻点的性质
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch8 Further differentiation 进阶微分]]（本章共 12 条）</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4326,8 +4796,26 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 术语与格式 Phy Ch7 物质与材料 §7.1、§7.2、§7.3、§7.4
 · 速览 §7.1 密度、§7.2 压强、§7.3 阿基米德原理、§7.4 压力与张力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 17 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. density = 密度
+· 2. pressure = 压强
+· 3. pascal = 帕斯卡
+· 4. upthrust = 浮力
+· 5. Archimedes' principle = 阿基米德原理
+· 6. tensile force = 张力
+· 7. compressive force = 压力
+· 8. Hooke's law = 胡克定律
+· 9. force constant = 劲度系数
+· 10. extension = 伸长量
+· 11. limit of proportionality = 比例极限
+· 12. elastic limit = 弹性极限
+· 13. elastic deformation = 弹性形变
+· 14. plastic deformation = 塑性形变
+· 15. stress = 应力
+· 16. strain = 应变
+· 17. Young modulus = 杨氏模量
+· 全部抄完后回看一遍：[[06_物理#Ch7 Matter and materials 物质与材料]]（本章共 17 条）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -4390,8 +4878,8 @@
 14:00-15:00 纯数
 术语与格式 P1 Ch8 进阶微分 §8.5
 · 速览 §8.5 相关变化率的实际应用（p.230，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[01_纯数学 P1#Ch8 Further differentiation 进阶微分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 15:15-16:15 纯数
 章末复习 P1 Ch8 进阶微分
 · 章末复习题 End-of-chapter review p.235，限时 30 分钟
@@ -4430,8 +4918,21 @@
 14:00-15:00 纯数
 术语与格式 P1 Ch9 积分 §9.1、§9.2、§9.3、§9.4
 · 速览 §9.1 积分是微分的逆运算、§9.2 求积分常数、§9.3 (ax+b)^n 型函数的积分、§9.4 进一步的不定积分（p.239、p.244、p.247、p.249，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. integration = 积分
+· 2. antidifferentiation = 反微分
+· 3. indefinite integral = 不定积分
+· 4. definite integral = 定积分
+· 5. constant of integration = 积分常数
+· 6. limits of integration = 积分上下限
+· 7. integrand = 被积函数
+· 8. area under a curve = 曲线下的面积
+· 9. volume of revolution = 旋转体体积
+· 10. solid of revolution = 旋转体
+· 11. improper integral = 反常（广义）积分
+· 12. Fundamental theorem of Calculus = 微积分基本定理
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch9 Integration 积分]]（本章共 12 条）
 15:15-16:15 纯数
 格式训练 P1 Ch9 积分（§9.1、§9.2）
 · Ex 9A 题 1–7（约 20 分钟，p.243）
@@ -4449,8 +4950,8 @@
 14:00-15:00 物理
 术语与格式 Phy Ch7 物质与材料 §7.5、§7.6
 · 速览 §7.5 材料的拉伸、§7.6 弹性势能（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 17 条）：[[06_物理#Ch7 Matter and materials 物质与材料]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 15:15-16:15 物理
 章末复习 Phy Ch7 物质与材料
 · 章末复习题 End-of-chapter review，限时 30 分钟
@@ -4489,8 +4990,24 @@
 14:00-15:00 应用数学
 术语与格式 S1 Ch1 数据的表示 §1.1、§1.2、§1.3、§1.4
 · 速览 §1.1 数据的类型、§1.2 离散数据的表示：茎叶图、§1.3 连续数据的表示：直方图、§1.4 连续数据的表示：累积频率图（p.2、p.3、p.6、p.13，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 15 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. qualitative data = 定性数据
+· 2. quantitative data = 定量数据
+· 3. discrete data = 离散数据
+· 4. continuous data = 连续数据
+· 5. stem-and-leaf diagram = 茎叶图
+· 6. back-to-back stem-and-leaf diagram = 背靠背茎叶图
+· 7. key = 图例（茎叶图说明）
+· 8. histogram = 直方图
+· 9. frequency density = 频率密度
+· 10. class width = 组距
+· 11. class boundary = 组界
+· 12. cumulative frequency = 累积频数
+· 13. cumulative frequency graph = 累积频数图
+· 14. modal class = 众数类
+· 15. skewed / positively skewed / negatively skewed = 偏斜的／正偏（右偏）／负偏（左偏）
+· 全部抄完后回看一遍：[[04_统计 S1#Ch1 Representation of data 数据的表示]]（本章共 15 条）
 20:00-21:00 应用数学
 格式训练 S1 Ch1 数据的表示（§1.1、§1.2）
 · Ex 1A 题 1–9（约 24 分钟，p.4）
@@ -4512,8 +5029,16 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch7 数学归纳法 §7.1、§7.2
 · 速览 §7.1 归纳过程、§7.2 整除性的归纳证明（p.140、p.146，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. mathematical induction = 数学归纳法
+· 2. basis (base case) = 基础步
+· 3. inductive hypothesis = 归纳假设
+· 4. inductive step = 归纳步
+· 5. divisible by = 被……整除
+· 6. conjecture = 猜想
+· 7. recurrence relation = 递推关系
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch7 Proof by induction 数学归纳法（9231 §1.7，Paper 1；只在 FM 考）]]（本章共 7 条）</t>
         </is>
       </c>
     </row>
@@ -4593,8 +5118,8 @@
 15:15-16:15 纯数
 术语与格式 P1 Ch9 积分 §9.5、§9.6、§9.7、§9.8
 · 速览 §9.5 定积分、§9.6 曲线下的面积、§9.7 曲线与直线/两曲线围成的面积、§9.8 反常（广义）积分（p.250、p.253、p.260、p.264，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[01_纯数学 P1#Ch9 Integration 积分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -4604,8 +5129,25 @@
 14:00-15:00 物理
 术语与格式 Phy Ch8 电流 §8.1、§8.2、§8.3、§8.4
 · 速览 §8.1 电路符号与电路图、§8.2 电流、§8.3 电流的公式、§8.4 电压的含义（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 16 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. electric current = 电流
+· 2. charge = 电荷
+· 3. coulomb = 库仑
+· 4. ampere = 安培
+· 5. conventional current = 常规电流
+· 6. drift velocity = 漂移速度
+· 7. number density = 数密度
+· 8. potential difference = 电势差
+· 9. volt = 伏特
+· 10. electromotive force (e.m.f.) = 电动势
+· 11. resistance = 电阻
+· 12. ohm = 欧姆
+· 13. electrical power = 电功率
+· 14. ammeter = 电流表
+· 15. voltmeter = 电压表
+· 16. circuit symbol = 电路符号
+· 全部抄完后回看一遍：[[06_物理#Ch8 Electric current 电流]]（本章共 16 条）
 15:15-16:15 物理
 格式训练 Phy Ch8 电流（§8.1、§8.2）
 · 节末 Questions 题 全部（约 25 分钟，p.223）
@@ -4653,8 +5195,8 @@
 15:15-16:15 物理
 术语与格式 Phy Ch8 电流 §8.5、§8.6
 · 速览 §8.5 电阻、§8.6 电功率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 16 条）：[[06_物理#Ch8 Electric current 电流]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -4704,8 +5246,8 @@
 14:00-15:00 纯数
 术语与格式 P1 Ch9 积分 §9.9
 · 速览 §9.9 旋转体体积（p.268，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[01_纯数学 P1#Ch9 Integration 积分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -4741,8 +5283,19 @@
 14:00-15:00 物理
 术语与格式 Phy Ch9 基尔霍夫定律 §9.1、§9.2、§9.3、§9.4
 · 速览 §9.1 基尔霍夫第一定律、§9.2 基尔霍夫第二定律、§9.3 基尔霍夫定律的应用、§9.4 电阻的组合（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. Kirchhoff's first law = 基尔霍夫第一定律
+· 2. Kirchhoff's second law = 基尔霍夫第二定律
+· 3. junction = 节点
+· 4. loop = 回路
+· 5. conservation of charge = 电荷守恒
+· 6. conservation of energy = 能量守恒
+· 7. series = 串联
+· 8. parallel = 并联
+· 9. combined resistance = 总电阻
+· 10. reciprocal = 倒数
+· 全部抄完后回看一遍：[[06_物理#Ch9 Kirchhoff's laws 基尔霍夫定律]]（本章共 10 条）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -4766,8 +5319,8 @@
 14:00-15:00 应用数学
 术语与格式 S1 Ch1 数据的表示 §1.5
 · 速览 §1.5 不同数据表示方法的比较（p.20，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 15 条）：[[04_统计 S1#Ch1 Representation of data 数据的表示]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -4796,8 +5349,21 @@
 14:00-15:00 纯数
 术语与格式 P2/3 Ch1 代数 §1.1、§1.2、§1.3、§1.4
 · 速览 §1.1 绝对值函数、§1.2 线性函数的绝对值图像、§1.3 绝对值不等式、§1.4 多项式的除法（p.2、p.7、p.8、p.11，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. modulus function, absolute value = 绝对值函数
+· 2. modulus equation / modulus inequality = 绝对值方程／不等式
+· 3. polynomial = 多项式
+· 4. degree of a polynomial = 多项式的次数
+· 5. dividend = 被除式
+· 6. divisor = 除式
+· 7. quotient = 商
+· 8. remainder = 余数／余式
+· 9. division algorithm for polynomials = 多项式除法算式
+· 10. factor theorem = 因式定理
+· 11. remainder theorem = 余数定理
+· 12. proper / improper algebraic fraction = 真／假分式
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch1 Algebra 代数]]（本章共 12 条）
 15:15-16:15 纯数
 格式训练 P2/3 Ch1 代数（§1.1、§1.2）
 · Ex 1A 题 1–9（约 24 分钟，p.6）
@@ -4844,8 +5410,8 @@
 15:15-16:15 纯数
 术语与格式 P2/3 Ch1 代数 §1.5、§1.6
 · 速览 §1.5 因式定理、§1.6 余数定理（p.14、p.18，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[02_纯数学 P2-3#Ch1 Algebra 代数]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -4855,8 +5421,18 @@
 14:00-15:00 物理
 术语与格式 Phy Ch10 电阻与电阻率 §10.1、§10.2、§10.3、§10.4
 · 速览 §10.1 金属导体的 I–V 特性、§10.2 欧姆定律、§10.3 电阻与温度、§10.4 电阻率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. Ohm's law = 欧姆定律
+· 2. I–V characteristic = 伏安特性
+· 3. ohmic conductor = 欧姆导体
+· 4. filament lamp = 白炽灯
+· 5. diode = 二极管
+· 6. forward bias = 正向偏置
+· 7. reverse bias = 反向偏置
+· 8. resistivity = 电阻率
+· 9. cross-sectional area = 横截面积
+· 全部抄完后回看一遍：[[06_物理#Ch10 Resistance and resistivity 电阻与电阻率]]（本章共 9 条）
 15:15-16:15 物理
 格式训练 Phy Ch10 电阻与电阻率（§10.1、§10.2）
 · 节末 Questions 题 全部（约 25 分钟，p.271）
@@ -4903,8 +5479,22 @@
 20:00-21:00 应用数学
 术语与格式 S1 Ch2 集中趋势的度量 §2.1、§2.2、§2.3
 · 速览 §2.1 众数与众数类、§2.2 平均数、§2.3 中位数（p.28、p.30、p.42，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. mode = 众数
+· 2. modal class = 众数类
+· 3. mean = 平均数
+· 4. median = 中位数
+· 5. measure of central tendency = 集中趋势度量
+· 6. mid-value / midpoint = 组中值
+· 7. coded data = 编码后的数据
+· 8. combined mean = 合并平均数
+· 9. frequency table = 频数表
+· 10. ungrouped data = 未分组数据
+· 11. grouped data = 分组数据
+· 12. symmetric distribution = 对称分布
+· 13. outlier = 异常值
+· 全部抄完后回看一遍：[[04_统计 S1#Ch2 Measures of central tendency 集中趋势的度量]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -4918,8 +5508,15 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch13 抛体运动 §13.1、§13.2
 · 速览 §13.1 竖直平面内的运动、§13.2 轨迹的直角坐标方程（p.309、p.314，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. projectile = 抛体
+· 2. angle of projection = 抛射角
+· 3. trajectory = 轨迹
+· 4. Cartesian equation of the trajectory = 轨迹的直角坐标方程
+· 5. range on a horizontal plane = 水平面射程
+· 6. greatest height = 最大高度
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch13 Projectiles 抛体运动（9231 §3.1，Paper 3；在 9709 基础上加深）]]（本章共 6 条）</t>
         </is>
       </c>
     </row>
@@ -4957,8 +5554,22 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch2 对数与指数函数 §2.1、§2.2、§2.3、§2.4
 · 速览 §2.1 以 10 为底的对数、§2.2 以 a 为底的对数、§2.3 对数的运算法则、§2.4 解对数方程（p.26、p.30、p.33、p.35，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. logarithm (log) = 对数
+· 2. base = 底数
+· 3. index, exponent = 指数
+· 4. laws of logarithms = 对数运算法则
+· 5. natural logarithm = 自然对数
+· 6. natural exponential function = 自然指数函数
+· 7. common logarithm = 常用对数
+· 8. exponential equation = 指数方程
+· 9. exponential inequality = 指数不等式
+· 10. inverse function = 反函数
+· 11. transforming to linear form = 化为线性形式
+· 12. gradient = 斜率／梯度
+· 13. intercept = 截距
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch2 Logarithmic and exponential functions 对数与指数函数]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4968,8 +5579,19 @@
 21:00-22:15 物理
 术语与格式 Phy Ch11 实用电路 §11.1、§11.2、§11.3、§11.4
 · 速览 §11.1 内阻、§11.2 分压器、§11.3 传感器、§11.4 电位器电路（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. internal resistance = 内阻
+· 2. terminal p.d. = 端电压
+· 3. lost volts = 内压降
+· 4. e.m.f. = 电动势
+· 5. potential divider = 分压器
+· 6. potentiometer = 电位器
+· 7. thermistor = 热敏电阻
+· 8. light-dependent resistor (LDR) = 光敏电阻
+· 9. sensor = 传感器
+· 10. null method = 零示法
+· 全部抄完后回看一遍：[[06_物理#Ch11 Practical circuits 实用电路]]（本章共 10 条）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -5126,8 +5748,8 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 术语与格式 P2/3 Ch2 对数与指数函数 §2.5、§2.6、§2.7、§2.8
 · 速览 §2.5 解指数方程、§2.6 解指数不等式、§2.7 自然对数、§2.8 把关系式化为线性形式（p.38、p.40、p.42、p.44，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[02_纯数学 P2-3#Ch2 Logarithmic and exponential functions 对数与指数函数]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -5143,8 +5765,24 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 术语与格式 Phy Ch12 波 §12.1、§12.2、§12.3、§12.4
 · 速览 §12.1 描述波、§12.2 横波与纵波、§12.3 波的能量、§12.4 波速（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 15 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. wave = 波
+· 2. transverse wave = 横波
+· 3. longitudinal wave = 纵波
+· 4. amplitude = 振幅
+· 5. wavelength = 波长
+· 6. frequency = 频率
+· 7. period = 周期
+· 8. displacement = 位移
+· 9. intensity = 强度
+· 10. Doppler effect = 多普勒效应
+· 11. electromagnetic spectrum = 电磁波谱
+· 12. polarisation = 偏振
+· 13. Malus's law = 马吕斯定律
+· 14. plane of polarisation = 偏振面
+· 15. order of magnitude = 数量级
+· 全部抄完后回看一遍：[[06_物理#Ch12 Waves 波]]（本章共 15 条）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -5168,8 +5806,21 @@
 14:00-15:00 应用数学
 术语与格式 S1 Ch3 离散程度的度量 §3.1、§3.2、§3.3
 · 速览 §3.1 极差、§3.2 四分位距与百分位数、§3.3 方差与标准差（p.55、p.56、p.65，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. range = 极差
+· 2. interquartile range (IQR) = 四分位距
+· 3. quartile = 四分位数
+· 4. lower quartile / upper quartile = 下四分位数／上四分位数
+· 5. percentile = 百分位数
+· 6. variance = 方差
+· 7. standard deviation (SD) = 标准差
+· 8. deviation = 偏差
+· 9. outlier = 异常值
+· 10. box-and-whisker diagram = 箱线图
+· 11. measure of variation = 离散程度度量
+· 12. coding = 编码
+· 全部抄完后回看一遍：[[04_统计 S1#Ch3 Measures of variation 离散程度的度量]]（本章共 12 条）
 20:00-21:00 应用数学
 格式训练 S1 Ch3 离散程度的度量（§3.1、§3.2）
 · Ex 3A 题 1–13（约 30 分钟，p.61）
@@ -5191,8 +5842,15 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch14 刚体平衡 §14.1、§14.2、§14.3、§14.4
 · 速览 §14.1 力矩、§14.2 杆与薄板的重心、§14.3 立体的重心、§14.4 物体的平衡（p.322、p.326、p.336、p.341，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. moment of a force = 力矩
+· 2. centre of mass = 质心
+· 3. centre of gravity = 重心
+· 4. composite body = 组合体
+· 5. toppling / sliding = 倾倒 / 滑动
+· 6. coplanar forces = 共面力系
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch14 Equilibrium of a rigid body 刚体平衡（9231 §3.2，Paper 3；部分为 FM 新内容）]]（本章共 6 条）</t>
         </is>
       </c>
     </row>
@@ -5280,8 +5938,26 @@
 20:00-21:00 应用数学
 术语与格式 S1 Ch4 概率 §4.1、§4.2、§4.3、§4.4
 · 速览 §4.1 试验、事件与结果、§4.2 互斥事件与加法法则、§4.3 独立事件与乘法法则、§4.4 条件概率（p.91、p.94、p.100、p.108，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 17 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. experiment / trial = 试验
+· 2. outcome = 结果
+· 3. event = 事件
+· 4. possibility space / sample space = 样本空间
+· 5. equally likely / equiprobable = 等可能
+· 6. complement = 对立事件
+· 7. exhaustive events = 完备事件
+· 8. mutually exclusive = 互斥
+· 9. independent = 独立
+· 10. conditional probability = 条件概率
+· 11. addition law = 加法法则
+· 12. multiplication law = 乘法法则
+· 13. tree diagram = 树状图
+· 14. Venn diagram = 韦恩图
+· 15. with / without replacement = 有放回／无放回
+· 16. relative frequency = 相对频率
+· 17. expectation = 期望次数
+· 全部抄完后回看一遍：[[04_统计 S1#Ch4 Probability 概率]]（本章共 17 条）</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -5311,8 +5987,19 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch3 三角学 §3.1、§3.2、§3.3、§3.4
 · 速览 §3.1 cosec / sec / cot、§3.2 和角公式、§3.3 倍角公式、§3.4 进阶三角恒等式（p.53、p.58、p.61、p.66，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. cosecant, cosec = 余割
+· 2. secant, sec = 正割
+· 3. cotangent, cot = 余切
+· 4. reciprocal trigonometric ratios = 倒数三角比
+· 5. trigonometrical identities = 三角恒等式
+· 6. compound angle formulae = 和角公式
+· 7. double angle formulae = 倍角公式
+· 8. auxiliary angle / R-form = 辅助角／R 形式
+· 9. exact value = 精确值
+· 10. maximum / minimum value = 最大值／最小值
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch3 Trigonometry 三角学]]（本章共 10 条）</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -5322,8 +6009,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch12 波 §12.5、§12.6、§12.7、§12.8
 · 速览 §12.5 声波的多普勒效应、§12.6 电磁波、§12.7 电磁辐射、§12.8 数量级（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 15 条）：[[06_物理#Ch12 Waves 波]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -5426,8 +6113,8 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch3 三角学 §3.5
 · 速览 §3.5 a sinθ + b cosθ 化为 R sin(θ±α)（p.68，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 10 条）：[[02_纯数学 P2-3#Ch3 Trigonometry 三角学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -5437,8 +6124,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch12 波 §12.9、§12.10
 · 速览 §12.9 电磁波的本质、§12.10 偏振（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 15 条）：[[06_物理#Ch12 Waves 波]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5488,8 +6175,8 @@
 14:00-15:00 应用数学
 术语与格式 S1 Ch4 概率 §4.5
 · 速览 §4.5 非独立事件与条件概率（p.112，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 17 条）：[[04_统计 S1#Ch4 Probability 概率]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 20:00-21:00 应用数学
 章末复习 S1 Ch4 概率
 · 章末复习题 End-of-chapter review p.118，限时 30 分钟
@@ -5509,8 +6196,15 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch15 圆周运动（进阶） §15.1、§15.2、§15.3
 · 速览 §15.1 水平圆、§15.2 三维情形、§15.3 竖直圆（p.355、p.360、p.365，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. angular speed = 角速度
+· 2. centripetal acceleration = 向心加速度
+· 3. conical pendulum = 圆锥摆
+· 4. vertical circle = 竖直圆
+· 5. complete circular motion = 完整圆周运动
+· 6. normal contact force = 法向接触力
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch15 Circular motion 圆周运动（进阶）（9231 §3.3，Paper 3；在 9709 基础上加深）]]（本章共 6 条）</t>
         </is>
       </c>
     </row>
@@ -5522,8 +6216,21 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch4 微分 §4.1、§4.2、§4.3、§4.4
 · 速览 §4.1 乘积法则、§4.2 商法则、§4.3 指数函数的导数、§4.4 自然对数函数的导数（p.81、p.84、p.87、p.91，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. derivative, gradient function = 导数／梯度函数
+· 2. chain rule = 链式法则
+· 3. product rule = 乘积法则
+· 4. quotient rule = 商法则
+· 5. explicit function = 显函数
+· 6. implicit function = 隐函数
+· 7. implicit differentiation = 隐函数求导
+· 8. parametric equations = 参数方程
+· 9. parameter = 参数
+· 10. tangent = 切线
+· 11. normal = 法线
+· 12. composite function = 复合函数
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch4 Differentiation 微分]]（本章共 12 条）</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -5533,8 +6240,22 @@
 21:00-22:15 物理
 术语与格式 Phy Ch13 波的叠加 §13.1、§13.2、§13.3、§13.4
 · 速览 §13.1 波的叠加原理、§13.2 波的衍射、§13.3 干涉、§13.4 杨氏双缝实验（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. superposition = 叠加
+· 2. diffraction = 衍射
+· 3. interference = 干涉
+· 4. coherent = 相干
+· 5. path difference = 波程差
+· 6. constructive interference = 相长干涉
+· 7. destructive interference = 相消干涉
+· 8. monochromatic = 单色
+· 9. fringe = 条纹
+· 10. double slit = 双缝
+· 11. diffraction grating = 衍射光栅
+· 12. grating spacing = 光栅间距
+· 13. order = 级次
+· 全部抄完后回看一遍：[[06_物理#Ch13 Superposition of waves 波的叠加]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -5665,8 +6386,19 @@
 14:00-15:00 应用数学
 术语与格式 S1 Ch5 排列与组合 §5.1、§5.2、§5.3、§5.4
 · 速览 §5.1 阶乘函数、§5.2 排列、§5.3 组合、§5.4 排列组合的应用（p.124、p.125、p.135、p.138，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. factorial = 阶乘
+· 2. permutation = 排列
+· 3. combination = 组合
+· 4. arrangement = 排列方式
+· 5. selection = 选择
+· 6. distinct objects = 不同物体
+· 7. identical objects = 相同物体
+· 8. multiplication principle = 乘法原理
+· 9. restriction = 限制条件
+· 10. with / without replacement = 有放回／无放回
+· 全部抄完后回看一遍：[[04_统计 S1#Ch5 Permutations and combinations 排列与组合]]（本章共 10 条）
 20:00-21:00 应用数学
 格式训练 S1 Ch5 排列与组合（§5.1、§5.2）
 · Ex 5A 题 1–9（约 24 分钟，p.124）
@@ -5704,8 +6436,8 @@
 14:00-15:00 纯数
 术语与格式 P2/3 Ch4 微分 §4.5、§4.6、§4.7
 · 速览 §4.5 三角函数的导数、§4.6 隐函数求导、§4.7 参数方程求导（p.95、p.99、p.103，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[02_纯数学 P2-3#Ch4 Differentiation 微分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 15:15-16:15 纯数
 格式训练 P2/3 Ch4 微分（§4.5、§4.6）
 · Ex 4E 题 1–17（约 35 分钟，p.98）
@@ -5723,8 +6455,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch13 波的叠加 §13.5
 · 速览 §13.5 衍射光栅（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[06_物理#Ch13 Superposition of waves 波的叠加]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5781,8 +6513,17 @@
 20:00-21:00 应用数学
 术语与格式 S1 Ch6 概率分布 §6.1、§6.2、§6.3
 · 速览 §6.1 离散随机变量、§6.2 概率分布、§6.3 离散随机变量的期望与方差（p.150、p.150、p.156，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 8 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. discrete random variable = 离散随机变量
+· 2. probability distribution = 概率分布
+· 3. probability distribution table = 概率分布表
+· 4. expectation / expected value = 期望／期望值
+· 5. variance = 方差
+· 6. standard deviation = 标准差
+· 7. long-term average = 长期平均值
+· 8. parameter = 参数
+· 全部抄完后回看一遍：[[04_统计 S1#Ch6 Probability distributions 概率分布]]（本章共 8 条）</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -5811,8 +6552,20 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch5 积分 §5.1、§5.2、§5.3、§5.4
 · 速览 §5.1 指数函数的积分、§5.2 1/(ax+b) 的积分、§5.3 sin/cos/sec²(ax+b) 的积分、§5.4 进一步的三角函数积分（p.112、p.115、p.118、p.121，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. integration = 积分
+· 2. indefinite integral = 不定积分
+· 3. definite integral = 定积分
+· 4. arbitrary constant of integration = 积分任意常数
+· 5. integrand = 被积函数
+· 6. validity = 适用范围
+· 7. trapezium rule = 梯形法则
+· 8. strip / interval = 条／区间
+· 9. ordinate = 纵坐标值
+· 10. overestimate / underestimate = 高估／低估
+· 11. double angle identities = 倍角公式
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch5 Integration 积分]]（本章共 11 条）</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -5822,8 +6575,18 @@
 21:00-22:15 物理
 术语与格式 Phy Ch14 驻波 §14.1、§14.2、§14.3、§14.4
 · 速览 §14.1 从行波到驻波、§14.2 波节与波腹、§14.3 驻波的形成、§14.4 测定声波的波长与速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. stationary wave = 驻波
+· 2. standing wave = 驻波
+· 3. node = 波节
+· 4. antinode = 波腹
+· 5. progressive wave = 行进波
+· 6. fundamental frequency = 基频
+· 7. first harmonic = 一次谐波
+· 8. in phase = 同相
+· 9. antiphase = 反相
+· 全部抄完后回看一遍：[[06_物理#Ch14 Stationary waves 驻波]]（本章共 9 条）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5905,8 +6668,15 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch16 胡克定律 §16.1、§16.2、§16.3
 · 速览 §16.1 胡克定律、§16.2 弹性势能、§16.3 功能原理（p.380、p.385、p.389，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. Hooke's law = 胡克定律
+· 2. modulus of elasticity = 弹性模量
+· 3. natural length = 自然长度
+· 4. extension / compression = 伸长 / 压缩
+· 5. elastic potential energy = 弹性势能
+· 6. slack string = 松弛的绳
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch16 Hooke's law 胡克定律（9231 §3.4，Paper 3；只在 FM 深入）]]（本章共 6 条）</t>
         </is>
       </c>
     </row>
@@ -5924,8 +6694,8 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 术语与格式 P2/3 Ch5 积分 §5.5
 · 速览 §5.5 梯形法则（p.126，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 11 条）：[[02_纯数学 P2-3#Ch5 Integration 积分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -5935,8 +6705,31 @@
 21:00-22:15 物理
 术语与格式 Phy Ch15 原子结构 §15.1、§15.2、§15.3、§15.4
 · 速览 §15.1 观察原子内部、§15.2 α 粒子散射与原子核、§15.3 原子的简单模型、§15.4 核子与电子（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 22 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. nucleus = 原子核
+· 2. nucleon = 核子
+· 3. proton = 质子
+· 4. neutron = 中子
+· 5. proton number = 质子数
+· 6. nucleon number = 核子数
+· 7. isotope = 同位素
+· 8. nuclide = 核素
+· 9. α-particle scattering = α 粒子散射
+· 10. radioactivity = 放射性
+· 11. β-particle = β 粒子
+· 12. γ-radiation = γ 射线
+· 13. neutrino = 中微子
+· 14. antineutrino = 反中微子
+· 15. positron = 正电子
+· 16. quark = 夸克
+· 17. lepton = 轻子
+· 18. hadron = 强子
+· 19. baryon = 重子
+· 20. meson = 介子
+· 21. mass–energy = 质能
+· 22. annihilation = 湮灭
+· 全部抄完后回看一遍：[[06_物理#Ch15 Atomic structure 原子结构]]（本章共 22 条）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -5987,8 +6780,18 @@
 14:00-15:00 应用数学
 术语与格式 S1 Ch7 二项分布与几何分布 §7.1、§7.2
 · 速览 §7.1 二项分布、§7.2 几何分布（p.166、p.175，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. binomial distribution = 二项分布
+· 2. geometric distribution = 几何分布
+· 3. trial = 试验
+· 4. success / failure = 成功／失败
+· 5. parameter = 参数
+· 6. constant probability = 概率恒定
+· 7. independent trials = 独立试验
+· 8. mode = 众数
+· 9. cumulative probability = 累积概率
+· 全部抄完后回看一遍：[[04_统计 S1#Ch7 The binomial and geometric distributions 二项分布与几何分布]]（本章共 9 条）
 20:00-21:00 应用数学
 章末复习 S1 Ch7 二项分布与几何分布
 · 章末复习题 End-of-chapter review p.185，限时 30 分钟
@@ -6024,8 +6827,19 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch6 方程的数值解法 §6.1、§6.2、§6.3
 · 速览 §6.1 寻找初始近似值、§6.2 改进解的精度、§6.3 迭代法的跨领域应用（p.135、p.140、p.149，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. root = 根
+· 2. approximation = 近似值
+· 3. iterative process / iteration = 迭代法
+· 4. converges = 收敛
+· 5. diverges = 发散
+· 6. change of sign = 变号
+· 7. continuous = 连续
+· 8. starting point / initial value = 初始近似值
+· 9. rearrangement = 变形／重新整理
+· 10. prescribed degree of accuracy = 指定精度
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch6 Numerical solutions of equations 方程的数值解法]]（本章共 10 条）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6063,8 +6877,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch15 原子结构 §15.5、§15.6、§15.7、§15.8
 · 速览 §15.5 原子核内的力、§15.6 放射性的发现、§15.7 放射性物质发出的射线、§15.8 α 与 β 衰变中的能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 22 条）：[[06_物理#Ch15 Atomic structure 原子结构]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 格式训练 Phy Ch15 原子结构（§15.5、§15.6）
 · 节末 Questions 题 全部（约 25 分钟，p.400）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -6163,8 +6977,22 @@
 14:00-15:00 应用数学
 术语与格式 S1 Ch8 正态分布 §8.1、§8.2、§8.3、§8.4
 · 速览 §8.1 连续随机变量、§8.2 正态分布、§8.3 用正态分布建模、§8.4 二项分布的正态近似（p.188、p.193、p.205、p.208，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. continuous random variable = 连续随机变量
+· 2. normal distribution = 正态分布
+· 3. normal curve = 正态曲线
+· 4. standard normal distribution = 标准正态分布
+· 5. standardise = 标准化
+· 6. z-value / standardised value = z 值／标准化值
+· 7. $\Phi(z)$ / $\phi(z)$ = 标准正态分布函数／密度函数
+· 8. probability density function (PDF) = 概率密度函数
+· 9. symmetry = 对称性
+· 10. inverse normal = 反查正态
+· 11. continuity correction = 连续性修正
+· 12. normal approximation = 正态近似
+· 13. modelling = 建模
+· 全部抄完后回看一遍：[[04_统计 S1#Ch8 The normal distribution 正态分布]]（本章共 13 条）
 20:00-21:00 应用数学
 格式训练 S1 Ch8 正态分布（§8.1、§8.2）
 · Ex 8A 题 1–6（约 19 分钟，p.191）
@@ -6208,8 +7036,22 @@
 15:15-16:15 纯数
 术语与格式 P2/3 Ch7 进阶代数 §7.1、§7.2、§7.3、§7.4
 · 速览 §7.1 假分式、§7.2 部分分式、§7.3 二项式展开 (1+x)^n（n 非正整数）、§7.4 二项式展开 (a+x)^n（n 非正整数）（p.166、p.168、p.174、p.177，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. rational function = 有理函数
+· 2. proper / improper algebraic fraction = 真／假分式
+· 3. partial fractions = 部分分式
+· 4. decompose / decomposition = 分解
+· 5. repeated linear factor = 重线性因式
+· 6. irreducible quadratic factor = 不可约二次因式
+· 7. equating coefficients = 比较系数
+· 8. cover-up method = 遮盖法
+· 9. binomial expansion = 二项式展开
+· 10. general binomial theorem = 广义二项式定理
+· 11. ascending powers = 升幂
+· 12. validity / range of validity = 成立范围
+· 13. identically equal ($\equiv$) = 恒等于
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch7 Further algebra 进阶代数（P3）]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -6227,8 +7069,8 @@
 15:15-16:15 物理
 术语与格式 Phy Ch15 原子结构 §15.9、§15.10、§15.11、§15.12
 · 速览 §15.9 放射性衰变方程、§15.10 基本粒子、§15.11 粒子家族、§15.12 再看 β 衰变（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 22 条）：[[06_物理#Ch15 Atomic structure 原子结构]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -6306,8 +7148,13 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch17 变力作用下的直线运动 §17.1、§17.2
 · 速览 §17.1 加速度关于时间、§17.2 加速度关于位移（p.398、p.403，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 4 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. variable force = 变力
+· 2. separable differential equation = 可分离变量的微分方程
+· 3. terminal velocity = 极限速度 / 收尾速度
+· 4. initial condition = 初始条件
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch17 Linear motion under a variable force 变力作用下的直线运动（9231 §3.5，Paper 3；只在 FM 深入）]]（本章共 4 条）</t>
         </is>
       </c>
     </row>
@@ -6319,8 +7166,8 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch7 进阶代数 §7.5
 · 速览 §7.5 部分分式与二项式展开（p.179，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[02_纯数学 P2-3#Ch7 Further algebra 进阶代数（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 章末复习 P2/3 Ch7 进阶代数
 · 章末复习题 End-of-chapter review p.182，限时 30 分钟
 · 本章要会：部分分式、除法算式与余数定理、代数式的组合运算
@@ -6350,8 +7197,18 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch8 进阶微积分 §8.1、§8.2、§8.3、§8.4
 · 速览 §8.1 tan⁻¹x 的导数、§8.2 1/(x²+a²) 的积分、§8.3 k f′(x)/f(x) 的积分、§8.4 换元积分法（p.186、p.187、p.189、p.191，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. inverse tangent = 反正切
+· 2. integration by substitution = 换元积分法
+· 3. integration by parts = 分部积分法
+· 4. recognise the form $kf'(x)/f(x)$ = 识别 $kf'/f$ 型
+· 5. partial fractions in integration = 用部分分式积分
+· 6. limits of integration = 积分上下限
+· 7. change the limits = 换限
+· 8. dummy variable = 哑变量
+· 9. integrand = 被积函数
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch8 Further calculus 进阶微积分（P3）]]（本章共 9 条）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -6361,8 +7218,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch15 原子结构 §15.13
 · 速览 §15.13 另一种核力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 22 条）：[[06_物理#Ch15 Atomic structure 原子结构]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -6443,8 +7300,8 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 术语与格式 Phy P1 实验技能 §P1.1–P1.5、§P1.6–P1.11
 · 速览 §P1.1–P1.5 实验操作与不确定度（一）、§P1.6–P1.11 数据处理与误差合成（二）（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡：打开 [[06_物理#P1]] 的术语表，把英文说法抄进 Anki（牌组「数理术语」，只抄术语，不抄公式），抄完打勾</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -6515,8 +7372,16 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch18 动量（进阶） §18.1、§18.2
 · 速览 §18.1 冲量与动量守恒、§18.2 斜碰撞及其他例子（p.411、p.417，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. coefficient of restitution = 恢复系数
+· 2. Newton's experimental law = 牛顿实验定律
+· 3. impulse = 冲量
+· 4. perfectly elastic = 完全弹性
+· 5. inelastic = 完全非弹性
+· 6. direct / oblique impact = 正碰 / 斜碰
+· 7. line of centres = 连心线
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch18 Momentum 动量（进阶）（9231 §3.6，Paper 3；含碰撞与恢复系数）]]（本章共 7 条）</t>
         </is>
       </c>
     </row>
@@ -6528,8 +7393,8 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch8 进阶微积分 §8.5、§8.6、§8.7
 · 速览 §8.5 部分分式在积分中的应用、§8.6 分部积分法、§8.7 进阶积分技巧（p.194、p.197、p.201，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 9 条）：[[02_纯数学 P2-3#Ch8 Further calculus 进阶微积分（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 格式训练 P2/3 Ch8 进阶微积分（§8.5、§8.6）
 · Ex 8E 题 1–6（约 19 分钟，p.196）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -6545,8 +7410,18 @@
 21:00-22:15 物理
 术语与格式 Phy Ch16 圆周运动 §16.1、§16.2、§16.3、§16.4
 · 速览 §16.1 描述圆周运动、§16.2 弧度、§16.3 恒定速率、变化速度、§16.4 角速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. radian = 弧度
+· 2. angular displacement = 角位移
+· 3. angular speed = 角速度
+· 4. period = 周期
+· 5. frequency = 频率
+· 6. centripetal acceleration = 向心加速度
+· 7. centripetal force = 向心力
+· 8. tangent = 切线
+· 9. conical pendulum = 锥摆
+· 全部抄完后回看一遍：[[06_物理#Ch16 Circular motion 圆周运动]]（本章共 9 条）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -6631,8 +7506,21 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch9 向量 §9.1、§9.2、§9.3、§9.4
 · 速览 §9.1 位移（平移）向量、§9.2 位置向量、§9.3 数量积、§9.4 直线的向量方程（p.211、p.220、p.225、p.231，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. displacement vector = 位移向量
+· 2. position vector = 位置向量
+· 3. magnitude (modulus) of a vector = 向量的模
+· 4. unit vector = 单位向量
+· 5. direction vector = 方向向量
+· 6. parameter = 参数
+· 7. scalar product / dot product = 数量积／点积
+· 8. parallel vectors = 平行向量
+· 9. perpendicular vectors = 垂直向量
+· 10. skew lines = 异面直线
+· 11. intersection = 交点
+· 12. vector equation of a line = 直线的向量方程
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch9 Vectors 向量（P3）]]（本章共 12 条）</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -6717,8 +7605,8 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 术语与格式 Phy Ch16 圆周运动 §16.5、§16.6、§16.7
 · 速览 §16.5 向心力、§16.6 计算加速度与力、§16.7 向心力的来源（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 9 条）：[[06_物理#Ch16 Circular motion 圆周运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -6790,8 +7678,15 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch8 连续随机变量 §8.1、§8.2、§8.3、§8.4
 · 速览 §8.1 概率密度函数、§8.2 累积分布函数、§8.3 计算连续随机变量的 E(g(X))、§8.4 由 Y=g(X) 求 pdf 与 cdf（p.155、p.161、p.174、p.178，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. probability density function (PDF) = 概率密度函数
+· 2. cumulative distribution function (CDF) = 累积分布函数
+· 3. piecewise = 分段的
+· 4. expectation of a function of $X$ = $E(g(X))$
+· 5. percentile = 百分位数
+· 6. variance = 方差
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch8 Continuous random variables 连续随机变量（9231 §4.1，Paper 4；只在 FM 考）]]（本章共 6 条）</t>
         </is>
       </c>
     </row>
@@ -6809,8 +7704,8 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 术语与格式 P2/3 Ch9 向量 §9.5
 · 速览 §9.5 两直线的交点（p.236，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[02_纯数学 P2-3#Ch9 Vectors 向量（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -6840,8 +7735,22 @@
 15:15-16:15 纯数
 术语与格式 P2/3 Ch10 微分方程 §10.1、§10.2
 · 速览 §10.1 分离变量法、§10.2 由实际问题建立微分方程（p.245、p.252，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. differential equation = 微分方程
+· 2. first order = 一阶
+· 3. separable = 可分离变量
+· 4. separating the variables = 分离变量
+· 5. general solution = 通解
+· 6. particular solution = 特解
+· 7. initial condition = 初始条件
+· 8. arbitrary constant = 任意常数
+· 9. rate of change = 变化率
+· 10. proportional to = 与……成正比
+· 11. exponential growth / decay = 指数增长／衰减
+· 12. Newton's law of cooling/heating = 牛顿冷却（加热）定律
+· 13. limiting value = 极限值
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch10 Differential equations 微分方程（P3）]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -6851,8 +7760,20 @@
 21:00-22:15 物理
 术语与格式 Phy Ch17 引力场 §17.1、§17.2、§17.3、§17.4
 · 速览 §17.1 表示引力场、§17.2 重力场强度 g、§17.3 引力场中的能量、§17.4 引力势（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. gravitational field = 引力场
+· 2. field line = 场线
+· 3. Newton's law of gravitation = 万有引力定律
+· 4. gravitational constant = 引力常量
+· 5. gravitational field strength = 重力场强度
+· 6. gravitational potential = 引力势
+· 7. gravitational potential energy = 引力势能
+· 8. inverse square law = 平方反比定律
+· 9. orbital period = 轨道周期
+· 10. geostationary orbit = 地球同步轨道
+· 11. centripetal force = 向心力
+· 全部抄完后回看一遍：[[06_物理#Ch17 Gravitational fields 引力场]]（本章共 11 条）</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -6946,8 +7867,26 @@
 21:00-22:15 纯数
 术语与格式 P2/3 Ch11 复数 §11.1、§11.2、§11.3、§11.4
 · 速览 §11.1 虚数、§11.2 复数、§11.3 复平面、§11.4 解方程（p.267、p.269、p.273、p.283，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 17 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. imaginary unit $\mathrm{i}$ = 虚数单位
+· 2. imaginary number = 虚数
+· 3. complex number = 复数
+· 4. Cartesian form = 笛卡尔形式
+· 5. real part / imaginary part = 实部／虚部
+· 6. conjugate ($z^*$) = 共轭
+· 7. modulus ($\lvert z\rvert$) = 模
+· 8. argument ($\arg z$) = 辐角
+· 9. principal argument = 主辐角
+· 10. Argand diagram = 阿冈图
+· 11. modulus-argument form = 模-辐角形式
+· 12. polar form = 极坐标形式
+· 13. exponential form = 指数形式
+· 14. locus (plural loci) = 轨迹
+· 15. perpendicular bisector = 垂直平分线
+· 16. conjugate pairs = 共轭对
+· 17. cube roots of unity = 单位立方根
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch11 Complex numbers 复数（P3）]]（本章共 17 条）</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -6957,8 +7896,8 @@
 21:00-22:15 物理
 术语与格式 Phy Ch17 引力场 §17.5、§17.6、§17.7
 · 速览 §17.5 在引力下运行、§17.6 轨道周期、§17.7 绕地球运行（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 11 条）：[[06_物理#Ch17 Gravitational fields 引力场]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -6982,8 +7921,17 @@
 14:00-15:00 进阶数学
 术语与格式 FM Ch9 推断统计 §9.1、§9.2、§9.3、§9.4
 · 速览 §9.1 t 分布、§9.2 两均值之差的假设检验、§9.3 配对 t 检验、§9.4 小样本均值的置信区间（p.190、p.197、p.203、p.207，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 8 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. $t$-distribution = $t$ 分布
+· 2. degrees of freedom = 自由度
+· 3. pooled estimate of variance = 合并方差估计
+· 4. paired sample = 配对样本
+· 5. confidence interval = 置信区间
+· 6. test statistic = 检验统计量
+· 7. null hypothesis / alternative hypothesis = 原假设 / 备择假设
+· 8. critical region = 拒绝域 / 临界区域
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch9 Inferential statistics 推断统计（9231 §4.2，Paper 4；只在 FM 考）]]（本章共 8 条）
 20:00-21:00 进阶数学
 格式训练 FM Ch9 推断统计（§9.1、§9.2）
 · Ex 9A 题 全部（约 25 分钟，p.192）
@@ -7055,8 +8003,8 @@
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 术语与格式 P2/3 Ch11 复数 §11.5
 · 速览 §11.5 轨迹（p.288，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 17 条）：[[02_纯数学 P2-3#Ch11 Complex numbers 复数（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -7093,8 +8041,8 @@
 14:00-15:00 进阶数学
 术语与格式 FM Ch9 推断统计 §9.5
 · 速览 §9.5 均值之差的置信区间（p.210，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 8 条）：[[05_进阶数学 FM#Ch9 Inferential statistics 推断统计（9231 §4.2，Paper 4；只在 FM 考）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 20:00-21:00 进阶数学
 章末复习 FM Ch9 推断统计
 · 章末复习题 End-of-chapter review p.219，限时 30 分钟
@@ -7114,8 +8062,16 @@
 20:00-21:00 进阶数学
 术语与格式 FM Ch10 卡方检验 §10.1、§10.2、§10.3、§10.4
 · 速览 §10.1 建立假设、§10.2 离散分布的拟合优度、§10.3 连续分布的拟合优度、§10.4 列联表检验相关性（p.221、p.227、p.231、p.237，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果</t>
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. goodness of fit = 拟合优度
+· 2. contingency table = 列联表
+· 3. expected frequency = 期望频数
+· 4. observed frequency = 观测频数
+· 5. degrees of freedom = 自由度
+· 6. independence = 独立性
+· 7. Yates' correction = Yates 连续性修正
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch10 Chi-squared tests 卡方检验（9231 §4.3，Paper 4；只在 FM 考）]]（本章共 7 条）</t>
         </is>
       </c>
     </row>
@@ -7145,8 +8101,23 @@
 14:00-15:00 物理
 术语与格式 Phy Ch18 振动 §18.1、§18.2、§18.3、§18.4
 · 速览 §18.1 自由振动与受迫振动、§18.2 观察振动、§18.3 描述振动、§18.4 简谐运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 抄下这些术语的英文说法，立刻入 Anki（只抄术语，不抄公式）
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. oscillation = 振动
+· 2. free oscillation = 自由振动
+· 3. forced oscillation = 受迫振动
+· 4. simple harmonic motion = 简谐运动
+· 5. displacement = 位移
+· 6. amplitude = 振幅
+· 7. period = 周期
+· 8. frequency = 频率
+· 9. angular frequency = 角频率
+· 10. damping = 阻尼
+· 11. critical damping = 临界阻尼
+· 12. natural frequency = 固有频率
+· 13. resonance = 共振
+· 14. driving frequency = 驱动频率
+· 全部抄完后回看一遍：[[06_物理#Ch18 Oscillations 振动]]（本章共 14 条）
 15:15-16:15 物理
 格式训练 Phy Ch18 振动（§18.1、§18.2）
 · 节末 Questions 题 全部（约 25 分钟，p.502）

--- a/StudyCompanionAndroid/assets/Schedule.xlsx
+++ b/StudyCompanionAndroid/assets/Schedule.xlsx
@@ -872,13 +872,7 @@
 术语与格式 Phy Ch1 运动学 §1.5、§1.6、§1.7、§1.8
 · 速览 §1.5 位移的合成、§1.6 速度的合成、§1.7 矢量的减法、§1.8 其他标量与矢量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch1 Kinematics 运动学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
-格式训练 Phy Ch1 运动学（§1.5、§1.6）
-· 节末 Questions 题 全部（约 25 分钟，p.28）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.30）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch1 Kinematics 运动学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -889,13 +883,7 @@
 术语与格式 P1 Ch1 二次方程 §1.5、§1.6、§1.7、§1.8
 · 速览 §1.5 更复杂的二次方程、§1.6 二次函数的最大值与最小值、§1.7 二次不等式、§1.8 二次方程根的个数（判别式）（p.15、p.17、p.21、p.24，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch1 Quadratics 二次方程]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
-格式训练 P1 Ch1 二次方程（§1.5、§1.6）
-· Ex 1E 题 1–5（约 18 分钟，p.16）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 1F 题 1–12（约 28 分钟，p.20）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch1 Quadratics 二次方程]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -903,12 +891,13 @@
           <t>10月22日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch1 运动学
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：用位移—时间与速度—时间图描述运动，区分标量与矢量
-· 过关自测：能画 v–t 图并求面积=位移、斜率=加速度；能分辨 x、v、a 三个量；Chapter 1 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 Phy Ch1 运动学（§1.5、§1.6）
+· 节末 Questions 题 全部（约 25 分钟，p.28）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.30）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -967,6 +956,33 @@
           <t>10月26日 周一
 ────────────
 21:00-22:15 纯数
+格式训练 P1 Ch1 二次方程（§1.5、§1.6）
+· Ex 1E 题 1–5（约 18 分钟，p.16）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1F 题 1–12（约 28 分钟，p.20）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>10月27日 周二
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch1 运动学
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：用位移—时间与速度—时间图描述运动，区分标量与矢量
+· 过关自测：能画 v–t 图并求面积=位移、斜率=加速度；能分辨 x、v、a 三个量；Chapter 1 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>10月28日 周三
+────────────
+21:00-22:15 纯数
 格式训练 P1 Ch1 二次方程（§1.7、§1.8）
 · Ex 1G 题 1–7（约 20 分钟，p.23）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -976,9 +992,9 @@
 · Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>10月27日 周二
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>10月29日 周四
 ────────────
 21:00-22:15 物理
 术语与格式 Phy Ch2 加速运动 §2.1、§2.2、§2.3、§2.4
@@ -998,31 +1014,6 @@
 · 11. time of flight = 飞行时间
 · 12. horizontal component = 水平分量
 · 全部抄完后回看一遍：[[06_物理#Ch2 Accelerated motion 加速运动]]（本章共 12 条）</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>10月28日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P1 Ch1 二次方程 §1.9
-· 速览 §1.9 直线与二次曲线的交点（p.27，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch1 Quadratics 二次方程]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>10月29日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch2 加速运动（§2.1、§2.2）
-· 节末 Questions 题 全部（约 25 分钟，p.41）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.42）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1144,25 +1135,34 @@
           <t>7月1日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-格式训练 Phy Ch18 振动（§18.3、§18.4）
-· 节末 Questions 题 全部（约 25 分钟，p.506）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.510）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
+章末复习 Phy P1 实验技能
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：测量不确定度、作图求斜率、误差分析、实验设计
+· 过关自测：能给结果配上绝对/相对不确定度；能画最佳拟合直线并求斜率；能识别系统误差与随机误差；P1.1–P1.11 全部读一遍并做笔记
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
-术语与格式 Phy Ch18 振动 §18.5、§18.6、§18.7、§18.8
-· 速览 §18.5 简谐运动的图像表示、§18.6 频率与角频率、§18.7 简谐运动方程、§18.8 简谐运动中的能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch18 Oscillations 振动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+术语与格式 Phy Ch16 圆周运动 §16.1、§16.2、§16.3、§16.4
+· 速览 §16.1 描述圆周运动、§16.2 弧度、§16.3 恒定速率、变化速度、§16.4 角速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. radian = 弧度
+· 2. angular displacement = 角位移
+· 3. angular speed = 角速度
+· 4. period = 周期
+· 5. frequency = 频率
+· 6. centripetal acceleration = 向心加速度
+· 7. centripetal force = 向心力
+· 8. tangent = 切线
+· 9. conical pendulum = 锥摆
+· 全部抄完后回看一遍：[[06_物理#Ch16 Circular motion 圆周运动]]（本章共 9 条）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>7月2日 周五 ◆暑假
 ────────────
-14:00-15:00 学术英语
+14:00-15:15 学术英语
 EAP 强化 05 presentation 限时演练与同伴反馈
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：自己 EAP 24 的 5 张幻灯片（或重做一版）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -1170,7 +1170,7 @@
 · ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-45 presentation 限时演练与同伴反馈」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
 · ✓ 合格线（自己判定）：3 条反馈具体可执行（能直接改下一次的动作）
 · 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
-15:15-16:15 学术英语
+15:15-16:30 学术英语
 EAP 强化 06 EAP 真题套卷（读 + 写）限时
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：剑桥雅思真题 15–20 里的一整套（Reading + Writing）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -1206,7 +1206,7 @@
           <t>7月4日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch11 ｜ Phy Ch18 ｜ FM Ch10
+· 回顾：P2/3 Ch8 ｜ Phy Ch16 ｜ FM Ch10
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -1231,15 +1231,31 @@
           <t>7月5日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-真题精练 9709 P3 2020 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
+术语与格式 P2/3 Ch9 向量 §9.1、§9.2、§9.3、§9.4
+· 速览 §9.1 位移（平移）向量、§9.2 位置向量、§9.3 数量积、§9.4 直线的向量方程（p.211、p.220、p.225、p.231，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. displacement vector = 位移向量
+· 2. position vector = 位置向量
+· 3. magnitude (modulus) of a vector = 向量的模
+· 4. unit vector = 单位向量
+· 5. direction vector = 方向向量
+· 6. parameter = 参数
+· 7. scalar product / dot product = 数量积／点积
+· 8. parallel vectors = 平行向量
+· 9. perpendicular vectors = 垂直向量
+· 10. skew lines = 异面直线
+· 11. intersection = 交点
+· 12. vector equation of a line = 直线的向量方程
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch9 Vectors 向量（P3）]]（本章共 12 条）
 15:15-16:15 纯数
-真题精练 9709 P1 2021 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
+格式训练 P2/3 Ch9 向量（§9.1、§9.2）
+· Ex 9A 题 1–7（约 20 分钟，p.218）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9B 题 1–13（约 30 分钟，p.223）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -1247,18 +1263,18 @@
           <t>7月6日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-格式训练 Phy Ch18 振动（§18.5、§18.6）
-· 节末 Questions 题 全部（约 25 分钟，p.511）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.514）
+格式训练 Phy Ch16 圆周运动（§16.1、§16.2）
+· 节末 Questions 题 全部（约 25 分钟，p.454）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.455）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
 15:15-16:15 物理
-格式训练 Phy Ch18 振动（§18.7、§18.8）
-· 节末 Questions 题 全部（约 25 分钟，p.516）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.522）
+格式训练 Phy Ch16 圆周运动（§16.3、§16.4）
+· 节末 Questions 题 全部（约 25 分钟，p.457）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.458）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -1269,15 +1285,18 @@
           <t>7月7日 周三 ◆暑假
 ────────────
 14:00-15:00 纯数
-真题精练 9709 P3 2021 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
+格式训练 P2/3 Ch9 向量（§9.3、§9.4）
+· Ex 9C 题 1–10（约 25 分钟，p.230）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9D 题 1–13（约 30 分钟，p.235）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 纯数
-真题精练 9709 P1 2022 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
+术语与格式 P2/3 Ch9 向量 §9.5
+· 速览 §9.5 两直线的交点（p.236，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[02_纯数学 P2-3#Ch9 Vectors 向量（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1285,24 +1304,25 @@
           <t>7月8日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-术语与格式 Phy Ch18 振动 §18.9、§18.10
-· 速览 §18.9 阻尼振动、§18.10 共振（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch18 Oscillations 振动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
+术语与格式 Phy Ch16 圆周运动 §16.5、§16.6、§16.7
+· 速览 §16.5 向心力、§16.6 计算加速度与力、§16.7 向心力的来源（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 9 条）：[[06_物理#Ch16 Circular motion 圆周运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 15:15-16:15 物理
-章末复习 Phy Ch18 振动
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：简谐运动、阻尼与共振
-· 过关自测：能默写 a=−ω²x 与 x=A cos ωt；能算周期 T=2π/ω；Chapter 18 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 Phy Ch16 圆周运动（§16.5、§16.6）
+· 节末 Questions 题 全部（约 25 分钟，p.461）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.464）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>7月9日 周五 ◆暑假
 ────────────
-14:00-15:00 学术英语
+14:00-15:15 学术英语
 EAP 强化 07 EAP 真题套卷（听 + 说）限时
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：剑桥雅思真题一整套（Listening + Speaking）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -1310,7 +1330,7 @@
 · ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-47 EAP 真题套卷（听 + 说）限时」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
 · ✓ 合格线（自己判定）：记录听力正确数与口语停顿次数；听力错题同样归因分类
 · 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
-15:15-16:15 学术英语
+15:15-16:30 学术英语
 EAP 强化 08 学术词汇综合自测（AWL 全表）
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：Anki 里 AWL 全部牌组（关掉提示，纯默写）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -1347,7 +1367,7 @@
           <t>7月11日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：Phy Ch18 ｜ FM Ch11
+· 回顾：P2/3 Ch9 ｜ Phy Ch16 ｜ FM Ch11
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -1364,17 +1384,31 @@
           <t>7月12日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-真题精练 9709 P3 2022 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-15:15-16:15 进阶数学
-章末复习 FM Ch11 非参数检验
-· 章末复习题 End-of-chapter review p.277，限时 30 分钟
-· 本章要会：能判断何时该用非参数检验并正确查临界值
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+章末复习 P2/3 Ch9 向量
+· 章末复习题 End-of-chapter review p.240，限时 30 分钟
+· 本章要会：三维向量运算、数量积、直线与平面的向量方程、夹角与交点
+· 过关自测：能默写直线与平面的向量方程；能求两直线夹角与交点；Ex 9A–9E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 纯数
+术语与格式 P2/3 Ch10 微分方程 §10.1、§10.2
+· 速览 §10.1 分离变量法、§10.2 由实际问题建立微分方程（p.245、p.252，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. differential equation = 微分方程
+· 2. first order = 一阶
+· 3. separable = 可分离变量
+· 4. separating the variables = 分离变量
+· 5. general solution = 通解
+· 6. particular solution = 特解
+· 7. initial condition = 初始条件
+· 8. arbitrary constant = 任意常数
+· 9. rate of change = 变化率
+· 10. proportional to = 与……成正比
+· 11. exponential growth / decay = 指数增长／衰减
+· 12. Newton's law of cooling/heating = 牛顿冷却（加热）定律
+· 13. limiting value = 极限值
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch10 Differential equations 微分方程（P3）]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1382,58 +1416,65 @@
           <t>7月13日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-术语与格式 Phy Ch19 热物理 §19.1、§19.2、§19.3、§19.4
-· 速览 §19.1 物态变化、§19.2 能量变化、§19.3 内能、§19.4 温度的含义（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. internal energy = 内能
-· 2. temperature = 温度
-· 3. thermal equilibrium = 热平衡
-· 4. absolute zero = 绝对零度
-· 5. Kelvin scale = 开尔文温标
-· 6. specific heat capacity = 比热容
-· 7. specific latent heat = 比潜热
-· 8. latent heat of fusion = 熔化潜热
-· 9. latent heat of vaporisation = 汽化潜热
-· 10. sublimation = 升华
-· 11. evaporation = 蒸发
-· 12. thermometer = 温度计
-· 13. thermocouple = 热电偶
-· 14. work done by a gas = 气体做功
-· 全部抄完后回看一遍：[[06_物理#Ch19 Thermal physics 热物理]]（本章共 14 条）
+章末复习 Phy Ch16 圆周运动
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：圆周运动、向心加速度、转动惯量概念
+· 过关自测：能默写 a=v²/r 与 F=mv²/r；能分析竖直圆周运动的临界点；Chapter 16 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
-格式训练 Phy Ch19 热物理（§19.1、§19.2）
-· 节末 Questions 题 全部（约 25 分钟，p.543）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.544）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 Phy Ch17 引力场 §17.1、§17.2、§17.3、§17.4
+· 速览 §17.1 表示引力场、§17.2 重力场强度 g、§17.3 引力场中的能量、§17.4 引力势（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. gravitational field = 引力场
+· 2. field line = 场线
+· 3. Newton's law of gravitation = 万有引力定律
+· 4. gravitational constant = 引力常量
+· 5. gravitational field strength = 重力场强度
+· 6. gravitational potential = 引力势
+· 7. gravitational potential energy = 引力势能
+· 8. inverse square law = 平方反比定律
+· 9. orbital period = 轨道周期
+· 10. geostationary orbit = 地球同步轨道
+· 11. centripetal force = 向心力
+· 全部抄完后回看一遍：[[06_物理#Ch17 Gravitational fields 引力场]]（本章共 11 条）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>7月14日 周三 ◆暑假
 ────────────
-14:00-15:00 进阶数学
-术语与格式 FM Ch12 概率母函数 §12.1、§12.2、§12.3、§12.4
-· 速览 §12.1 概率母函数、§12.2 用 pgf 求 E(X) 与 Var(X)、§12.3 独立随机变量之和、§12.4 三个及以上随机变量（p.280、p.287、p.292、p.298，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. probability generating function (PGF) = 概率母函数
-· 2. discrete uniform distribution = 离散均匀分布
-· 3. geometric distribution = 几何分布
-· 4. Poisson distribution = 泊松分布
-· 5. independent random variables = 独立随机变量
-· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch12 Probability generating functions 概率母函数（9231 §4.5，Paper 4；只在 FM 考）]]（本章共 5 条）
-15:15-16:15 进阶数学
-格式训练 FM Ch12 概率母函数（§12.1、§12.2）
-· Ex 12A 题 全部（约 25 分钟，p.282）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 12B 题 全部（约 25 分钟，p.289）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+14:00-15:00 纯数
+章末复习 P2/3 Ch10 微分方程
+· 章末复习题 End-of-chapter review p.262，限时 30 分钟
+· 本章要会：识别并求解一阶可分离变量微分方程、用初始条件定常数
+· 过关自测：能判断方程是否可分离变量；Ex 10A–10B 错题清零；能完整写出「分离→积分→代初值→写解」四步
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 纯数
+术语与格式 P2/3 Ch11 复数 §11.1、§11.2、§11.3、§11.4
+· 速览 §11.1 虚数、§11.2 复数、§11.3 复平面、§11.4 解方程（p.267、p.269、p.273、p.283，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 17 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. imaginary unit $\mathrm{i}$ = 虚数单位
+· 2. imaginary number = 虚数
+· 3. complex number = 复数
+· 4. Cartesian form = 笛卡尔形式
+· 5. real part / imaginary part = 实部／虚部
+· 6. conjugate ($z^*$) = 共轭
+· 7. modulus ($\lvert z\rvert$) = 模
+· 8. argument ($\arg z$) = 辐角
+· 9. principal argument = 主辐角
+· 10. Argand diagram = 阿冈图
+· 11. modulus-argument form = 模-辐角形式
+· 12. polar form = 极坐标形式
+· 13. exponential form = 指数形式
+· 14. locus (plural loci) = 轨迹
+· 15. perpendicular bisector = 垂直平分线
+· 16. conjugate pairs = 共轭对
+· 17. cube roots of unity = 单位立方根
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch11 Complex numbers 复数（P3）]]（本章共 17 条）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1441,25 +1482,28 @@
           <t>7月15日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
-格式训练 Phy Ch19 热物理（§19.3、§19.4）
-· 节末 Questions 题 全部（约 25 分钟，p.551）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.552）
+格式训练 Phy Ch17 引力场（§17.1、§17.2）
+· 节末 Questions 题 全部（约 25 分钟，p.480）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.482）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
 15:15-16:15 物理
-术语与格式 Phy Ch19 热物理 §19.5、§19.6
-· 速览 §19.5 温度计、§19.6 计算能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch19 Thermal physics 热物理]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 Phy Ch17 引力场（§17.3、§17.4）
+· 节末 Questions 题 全部（约 25 分钟，p.484）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.486）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>7月16日 周五 ◆暑假
 ────────────
-14:00-15:00 学术英语
+14:00-15:15 学术英语
 EAP 强化 09 个人陈述 + 面试问答演练
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：EAP 40 定稿的 PS；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -1467,7 +1511,7 @@
 · ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-49 个人陈述 + 面试问答演练」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
 · ✓ 合格线（自己判定）：2 分钟能讲完；5 个问题都能答满 30 秒且不跑题
 · 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
-15:15-16:15 学术英语
+15:15-16:30 学术英语
 EAP 强化 10 学年总结：错题 / 弱项清单与下阶段目标
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：全年错题本 + EAP 全部笔记 + 雅思模考曲线；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -1482,13 +1526,149 @@
           <t>7月17日 周六 ◆暑假
 ────────────
 14:00-15:00 进阶数学
+章末复习 FM Ch11 非参数检验
+· 章末复习题 End-of-chapter review p.277，限时 30 分钟
+· 本章要会：能判断何时该用非参数检验并正确查临界值
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+20:00-21:00 进阶数学
+术语与格式 FM Ch12 概率母函数 §12.1、§12.2、§12.3、§12.4
+· 速览 §12.1 概率母函数、§12.2 用 pgf 求 E(X) 与 Var(X)、§12.3 独立随机变量之和、§12.4 三个及以上随机变量（p.280、p.287、p.292、p.298，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. probability generating function (PGF) = 概率母函数
+· 2. discrete uniform distribution = 离散均匀分布
+· 3. geometric distribution = 几何分布
+· 4. Poisson distribution = 泊松分布
+· 5. independent random variables = 独立随机变量
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch12 Probability generating functions 概率母函数（9231 §4.5，Paper 4；只在 FM 考）]]（本章共 5 条）</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>7月18日 周日 ◆暑假
+────────────
+14:00-15:00 复习/测试
+· 回顾：P2/3 Ch11 ｜ Phy Ch17 ｜ FM Ch12
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+格式训练 FM Ch12 概率母函数（§12.1、§12.2）
+· Ex 12A 题 全部（约 25 分钟，p.282）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 12B 题 全部（约 25 分钟，p.289）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>7月19日 周一 ◆暑假
+────────────
+14:00-15:00 纯数
+格式训练 P2/3 Ch11 复数（§11.1、§11.2）
+· Ex 11A 题 1–6（约 19 分钟，p.269）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11B 题 1–10（约 25 分钟，p.272）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
+格式训练 P2/3 Ch11 复数（§11.3、§11.4）
+· Ex 11C 题 1–12（约 28 分钟，p.282）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 11D 题 1–10（约 25 分钟，p.288）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>7月20日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch17 引力场 §17.5、§17.6、§17.7
+· 速览 §17.5 在引力下运行、§17.6 轨道周期、§17.7 绕地球运行（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 11 条）：[[06_物理#Ch17 Gravitational fields 引力场]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
+15:15-16:15 物理
+格式训练 Phy Ch17 引力场（§17.5、§17.6）
+· 节末 Questions 题 全部（约 25 分钟，p.488）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.490）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>7月21日 周三 ◆暑假
+────────────
+14:00-15:00 纯数
+术语与格式 P2/3 Ch11 复数 §11.5
+· 速览 §11.5 轨迹（p.288，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 17 条）：[[02_纯数学 P2-3#Ch11 Complex numbers 复数（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
+15:15-16:15 纯数
+章末复习 P2/3 Ch11 复数
+· 章末复习题 End-of-chapter review p.297，限时 30 分钟
+· 本章要会：复数四则运算、模与辐角、Argand 图、复数方程与几何意义
+· 过关自测：能默写 i²=−1、模与辐角定义；能把复数在 Argand 图上表示；Ex 11A–11E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>7月22日 周四 ◆暑假
+────────────
+14:00-15:00 物理
+章末复习 Phy Ch17 引力场
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：引力场、场强、引力势与轨道运动
+· 过关自测：能默写 F=GMm/r² 与 g=GM/r²；能区分场强与势；Chapter 17 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 物理
+术语与格式 Phy Ch18 振动 §18.1、§18.2、§18.3、§18.4
+· 速览 §18.1 自由振动与受迫振动、§18.2 观察振动、§18.3 描述振动、§18.4 简谐运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. oscillation = 振动
+· 2. free oscillation = 自由振动
+· 3. forced oscillation = 受迫振动
+· 4. simple harmonic motion = 简谐运动
+· 5. displacement = 位移
+· 6. amplitude = 振幅
+· 7. period = 周期
+· 8. frequency = 频率
+· 9. angular frequency = 角频率
+· 10. damping = 阻尼
+· 11. critical damping = 临界阻尼
+· 12. natural frequency = 固有频率
+· 13. resonance = 共振
+· 14. driving frequency = 驱动频率
+· 全部抄完后回看一遍：[[06_物理#Ch18 Oscillations 振动]]（本章共 14 条）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>7月23日 周五 ◆暑假
+────────────
+14:00-15:00 进阶数学
 章末复习 FM Ch12 概率母函数
 · 章末复习题 End-of-chapter review p.304，限时 30 分钟
 · 本章要会：能用 pgf 求均值、方差与独立和
 · 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-20:00-21:00 进阶数学
+15:15-16:15 进阶数学
 术语与格式 FM Ch19 双曲函数 §19.1、§19.2、§19.3、§19.4
 · 速览 §19.1 双曲函数的指数形式、§19.2 双曲恒等式、§19.3 反双曲函数、§19.4 反双曲函数的对数形式（p.432、p.438、p.440、p.442，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
@@ -1501,38 +1681,35 @@
 · 全部抄完后回看一遍：[[05_进阶数学 FM#Ch19 Hyperbolic functions 双曲函数（9231 §2.1，Paper 2；只在 FM 考）]]（本章共 5 条）</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>7月18日 周日 ◆暑假
-────────────
-14:00-15:00 复习/测试
-· 回顾：Phy Ch19 ｜ FM Ch19
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>7月24日 周六 ◆暑假
+────────────
+14:00-15:00 进阶数学
 格式训练 FM Ch19 双曲函数（§19.1、§19.2）
 · Ex 19A 题 全部（约 25 分钟，p.434）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 19B 题 全部（约 25 分钟，p.439）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>7月19日 周一 ◆暑假
-────────────
-14:00-15:00 进阶数学
+· Anki 术语卡复习 5 分钟
+20:00-21:00 进阶数学
 章末复习 FM Ch19 双曲函数
 · 章末复习题 End-of-chapter review p.446，限时 30 分钟
 · 本章要会：能默写双曲函数的指数定义与恒等式、反双曲函数对数形式
 · 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
 · 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 进阶数学
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>7月25日 周日 ◆暑假
+────────────
+14:00-15:00 复习/测试
+★ 暑期测试：P2/3 Ch6-8｜物理 Ch13-16
+· 限时作答后逐题订正，记录失分点
+20:00-21:00 进阶数学
 术语与格式 FM Ch20 矩阵 2 §20.1、§20.2、§20.3、§20.4
 · 速览 §20.1 特征值与特征向量、§20.2 矩阵代数、§20.3 对角化、§20.4 方程组（p.448、p.451、p.461、p.465，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
@@ -1547,42 +1724,84 @@
 · 全部抄完后回看一遍：[[05_进阶数学 FM#Ch20 Matrices 2 矩阵 2（9231 §2.2，Paper 2；只在 FM 考）]]（本章共 7 条）</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>7月20日 周二 ◆暑假
+    </row>
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>7月26日 周一 ◆暑假
+────────────
+14:00-15:00 纯数
+真题精练 9709 P1 2019 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 纯数
+真题精练 9709 P3 2019 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>7月27日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-章末复习 Phy Ch19 热物理
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：比热容、潜热、理想气体与热力学第一定律
-· 过关自测：能默写 Q=mcΔθ 与 Q=ml；能列 ΔU=Q+W；Chapter 19 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+格式训练 Phy Ch18 振动（§18.1、§18.2）
+· 节末 Questions 题 全部（约 25 分钟，p.502）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.504）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 物理
-术语与格式 Phy Ch20 理想气体 §20.1、§20.2、§20.3、§20.4
-· 速览 §20.1 气体的粒子模型、§20.2 解释压强、§20.3 测量气体、§20.4 玻意耳定律（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. ideal gas = 理想气体
-· 2. kinetic theory = 分子动理论
-· 3. mole = 摩尔
-· 4. Avogadro constant = 阿伏伽德罗常数
-· 5. molar gas constant = 摩尔气体常量
-· 6. Boltzmann constant = 玻尔兹曼常量
-· 7. equation of state = 状态方程
-· 8. Boyle's law = 玻意耳定律
-· 9. pressure law = 压强定律
-· 10. Charles's law = 查理定律
-· 11. root-mean-square speed = 均方根速率
-· 12. mean translational kinetic energy = 平均平动动能
-· 13. number density = 数密度
-· 14. elastic collision = 弹性碰撞
-· 全部抄完后回看一遍：[[06_物理#Ch20 Ideal gases 理想气体]]（本章共 14 条）</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>7月21日 周三 ◆暑假
+格式训练 Phy Ch18 振动（§18.3、§18.4）
+· 节末 Questions 题 全部（约 25 分钟，p.506）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.510）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>7月28日 周三 ◆暑假
+────────────
+14:00-15:00 纯数
+真题精练 9709 P1 2020 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 纯数
+真题精练 9709 P3 2020 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>7月29日 周四 ◆暑假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch18 振动 §18.5、§18.6、§18.7、§18.8
+· 速览 §18.5 简谐运动的图像表示、§18.6 频率与角频率、§18.7 简谐运动方程、§18.8 简谐运动中的能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch18 Oscillations 振动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
+15:15-16:15 物理
+格式训练 Phy Ch18 振动（§18.5、§18.6）
+· 节末 Questions 题 全部（约 25 分钟，p.511）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.514）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>7月30日 周五 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 格式训练 FM Ch20 矩阵 2（§20.1、§20.2）
@@ -1601,31 +1820,9 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>7月22日 周四 ◆暑假
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch20 理想气体（§20.1、§20.2）
-· 节末 Questions 题 全部（约 25 分钟，p.571）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.572）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-15:15-16:15 物理
-格式训练 Phy Ch20 理想气体（§20.3、§20.4）
-· 节末 Questions 题 全部（约 25 分钟，p.574）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.575）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>7月23日 周五 ◆暑假
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>7月31日 周六 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 术语与格式 FM Ch21 微分（进阶） §21.1、§21.2、§21.3、§21.4
@@ -1637,7 +1834,7 @@
 · 3. Maclaurin's series = 麦克劳林级数
 · 4. second derivative = 二阶导数
 · 全部抄完后回看一遍：[[05_进阶数学 FM#Ch21 Differentiation 微分（进阶）（9231 §2.3，Paper 2；只在 FM 考）]]（本章共 4 条）
-15:15-16:15 进阶数学
+20:00-21:00 进阶数学
 格式训练 FM Ch21 微分（进阶）（§21.1、§21.2）
 · Ex 21A 题 全部（约 25 分钟，p.475）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -1645,193 +1842,6 @@
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>7月24日 周六 ◆暑假
-────────────
-14:00-15:00 进阶数学
-章末复习 FM Ch21 微分（进阶）
-· 章末复习题 End-of-chapter review p.496，限时 30 分钟
-· 本章要会：能用隐函数/参数方程求导并写出 Maclaurin 展开
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-20:00-21:00 进阶数学
-术语与格式 FM Ch22 积分（进阶） §22.1、§22.2、§22.3、§22.4
-· 速览 §22.1 积分技巧、§22.2 递推公式、§22.3 弧长与表面积、§22.4 面积的极限（p.498、p.503、p.509、p.515，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. reduction formula = 递推公式
-· 2. completing the square = 配方
-· 3. arc length = 弧长
-· 4. surface area of revolution = 旋转曲面面积
-· 5. integration by parts = 分部积分
-· 6. substitution = 换元
-· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch22 Integration 积分（进阶）（9231 §2.4，Paper 2；只在 FM 考）]]（本章共 6 条）</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>7月25日 周日 ◆暑假
-────────────
-14:00-15:00 复习/测试
-★ 暑期测试：P2/3 Ch6-8｜物理 Ch13-16
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-格式训练 FM Ch22 积分（进阶）（§22.1、§22.2）
-· Ex 22A 题 全部（约 25 分钟，p.500）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 22B 题 全部（约 25 分钟，p.505）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>7月26日 周一 ◆暑假
-────────────
-14:00-15:00 进阶数学
-章末复习 FM Ch22 积分（进阶）
-· 章末复习题 End-of-chapter review p.523，限时 30 分钟
-· 本章要会：能选对积分技巧、用递推公式、求弧长与旋转面面积
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 进阶数学
-术语与格式 FM Ch23 复数（进阶） §23.1、§23.2、§23.3、§23.4
-· 速览 §23.1 棣莫弗定理、§23.2 正弦与余弦的幂、§23.3 单位根、§23.4 复数求和（p.525、p.529、p.532、p.537，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. de Moivre's theorem = 棣莫弗定理
-· 2. modulus–argument form = 模–辐角形式
-· 3. argument (principal value) = 辐角（主值）
-· 4. $n$th roots of unity = $n$ 次单位根
-· 5. conjugate = 共轭
-· 6. multiple angle = 多倍角
-· 7. $\mathrm{C}+iS$ method = $C+iS$ 求和法
-· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch23 Complex numbers 复数（进阶）（9231 §2.5，Paper 2；只在 FM 考）]]（本章共 7 条）</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>7月27日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch20 理想气体 §20.5、§20.6、§20.7、§20.8
-· 速览 §20.5 温度变化、§20.6 理想气体方程、§20.7 气体建模：动力学模型、§20.8 温度与分子能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch20 Ideal gases 理想气体]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
-15:15-16:15 物理
-格式训练 Phy Ch20 理想气体（§20.5、§20.6）
-· 节末 Questions 题 全部（约 25 分钟，p.577）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.580）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>7月28日 周三 ◆暑假
-────────────
-14:00-15:00 进阶数学
-格式训练 FM Ch23 复数（进阶）（§23.1、§23.2）
-· Ex 23A 题 全部（约 25 分钟，p.527）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 23B 题 全部（约 25 分钟，p.531）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-15:15-16:15 进阶数学
-章末复习 FM Ch23 复数（进阶）
-· 章末复习题 End-of-chapter review p.543，限时 30 分钟
-· 本章要会：能用 de Moivre 定理求幂、根与复数和
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>7月29日 周四 ◆暑假
-────────────
-14:00-15:00 物理
-章末复习 Phy Ch20 理想气体
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：理想气体状态方程与分子运动论
-· 过关自测：能默写 pV=nRT 与 pV=NkT；能解释压强与温度的微观意义；Chapter 20 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-15:15-16:15 物理
-术语与格式 Phy Ch21 匀强电场 §21.1、§21.2、§21.3、§21.4
-· 速览 §21.1 吸引与排斥、§21.2 电场概念、§21.3 电场强度、§21.4 电荷受到的力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. electric field = 电场
-· 2. electric field line = 电场线
-· 3. electric field strength = 电场强度
-· 4. uniform field = 匀强电场
-· 5. test charge = 试探电荷
-· 6. force on a charge = 电荷受力
-· 7. potential difference = 电势差
-· 8. N C⁻¹ = 牛每库仑
-· 9. V m⁻¹ = 伏每米
-· 10. parabolic path = 抛物线轨迹
-· 11. Coulomb's law = 库仑定律
-· 12. permittivity of free space = 真空介电常数
-· 13. electric potential = 电势
-· 14. electric potential energy = 电势能
-· 全部抄完后回看一遍：[[06_物理#Ch21 Uniform electric fields 匀强电场]]（本章共 14 条）</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>7月30日 周五 ◆暑假
-────────────
-14:00-15:00 进阶数学
-术语与格式 FM Ch24 微分方程（进阶） §24.1、§24.2、§24.3、§24.4
-· 速览 §24.1 一阶微分方程、§24.2 二阶微分方程：齐次情形、§24.3 二阶微分方程：非齐次情形、§24.4 微分方程的代换法（p.545、p.550、p.557、p.565，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. integrating factor = 积分因子
-· 2. complementary function (CF) = 余函数 / 互补函数
-· 3. particular integral (PI) = 特解 / 特积分
-· 4. auxiliary equation = 辅助方程
-· 5. general solution / particular solution = 通解 / 特解
-· 6. initial condition = 初始条件
-· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch24 Differential equations 微分方程（进阶）（9231 §2.6，Paper 2；只在 FM 考）]]（本章共 6 条）
-15:15-16:15 进阶数学
-格式训练 FM Ch24 微分方程（进阶）（§24.1、§24.2）
-· Ex 24A 题 全部（约 25 分钟，p.547）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 24B 题 全部（约 25 分钟，p.552）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>7月31日 周六 ◆暑假
-────────────
-14:00-15:00 进阶数学
-章末复习 FM Ch24 微分方程（进阶）
-· 章末复习题 End-of-chapter review p.575，限时 30 分钟
-· 本章要会：能解一阶与二阶（齐次/非齐次）微分方程
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-20:00-21:00 进阶数学
-真题精练 9231 FP1 2019 Paper 1
-· 进阶数学真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
@@ -1908,106 +1918,452 @@
           <t>8月1日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：Phy Ch21 ｜ FM Ch24
+· 回顾：Phy Ch18 ｜ FM Ch21
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
+章末复习 FM Ch21 微分（进阶）
+· 章末复习题 End-of-chapter review p.496，限时 30 分钟
+· 本章要会：能用隐函数/参数方程求导并写出 Maclaurin 展开
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>8月2日 周一 ◆暑假
+────────────
+14:00-15:00 纯数
+真题精练 9709 P1 2021 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 纯数
+真题精练 9709 P3 2021 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>8月3日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch18 振动（§18.7、§18.8）
+· 节末 Questions 题 全部（约 25 分钟，p.516）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.522）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+术语与格式 Phy Ch18 振动 §18.9、§18.10
+· 速览 §18.9 阻尼振动、§18.10 共振（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch18 Oscillations 振动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>8月4日 周三 ◆暑假
+────────────
+14:00-15:00 纯数
+真题精练 9709 P1 2022 Paper 1
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 纯数
+真题精练 9709 P3 2022 Paper 3
+· 纯数真题卷，限时 1 小时 50 分
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>8月5日 周四 ◆暑假
+────────────
+14:00-15:00 物理
+章末复习 Phy Ch18 振动
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：简谐运动、阻尼与共振
+· 过关自测：能默写 a=−ω²x 与 x=A cos ωt；能算周期 T=2π/ω；Chapter 18 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 物理
+术语与格式 Phy Ch19 热物理 §19.1、§19.2、§19.3、§19.4
+· 速览 §19.1 物态变化、§19.2 能量变化、§19.3 内能、§19.4 温度的含义（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. internal energy = 内能
+· 2. temperature = 温度
+· 3. thermal equilibrium = 热平衡
+· 4. absolute zero = 绝对零度
+· 5. Kelvin scale = 开尔文温标
+· 6. specific heat capacity = 比热容
+· 7. specific latent heat = 比潜热
+· 8. latent heat of fusion = 熔化潜热
+· 9. latent heat of vaporisation = 汽化潜热
+· 10. sublimation = 升华
+· 11. evaporation = 蒸发
+· 12. thermometer = 温度计
+· 13. thermocouple = 热电偶
+· 14. work done by a gas = 气体做功
+· 全部抄完后回看一遍：[[06_物理#Ch19 Thermal physics 热物理]]（本章共 14 条）</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>8月6日 周五 ◆暑假
+────────────
+14:00-15:00 进阶数学
+术语与格式 FM Ch22 积分（进阶） §22.1、§22.2、§22.3、§22.4
+· 速览 §22.1 积分技巧、§22.2 递推公式、§22.3 弧长与表面积、§22.4 面积的极限（p.498、p.503、p.509、p.515，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. reduction formula = 递推公式
+· 2. completing the square = 配方
+· 3. arc length = 弧长
+· 4. surface area of revolution = 旋转曲面面积
+· 5. integration by parts = 分部积分
+· 6. substitution = 换元
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch22 Integration 积分（进阶）（9231 §2.4，Paper 2；只在 FM 考）]]（本章共 6 条）
+15:15-16:15 进阶数学
+格式训练 FM Ch22 积分（进阶）（§22.1、§22.2）
+· Ex 22A 题 全部（约 25 分钟，p.500）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 22B 题 全部（约 25 分钟，p.505）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>8月7日 周六 ◆暑假
+────────────
+14:00-15:00 进阶数学
+章末复习 FM Ch22 积分（进阶）
+· 章末复习题 End-of-chapter review p.523，限时 30 分钟
+· 本章要会：能选对积分技巧、用递推公式、求弧长与旋转面面积
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+20:00-21:00 进阶数学
+术语与格式 FM Ch23 复数（进阶） §23.1、§23.2、§23.3、§23.4
+· 速览 §23.1 棣莫弗定理、§23.2 正弦与余弦的幂、§23.3 单位根、§23.4 复数求和（p.525、p.529、p.532、p.537，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 7 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. de Moivre's theorem = 棣莫弗定理
+· 2. modulus–argument form = 模–辐角形式
+· 3. argument (principal value) = 辐角（主值）
+· 4. $n$th roots of unity = $n$ 次单位根
+· 5. conjugate = 共轭
+· 6. multiple angle = 多倍角
+· 7. $\mathrm{C}+iS$ method = $C+iS$ 求和法
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch23 Complex numbers 复数（进阶）（9231 §2.5，Paper 2；只在 FM 考）]]（本章共 7 条）</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>8月8日 周日 ◆暑假
+────────────
+14:00-15:00 复习/测试
+· 回顾：Phy Ch19 ｜ FM Ch23
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+格式训练 FM Ch23 复数（进阶）（§23.1、§23.2）
+· Ex 23A 题 全部（约 25 分钟，p.527）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 23B 题 全部（约 25 分钟，p.531）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>8月9日 周一 ◆暑假
+────────────
+14:00-15:00 进阶数学
+章末复习 FM Ch23 复数（进阶）
+· 章末复习题 End-of-chapter review p.543，限时 30 分钟
+· 本章要会：能用 de Moivre 定理求幂、根与复数和
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 进阶数学
+术语与格式 FM Ch24 微分方程（进阶） §24.1、§24.2、§24.3、§24.4
+· 速览 §24.1 一阶微分方程、§24.2 二阶微分方程：齐次情形、§24.3 二阶微分方程：非齐次情形、§24.4 微分方程的代换法（p.545、p.550、p.557、p.565，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 6 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. integrating factor = 积分因子
+· 2. complementary function (CF) = 余函数 / 互补函数
+· 3. particular integral (PI) = 特解 / 特积分
+· 4. auxiliary equation = 辅助方程
+· 5. general solution / particular solution = 通解 / 特解
+· 6. initial condition = 初始条件
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch24 Differential equations 微分方程（进阶）（9231 §2.6，Paper 2；只在 FM 考）]]（本章共 6 条）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>8月10日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch19 热物理（§19.1、§19.2）
+· 节末 Questions 题 全部（约 25 分钟，p.543）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.544）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+格式训练 Phy Ch19 热物理（§19.3、§19.4）
+· 节末 Questions 题 全部（约 25 分钟，p.551）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.552）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+20:00-21:00 物理
+术语与格式 Phy Ch19 热物理 §19.5、§19.6
+· 速览 §19.5 温度计、§19.6 计算能量变化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch19 Thermal physics 热物理]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>8月11日 周三 ◆暑假
+────────────
+14:00-15:00 进阶数学
+格式训练 FM Ch24 微分方程（进阶）（§24.1、§24.2）
+· Ex 24A 题 全部（约 25 分钟，p.547）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 24B 题 全部（约 25 分钟，p.552）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 进阶数学
+章末复习 FM Ch24 微分方程（进阶）
+· 章末复习题 End-of-chapter review p.575，限时 30 分钟
+· 本章要会：能解一阶与二阶（齐次/非齐次）微分方程
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>8月12日 周四 ◆暑假
+────────────
+14:00-15:00 物理
+章末复习 Phy Ch19 热物理
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：比热容、潜热、理想气体与热力学第一定律
+· 过关自测：能默写 Q=mcΔθ 与 Q=ml；能列 ΔU=Q+W；Chapter 19 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 物理
+术语与格式 Phy Ch20 理想气体 §20.1、§20.2、§20.3、§20.4
+· 速览 §20.1 气体的粒子模型、§20.2 解释压强、§20.3 测量气体、§20.4 玻意耳定律（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. ideal gas = 理想气体
+· 2. kinetic theory = 分子动理论
+· 3. mole = 摩尔
+· 4. Avogadro constant = 阿伏伽德罗常数
+· 5. molar gas constant = 摩尔气体常量
+· 6. Boltzmann constant = 玻尔兹曼常量
+· 7. equation of state = 状态方程
+· 8. Boyle's law = 玻意耳定律
+· 9. pressure law = 压强定律
+· 10. Charles's law = 查理定律
+· 11. root-mean-square speed = 均方根速率
+· 12. mean translational kinetic energy = 平均平动动能
+· 13. number density = 数密度
+· 14. elastic collision = 弹性碰撞
+· 全部抄完后回看一遍：[[06_物理#Ch20 Ideal gases 理想气体]]（本章共 14 条）
+20:00-21:00 物理
+格式训练 Phy Ch20 理想气体（§20.1、§20.2）
+· 节末 Questions 题 全部（约 25 分钟，p.571）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.572）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>8月13日 周五 ◆暑假
+────────────
+14:00-15:00 进阶数学
+真题精练 9231 FP1 2019 Paper 1
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+15:15-16:15 进阶数学
 真题精练 9231 FP2 2019 Paper 2
 · 进阶数学真题卷
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>8月2日 周一 ◆暑假
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>8月14日 周六 ◆暑假
 ────────────
 14:00-15:00 进阶数学
 真题精练 9231 FS 2019 Paper 3
 · 进阶数学真题卷
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题
-15:15-16:15 进阶数学
+20:00-21:00 进阶数学
 真题精练 9231 FM 2019 Paper 4
 · 进阶数学真题卷
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>8月3日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch21 匀强电场（§21.1、§21.2）
-· 节末 Questions 题 全部（约 25 分钟，p.595）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.597）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-15:15-16:15 物理
-章末复习 Phy Ch21 匀强电场
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：匀强电场、电势与电容器
-· 过关自测：能默写 E=V/d 与 F=qE；能算电容器储能 W=½QV；Chapter 21 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>8月4日 周三 ◆暑假
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>8月15日 周日 ◆暑假
+────────────
+14:00-15:00 复习/测试
+· 回顾：Phy Ch20 ｜ FM Ch24
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+真题精练 9231 FP1 2020 Paper 1
+· 进阶数学真题卷
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="178" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>8月16日 周一 ◆暑假
 ────────────
 14:00-15:00 进阶数学
-真题精练 9231 FP1 2020 Paper 1
+真题精练 9231 FP2 2020 Paper 2
 · 进阶数学真题卷
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题
 15:15-16:15 进阶数学
-真题精练 9231 FP2 2020 Paper 2
+真题精练 9231 FS 2020 Paper 3
 · 进阶数学真题卷
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>8月5日 周四 ◆暑假
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>8月17日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-真题精练 9702 AS 2019 Paper 1
-· 物理 AS 真题（选择题/结构题）
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
+格式训练 Phy Ch20 理想气体（§20.3、§20.4）
+· 节末 Questions 题 全部（约 25 分钟，p.574）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.575）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 物理
-真题精练 9702 AS 2019 Paper 2
-· 物理 AS 真题（选择题/结构题）
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>8月6日 周五 ◆暑假
+术语与格式 Phy Ch20 理想气体 §20.5、§20.6、§20.7、§20.8
+· 速览 §20.5 温度变化、§20.6 理想气体方程、§20.7 气体建模：动力学模型、§20.8 温度与分子能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[06_物理#Ch20 Ideal gases 理想气体]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
+20:00-21:00 物理
+格式训练 Phy Ch20 理想气体（§20.5、§20.6）
+· 节末 Questions 题 全部（约 25 分钟，p.577）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.580）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>8月18日 周三 ◆暑假
 ────────────
 14:00-15:00 进阶数学
-真题精练 9231 FS 2020 Paper 3
+真题精练 9231 FM 2020 Paper 4
 · 进阶数学真题卷
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题
-15:15-16:15 进阶数学
-真题精练 9231 FM 2020 Paper 4
-· 进阶数学真题卷
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>8月7日 周六 ◆暑假
+15:15-16:15 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>8月19日 周四 ◆暑假
+────────────
+14:00-15:00 物理
+章末复习 Phy Ch20 理想气体
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：理想气体状态方程与分子运动论
+· 过关自测：能默写 pV=nRT 与 pV=NkT；能解释压强与温度的微观意义；Chapter 20 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 物理
+术语与格式 Phy Ch21 匀强电场 §21.1、§21.2、§21.3、§21.4
+· 速览 §21.1 吸引与排斥、§21.2 电场概念、§21.3 电场强度、§21.4 电荷受到的力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. electric field = 电场
+· 2. electric field line = 电场线
+· 3. electric field strength = 电场强度
+· 4. uniform field = 匀强电场
+· 5. test charge = 试探电荷
+· 6. force on a charge = 电荷受力
+· 7. potential difference = 电势差
+· 8. N C⁻¹ = 牛每库仑
+· 9. V m⁻¹ = 伏每米
+· 10. parabolic path = 抛物线轨迹
+· 11. Coulomb's law = 库仑定律
+· 12. permittivity of free space = 真空介电常数
+· 13. electric potential = 电势
+· 14. electric potential energy = 电势能
+· 全部抄完后回看一遍：[[06_物理#Ch21 Uniform electric fields 匀强电场]]（本章共 14 条）
+20:00-21:00 物理
+格式训练 Phy Ch21 匀强电场（§21.1、§21.2）
+· 节末 Questions 题 全部（约 25 分钟，p.595）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.597）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>8月20日 周五 ◆暑假
+────────────
+14:00-15:00 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>8月21日 周六 ◆暑假
 ────────────
 14:00-15:00 应用数学
 本阶段内容已全部完成
@@ -2017,9 +2373,9 @@
 · 自由复习 / 自主拓展</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>8月8日 周日 ◆暑假
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>8月22日 周日 ◆暑假
 ────────────
 14:00-15:00 复习/测试
 · 回顾：Phy Ch21
@@ -2031,10 +2387,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>8月9日 周一 ◆暑假
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>8月23日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
 本阶段内容已全部完成
@@ -2044,9 +2400,44 @@
 · 自由复习 / 自主拓展</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>8月10日 周二 ◆暑假
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>8月24日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+章末复习 Phy Ch21 匀强电场
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：匀强电场、电势与电容器
+· 过关自测：能默写 E=V/d 与 F=qE；能算电容器储能 W=½QV；Chapter 21 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 物理
+真题精练 9702 AS 2019 Paper 1
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+20:00-21:00 物理
+真题精练 9702 AS 2019 Paper 2
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>8月25日 周三 ◆暑假
+────────────
+14:00-15:00 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 纯数
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>8月26日 周四 ◆暑假
 ────────────
 14:00-15:00 物理
 真题精练 9702 AS 2020 Paper 1
@@ -2057,12 +2448,55 @@
 真题精练 9702 AS 2020 Paper 2
 · 物理 AS 真题（选择题/结构题）
 · 限时 55 分钟作答 + 即时对答案
+· 错题归档，次日二刷错题
+20:00-21:00 物理
+真题精练 9702 AS 2021 Paper 1
+· 物理 AS 真题（选择题/结构题）
+· 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>8月11日 周三 ◆暑假
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>8月27日 周五 ◆暑假
+────────────
+14:00-15:00 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+15:15-16:15 学术英语
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>8月28日 周六 ◆暑假
+────────────
+14:00-15:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展
+20:00-21:00 应用数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>8月29日 周日 ◆暑假
+────────────
+14:00-15:00 复习/测试
+★ 暑期总测试：三科综合卷（P2/3 + 物理 + FM，真题限时）
+· 限时作答后逐题订正，记录失分点
+20:00-21:00 进阶数学
+本阶段内容已全部完成
+· 自由复习 / 自主拓展</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="178" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>8月30日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
 本阶段内容已全部完成
@@ -2072,260 +2506,25 @@
 · 自由复习 / 自主拓展</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>8月12日 周四 ◆暑假
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>8月31日 周二 ◆暑假
 ────────────
 14:00-15:00 物理
-真题精练 9702 AS 2021 Paper 1
+真题精练 9702 AS 2021 Paper 2
 · 物理 AS 真题（选择题/结构题）
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题
 15:15-16:15 物理
-真题精练 9702 AS 2021 Paper 2
-· 物理 AS 真题（选择题/结构题）
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>8月13日 周五 ◆暑假
-────────────
-14:00-15:00 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>8月14日 周六 ◆暑假
-────────────
-14:00-15:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-20:00-21:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>8月15日 周日 ◆暑假
-────────────
-14:00-15:00 复习/测试
-· 回顾：整理本周笔记
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="178" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>8月16日 周一 ◆暑假
-────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>8月17日 周二 ◆暑假
-────────────
-14:00-15:00 物理
 真题精练 9702 AS 2022 Paper 1
 · 物理 AS 真题（选择题/结构题）
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题
-15:15-16:15 物理
+20:00-21:00 物理
 真题精练 9702 AS 2022 Paper 2
 · 物理 AS 真题（选择题/结构题）
 · 限时 55 分钟作答 + 即时对答案
 · 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>8月18日 周三 ◆暑假
-────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>8月19日 周四 ◆暑假
-────────────
-14:00-15:00 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>8月20日 周五 ◆暑假
-────────────
-14:00-15:00 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>8月21日 周六 ◆暑假
-────────────
-14:00-15:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-20:00-21:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>8月22日 周日 ◆暑假
-────────────
-14:00-15:00 复习/测试
-· 回顾：整理本周笔记
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>8月23日 周一 ◆暑假
-────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>8月24日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>8月25日 周三 ◆暑假
-────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>8月26日 周四 ◆暑假
-────────────
-14:00-15:00 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>8月27日 周五 ◆暑假
-────────────
-14:00-15:00 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 学术英语
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>8月28日 周六 ◆暑假
-────────────
-14:00-15:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-20:00-21:00 应用数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>8月29日 周日 ◆暑假
-────────────
-14:00-15:00 复习/测试
-★ 暑期总测试：三科综合卷（P2/3 + 物理 + FM，真题限时）
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="178" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>8月30日 周一 ◆暑假
-────────────
-14:00-15:00 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 纯数
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>8月31日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展
-15:15-16:15 物理
-本阶段内容已全部完成
-· 自由复习 / 自主拓展</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -2518,7 +2717,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>529.25</v>
+        <v>541.33</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2585,7 +2784,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch3 ｜ 物理 Phy Ch3 ｜ 应用数学 M1 Ch4 ｜ 进阶数学 FM Ch3</t>
+          <t>纯数 P1 Ch2 ｜ 物理 Phy Ch2 ｜ 应用数学 M1 Ch4 ｜ 进阶数学 FM Ch3</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2801,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch5 ｜ 物理 Phy Ch5 ｜ 应用数学 M1 Ch6 ｜ 进阶数学 FM Ch5</t>
+          <t>纯数 P1 Ch4 ｜ 物理 Phy Ch4 ｜ 应用数学 M1 Ch6 ｜ 进阶数学 FM Ch5</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2818,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>纯数 P1 Ch8 ｜ 物理 Phy Ch7 ｜ 应用数学 M1 Ch9 ｜ 进阶数学 FM Ch6</t>
+          <t>纯数 P1 Ch6 ｜ 物理 Phy Ch5 ｜ 应用数学 M1 Ch9 ｜ 进阶数学 FM Ch6</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2835,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch2 ｜ 物理 Phy Ch11 ｜ 应用数学 S1 Ch2 ｜ 进阶数学 FM Ch13</t>
+          <t>纯数 P1 Ch9 ｜ 物理 Phy Ch8 ｜ 应用数学 S1 Ch2 ｜ 进阶数学 FM Ch13</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2852,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch3 ｜ 物理 Phy Ch12 ｜ 应用数学 S1 Ch4 ｜ 进阶数学 FM Ch15</t>
+          <t>纯数 P2/3 Ch2 ｜ 物理 Phy Ch11 ｜ 应用数学 S1 Ch4 ｜ 进阶数学 FM Ch15</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2869,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch5 ｜ 物理 Phy Ch15 ｜ 应用数学 S1 Ch7 ｜ 进阶数学 FM Ch16</t>
+          <t>纯数 P2/3 Ch3 ｜ 物理 Phy Ch12 ｜ 应用数学 S1 Ch7 ｜ 进阶数学 FM Ch16</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2886,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch8 ｜ 物理 Phy Ch16 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch18</t>
+          <t>纯数 P2/3 Ch6 ｜ 物理 Phy Ch15 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch18</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2903,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch17 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch10</t>
+          <t>纯数 P2/3 Ch8 ｜ 物理 Phy Ch15 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch10</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2920,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch20 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch22</t>
+          <t>纯数 P2/3 Ch11 ｜ 物理 Phy Ch18 ｜ 应用数学 S1 Ch8 ｜ 进阶数学 FM Ch20</t>
         </is>
       </c>
     </row>
@@ -3095,6 +3294,31 @@
           <t>11月2日 周一
 ────────────
 21:00-22:15 纯数
+术语与格式 P1 Ch1 二次方程 §1.9
+· 速览 §1.9 直线与二次曲线的交点（p.27，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch1 Quadratics 二次方程]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>11月3日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch2 加速运动（§2.1、§2.2）
+· 节末 Questions 题 全部（约 25 分钟，p.41）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.42）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>11月4日 周三
+────────────
+21:00-22:15 纯数
 章末复习 P1 Ch1 二次方程
 · 章末复习题 End-of-chapter review p.31，限时 30 分钟
 · 本章要会：把任意二次式配方、用判别式判断根的个数、解二次不等式与「一个线性一个二次」的联立方程
@@ -3103,9 +3327,9 @@
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>11月3日 周二
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>11月5日 周四
 ────────────
 21:00-22:15 物理
 格式训练 Phy Ch2 加速运动（§2.3、§2.4）
@@ -3114,15 +3338,67 @@
 · 节末 Questions 题 全部（约 25 分钟，p.45）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-术语与格式 Phy Ch2 加速运动 §2.5、§2.6、§2.7、§2.8
-· 速览 §2.5 推导位移、§2.6 测量速度与加速度、§2.7 实验室中测定速度与加速度、§2.8 运动方程（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch2 Accelerated motion 加速运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>11月4日 周三
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>11月6日 周五
+────────────
+21:00-22:15 学术英语
+EAP 06 学术词汇②：AWL Sublist 3-4
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Anki 牌组「英语词汇::AWL」的 Sublist 3-4；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：开 15–20 张新卡（20 分钟封顶）+ 用当天 10 个新词写 120 词学术段落
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-06 学术词汇②：AWL Sublist 3-4」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：10 个新词主动用出 ≥6 个；段落四项自检各指出 1 处不足
+· 本类（词汇类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>11月7日 周六
+────────────
+14:00-15:00 应用数学
+格式训练 M1 Ch2 一维力与运动（§2.1、§2.2）
+· Ex 2A 题 全部（约 25 分钟，p.38）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 全部（约 25 分钟，p.41）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+20:00-21:00 应用数学
+章末复习 M1 Ch2 一维力与运动
+· 章末复习题 End-of-chapter review p.51，限时 30 分钟
+· 本章要会：牛顿第二定律 F=ma 在一维的应用、重量与法向力
+· 过关自测：能画一维受力图（free-body diagram）；能处理竖直方向运动；Ex 2A–2D 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>11月8日 周日
+────────────
+14:00-15:00 复习/测试
+· 回顾：P1 Ch1 ｜ Phy Ch2 ｜ M1 Ch2
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+格式训练 FM Ch2 有理函数（§2.1、§2.2）
+· Ex 2A 题 全部（约 25 分钟，p.19）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 全部（约 25 分钟，p.26）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>11月9日 周一
 ────────────
 21:00-22:15 纯数
 术语与格式 P1 Ch2 函数 §2.1、§2.2、§2.3、§2.4
@@ -3143,18 +3419,37 @@
 · 12. stretch factor = 伸缩因子
 · 13. invariant = 不变的（固定线）
 · 14. order of operations = 运算顺序
-· 全部抄完后回看一遍：[[01_纯数学 P1#Ch2 Functions 函数]]（本章共 14 条）
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch2 Functions 函数]]（本章共 14 条）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>11月10日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch2 加速运动 §2.5、§2.6、§2.7、§2.8
+· 速览 §2.5 推导位移、§2.6 测量速度与加速度、§2.7 实验室中测定速度与加速度、§2.8 运动方程（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch2 Accelerated motion 加速运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>11月11日 周三
+────────────
+21:00-22:15 纯数
 格式训练 P1 Ch2 函数（§2.1、§2.2）
 · Ex 2A 题 1–16（约 34 分钟，p.37）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 2B 题 1–19（约 35 分钟，p.41）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>11月5日 周四
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>11月12日 周四
 ────────────
 21:00-22:15 物理
 格式训练 Phy Ch2 加速运动（§2.5、§2.6）
@@ -3164,111 +3459,6 @@
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>11月6日 周五
-────────────
-21:00-22:15 学术英语
-EAP 06 学术词汇②：AWL Sublist 3-4
-· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
-· ② 输入（25 分钟）：Anki 牌组「英语词汇::AWL」的 Sublist 3-4；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
-· ③ 产出（30 分钟）：开 15–20 张新卡（20 分钟封顶）+ 用当天 10 个新词写 120 词学术段落
-· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-06 学术词汇②：AWL Sublist 3-4」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
-· ✓ 合格线（自己判定）：10 个新词主动用出 ≥6 个；段落四项自检各指出 1 处不足
-· 本类（词汇类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>11月7日 周六
-────────────
-14:00-15:00 应用数学
-格式训练 M1 Ch2 一维力与运动（§2.1、§2.2）
-· Ex 2A 题 全部（约 25 分钟，p.38）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2B 题 全部（约 25 分钟，p.41）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-20:00-21:00 应用数学
-章末复习 M1 Ch2 一维力与运动
-· 章末复习题 End-of-chapter review p.51，限时 30 分钟
-· 本章要会：牛顿第二定律 F=ma 在一维的应用、重量与法向力
-· 过关自测：能画一维受力图（free-body diagram）；能处理竖直方向运动；Ex 2A–2D 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>11月8日 周日
-────────────
-14:00-15:00 复习/测试
-· 回顾：P1 Ch2 ｜ Phy Ch2 ｜ M1 Ch2
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-格式训练 FM Ch2 有理函数（§2.1、§2.2）
-· Ex 2A 题 全部（约 25 分钟，p.19）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2B 题 全部（约 25 分钟，p.26）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>11月9日 周一
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch2 函数（§2.3、§2.4）
-· Ex 2C 题 1–16（约 34 分钟，p.46）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2D 题 1–6（约 19 分钟，p.50）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>11月10日 周二
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch2 加速运动（§2.7、§2.8）
-· 节末 Questions 题 全部（约 25 分钟，p.51）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.56）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>11月11日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P1 Ch2 函数 §2.5、§2.6、§2.7、§2.8
-· 速览 §2.5 函数的图像变换、§2.6 反射变换、§2.7 伸缩变换、§2.8 复合变换（p.51、p.55、p.57、p.59，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch2 Functions 函数]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>11月12日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch2 加速运动 §2.9、§2.10、§2.11、§2.12
-· 速览 §2.9 运动方程的推导、§2.10 匀变速与非匀变速、§2.11 重力加速度、§2.12 测定 g（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch2 Accelerated motion 加速运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -3343,6 +3533,112 @@
           <t>11月16日 周一
 ────────────
 21:00-22:15 纯数
+格式训练 P1 Ch2 函数（§2.3、§2.4）
+· Ex 2C 题 1–16（约 34 分钟，p.46）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2D 题 1–6（约 19 分钟，p.50）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>11月17日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch2 加速运动（§2.7、§2.8）
+· 节末 Questions 题 全部（约 25 分钟，p.51）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.56）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>11月18日 周三
+────────────
+21:00-22:15 纯数
+术语与格式 P1 Ch2 函数 §2.5、§2.6、§2.7、§2.8
+· 速览 §2.5 函数的图像变换、§2.6 反射变换、§2.7 伸缩变换、§2.8 复合变换（p.51、p.55、p.57、p.59，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch2 Functions 函数]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>11月19日 周四
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch2 加速运动 §2.9、§2.10、§2.11、§2.12
+· 速览 §2.9 运动方程的推导、§2.10 匀变速与非匀变速、§2.11 重力加速度、§2.12 测定 g（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch2 Accelerated motion 加速运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>11月20日 周五
+────────────
+21:00-22:15 学术英语
+EAP 08 引用规范：Harvard 格式入门与学术诚信
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：Purdue OWL（https://owl.purdue.edu/owl/research_and_citation/resources.html）+ EAP Foundation 的 Citation 页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：对 2 条真实来源（课本/论文/网页）各做出：1 条文内引用 + 1 条参考文献条目，逐字符核对标点
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-08 引用规范：Harvard 格式入门与学术诚信」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：与 OWL 样例逐字符一致（含斜体、逗号、句号位置）；存进 EAP-08 笔记，以后每次写作业直接复制这份样例
+· 本类（引用类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>11月21日 周六
+────────────
+14:00-15:00 应用数学
+格式训练 M1 Ch3 二维力（§3.3、§3.4）
+· Ex 3C 题 全部（约 25 分钟，p.64）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3D 题 全部（约 25 分钟，p.68）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+20:00-21:00 应用数学
+术语与格式 M1 Ch3 二维力 §3.5
+· 速览 §3.5 求合力与加速度方向（p.71，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[03_力学 M1#Ch3 Forces in two dimensions 二维力]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>11月22日 周日
+────────────
+14:00-15:00 复习/测试
+· 回顾：P1 Ch2 ｜ Phy Ch2 ｜ M1 Ch3
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+术语与格式 FM Ch3 级数求和 §3.1、§3.2
+· 速览 §3.1 Σr、Σr²、Σr³ 求和公式、§3.2 收敛级数（p.46、p.51，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. summation of series = 级数求和
+· 2. method of differences = 差分法 / 逐项相消
+· 3. sum to infinity = 无穷和
+· 4. convergent / divergent = 收敛的 / 发散的
+· 5. partial fractions = 部分分式
+· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch3 Summation of series 级数求和（9231 §1.3，Paper 1；只在 FM 考）]]（本章共 5 条）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="178" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>11月23日 周一
+────────────
+21:00-22:15 纯数
 格式训练 P1 Ch2 函数（§2.5、§2.6）
 · Ex 2E 题 1–7（约 20 分钟，p.54）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -3352,9 +3648,9 @@
 · Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>11月17日 周二
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>11月24日 周二
 ────────────
 21:00-22:15 物理
 格式训练 Phy Ch2 加速运动（§2.9、§2.10）
@@ -3363,17 +3659,12 @@
 · 节末 Questions 题 全部（约 25 分钟，p.60）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-格式训练 Phy Ch2 加速运动（§2.11、§2.12）
-· 节末 Questions 题 全部（约 25 分钟，p.62）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.67）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>11月18日 周三
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>11月25日 周三
 ────────────
 21:00-22:15 纯数
 章末复习 P1 Ch2 函数
@@ -3381,7 +3672,93 @@
 · 本章要会：判断映射是否为一对一、求反函数与复合函数、画 y=f(x) 的图象变换
 · 过关自测：能不看笔记写出 4 种图象变换（平移/拉伸/反射）的规则；Ex 2A–2H 错题清零；能解释「定义域限制」从哪来
 · 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>11月26日 周四
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch2 加速运动（§2.11、§2.12）
+· 节末 Questions 题 全部（约 25 分钟，p.62）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.67）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>11月27日 周五
+────────────
+21:00-22:15 学术英语
+EAP 09 学术听力①：康奈尔笔记法与讲座笔记符号
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP Foundation 听力区「讲座信号词 / 笔记符号」一节（https://www.eapfoundation.com/listening/lectures/；大陆镜像 http://i.youku.com/eapfoundation）——看完教程立刻关掉；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：关掉教程，直接听一段 5–8 分钟真讲座做康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）+ 2 分钟口头复述录音
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-09 学术听力①：康奈尔笔记法与讲座笔记符号」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：复述能连续讲满 2 分钟且停顿 &lt;5 次；笔记不看原文也能支撑复述
+· 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>11月28日 周六
+────────────
+14:00-15:00 应用数学
+章末复习 M1 Ch3 二维力
+· 章末复习题 End-of-chapter review p.77，限时 30 分钟
+· 本章要会：二维受力分解、平衡方程、Lami 定理、斜面上的合成
+· 过关自测：能把任意方向的力分解到水平和竖直；能对斜面问题分解成平行/垂直分量；Ex 3A–3E 错题清零
+· 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+20:00-21:00 应用数学
+术语与格式 M1 Ch4 摩擦力 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 摩擦力作为接触力的一部分、§4.2 摩擦极限、§4.3 运动不同阶段摩擦方向的变化、§4.4 摩擦角（p.83、p.90、p.95、p.100，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. friction = 摩擦力
+· 2. limiting friction = 极限摩擦
+· 3. limiting equilibrium = 极限平衡
+· 4. coefficient of friction = 摩擦系数
+· 5. smooth / rough = 光滑 / 粗糙
+· 6. contact force = 接触力
+· 7. normal contact force $R$ = 法向力
+· 8. on the point of sliding = 临界滑动
+· 9. impending motion = 即将发生的运动
+· 10. opposes motion = 阻碍运动
+· 11. angle of friction = 摩擦角
+· 12. resultant of two perpendicular forces = 互相垂直两力的合力
+· 13. rough surface = 粗糙面
+· 14. threshold / least value = 临界值 / 最小值
+· 全部抄完后回看一遍：[[03_力学 M1#Ch4 Friction 摩擦力]]（本章共 14 条）</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>11月29日 周日
+────────────
+14:00-15:00 复习/测试
+★ 11月测试：P1 Ch1-3｜物理 Ch1-2
+· 限时作答后逐题订正，记录失分点
+20:00-21:00 进阶数学
+章末复习 FM Ch3 级数求和
+· 章末复习题 End-of-chapter review p.57，限时 30 分钟
+· 本章要会：能默写 Σr、Σr²、Σr³ 公式并求无穷等比级数和
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="178" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>11月30日 周一
+────────────
+21:00-22:15 纯数
 术语与格式 P1 Ch3 坐标几何 §3.1、§3.2、§3.3、§3.4
 · 速览 §3.1 线段长度与中点、§3.2 平行与垂直、§3.3 直线的方程、§3.4 圆的方程（p.72、p.75、p.78、p.82，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
@@ -3401,218 +3778,6 @@
 · 13. tangent = 切线
 · 14. repeated root = 重根
 · 全部抄完后回看一遍：[[01_纯数学 P1#Ch3 Coordinate geometry 坐标几何]]（本章共 14 条）</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>11月19日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch2 加速运动 §2.13、§2.14
-· 速览 §2.13 二维运动：抛体、§2.14 理解抛体运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch2 Accelerated motion 加速运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>11月20日 周五
-────────────
-21:00-22:15 学术英语
-EAP 08 引用规范：Harvard 格式入门与学术诚信
-· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
-· ② 输入（25 分钟）：Purdue OWL（https://owl.purdue.edu/owl/research_and_citation/resources.html）+ EAP Foundation 的 Citation 页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
-· ③ 产出（30 分钟）：对 2 条真实来源（课本/论文/网页）各做出：1 条文内引用 + 1 条参考文献条目，逐字符核对标点
-· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-08 引用规范：Harvard 格式入门与学术诚信」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
-· ✓ 合格线（自己判定）：与 OWL 样例逐字符一致（含斜体、逗号、句号位置）；存进 EAP-08 笔记，以后每次写作业直接复制这份样例
-· 本类（引用类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>11月21日 周六
-────────────
-14:00-15:00 应用数学
-格式训练 M1 Ch3 二维力（§3.3、§3.4）
-· Ex 3C 题 全部（约 25 分钟，p.64）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 3D 题 全部（约 25 分钟，p.68）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-20:00-21:00 应用数学
-术语与格式 M1 Ch3 二维力 §3.5
-· 速览 §3.5 求合力与加速度方向（p.71，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 14 条）：[[03_力学 M1#Ch3 Forces in two dimensions 二维力]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>11月22日 周日
-────────────
-14:00-15:00 复习/测试
-· 回顾：P1 Ch3 ｜ Phy Ch2 ｜ M1 Ch3
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-术语与格式 FM Ch3 级数求和 §3.1、§3.2
-· 速览 §3.1 Σr、Σr²、Σr³ 求和公式、§3.2 收敛级数（p.46、p.51，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 5 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. summation of series = 级数求和
-· 2. method of differences = 差分法 / 逐项相消
-· 3. sum to infinity = 无穷和
-· 4. convergent / divergent = 收敛的 / 发散的
-· 5. partial fractions = 部分分式
-· 全部抄完后回看一遍：[[05_进阶数学 FM#Ch3 Summation of series 级数求和（9231 §1.3，Paper 1；只在 FM 考）]]（本章共 5 条）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="178" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>11月23日 周一
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch3 坐标几何（§3.1、§3.2）
-· Ex 3A 题 1–12（约 28 分钟，p.74）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 3B 题 1–11（约 26 分钟，p.77）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>11月24日 周二
-────────────
-21:00-22:15 物理
-章末复习 Phy Ch2 加速运动
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：用四个匀加速公式与图象解多阶段运动
-· 过关自测：四个公式默写全对；能从 v–t 图求位移；能处理自由落体与抛体；Chapter 2 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>11月25日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch3 坐标几何（§3.3、§3.4）
-· Ex 3C 题 1–16（约 34 分钟，p.80）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 3D 题 1–17（约 35 分钟，p.87）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>11月26日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch3 动力学 §3.1、§3.2、§3.3、§3.4
-· 速览 §3.1 力、质量与加速度、§3.2 识别力、§3.3 重力、摩擦与引力、§3.4 质量与惯性（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 16 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. resultant force = 合力
-· 2. free-body diagram = 受力图
-· 3. Newton's first law = 牛顿第一定律
-· 4. Newton's second law = 牛顿第二定律
-· 5. Newton's third law = 牛顿第三定律
-· 6. weight = 重力
-· 7. mass = 质量
-· 8. inertia = 惯性
-· 9. friction = 摩擦力
-· 10. drag = 阻力
-· 11. terminal velocity = 终端速度
-· 12. normal contact force = 法向接触力
-· 13. tension = 张力
-· 14. upthrust = 浮力
-· 15. base unit = 基本单位
-· 16. derived unit = 导出单位
-· 全部抄完后回看一遍：[[06_物理#Ch3 Dynamics 动力学]]（本章共 16 条）</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>11月27日 周五
-────────────
-21:00-22:15 学术英语
-EAP 09 学术听力①：康奈尔笔记法与讲座笔记符号
-· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
-· ② 输入（25 分钟）：EAP Foundation 听力区「讲座信号词 / 笔记符号」一节（https://www.eapfoundation.com/listening/lectures/；大陆镜像 http://i.youku.com/eapfoundation）——看完教程立刻关掉；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
-· ③ 产出（30 分钟）：关掉教程，直接听一段 5–8 分钟真讲座做康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）+ 2 分钟口头复述录音
-· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-09 学术听力①：康奈尔笔记法与讲座笔记符号」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
-· ✓ 合格线（自己判定）：复述能连续讲满 2 分钟且停顿 &lt;5 次；笔记不看原文也能支撑复述
-· 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>11月28日 周六
-────────────
-14:00-15:00 应用数学
-章末复习 M1 Ch3 二维力
-· 章末复习题 End-of-chapter review p.77，限时 30 分钟
-· 本章要会：二维受力分解、平衡方程、Lami 定理、斜面上的合成
-· 过关自测：能把任意方向的力分解到水平和竖直；能对斜面问题分解成平行/垂直分量；Ex 3A–3E 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-20:00-21:00 应用数学
-术语与格式 M1 Ch4 摩擦力 §4.1、§4.2、§4.3、§4.4
-· 速览 §4.1 摩擦力作为接触力的一部分、§4.2 摩擦极限、§4.3 运动不同阶段摩擦方向的变化、§4.4 摩擦角（p.83、p.90、p.95、p.100，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. friction = 摩擦力
-· 2. limiting friction = 极限摩擦
-· 3. limiting equilibrium = 极限平衡
-· 4. coefficient of friction = 摩擦系数
-· 5. smooth / rough = 光滑 / 粗糙
-· 6. contact force = 接触力
-· 7. normal contact force $R$ = 法向力
-· 8. on the point of sliding = 临界滑动
-· 9. impending motion = 即将发生的运动
-· 10. opposes motion = 阻碍运动
-· 11. angle of friction = 摩擦角
-· 12. resultant of two perpendicular forces = 互相垂直两力的合力
-· 13. rough surface = 粗糙面
-· 14. threshold / least value = 临界值 / 最小值
-· 全部抄完后回看一遍：[[03_力学 M1#Ch4 Friction 摩擦力]]（本章共 14 条）</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>11月29日 周日
-────────────
-14:00-15:00 复习/测试
-★ 11月测试：P1 Ch1-3｜物理 Ch1-2
-· 限时作答后逐题订正，记录失分点
-20:00-21:00 进阶数学
-章末复习 FM Ch3 级数求和
-· 章末复习题 End-of-chapter review p.57，限时 30 分钟
-· 本章要会：能默写 Σr、Σr²、Σr³ 公式并求无穷等比级数和
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="178" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>11月30日 周一
-────────────
-21:00-22:15 纯数
-术语与格式 P1 Ch3 坐标几何 §3.5
-· 速览 §3.5 直线与圆的交点问题（p.88，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch3 Coordinate geometry 坐标几何]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -3689,18 +3854,10 @@
           <t>12月1日 周二
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch3 动力学（§3.1、§3.2）
-· 节末 Questions 题 全部（约 25 分钟，p.87）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.88）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-格式训练 Phy Ch3 动力学（§3.3、§3.4）
-· 节末 Questions 题 全部（约 25 分钟，p.89）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.94）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+术语与格式 Phy Ch2 加速运动 §2.13、§2.14
+· 速览 §2.13 二维运动：抛体、§2.14 理解抛体运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch2 Accelerated motion 加速运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -3708,30 +3865,13 @@
           <t>12月2日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P1 Ch3 坐标几何
-· 章末复习题 End-of-chapter review p.92，限时 30 分钟
-· 本章要会：求两点间距离与中点、直线方程、直线交点与垂直/平行条件
-· 过关自测：能把「两点式/斜截式/一般式」互相转换；Ex 3A–3E 错题清零；圆与直线关系的 3 种情况能画图说明
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-术语与格式 P1 Ch4 弧度制 §4.1、§4.2、§4.3
-· 速览 §4.1 弧度、§4.2 弧长、§4.3 扇形面积（p.101、p.104、p.107，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. radian = 弧度
-· 2. arc length = 弧长
-· 3. sector = 扇形
-· 4. minor sector / major sector = 小扇形 / 大扇形
-· 5. segment = 弓形
-· 6. minor arc / major arc = 劣弧 / 优弧
-· 7. chord = 弦
-· 8. subtend = 对（弧对圆心角）
-· 9. circumference = 圆周（周长）
-· 10. perimeter = 周长
-· 11. sine rule / cosine rule = 正弦定理 / 余弦定理
-· 12. significant figures = 有效数字
-· 13. inscribed circle = 内切圆
-· 全部抄完后回看一遍：[[01_纯数学 P1#Ch4 Circular measure 弧度制]]（本章共 13 条）</t>
+格式训练 P1 Ch3 坐标几何（§3.1、§3.2）
+· Ex 3A 题 1–12（约 28 分钟，p.74）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3B 题 1–11（约 26 分钟，p.77）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -3739,10 +3879,12 @@
           <t>12月3日 周四
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch3 动力学 §3.5、§3.6、§3.7
-· 速览 §3.5 在流体中运动、§3.6 牛顿第三定律、§3.7 理解 SI 单位（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 16 条）：[[06_物理#Ch3 Dynamics 动力学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+章末复习 Phy Ch2 加速运动
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：用四个匀加速公式与图象解多阶段运动
+· 过关自测：四个公式默写全对；能从 v–t 图求位移；能处理自由落体与抛体；Chapter 2 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -3785,7 +3927,7 @@
           <t>12月6日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch4 ｜ Phy Ch3 ｜ M1 Ch4
+· 回顾：P1 Ch3 ｜ Phy Ch2 ｜ M1 Ch4
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -3810,10 +3952,10 @@
           <t>12月7日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P1 Ch4 弧度制（§4.1、§4.2）
-· Ex 4A 题 1–9（约 24 分钟，p.102）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 4B 题 1–10（约 25 分钟，p.105）
+格式训练 P1 Ch3 坐标几何（§3.3、§3.4）
+· Ex 3C 题 1–16（约 34 分钟，p.80）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3D 题 1–17（约 35 分钟，p.87）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -3824,13 +3966,27 @@
           <t>12月8日 周二
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch3 动力学（§3.5、§3.6）
-· 节末 Questions 题 全部（约 25 分钟，p.98）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.101）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 Phy Ch3 动力学 §3.1、§3.2、§3.3、§3.4
+· 速览 §3.1 力、质量与加速度、§3.2 识别力、§3.3 重力、摩擦与引力、§3.4 质量与惯性（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 16 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. resultant force = 合力
+· 2. free-body diagram = 受力图
+· 3. Newton's first law = 牛顿第一定律
+· 4. Newton's second law = 牛顿第二定律
+· 5. Newton's third law = 牛顿第三定律
+· 6. weight = 重力
+· 7. mass = 质量
+· 8. inertia = 惯性
+· 9. friction = 摩擦力
+· 10. drag = 阻力
+· 11. terminal velocity = 终端速度
+· 12. normal contact force = 法向接触力
+· 13. tension = 张力
+· 14. upthrust = 浮力
+· 15. base unit = 基本单位
+· 16. derived unit = 导出单位
+· 全部抄完后回看一遍：[[06_物理#Ch3 Dynamics 动力学]]（本章共 16 条）</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3838,12 +3994,10 @@
           <t>12月9日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P1 Ch4 弧度制
-· 章末复习题 End-of-chapter review p.112，限时 30 分钟
-· 本章要会：弧度制、扇形弧长与面积、弧度下的三角比
-· 过关自测：弧长 s=rθ 与面积 A=½r²θ 能默写；Ex 4A–4C 错题清零；能在 30 秒内把 60°/90°/180° 换成弧度
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 P1 Ch3 坐标几何 §3.5
+· 速览 §3.5 直线与圆的交点问题（p.88，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 14 条）：[[01_纯数学 P1#Ch3 Coordinate geometry 坐标几何]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -3851,12 +4005,13 @@
           <t>12月10日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch3 动力学
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：牛顿三定律、动量与冲量、平衡与合力
-· 过关自测：能画受力图；能区分质量与重量；能解连接体问题；Chapter 3 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 Phy Ch3 动力学（§3.1、§3.2）
+· 节末 Questions 题 全部（约 25 分钟，p.87）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.88）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -3913,7 +4068,7 @@
           <t>12月13日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch4 ｜ Phy Ch3 ｜ M1 Ch5
+· 回顾：P1 Ch3 ｜ Phy Ch3 ｜ M1 Ch5
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -3933,87 +4088,62 @@
           <t>12月14日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P1 Ch5 三角学 §5.1、§5.2、§5.3、§5.4
-· 速览 §5.1 0°–90° 之间的角、§5.2 角的一般定义、§5.3 任意角的三角比、§5.4 三角函数的图像（p.118、p.121、p.123、p.127，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+章末复习 P1 Ch3 坐标几何
+· 章末复习题 End-of-chapter review p.92，限时 30 分钟
+· 本章要会：求两点间距离与中点、直线方程、直线交点与垂直/平行条件
+· 过关自测：能把「两点式/斜截式/一般式」互相转换；Ex 3A–3E 错题清零；圆与直线关系的 3 种情况能画图说明
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>12月15日 周二
+────────────
+21:00-22:15 物理
+格式训练 Phy Ch3 动力学（§3.3、§3.4）
+· 节末 Questions 题 全部（约 25 分钟，p.89）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.94）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>12月16日 周三
+────────────
+21:00-22:15 纯数
+术语与格式 P1 Ch4 弧度制 §4.1、§4.2、§4.3
+· 速览 §4.1 弧度、§4.2 弧长、§4.3 扇形面积（p.101、p.104、p.107，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 · 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. basic angle (reference angle) = 基准角（参考角）
-· 2. general definition of an angle = 角的通用定义
-· 3. quadrant = 象限
-· 4. period / periodic function = 周期 / 周期函数
-· 5. amplitude = 振幅
-· 6. principal axis = 中轴
-· 7. asymptote = 渐近线
-· 8. stretch factor = 伸缩因子
-· 9. inverse trigonometric function = 反三角函数
-· 10. principal angle (principal value) = 主值角
-· 11. one-one function = 一对一函数
-· 12. identity = 恒等式
-· 13. LHS / RHS = 左边 / 右边
-· 全部抄完后回看一遍：[[01_纯数学 P1#Ch5 Trigonometry 三角学]]（本章共 13 条）</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>12月15日 周二
+· 1. radian = 弧度
+· 2. arc length = 弧长
+· 3. sector = 扇形
+· 4. minor sector / major sector = 小扇形 / 大扇形
+· 5. segment = 弓形
+· 6. minor arc / major arc = 劣弧 / 优弧
+· 7. chord = 弦
+· 8. subtend = 对（弧对圆心角）
+· 9. circumference = 圆周（周长）
+· 10. perimeter = 周长
+· 11. sine rule / cosine rule = 正弦定理 / 余弦定理
+· 12. significant figures = 有效数字
+· 13. inscribed circle = 内切圆
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch4 Circular measure 弧度制]]（本章共 13 条）</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>12月17日 周四
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch4 力 §4.1、§4.2、§4.3、§4.4
-· 速览 §4.1 力的合成、§4.2 矢量的分量、§4.3 重心、§4.4 力的转动效应（力矩）（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. moment = 力矩
-· 2. torque of a couple = 力偶矩
-· 3. couple = 力偶
-· 4. pivot = 支点
-· 5. perpendicular distance = 垂直距离
-· 6. principle of moments = 力矩平衡原理
-· 7. centre of gravity = 重心
-· 8. equilibrium = 平衡
-· 9. resolving = 分解
-· 10. component = 分量
-· 11. lamina = 薄片
-· 12. plumb line = 铅垂线
-· 全部抄完后回看一遍：[[06_物理#Ch4 Forces 力]]（本章共 12 条）
-格式训练 Phy Ch4 力（§4.1、§4.2）
-· 节末 Questions 题 全部（约 25 分钟，p.116）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.120）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>12月16日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P1 Ch5 三角学（§5.1、§5.2）
-· Ex 5A 题 1–6（约 19 分钟，p.120）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 5B 题 1–9（约 24 分钟，p.122）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-格式训练 P1 Ch5 三角学（§5.3、§5.4）
-· Ex 5C 题 1–13（约 30 分钟，p.126）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 5D 题 1–17（约 35 分钟，p.134）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>12月17日 周四
-────────────
-21:00-22:15 物理
-格式训练 Phy Ch4 力（§4.3、§4.4）
-· 节末 Questions 题 全部（约 25 分钟，p.122）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.127）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 Phy Ch3 动力学 §3.5、§3.6、§3.7
+· 速览 §3.5 在流体中运动、§3.6 牛顿第三定律、§3.7 理解 SI 单位（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 16 条）：[[06_物理#Ch3 Dynamics 动力学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -4068,7 +4198,7 @@
           <t>12月20日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch5 ｜ Phy Ch4 ｜ M1 Ch6
+· 回顾：P1 Ch4 ｜ Phy Ch3 ｜ M1 Ch6
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -4087,10 +4217,13 @@
           <t>12月21日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P1 Ch5 三角学 §5.5、§5.6、§5.7、§5.8
-· 速览 §5.5 反三角函数、§5.6 三角方程、§5.7 三角恒等式、§5.8 更复杂的三角方程（p.136、p.140、p.145、p.149，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 13 条）：[[01_纯数学 P1#Ch5 Trigonometry 三角学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 P1 Ch4 弧度制（§4.1、§4.2）
+· Ex 4A 题 1–9（约 24 分钟，p.102）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 1–10（约 25 分钟，p.105）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -4098,10 +4231,13 @@
           <t>12月22日 周二
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch4 力 §4.5
-· 速览 §4.5 力偶的力矩（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch4 Forces 力]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 Phy Ch3 动力学（§3.5、§3.6）
+· 节末 Questions 题 全部（约 25 分钟，p.98）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.101）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -4109,13 +4245,12 @@
           <t>12月23日 周三
 ────────────
 21:00-22:15 纯数
-格式训练 P1 Ch5 三角学（§5.5、§5.6）
-· Ex 5E 题 1–9（约 24 分钟，p.139）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 5F 题 1–11（约 26 分钟，p.144）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+章末复习 P1 Ch4 弧度制
+· 章末复习题 End-of-chapter review p.112，限时 30 分钟
+· 本章要会：弧度制、扇形弧长与面积、弧度下的三角比
+· 过关自测：弧长 s=rθ 与面积 A=½r²θ 能默写；Ex 4A–4C 错题清零；能在 30 秒内把 60°/90°/180° 换成弧度
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4123,36 +4258,37 @@
           <t>12月24日 周四 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 物理
-章末复习 Phy Ch4 力
+章末复习 Phy Ch3 动力学
 · 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：力矩、平衡、重心、压强与密度
-· 过关自测：能对悬空/靠墙物体列力矩方程；能把力分解到任意方向；Chapter 4 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章要会：牛顿三定律、动量与冲量、平衡与合力
+· 过关自测：能画受力图；能区分质量与重量；能解连接体问题；Chapter 3 EXAM-STYLE QUESTIONS 限时做完并批改
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 物理
-术语与格式 Phy Ch5 功、能与功率 §5.1、§5.2、§5.3、§5.4
-· 速览 §5.1 做功与能量转移、§5.2 重力势能、§5.3 动能、§5.4 重力势能→动能转化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. work done = 做功
-· 2. joule = 焦耳
-· 3. gravitational potential energy = 重力势能
-· 4. kinetic energy = 动能
-· 5. conservation of energy = 能量守恒
-· 6. efficiency = 效率
-· 7. power = 功率
-· 8. watt = 瓦特
-· 9. Sankey diagram = 能流图
-· 10. dissipate = 耗散
-· 11. transformation = 能量转化
-· 全部抄完后回看一遍：[[06_物理#Ch5 Work, energy and power 功、能与功率]]（本章共 11 条）</t>
+术语与格式 Phy Ch4 力 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 力的合成、§4.2 矢量的分量、§4.3 重心、§4.4 力的转动效应（力矩）（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. moment = 力矩
+· 2. torque of a couple = 力偶矩
+· 3. couple = 力偶
+· 4. pivot = 支点
+· 5. perpendicular distance = 垂直距离
+· 6. principle of moments = 力矩平衡原理
+· 7. centre of gravity = 重心
+· 8. equilibrium = 平衡
+· 9. resolving = 分解
+· 10. component = 分量
+· 11. lamina = 薄片
+· 12. plumb line = 铅垂线
+· 全部抄完后回看一遍：[[06_物理#Ch4 Forces 力]]（本章共 12 条）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>12月25日 周五 ◆圣诞·元旦假期
 ────────────
-14:00-15:00 学术英语
+14:00-15:15 学术英语
 EAP 13 学术听力②：TED-Ed / BBC 学术播客精听
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：TED-Ed 一段（≤8 分钟），先开英文字幕看一遍，再关字幕听一遍；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -4160,7 +4296,7 @@
 · ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-13 学术听力②：TED-Ed / BBC 学术播客精听」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
 · ✓ 合格线（自己判定）：复述停顿 &lt;5 次；标出的连读弱读 ≥5 处
 · 本类（听力类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
-15:15-16:15 学术英语
+15:15-16:30 学术英语
 EAP 14 学术写作②：议论文与反驳段
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：Manchester Academic Phrasebank（https://www.phrasebank.manchester.ac.uk/）的 Comparing ideas / Referring to sources——只借结构，不整句背；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -4218,31 +4354,32 @@
           <t>12月28日 周一 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 纯数
-章末复习 P1 Ch5 三角学
-· 章末复习题 End-of-chapter review p.153，限时 30 分钟
-· 本章要会：六个三角函数的图象与恒等式、解三角方程、和角公式与 R sin(θ±α)
-· 过关自测：能默写 sin²+cos²=1 及两个变形、和角公式、倍角公式；Ex 5A–5H 错题清零；能口述「为什么解三角方程要注意区间」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+术语与格式 P1 Ch5 三角学 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 0°–90° 之间的角、§5.2 角的一般定义、§5.3 任意角的三角比、§5.4 三角函数的图像（p.118、p.121、p.123、p.127，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. basic angle (reference angle) = 基准角（参考角）
+· 2. general definition of an angle = 角的通用定义
+· 3. quadrant = 象限
+· 4. period / periodic function = 周期 / 周期函数
+· 5. amplitude = 振幅
+· 6. principal axis = 中轴
+· 7. asymptote = 渐近线
+· 8. stretch factor = 伸缩因子
+· 9. inverse trigonometric function = 反三角函数
+· 10. principal angle (principal value) = 主值角
+· 11. one-one function = 一对一函数
+· 12. identity = 恒等式
+· 13. LHS / RHS = 左边 / 右边
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch5 Trigonometry 三角学]]（本章共 13 条）
 15:15-16:15 纯数
-术语与格式 P1 Ch6 数列 §6.1、§6.2、§6.3、§6.4
-· 速览 §6.1 (a+b)^n 的二项式展开、§6.2 二项式系数、§6.3 等差数列、§6.4 等比数列（p.156、p.160、p.166、p.171，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. binomial expansion = 二项式展开
-· 2. binomial coefficient = 二项式系数
-· 3. Pascal's triangle = 杨辉三角
-· 4. factorial = 阶乘
-· 5. sequence = 数列
-· 6. series = 级数
-· 7. arithmetic progression = 等差数列
-· 8. common difference = 公差
-· 9. geometric progression = 等比数列
-· 10. common ratio = 公比
-· 11. convergent series = 收敛级数
-· 12. sum to infinity = 无穷和
-· 13. term = 项
-· 全部抄完后回看一遍：[[01_纯数学 P1#Ch6 Series 数列]]（本章共 13 条）</t>
+格式训练 P1 Ch5 三角学（§5.1、§5.2）
+· Ex 5A 题 1–6（约 19 分钟，p.120）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5B 题 1–9（约 24 分钟，p.122）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -4250,18 +4387,18 @@
           <t>12月29日 周二 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 物理
-格式训练 Phy Ch5 功、能与功率（§5.1、§5.2）
-· 节末 Questions 题 全部（约 25 分钟，p.142）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.146）
+格式训练 Phy Ch4 力（§4.1、§4.2）
+· 节末 Questions 题 全部（约 25 分钟，p.116）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.120）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
 15:15-16:15 物理
-格式训练 Phy Ch5 功、能与功率（§5.3、§5.4）
-· 节末 Questions 题 全部（约 25 分钟，p.148）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.149）
+格式训练 Phy Ch4 力（§4.3、§4.4）
+· 节末 Questions 题 全部（约 25 分钟，p.122）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.127）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -4271,22 +4408,19 @@
         <is>
           <t>12月30日 周三 ◆圣诞·元旦假期
 ────────────
-14:00-15:00 纯数
-格式训练 P1 Ch6 数列（§6.1、§6.2）
-· Ex 6A 题 1–16（约 34 分钟，p.158）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 6B 题 1–15（约 32 分钟，p.165）
+14:00-15:10 纯数
+格式训练 P1 Ch5 三角学（§5.3、§5.4）
+· Ex 5C 题 1–13（约 30 分钟，p.126）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5D 题 1–17（约 35 分钟，p.134）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
 15:15-16:15 纯数
-格式训练 P1 Ch6 数列（§6.3、§6.4）
-· Ex 6C 题 1–20（约 35 分钟，p.170）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 6D 题 1–16（约 34 分钟，p.174）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 P1 Ch5 三角学 §5.5、§5.6、§5.7、§5.8
+· 速览 §5.5 反三角函数、§5.6 三角方程、§5.7 三角恒等式、§5.8 更复杂的三角方程（p.136、p.140、p.145、p.149，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[01_纯数学 P1#Ch5 Trigonometry 三角学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4294,18 +4428,17 @@
           <t>12月31日 周四 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 物理
-术语与格式 Phy Ch5 功、能与功率 §5.5、§5.6、§5.7
-· 速览 §5.5 下降、上升、下降：能量变化、§5.6 能量转移、§5.7 功率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 11 条）：[[06_物理#Ch5 Work, energy and power 功、能与功率]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
+术语与格式 Phy Ch4 力 §4.5
+· 速览 §4.5 力偶的力矩（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[06_物理#Ch4 Forces 力]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
 15:15-16:15 物理
-格式训练 Phy Ch5 功、能与功率（§5.5、§5.6）
-· 节末 Questions 题 全部（约 25 分钟，p.152）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.153）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+章末复习 Phy Ch4 力
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：力矩、平衡、重心、压强与密度
+· 过关自测：能对悬空/靠墙物体列力矩方程；能把力分解到任意方向；Chapter 4 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="E6" s="3" t="n"/>
@@ -4381,7 +4514,7 @@
         <is>
           <t>1月1日 周五 ◆圣诞·元旦假期
 ────────────
-14:00-15:00 学术英语
+14:00-15:15 学术英语
 EAP 15 学术词汇④：AWL Sublist 7-10
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：Anki 牌组「英语词汇::AWL」的 Sublist 7-10；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -4389,7 +4522,7 @@
 · ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-15 学术词汇④：AWL Sublist 7-10」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
 · ✓ 合格线（自己判定）：10 个新词主动用出 ≥6 个；AWL 全表累计主动词 ≥100
 · 本类（词汇类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
-15:15-16:15 学术英语
+15:15-16:30 学术英语
 EAP 16 学术讨论：seminar 发言、提问与回应
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：自问自答材料：从本周课本里挑一个可争论的问题（如「实验误差应该归因于仪器还是方法」）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -4437,7 +4570,7 @@
           <t>1月3日 周日 ◆圣诞·元旦假期
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch6 ｜ Phy Ch5 ｜ M1 Ch7
+· 回顾：P1 Ch5 ｜ Phy Ch4 ｜ M1 Ch7
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -4456,10 +4589,13 @@
           <t>1月4日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P1 Ch6 数列 §6.5、§6.6
-· 速览 §6.5 无穷等比级数、§6.6 综合等差与等比数列（p.175、p.180，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 13 条）：[[01_纯数学 P1#Ch6 Series 数列]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 P1 Ch5 三角学（§5.5、§5.6）
+· Ex 5E 题 1–9（约 24 分钟，p.139）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5F 题 1–11（约 26 分钟，p.144）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4467,69 +4603,49 @@
           <t>1月5日 周二
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch5 功、能与功率
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：功、功率、效率、动能与势能转换
-· 过关自测：能算 W=Fs cosθ 与 P=W/t、P=Fv；能列能量守恒式；Chapter 5 EXAM-STYLE QUESTIONS 限时做完并批改
+术语与格式 Phy Ch5 功、能与功率 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 做功与能量转移、§5.2 重力势能、§5.3 动能、§5.4 重力势能→动能转化（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. work done = 做功
+· 2. joule = 焦耳
+· 3. gravitational potential energy = 重力势能
+· 4. kinetic energy = 动能
+· 5. conservation of energy = 能量守恒
+· 6. efficiency = 效率
+· 7. power = 功率
+· 8. watt = 瓦特
+· 9. Sankey diagram = 能流图
+· 10. dissipate = 耗散
+· 11. transformation = 能量转化
+· 全部抄完后回看一遍：[[06_物理#Ch5 Work, energy and power 功、能与功率]]（本章共 11 条）</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>1月6日 周三
+────────────
+21:00-22:15 纯数
+章末复习 P1 Ch5 三角学
+· 章末复习题 End-of-chapter review p.153，限时 30 分钟
+· 本章要会：六个三角函数的图象与恒等式、解三角方程、和角公式与 R sin(θ±α)
+· 过关自测：能默写 sin²+cos²=1 及两个变形、和角公式、倍角公式；Ex 5A–5H 错题清零；能口述「为什么解三角方程要注意区间」
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>1月6日 周三
-────────────
-21:00-22:15 纯数
-章末复习 P1 Ch6 数列
-· 章末复习题 End-of-chapter review p.183，限时 30 分钟
-· 本章要会：等差/等比数列通项与求和、无穷等比级数收敛条件
-· 过关自测：默写等差/等比通项与求和公式；能判断 |r|&lt;1；Ex 6A–6F 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-术语与格式 P1 Ch7 微分 §7.1、§7.2、§7.3、§7.4
-· 速览 §7.1 导数与梯度函数、§7.2 链式法则、§7.3 切线与法线、§7.4 二阶导数（p.191、p.198、p.201、p.205，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. derivative = 导数
-· 2. differentiation = 微分（求导）
-· 3. differentiation from first principles = 用定义求导
-· 4. gradient function = 梯度函数
-· 5. chain rule = 链式法则
-· 6. composite function = 复合函数
-· 7. tangent = 切线
-· 8. normal = 法线
-· 9. second derivative = 二阶导数
-· 10. scalar multiple rule = 常数倍法则
-· 11. small increment = 微小增量
-· 全部抄完后回看一遍：[[01_纯数学 P1#Ch7 Differentiation 微分]]（本章共 11 条）</t>
-        </is>
-      </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
           <t>1月7日 周四
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch6 动量 §6.1、§6.2、§6.3、§6.4
-· 速览 §6.1 动量的概念、§6.2 碰撞建模、§6.3 理解碰撞、§6.4 爆炸与撞击（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. momentum = 动量
-· 2. linear momentum = 线动量
-· 3. closed system = 封闭系统
-· 4. conservation of momentum = 动量守恒
-· 5. elastic collision = 弹性碰撞
-· 6. inelastic collision = 非弹性碰撞
-· 7. impulse = 冲量
-· 8. explosion = 爆炸
-· 9. resultant external force = 合外力
-· 10. crumple zone = 溃缩区
-· 全部抄完后回看一遍：[[06_物理#Ch6 Momentum 动量]]（本章共 10 条）
-格式训练 Phy Ch6 动量（§6.1、§6.2）
-· 节末 Questions 题 全部（约 25 分钟，p.167）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.170）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+格式训练 Phy Ch5 功、能与功率（§5.1、§5.2）
+· 节末 Questions 题 全部（约 25 分钟，p.142）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.146）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -4586,7 +4702,7 @@
           <t>1月10日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch7 ｜ Phy Ch6 ｜ M1 Ch8
+· 回顾：P1 Ch5 ｜ Phy Ch5 ｜ M1 Ch8
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -4611,13 +4727,24 @@
           <t>1月11日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P1 Ch7 微分（§7.1、§7.2）
-· Ex 7A 题 1–19（约 35 分钟，p.197）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 7B 题 1–8（约 22 分钟，p.201）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 P1 Ch6 数列 §6.1、§6.2、§6.3、§6.4
+· 速览 §6.1 (a+b)^n 的二项式展开、§6.2 二项式系数、§6.3 等差数列、§6.4 等比数列（p.156、p.160、p.166、p.171，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. binomial expansion = 二项式展开
+· 2. binomial coefficient = 二项式系数
+· 3. Pascal's triangle = 杨辉三角
+· 4. factorial = 阶乘
+· 5. sequence = 数列
+· 6. series = 级数
+· 7. arithmetic progression = 等差数列
+· 8. common difference = 公差
+· 9. geometric progression = 等比数列
+· 10. common ratio = 公比
+· 11. convergent series = 收敛级数
+· 12. sum to infinity = 无穷和
+· 13. term = 项
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch6 Series 数列]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -4625,10 +4752,10 @@
           <t>1月12日 周二
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch6 动量（§6.3、§6.4）
-· 节末 Questions 题 全部（约 25 分钟，p.175）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.178）
+格式训练 Phy Ch5 功、能与功率（§5.3、§5.4）
+· 节末 Questions 题 全部（约 25 分钟，p.148）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.149）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -4639,12 +4766,13 @@
           <t>1月13日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P1 Ch7 微分
-· 章末复习题 End-of-chapter review p.209，限时 30 分钟
-· 本章要会：用导数定义求导、求切线/法线、判断增减性
-· 过关自测：能把 (x+h) 展开法做一遍；Ex 7A–7D 错题清零；能说清「驻点不一定是极值点」并举反例
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 P1 Ch6 数列（§6.1、§6.2）
+· Ex 6A 题 1–16（约 34 分钟，p.158）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6B 题 1–15（约 32 分钟，p.165）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -4652,10 +4780,10 @@
           <t>1月14日 周四
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch6 动量 §6.5、§6.6、§6.7
-· 速览 §6.5 二维碰撞、§6.6 动量与牛顿定律、§6.7 理解运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 10 条）：[[06_物理#Ch6 Momentum 动量]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+术语与格式 Phy Ch5 功、能与功率 §5.5、§5.6、§5.7
+· 速览 §5.5 下降、上升、下降：能量变化、§5.6 能量转移、§5.7 功率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 11 条）：[[06_物理#Ch5 Work, energy and power 功、能与功率]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -4711,7 +4839,7 @@
           <t>1月17日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch7 ｜ Phy Ch6 ｜ M1 Ch9
+· 回顾：P1 Ch6 ｜ Phy Ch5 ｜ M1 Ch9
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -4731,23 +4859,13 @@
           <t>1月18日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P1 Ch8 进阶微分 §8.1、§8.2、§8.3、§8.4
-· 速览 §8.1 增函数与减函数、§8.2 驻点、§8.3 实际最大最小值问题、§8.4 变化率（p.213、p.216、p.221、p.227，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. increasing function = 增函数
-· 2. decreasing function = 减函数
-· 3. stationary point = 驻点
-· 4. turning point = 极值点
-· 5. maximum point = 极大值点
-· 6. minimum point = 极小值点
-· 7. point of inflexion = 拐点
-· 8. first derivative test = 一阶导数检验
-· 9. second derivative test = 二阶导数检验
-· 10. rate of change = 变化率
-· 11. connected rates of change = 相关变化率
-· 12. nature of a stationary point = 驻点的性质
-· 全部抄完后回看一遍：[[01_纯数学 P1#Ch8 Further differentiation 进阶微分]]（本章共 12 条）</t>
+格式训练 P1 Ch6 数列（§6.3、§6.4）
+· Ex 6C 题 1–20（约 35 分钟，p.170）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6D 题 1–16（约 34 分钟，p.174）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4755,10 +4873,10 @@
           <t>1月19日 周二
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch6 动量（§6.5、§6.6）
-· 节末 Questions 题 全部（约 25 分钟，p.181）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.183）
+格式训练 Phy Ch5 功、能与功率（§5.5、§5.6）
+· 节末 Questions 题 全部（约 25 分钟，p.152）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.153）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -4769,18 +4887,10 @@
           <t>1月20日 周三
 ────────────
 21:00-22:15 纯数
-格式训练 P1 Ch8 进阶微分（§8.1、§8.2）
-· Ex 8A 题 1–9（约 24 分钟，p.215）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 8B 题 1–13（约 30 分钟，p.220）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-格式训练 P1 Ch8 进阶微分（§8.3、§8.4）
-· Ex 8C 题 1–15（约 32 分钟，p.224）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 8D 题 1–9（约 24 分钟，p.229）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+术语与格式 P1 Ch6 数列 §6.5、§6.6
+· 速览 §6.5 无穷等比级数、§6.6 综合等差与等比数列（p.175、p.180，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[01_纯数学 P1#Ch6 Series 数列]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -4788,34 +4898,12 @@
           <t>1月21日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch6 动量
+章末复习 Phy Ch5 功、能与功率
 · 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：动量守恒与碰撞（含弹性/非弹性）
-· 过关自测：能判断动量守恒的方向；能用动能计算判断碰撞类型；Chapter 6 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-术语与格式 Phy Ch7 物质与材料 §7.1、§7.2、§7.3、§7.4
-· 速览 §7.1 密度、§7.2 压强、§7.3 阿基米德原理、§7.4 压力与张力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 17 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. density = 密度
-· 2. pressure = 压强
-· 3. pascal = 帕斯卡
-· 4. upthrust = 浮力
-· 5. Archimedes' principle = 阿基米德原理
-· 6. tensile force = 张力
-· 7. compressive force = 压力
-· 8. Hooke's law = 胡克定律
-· 9. force constant = 劲度系数
-· 10. extension = 伸长量
-· 11. limit of proportionality = 比例极限
-· 12. elastic limit = 弹性极限
-· 13. elastic deformation = 弹性形变
-· 14. plastic deformation = 塑性形变
-· 15. stress = 应力
-· 16. strain = 应变
-· 17. Young modulus = 杨氏模量
-· 全部抄完后回看一遍：[[06_物理#Ch7 Matter and materials 物质与材料]]（本章共 17 条）</t>
+· 本章要会：功、功率、效率、动能与势能转换
+· 过关自测：能算 W=Fs cosθ 与 P=W/t、P=Fv；能列能量守恒式；Chapter 5 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -4876,96 +4964,106 @@
           <t>1月25日 周一 ◆寒假
 ────────────
 14:00-15:00 纯数
-术语与格式 P1 Ch8 进阶微分 §8.5
-· 速览 §8.5 相关变化率的实际应用（p.230，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[01_纯数学 P1#Ch8 Further differentiation 进阶微分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
+章末复习 P1 Ch6 数列
+· 章末复习题 End-of-chapter review p.183，限时 30 分钟
+· 本章要会：等差/等比数列通项与求和、无穷等比级数收敛条件
+· 过关自测：默写等差/等比通项与求和公式；能判断 |r|&lt;1；Ex 6A–6F 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
 15:15-16:15 纯数
-章末复习 P1 Ch8 进阶微分
-· 章末复习题 End-of-chapter review p.235，限时 30 分钟
-· 本章要会：链式法则、乘积/商法则、隐函数与参数方程求导
-· 过关自测：三类法则各能默写并各做 5 题全对；Ex 8A–8E 错题清零；能说清 dy/dx 里「谁是自变量」
+术语与格式 P1 Ch7 微分 §7.1、§7.2、§7.3、§7.4
+· 速览 §7.1 导数与梯度函数、§7.2 链式法则、§7.3 切线与法线、§7.4 二阶导数（p.191、p.198、p.201、p.205，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. derivative = 导数
+· 2. differentiation = 微分（求导）
+· 3. differentiation from first principles = 用定义求导
+· 4. gradient function = 梯度函数
+· 5. chain rule = 链式法则
+· 6. composite function = 复合函数
+· 7. tangent = 切线
+· 8. normal = 法线
+· 9. second derivative = 二阶导数
+· 10. scalar multiple rule = 常数倍法则
+· 11. small increment = 微小增量
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch7 Differentiation 微分]]（本章共 11 条）</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>1月26日 周二 ◆寒假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch6 动量 §6.1、§6.2、§6.3、§6.4
+· 速览 §6.1 动量的概念、§6.2 碰撞建模、§6.3 理解碰撞、§6.4 爆炸与撞击（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. momentum = 动量
+· 2. linear momentum = 线动量
+· 3. closed system = 封闭系统
+· 4. conservation of momentum = 动量守恒
+· 5. elastic collision = 弹性碰撞
+· 6. inelastic collision = 非弹性碰撞
+· 7. impulse = 冲量
+· 8. explosion = 爆炸
+· 9. resultant external force = 合外力
+· 10. crumple zone = 溃缩区
+· 全部抄完后回看一遍：[[06_物理#Ch6 Momentum 动量]]（本章共 10 条）
+15:15-16:15 物理
+格式训练 Phy Ch6 动量（§6.1、§6.2）
+· 节末 Questions 题 全部（约 25 分钟，p.167）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.170）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>1月27日 周三 ◆寒假
+────────────
+14:00-15:05 纯数
+格式训练 P1 Ch7 微分（§7.1、§7.2）
+· Ex 7A 题 1–19（约 35 分钟，p.197）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 7B 题 1–8（约 22 分钟，p.201）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
+章末复习 P1 Ch7 微分
+· 章末复习题 End-of-chapter review p.209，限时 30 分钟
+· 本章要会：用导数定义求导、求切线/法线、判断增减性
+· 过关自测：能把 (x+h) 展开法做一遍；Ex 7A–7D 错题清零；能说清「驻点不一定是极值点」并举反例
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>1月26日 周二 ◆寒假
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>1月28日 周四 ◆寒假
 ────────────
 14:00-15:00 物理
-格式训练 Phy Ch7 物质与材料（§7.1、§7.2）
-· 节末 Questions 题 全部（约 25 分钟，p.195）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.196）
+格式训练 Phy Ch6 动量（§6.3、§6.4）
+· 节末 Questions 题 全部（约 25 分钟，p.175）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.178）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
 15:15-16:15 物理
-格式训练 Phy Ch7 物质与材料（§7.3、§7.4）
-· 节末 Questions 题 全部（约 25 分钟，p.200）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.201）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>1月27日 周三 ◆寒假
-────────────
-14:00-15:00 纯数
-术语与格式 P1 Ch9 积分 §9.1、§9.2、§9.3、§9.4
-· 速览 §9.1 积分是微分的逆运算、§9.2 求积分常数、§9.3 (ax+b)^n 型函数的积分、§9.4 进一步的不定积分（p.239、p.244、p.247、p.249，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. integration = 积分
-· 2. antidifferentiation = 反微分
-· 3. indefinite integral = 不定积分
-· 4. definite integral = 定积分
-· 5. constant of integration = 积分常数
-· 6. limits of integration = 积分上下限
-· 7. integrand = 被积函数
-· 8. area under a curve = 曲线下的面积
-· 9. volume of revolution = 旋转体体积
-· 10. solid of revolution = 旋转体
-· 11. improper integral = 反常（广义）积分
-· 12. Fundamental theorem of Calculus = 微积分基本定理
-· 全部抄完后回看一遍：[[01_纯数学 P1#Ch9 Integration 积分]]（本章共 12 条）
-15:15-16:15 纯数
-格式训练 P1 Ch9 积分（§9.1、§9.2）
-· Ex 9A 题 1–7（约 20 分钟，p.243）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9B 题 1–18（约 35 分钟，p.245）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>1月28日 周四 ◆寒假
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch7 物质与材料 §7.5、§7.6
-· 速览 §7.5 材料的拉伸、§7.6 弹性势能（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 17 条）：[[06_物理#Ch7 Matter and materials 物质与材料]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
-15:15-16:15 物理
-章末复习 Phy Ch7 物质与材料
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：材料力学性质、应力应变、杨氏模量、弹性形变
-· 过关自测：能画应力—应变图并标出弹性极限/屈服点；能算 Young 模量 E=Fl/Ax；Chapter 7 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 Phy Ch6 动量 §6.5、§6.6、§6.7
+· 速览 §6.5 二维碰撞、§6.6 动量与牛顿定律、§6.7 理解运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 10 条）：[[06_物理#Ch6 Momentum 动量]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>1月29日 周五 ◆寒假
 ────────────
-14:00-15:00 学术英语
+14:00-15:15 学术英语
 EAP 20 扩展论文：选题、文献检索与提纲
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：Google Scholar + Phrasebank 的 Introduction 页（只用来学结构）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -4973,7 +5071,7 @@
 · ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-20 扩展论文：选题、文献检索与提纲」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
 · ✓ 合格线（自己判定）：3 个分论点互不重叠；来源信息完整到能再次找到
 · 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
-15:15-16:15 学术英语
+15:15-16:30 学术英语
 EAP 21 学术写作⑤：引言与结论的写法
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：Phrasebank 的 Introduction / Conclusions 两页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -5023,7 +5121,7 @@
           <t>1月31日 周日 ◆寒假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P1 Ch9 ｜ Phy Ch7 ｜ S1 Ch1
+· 回顾：P1 Ch7 ｜ Phy Ch6 ｜ S1 Ch1
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -5108,25 +5206,290 @@
           <t>2月1日 周一 ◆寒假
 ────────────
 14:00-15:00 纯数
+术语与格式 P1 Ch8 进阶微分 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 增函数与减函数、§8.2 驻点、§8.3 实际最大最小值问题、§8.4 变化率（p.213、p.216、p.221、p.227，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. increasing function = 增函数
+· 2. decreasing function = 减函数
+· 3. stationary point = 驻点
+· 4. turning point = 极值点
+· 5. maximum point = 极大值点
+· 6. minimum point = 极小值点
+· 7. point of inflexion = 拐点
+· 8. first derivative test = 一阶导数检验
+· 9. second derivative test = 二阶导数检验
+· 10. rate of change = 变化率
+· 11. connected rates of change = 相关变化率
+· 12. nature of a stationary point = 驻点的性质
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch8 Further differentiation 进阶微分]]（本章共 12 条）
+15:15-16:15 纯数
+格式训练 P1 Ch8 进阶微分（§8.1、§8.2）
+· Ex 8A 题 1–9（约 24 分钟，p.215）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 1–13（约 30 分钟，p.220）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2月2日 周二 ◆寒假
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch6 动量（§6.5、§6.6）
+· 节末 Questions 题 全部（约 25 分钟，p.181）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.183）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 物理
+章末复习 Phy Ch6 动量
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：动量守恒与碰撞（含弹性/非弹性）
+· 过关自测：能判断动量守恒的方向；能用动能计算判断碰撞类型；Chapter 6 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>2月3日 周三 ◆寒假
+────────────
+14:00-15:05 纯数
+格式训练 P1 Ch8 进阶微分（§8.3、§8.4）
+· Ex 8C 题 1–15（约 32 分钟，p.224）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8D 题 1–9（约 24 分钟，p.229）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
+术语与格式 P1 Ch8 进阶微分 §8.5
+· 速览 §8.5 相关变化率的实际应用（p.230，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[01_纯数学 P1#Ch8 Further differentiation 进阶微分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>2月4日 周四 ◆寒假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch7 物质与材料 §7.1、§7.2、§7.3、§7.4
+· 速览 §7.1 密度、§7.2 压强、§7.3 阿基米德原理、§7.4 压力与张力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 17 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. density = 密度
+· 2. pressure = 压强
+· 3. pascal = 帕斯卡
+· 4. upthrust = 浮力
+· 5. Archimedes' principle = 阿基米德原理
+· 6. tensile force = 张力
+· 7. compressive force = 压力
+· 8. Hooke's law = 胡克定律
+· 9. force constant = 劲度系数
+· 10. extension = 伸长量
+· 11. limit of proportionality = 比例极限
+· 12. elastic limit = 弹性极限
+· 13. elastic deformation = 弹性形变
+· 14. plastic deformation = 塑性形变
+· 15. stress = 应力
+· 16. strain = 应变
+· 17. Young modulus = 杨氏模量
+· 全部抄完后回看一遍：[[06_物理#Ch7 Matter and materials 物质与材料]]（本章共 17 条）
+15:15-16:15 物理
+格式训练 Phy Ch7 物质与材料（§7.1、§7.2）
+· 节末 Questions 题 全部（约 25 分钟，p.195）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.196）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>2月5日 周五 ◆寒假
+────────────
+14:00-15:15 学术英语
+EAP 22 数据与公式的英文表达（数理语境）
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：自己的物理/数学课本里的英文段落（就用课本原文，一举两得）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：从课本抄 10 个含数据的英文句子，每个改写成三种说法（如 increase by 20% / a 20% increase / rises 20 per cent），再把术语入 Anki
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-22 数据与公式的英文表达（数理语境）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：10 句改写全部语法正确；入 Anki 的术语卡 ≥10 张
+· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>2月6日 周六 ◆寒假
+────────────
+14:00-15:00 应用数学
+格式训练 S1 Ch1 数据的表示（§1.3、§1.4）
+· Ex 1C 题 1–11（约 26 分钟，p.16）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1D 题 1–9（约 24 分钟，p.21）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>2月7日 周日 ◆寒假
+────────────
+14:00-15:00 复习/测试
+· 回顾：P1 Ch8 ｜ Phy Ch7 ｜ S1 Ch1
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="178" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2月8日 周一 ◆寒假
+────────────
+14:00-15:00 纯数
+章末复习 P1 Ch8 进阶微分
+· 章末复习题 End-of-chapter review p.235，限时 30 分钟
+· 本章要会：链式法则、乘积/商法则、隐函数与参数方程求导
+· 过关自测：三类法则各能默写并各做 5 题全对；Ex 8A–8E 错题清零；能说清 dy/dx 里「谁是自变量」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2月9日 周二 ◆寒假
+────────────
+14:00-15:00 物理
+格式训练 Phy Ch7 物质与材料（§7.3、§7.4）
+· 节末 Questions 题 全部（约 25 分钟，p.200）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.201）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>2月10日 周三 ◆寒假
+────────────
+14:00-15:00 纯数
+术语与格式 P1 Ch9 积分 §9.1、§9.2、§9.3、§9.4
+· 速览 §9.1 积分是微分的逆运算、§9.2 求积分常数、§9.3 (ax+b)^n 型函数的积分、§9.4 进一步的不定积分（p.239、p.244、p.247、p.249，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. integration = 积分
+· 2. antidifferentiation = 反微分
+· 3. indefinite integral = 不定积分
+· 4. definite integral = 定积分
+· 5. constant of integration = 积分常数
+· 6. limits of integration = 积分上下限
+· 7. integrand = 被积函数
+· 8. area under a curve = 曲线下的面积
+· 9. volume of revolution = 旋转体体积
+· 10. solid of revolution = 旋转体
+· 11. improper integral = 反常（广义）积分
+· 12. Fundamental theorem of Calculus = 微积分基本定理
+· 全部抄完后回看一遍：[[01_纯数学 P1#Ch9 Integration 积分]]（本章共 12 条）</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>2月11日 周四 ◆寒假
+────────────
+14:00-15:00 物理
+术语与格式 Phy Ch7 物质与材料 §7.5、§7.6
+· 速览 §7.5 材料的拉伸、§7.6 弹性势能（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 17 条）：[[06_物理#Ch7 Matter and materials 物质与材料]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2月12日 周五 ◆寒假
+────────────
+14:00-15:15 学术英语
+EAP 23 学术演讲①：presentation 结构与开场
+· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
+· ② 输入（25 分钟）：EAP Foundation 口语 / Presentation 区——只看结构那一页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
+· ③ 产出（30 分钟）：选题（如「为什么我要学 EEE」），写 1 页大纲（hook → 3 个点 → 收尾），录 2 分钟
+· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-23 学术演讲①：presentation 结构与开场」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
+· ✓ 合格线（自己判定）：录音回放能听出 3 个该改的地方；开场没有「Hello everyone, today I will talk about」这种套话
+· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>2月13日 周六 ◆寒假
+────────────
+14:00-15:00 应用数学
+术语与格式 S1 Ch1 数据的表示 §1.5
+· 速览 §1.5 不同数据表示方法的比较（p.20，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 15 条）：[[04_统计 S1#Ch1 Representation of data 数据的表示]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>2月14日 周日 ◆寒假
+────────────
+14:00-15:00 复习/测试
+· 回顾：P1 Ch9 ｜ Phy Ch7 ｜ S1 Ch1
+· Anki 术语卡 15′ + 错题本整理
+· 预习下周内容，制定周计划
+20:00-21:00 进阶数学
+章末复习 FM Ch7 数学归纳法
+· 章末复习题 End-of-chapter review p.151，限时 30 分钟
+· 本章要会：能写标准归纳法三步并证明整除性命题
+· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="178" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2月15日 周一 ◆寒假
+────────────
+14:00-15:00 纯数
+格式训练 P1 Ch9 积分（§9.1、§9.2）
+· Ex 9A 题 1–7（约 20 分钟，p.243）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9B 题 1–18（约 35 分钟，p.245）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
 格式训练 P1 Ch9 积分（§9.3、§9.4）
 · Ex 9C 题 1–8（约 22 分钟，p.248）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · Ex 9D 题 1–8（约 22 分钟，p.249）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-15:15-16:15 纯数
-术语与格式 P1 Ch9 积分 §9.5、§9.6、§9.7、§9.8
-· 速览 §9.5 定积分、§9.6 曲线下的面积、§9.7 曲线与直线/两曲线围成的面积、§9.8 反常（广义）积分（p.250、p.253、p.260、p.264，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[01_纯数学 P1#Ch9 Integration 积分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2月2日 周二 ◆寒假
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2月16日 周二 ◆寒假
 ────────────
 14:00-15:00 物理
+章末复习 Phy Ch7 物质与材料
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：材料力学性质、应力应变、杨氏模量、弹性形变
+· 过关自测：能画应力—应变图并标出弹性极限/屈服点；能算 Young 模量 E=Fl/Ax；Chapter 7 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 物理
 术语与格式 Phy Ch8 电流 §8.1、§8.2、§8.3、§8.4
 · 速览 §8.1 电路符号与电路图、§8.2 电流、§8.3 电流的公式、§8.4 电压的含义（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
@@ -5147,299 +5510,47 @@
 · 14. ammeter = 电流表
 · 15. voltmeter = 电压表
 · 16. circuit symbol = 电路符号
-· 全部抄完后回看一遍：[[06_物理#Ch8 Electric current 电流]]（本章共 16 条）
-15:15-16:15 物理
+· 全部抄完后回看一遍：[[06_物理#Ch8 Electric current 电流]]（本章共 16 条）</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2月17日 周三 ◆寒假
+────────────
+14:00-15:00 纯数
+术语与格式 P1 Ch9 积分 §9.5、§9.6、§9.7、§9.8
+· 速览 §9.5 定积分、§9.6 曲线下的面积、§9.7 曲线与直线/两曲线围成的面积、§9.8 反常（广义）积分（p.250、p.253、p.260、p.264，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[01_纯数学 P1#Ch9 Integration 积分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
+15:15-16:15 纯数
+格式训练 P1 Ch9 积分（§9.5、§9.6）
+· Ex 9E 题 1–9（约 24 分钟，p.252）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9F 题 1–14（约 31 分钟，p.256）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2月18日 周四 ◆寒假
+────────────
+14:00-15:00 物理
 格式训练 Phy Ch8 电流（§8.1、§8.2）
 · 节末 Questions 题 全部（约 25 分钟，p.223）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.226）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>2月3日 周三 ◆寒假
-────────────
-14:00-15:00 纯数
-格式训练 P1 Ch9 积分（§9.5、§9.6）
-· Ex 9E 题 1–9（约 24 分钟，p.252）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9F 题 1–14（约 31 分钟，p.256）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
-15:15-16:15 纯数
-格式训练 P1 Ch9 积分（§9.7、§9.8）
-· Ex 9G 题 1–10（约 25 分钟，p.262）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9H 题 1–4（约 16 分钟，p.267）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>2月4日 周四 ◆寒假
-────────────
-14:00-15:00 物理
+15:15-16:15 物理
 格式训练 Phy Ch8 电流（§8.3、§8.4）
 · 节末 Questions 题 全部（约 25 分钟，p.228）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
 · 节末 Questions 题 全部（约 25 分钟，p.233）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-15:15-16:15 物理
-术语与格式 Phy Ch8 电流 §8.5、§8.6
-· 速览 §8.5 电阻、§8.6 电功率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 16 条）：[[06_物理#Ch8 Electric current 电流]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2月5日 周五 ◆寒假
-────────────
-14:00-15:00 学术英语
-EAP 22 数据与公式的英文表达（数理语境）
-· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
-· ② 输入（25 分钟）：自己的物理/数学课本里的英文段落（就用课本原文，一举两得）；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
-· ③ 产出（30 分钟）：从课本抄 10 个含数据的英文句子，每个改写成三种说法（如 increase by 20% / a 20% increase / rises 20 per cent），再把术语入 Anki
-· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-22 数据与公式的英文表达（数理语境）」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
-· ✓ 合格线（自己判定）：10 句改写全部语法正确；入 Anki 的术语卡 ≥10 张
-· 本类（写作类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>2月6日 周六 ◆寒假
-────────────
-14:00-15:00 应用数学
-格式训练 S1 Ch1 数据的表示（§1.3、§1.4）
-· Ex 1C 题 1–11（约 26 分钟，p.16）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 1D 题 1–9（约 24 分钟，p.21）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>2月7日 周日 ◆寒假
-────────────
-14:00-15:00 复习/测试
-· 回顾：P1 Ch9 ｜ Phy Ch8 ｜ S1 Ch1
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="178" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2月8日 周一 ◆寒假
-────────────
-14:00-15:00 纯数
-术语与格式 P1 Ch9 积分 §9.9
-· 速览 §9.9 旋转体体积（p.268，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[01_纯数学 P1#Ch9 Integration 积分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2月9日 周二 ◆寒假
-────────────
-14:00-15:00 物理
-章末复习 Phy Ch8 电流
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：电流、电荷守恒、基尔霍夫电流定律
-· 过关自测：能默写 I=Q/t；能在电路图中标出电流方向与大小；Chapter 8 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>2月10日 周三 ◆寒假
-────────────
-14:00-15:00 纯数
-章末复习 P1 Ch9 积分
-· 章末复习题 End-of-chapter review p.276，限时 30 分钟
-· 本章要会：不定积分与定积分、面积与体积、换元与分部积分
-· 过关自测：能默写 ∫xⁿ、∫sin、∫cos、∫eˣ 的积分表；Ex 9A–9I 错题清零；能用定积分求一条曲线与 x 轴围成的面积
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>2月11日 周四 ◆寒假
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch9 基尔霍夫定律 §9.1、§9.2、§9.3、§9.4
-· 速览 §9.1 基尔霍夫第一定律、§9.2 基尔霍夫第二定律、§9.3 基尔霍夫定律的应用、§9.4 电阻的组合（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. Kirchhoff's first law = 基尔霍夫第一定律
-· 2. Kirchhoff's second law = 基尔霍夫第二定律
-· 3. junction = 节点
-· 4. loop = 回路
-· 5. conservation of charge = 电荷守恒
-· 6. conservation of energy = 能量守恒
-· 7. series = 串联
-· 8. parallel = 并联
-· 9. combined resistance = 总电阻
-· 10. reciprocal = 倒数
-· 全部抄完后回看一遍：[[06_物理#Ch9 Kirchhoff's laws 基尔霍夫定律]]（本章共 10 条）</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2月12日 周五 ◆寒假
-────────────
-14:00-15:00 学术英语
-EAP 23 学术演讲①：presentation 结构与开场
-· ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
-· ② 输入（25 分钟）：EAP Foundation 口语 / Presentation 区——只看结构那一页；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
-· ③ 产出（30 分钟）：选题（如「为什么我要学 EEE」），写 1 页大纲（hook → 3 个点 → 收尾），录 2 分钟
-· ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-23 学术演讲①：presentation 结构与开场」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
-· ✓ 合格线（自己判定）：录音回放能听出 3 个该改的地方；开场没有「Hello everyone, today I will talk about」这种套话
-· 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2月13日 周六 ◆寒假
-────────────
-14:00-15:00 应用数学
-术语与格式 S1 Ch1 数据的表示 §1.5
-· 速览 §1.5 不同数据表示方法的比较（p.20，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 15 条）：[[04_统计 S1#Ch1 Representation of data 数据的表示]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>2月14日 周日 ◆寒假
-────────────
-14:00-15:00 复习/测试
-· 回顾：P1 Ch9 ｜ Phy Ch9 ｜ S1 Ch1
-· Anki 术语卡 15′ + 错题本整理
-· 预习下周内容，制定周计划
-20:00-21:00 进阶数学
-章末复习 FM Ch7 数学归纳法
-· 章末复习题 End-of-chapter review p.151，限时 30 分钟
-· 本章要会：能写标准归纳法三步并证明整除性命题
-· 过关自测：EOC 自测≥70%（这套书对标 A 档）；公式卡默写全对；能对错题口述「我错在哪一步」
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="178" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2月15日 周一 ◆寒假
-────────────
-14:00-15:00 纯数
-术语与格式 P2/3 Ch1 代数 §1.1、§1.2、§1.3、§1.4
-· 速览 §1.1 绝对值函数、§1.2 线性函数的绝对值图像、§1.3 绝对值不等式、§1.4 多项式的除法（p.2、p.7、p.8、p.11，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. modulus function, absolute value = 绝对值函数
-· 2. modulus equation / modulus inequality = 绝对值方程／不等式
-· 3. polynomial = 多项式
-· 4. degree of a polynomial = 多项式的次数
-· 5. dividend = 被除式
-· 6. divisor = 除式
-· 7. quotient = 商
-· 8. remainder = 余数／余式
-· 9. division algorithm for polynomials = 多项式除法算式
-· 10. factor theorem = 因式定理
-· 11. remainder theorem = 余数定理
-· 12. proper / improper algebraic fraction = 真／假分式
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch1 Algebra 代数]]（本章共 12 条）
-15:15-16:15 纯数
-格式训练 P2/3 Ch1 代数（§1.1、§1.2）
-· Ex 1A 题 1–9（约 24 分钟，p.6）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 1B 题 1–8（约 22 分钟，p.8）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2月16日 周二 ◆寒假
-────────────
-14:00-15:00 物理
-格式训练 Phy Ch9 基尔霍夫定律（§9.1、§9.2）
-· 节末 Questions 题 全部（约 25 分钟，p.249）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.251）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-15:15-16:15 物理
-章末复习 Phy Ch9 基尔霍夫定律
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：基尔霍夫定律与电路求解、电动势与内阻
-· 过关自测：能对回路列 KVL；能算端电压 U=ε−Ir；Chapter 9 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2月17日 周三 ◆寒假
-────────────
-14:00-15:00 纯数
-格式训练 P2/3 Ch1 代数（§1.3、§1.4）
-· Ex 1C 题 1–6（约 19 分钟，p.10）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 1D 题 1–7（约 20 分钟，p.13）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟
-15:15-16:15 纯数
-术语与格式 P2/3 Ch1 代数 §1.5、§1.6
-· 速览 §1.5 因式定理、§1.6 余数定理（p.14、p.18，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[02_纯数学 P2-3#Ch1 Algebra 代数]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2月18日 周四 ◆寒假
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch10 电阻与电阻率 §10.1、§10.2、§10.3、§10.4
-· 速览 §10.1 金属导体的 I–V 特性、§10.2 欧姆定律、§10.3 电阻与温度、§10.4 电阻率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. Ohm's law = 欧姆定律
-· 2. I–V characteristic = 伏安特性
-· 3. ohmic conductor = 欧姆导体
-· 4. filament lamp = 白炽灯
-· 5. diode = 二极管
-· 6. forward bias = 正向偏置
-· 7. reverse bias = 反向偏置
-· 8. resistivity = 电阻率
-· 9. cross-sectional area = 横截面积
-· 全部抄完后回看一遍：[[06_物理#Ch10 Resistance and resistivity 电阻与电阻率]]（本章共 9 条）
-15:15-16:15 物理
-格式训练 Phy Ch10 电阻与电阻率（§10.1、§10.2）
-· 节末 Questions 题 全部（约 25 分钟，p.271）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.273）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
@@ -5447,7 +5558,7 @@
         <is>
           <t>2月19日 周五 ◆寒假
 ────────────
-14:00-15:00 学术英语
+14:00-15:15 学术英语
 EAP 24 学术演讲②：幻灯片设计与视觉辅助
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：自己 EAP 23 写的大纲；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -5455,7 +5566,7 @@
 · ④ 固化（10 分钟）：术语进 Anki → 产物存进 Obsidian「EAP/EAP-24 学术演讲②：幻灯片设计与视觉辅助」→ 勾掉 00_学术英语总览 §3 的勾选框 → 写一句「下次开口先说什么」
 · ✓ 合格线（自己判定）：每张幻灯片上没有一个完整句子（幻灯片不是提词器）
 · 本类（口语类）的合格线口径与硬标准：Obsidian「EAP/03_专题学习法」§2；笔记模板见「EAP/_模板 EAP 专题笔记」
-15:15-16:15 学术英语
+15:15-16:30 学术英语
 EAP 25 数学与物理术语英汉对照复习（配 Anki）
 · ① 回收（10 分钟）：合上笔记口头复述上一节要点；读上次的产物，用红笔标出 1 处要改
 · ② 输入（25 分钟）：Anki 里的数理术语牌组 + 本书 EAP 文件夹；边看边写康奈尔笔记（左栏关键词 / 右栏细节 / 底部一句话总结）
@@ -5502,7 +5613,7 @@
           <t>2月21日 周日 ◆寒假
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch1 ｜ Phy Ch10 ｜ S1 Ch2
+· 回顾：P1 Ch9 ｜ Phy Ch8 ｜ S1 Ch2
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -5526,72 +5637,48 @@
           <t>2月22日 周一
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch1 代数
-· 章末复习题 End-of-chapter review p.22，限时 30 分钟
-· 本章要会：指数与对数运算法则、解指数/对数方程与不等式
-· 过关自测：默写 3 条对数法则；Ex 1A–1F 错题清零；能判断写出 log 时定义域的限制
+格式训练 P1 Ch9 积分（§9.7、§9.8）
+· Ex 9G 题 1–10（约 25 分钟，p.262）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 9H 题 1–4（约 16 分钟，p.267）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2月23日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch8 电流 §8.5、§8.6
+· 速览 §8.5 电阻、§8.6 电功率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 16 条）：[[06_物理#Ch8 Electric current 电流]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2月24日 周三
+────────────
+21:00-22:15 纯数
+术语与格式 P1 Ch9 积分 §9.9
+· 速览 §9.9 旋转体体积（p.268，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[01_纯数学 P1#Ch9 Integration 积分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2月25日 周四
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch8 电流
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：电流、电荷守恒、基尔霍夫电流定律
+· 过关自测：能默写 I=Q/t；能在电路图中标出电流方向与大小；Chapter 8 EXAM-STYLE QUESTIONS 限时做完并批改
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2月23日 周二
-────────────
-21:00-22:15 物理
-章末复习 Phy Ch10 电阻与电阻率
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：电阻、电阻率、温度对电阻的影响
-· 过关自测：能默写 R=ρl/A；能画 I–V 图并区分欧姆/非欧姆器件；Chapter 10 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>2月24日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch2 对数与指数函数 §2.1、§2.2、§2.3、§2.4
-· 速览 §2.1 以 10 为底的对数、§2.2 以 a 为底的对数、§2.3 对数的运算法则、§2.4 解对数方程（p.26、p.30、p.33、p.35，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. logarithm (log) = 对数
-· 2. base = 底数
-· 3. index, exponent = 指数
-· 4. laws of logarithms = 对数运算法则
-· 5. natural logarithm = 自然对数
-· 6. natural exponential function = 自然指数函数
-· 7. common logarithm = 常用对数
-· 8. exponential equation = 指数方程
-· 9. exponential inequality = 指数不等式
-· 10. inverse function = 反函数
-· 11. transforming to linear form = 化为线性形式
-· 12. gradient = 斜率／梯度
-· 13. intercept = 截距
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch2 Logarithmic and exponential functions 对数与指数函数]]（本章共 13 条）</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2月25日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch11 实用电路 §11.1、§11.2、§11.3、§11.4
-· 速览 §11.1 内阻、§11.2 分压器、§11.3 传感器、§11.4 电位器电路（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. internal resistance = 内阻
-· 2. terminal p.d. = 端电压
-· 3. lost volts = 内压降
-· 4. e.m.f. = 电动势
-· 5. potential divider = 分压器
-· 6. potentiometer = 电位器
-· 7. thermistor = 热敏电阻
-· 8. light-dependent resistor (LDR) = 光敏电阻
-· 9. sensor = 传感器
-· 10. null method = 零示法
-· 全部抄完后回看一遍：[[06_物理#Ch11 Practical circuits 实用电路]]（本章共 10 条）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -5712,13 +5799,12 @@
           <t>3月1日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch2 对数与指数函数（§2.1、§2.2）
-· Ex 2A 题 1–7（约 20 分钟，p.29）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2B 题 1–9（约 24 分钟，p.32）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+章末复习 P1 Ch9 积分
+· 章末复习题 End-of-chapter review p.276，限时 30 分钟
+· 本章要会：不定积分与定积分、面积与体积、换元与分部积分
+· 过关自测：能默写 ∫xⁿ、∫sin、∫cos、∫eˣ 的积分表；Ex 9A–9I 错题清零；能用定积分求一条曲线与 x 轴围成的面积
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -5726,13 +5812,21 @@
           <t>3月2日 周二
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch11 实用电路（§11.1、§11.2）
-· 节末 Questions 题 全部（约 25 分钟，p.292）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.295）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 Phy Ch9 基尔霍夫定律 §9.1、§9.2、§9.3、§9.4
+· 速览 §9.1 基尔霍夫第一定律、§9.2 基尔霍夫第二定律、§9.3 基尔霍夫定律的应用、§9.4 电阻的组合（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. Kirchhoff's first law = 基尔霍夫第一定律
+· 2. Kirchhoff's second law = 基尔霍夫第二定律
+· 3. junction = 节点
+· 4. loop = 回路
+· 5. conservation of charge = 电荷守恒
+· 6. conservation of energy = 能量守恒
+· 7. series = 串联
+· 8. parallel = 并联
+· 9. combined resistance = 总电阻
+· 10. reciprocal = 倒数
+· 全部抄完后回看一遍：[[06_物理#Ch9 Kirchhoff's laws 基尔霍夫定律]]（本章共 10 条）</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -5740,16 +5834,23 @@
           <t>3月3日 周三
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch2 对数与指数函数（§2.3、§2.4）
-· Ex 2C 题 1–13（约 30 分钟，p.34）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2D 题 1–10（约 25 分钟，p.37）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-术语与格式 P2/3 Ch2 对数与指数函数 §2.5、§2.6、§2.7、§2.8
-· 速览 §2.5 解指数方程、§2.6 解指数不等式、§2.7 自然对数、§2.8 把关系式化为线性形式（p.38、p.40、p.42、p.44，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 13 条）：[[02_纯数学 P2-3#Ch2 Logarithmic and exponential functions 对数与指数函数]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+术语与格式 P2/3 Ch1 代数 §1.1、§1.2、§1.3、§1.4
+· 速览 §1.1 绝对值函数、§1.2 线性函数的绝对值图像、§1.3 绝对值不等式、§1.4 多项式的除法（p.2、p.7、p.8、p.11，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. modulus function, absolute value = 绝对值函数
+· 2. modulus equation / modulus inequality = 绝对值方程／不等式
+· 3. polynomial = 多项式
+· 4. degree of a polynomial = 多项式的次数
+· 5. dividend = 被除式
+· 6. divisor = 除式
+· 7. quotient = 商
+· 8. remainder = 余数／余式
+· 9. division algorithm for polynomials = 多项式除法算式
+· 10. factor theorem = 因式定理
+· 11. remainder theorem = 余数定理
+· 12. proper / improper algebraic fraction = 真／假分式
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch1 Algebra 代数]]（本章共 12 条）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -5757,32 +5858,13 @@
           <t>3月4日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch11 实用电路
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：分压与分流、电位器、内阻影响
-· 过关自测：能设计分压电路；能算串联/并联等效电阻；Chapter 11 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-术语与格式 Phy Ch12 波 §12.1、§12.2、§12.3、§12.4
-· 速览 §12.1 描述波、§12.2 横波与纵波、§12.3 波的能量、§12.4 波速（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 15 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. wave = 波
-· 2. transverse wave = 横波
-· 3. longitudinal wave = 纵波
-· 4. amplitude = 振幅
-· 5. wavelength = 波长
-· 6. frequency = 频率
-· 7. period = 周期
-· 8. displacement = 位移
-· 9. intensity = 强度
-· 10. Doppler effect = 多普勒效应
-· 11. electromagnetic spectrum = 电磁波谱
-· 12. polarisation = 偏振
-· 13. Malus's law = 马吕斯定律
-· 14. plane of polarisation = 偏振面
-· 15. order of magnitude = 数量级
-· 全部抄完后回看一遍：[[06_物理#Ch12 Waves 波]]（本章共 15 条）</t>
+格式训练 Phy Ch9 基尔霍夫定律（§9.1、§9.2）
+· 节末 Questions 题 全部（约 25 分钟，p.249）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.251）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -5821,7 +5903,7 @@
 · 11. measure of variation = 离散程度度量
 · 12. coding = 编码
 · 全部抄完后回看一遍：[[04_统计 S1#Ch3 Measures of variation 离散程度的度量]]（本章共 12 条）
-20:00-21:00 应用数学
+20:00-21:05 应用数学
 格式训练 S1 Ch3 离散程度的度量（§3.1、§3.2）
 · Ex 3A 题 1–13（约 30 分钟，p.61）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -5836,7 +5918,7 @@
           <t>3月7日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch2 ｜ Phy Ch12 ｜ S1 Ch3
+· 回顾：P2/3 Ch1 ｜ Phy Ch9 ｜ S1 Ch3
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -5860,10 +5942,10 @@
           <t>3月8日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch2 对数与指数函数（§2.5、§2.6）
-· Ex 2E 题 1–13（约 30 分钟，p.39）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 2F 题 1–7（约 20 分钟，p.41）
+格式训练 P2/3 Ch1 代数（§1.1、§1.2）
+· Ex 1A 题 1–9（约 24 分钟，p.6）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1B 题 1–8（约 22 分钟，p.8）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -5874,13 +5956,12 @@
           <t>3月9日 周二
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch12 波（§12.1、§12.2）
-· 节末 Questions 题 全部（约 25 分钟，p.313）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.314）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+章末复习 Phy Ch9 基尔霍夫定律
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：基尔霍夫定律与电路求解、电动势与内阻
+· 过关自测：能对回路列 KVL；能算端电压 U=ε−Ir；Chapter 9 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -5888,12 +5969,13 @@
           <t>3月10日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch2 对数与指数函数
-· 章末复习题 End-of-chapter review p.50，限时 30 分钟
-· 本章要会：eˣ 与 ln x 的图象与性质、把它们用于建模（增长/衰减）
-· 过关自测：能画 y=eˣ 与 y=ln x 并说出互为反函数；Ex 2A–2H 错题清零；能把「翻倍时间」问题列成指数方程
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 P2/3 Ch1 代数（§1.3、§1.4）
+· Ex 1C 题 1–6（约 19 分钟，p.10）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 1D 题 1–7（约 20 分钟，p.13）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -5901,13 +5983,20 @@
           <t>3月11日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch12 波（§12.3、§12.4）
-· 节末 Questions 题 全部（约 25 分钟，p.316）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.319）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 Phy Ch10 电阻与电阻率 §10.1、§10.2、§10.3、§10.4
+· 速览 §10.1 金属导体的 I–V 特性、§10.2 欧姆定律、§10.3 电阻与温度、§10.4 电阻率（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. Ohm's law = 欧姆定律
+· 2. I–V characteristic = 伏安特性
+· 3. ohmic conductor = 欧姆导体
+· 4. filament lamp = 白炽灯
+· 5. diode = 二极管
+· 6. forward bias = 正向偏置
+· 7. reverse bias = 反向偏置
+· 8. resistivity = 电阻率
+· 9. cross-sectional area = 横截面积
+· 全部抄完后回看一遍：[[06_物理#Ch10 Resistance and resistivity 电阻与电阻率]]（本章共 9 条）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -5965,7 +6054,7 @@
           <t>3月14日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch2 ｜ Phy Ch12 ｜ S1 Ch4
+· 回顾：P2/3 Ch1 ｜ Phy Ch10 ｜ S1 Ch4
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -5985,21 +6074,10 @@
           <t>3月15日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P2/3 Ch3 三角学 §3.1、§3.2、§3.3、§3.4
-· 速览 §3.1 cosec / sec / cot、§3.2 和角公式、§3.3 倍角公式、§3.4 进阶三角恒等式（p.53、p.58、p.61、p.66，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. cosecant, cosec = 余割
-· 2. secant, sec = 正割
-· 3. cotangent, cot = 余切
-· 4. reciprocal trigonometric ratios = 倒数三角比
-· 5. trigonometrical identities = 三角恒等式
-· 6. compound angle formulae = 和角公式
-· 7. double angle formulae = 倍角公式
-· 8. auxiliary angle / R-form = 辅助角／R 形式
-· 9. exact value = 精确值
-· 10. maximum / minimum value = 最大值／最小值
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch3 Trigonometry 三角学]]（本章共 10 条）</t>
+术语与格式 P2/3 Ch1 代数 §1.5、§1.6
+· 速览 §1.5 因式定理、§1.6 余数定理（p.14、p.18，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[02_纯数学 P2-3#Ch1 Algebra 代数]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -6007,10 +6085,13 @@
           <t>3月16日 周二
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch12 波 §12.5、§12.6、§12.7、§12.8
-· 速览 §12.5 声波的多普勒效应、§12.6 电磁波、§12.7 电磁辐射、§12.8 数量级（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 15 条）：[[06_物理#Ch12 Waves 波]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 Phy Ch10 电阻与电阻率（§10.1、§10.2）
+· 节末 Questions 题 全部（约 25 分钟，p.271）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.273）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -6018,18 +6099,12 @@
           <t>3月17日 周三
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch3 三角学（§3.1、§3.2）
-· Ex 3A 题 1–14（约 31 分钟，p.56）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 3B 题 1–17（约 35 分钟，p.60）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-格式训练 P2/3 Ch3 三角学（§3.3、§3.4）
-· Ex 3C 题 1–19（约 35 分钟，p.64）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 3D 题 1–6（约 19 分钟，p.67）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+章末复习 P2/3 Ch1 代数
+· 章末复习题 End-of-chapter review p.22，限时 30 分钟
+· 本章要会：指数与对数运算法则、解指数/对数方程与不等式
+· 过关自测：默写 3 条对数法则；Ex 1A–1F 错题清零；能判断写出 log 时定义域的限制
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -6037,18 +6112,12 @@
           <t>3月18日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch12 波（§12.5、§12.6）
-· 节末 Questions 题 全部（约 25 分钟，p.320）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.323）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-格式训练 Phy Ch12 波（§12.7、§12.8）
-· 节末 Questions 题 全部（约 25 分钟，p.325）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.326）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+章末复习 Phy Ch10 电阻与电阻率
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：电阻、电阻率、温度对电阻的影响
+· 过关自测：能默写 R=ρl/A；能画 I–V 图并区分欧姆/非欧姆器件；Chapter 10 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -6077,7 +6146,7 @@
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
-20:00-21:00 应用数学
+20:00-21:05 应用数学
 格式训练 S1 Ch4 概率（§4.3、§4.4）
 · Ex 4C 题 1–16（约 34 分钟，p.102）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -6092,7 +6161,7 @@
           <t>3月21日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch3 ｜ Phy Ch12 ｜ S1 Ch4
+· 回顾：P2/3 Ch1 ｜ Phy Ch10 ｜ S1 Ch4
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -6111,10 +6180,24 @@
           <t>3月22日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P2/3 Ch3 三角学 §3.5
-· 速览 §3.5 a sinθ + b cosθ 化为 R sin(θ±α)（p.68，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 10 条）：[[02_纯数学 P2-3#Ch3 Trigonometry 三角学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+术语与格式 P2/3 Ch2 对数与指数函数 §2.1、§2.2、§2.3、§2.4
+· 速览 §2.1 以 10 为底的对数、§2.2 以 a 为底的对数、§2.3 对数的运算法则、§2.4 解对数方程（p.26、p.30、p.33、p.35，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. logarithm (log) = 对数
+· 2. base = 底数
+· 3. index, exponent = 指数
+· 4. laws of logarithms = 对数运算法则
+· 5. natural logarithm = 自然对数
+· 6. natural exponential function = 自然指数函数
+· 7. common logarithm = 常用对数
+· 8. exponential equation = 指数方程
+· 9. exponential inequality = 指数不等式
+· 10. inverse function = 反函数
+· 11. transforming to linear form = 化为线性形式
+· 12. gradient = 斜率／梯度
+· 13. intercept = 截距
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch2 Logarithmic and exponential functions 对数与指数函数]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -6122,10 +6205,21 @@
           <t>3月23日 周二
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch12 波 §12.9、§12.10
-· 速览 §12.9 电磁波的本质、§12.10 偏振（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 15 条）：[[06_物理#Ch12 Waves 波]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+术语与格式 Phy Ch11 实用电路 §11.1、§11.2、§11.3、§11.4
+· 速览 §11.1 内阻、§11.2 分压器、§11.3 传感器、§11.4 电位器电路（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. internal resistance = 内阻
+· 2. terminal p.d. = 端电压
+· 3. lost volts = 内压降
+· 4. e.m.f. = 电动势
+· 5. potential divider = 分压器
+· 6. potentiometer = 电位器
+· 7. thermistor = 热敏电阻
+· 8. light-dependent resistor (LDR) = 光敏电阻
+· 9. sensor = 传感器
+· 10. null method = 零示法
+· 全部抄完后回看一遍：[[06_物理#Ch11 Practical circuits 实用电路]]（本章共 10 条）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -6133,12 +6227,13 @@
           <t>3月24日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch3 三角学
-· 章末复习题 End-of-chapter review p.74，限时 30 分钟
-· 本章要会：反三角与小角度近似、R 形式求解、更复杂的三角方程
-· 过关自测：能默写 asin/acos/atan 的值域（这是考点）；Ex 3A–3E 错题清零；能把 a sinθ+b cosθ 化成 R sin(θ+α)
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 P2/3 Ch2 对数与指数函数（§2.1、§2.2）
+· Ex 2A 题 1–7（约 20 分钟，p.29）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2B 题 1–9（约 24 分钟，p.32）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -6146,12 +6241,13 @@
           <t>3月25日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch12 波
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：波的基本性质：频率、波长、波速、横波纵波、电磁波
-· 过关自测：能默写 v=fλ；能区分横波纵波与偏振；能读示波器波形；Chapter 12 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 Phy Ch11 实用电路（§11.1、§11.2）
+· 节末 Questions 题 全部（约 25 分钟，p.292）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.295）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -6214,23 +6310,13 @@
           <t>3月29日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P2/3 Ch4 微分 §4.1、§4.2、§4.3、§4.4
-· 速览 §4.1 乘积法则、§4.2 商法则、§4.3 指数函数的导数、§4.4 自然对数函数的导数（p.81、p.84、p.87、p.91，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. derivative, gradient function = 导数／梯度函数
-· 2. chain rule = 链式法则
-· 3. product rule = 乘积法则
-· 4. quotient rule = 商法则
-· 5. explicit function = 显函数
-· 6. implicit function = 隐函数
-· 7. implicit differentiation = 隐函数求导
-· 8. parametric equations = 参数方程
-· 9. parameter = 参数
-· 10. tangent = 切线
-· 11. normal = 法线
-· 12. composite function = 复合函数
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch4 Differentiation 微分]]（本章共 12 条）</t>
+格式训练 P2/3 Ch2 对数与指数函数（§2.3、§2.4）
+· Ex 2C 题 1–13（约 30 分钟，p.34）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2D 题 1–10（约 25 分钟，p.37）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -6238,24 +6324,12 @@
           <t>3月30日 周二
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch13 波的叠加 §13.1、§13.2、§13.3、§13.4
-· 速览 §13.1 波的叠加原理、§13.2 波的衍射、§13.3 干涉、§13.4 杨氏双缝实验（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. superposition = 叠加
-· 2. diffraction = 衍射
-· 3. interference = 干涉
-· 4. coherent = 相干
-· 5. path difference = 波程差
-· 6. constructive interference = 相长干涉
-· 7. destructive interference = 相消干涉
-· 8. monochromatic = 单色
-· 9. fringe = 条纹
-· 10. double slit = 双缝
-· 11. diffraction grating = 衍射光栅
-· 12. grating spacing = 光栅间距
-· 13. order = 级次
-· 全部抄完后回看一遍：[[06_物理#Ch13 Superposition of waves 波的叠加]]（本章共 13 条）</t>
+章末复习 Phy Ch11 实用电路
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：分压与分流、电位器、内阻影响
+· 过关自测：能设计分压电路；能算串联/并联等效电阻；Chapter 11 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -6263,18 +6337,10 @@
           <t>3月31日 周三
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch4 微分（§4.1、§4.2）
-· Ex 4A 题 1–8（约 22 分钟，p.83）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 4B 题 1–13（约 30 分钟，p.87）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-格式训练 P2/3 Ch4 微分（§4.3、§4.4）
-· Ex 4C 题 1–14（约 31 分钟，p.90）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 4D 题 1–12（约 28 分钟，p.94）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+术语与格式 P2/3 Ch2 对数与指数函数 §2.5、§2.6、§2.7、§2.8
+· 速览 §2.5 解指数方程、§2.6 解指数不等式、§2.7 自然对数、§2.8 把关系式化为线性形式（p.38、p.40、p.42、p.44，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[02_纯数学 P2-3#Ch2 Logarithmic and exponential functions 对数与指数函数]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
@@ -6351,18 +6417,26 @@
           <t>4月1日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch13 波的叠加（§13.1、§13.2）
-· 节末 Questions 题 全部（约 25 分钟，p.341）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.343）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-格式训练 Phy Ch13 波的叠加（§13.3、§13.4）
-· 节末 Questions 题 全部（约 25 分钟，p.347）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.356）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+术语与格式 Phy Ch12 波 §12.1、§12.2、§12.3、§12.4
+· 速览 §12.1 描述波、§12.2 横波与纵波、§12.3 波的能量、§12.4 波速（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 15 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. wave = 波
+· 2. transverse wave = 横波
+· 3. longitudinal wave = 纵波
+· 4. amplitude = 振幅
+· 5. wavelength = 波长
+· 6. frequency = 频率
+· 7. period = 周期
+· 8. displacement = 位移
+· 9. intensity = 强度
+· 10. Doppler effect = 多普勒效应
+· 11. electromagnetic spectrum = 电磁波谱
+· 12. polarisation = 偏振
+· 13. Malus's law = 马吕斯定律
+· 14. plane of polarisation = 偏振面
+· 15. order of magnitude = 数量级
+· 全部抄完后回看一遍：[[06_物理#Ch12 Waves 波]]（本章共 15 条）</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -6414,7 +6488,7 @@
           <t>4月4日 周日 ◆清明节假期
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch4 ｜ Phy Ch13 ｜ S1 Ch5
+· 回顾：P2/3 Ch2 ｜ Phy Ch12 ｜ S1 Ch5
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -6434,18 +6508,20 @@
           <t>4月5日 周一 ◆清明节假期
 ────────────
 14:00-15:00 纯数
-术语与格式 P2/3 Ch4 微分 §4.5、§4.6、§4.7
-· 速览 §4.5 三角函数的导数、§4.6 隐函数求导、§4.7 参数方程求导（p.95、p.99、p.103，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[02_纯数学 P2-3#Ch4 Differentiation 微分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
+格式训练 P2/3 Ch2 对数与指数函数（§2.5、§2.6）
+· Ex 2E 题 1–13（约 30 分钟，p.39）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 2F 题 1–7（约 20 分钟，p.41）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 纯数
-格式训练 P2/3 Ch4 微分（§4.5、§4.6）
-· Ex 4E 题 1–17（约 35 分钟，p.98）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 4F 题 1–14（约 31 分钟，p.101）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+章末复习 P2/3 Ch2 对数与指数函数
+· 章末复习题 End-of-chapter review p.50，限时 30 分钟
+· 本章要会：eˣ 与 ln x 的图象与性质、把它们用于建模（增长/衰减）
+· 过关自测：能画 y=eˣ 与 y=ln x 并说出互为反函数；Ex 2A–2H 错题清零；能把「翻倍时间」问题列成指数方程
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -6453,10 +6529,13 @@
           <t>4月6日 周二
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch13 波的叠加 §13.5
-· 速览 §13.5 衍射光栅（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 13 条）：[[06_物理#Ch13 Superposition of waves 波的叠加]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 Phy Ch12 波（§12.1、§12.2）
+· 节末 Questions 题 全部（约 25 分钟，p.313）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.314）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -6464,12 +6543,21 @@
           <t>4月7日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch4 微分
-· 章末复习题 End-of-chapter review p.108，限时 30 分钟
-· 本章要会：乘积/商/链式法则的综合运用、隐函数与参数方程二阶导、导数用于变化率
-· 过关自测：参数方程求二阶导能独立做对；Ex 4A–4G 错题清零；能说清隐函数求导何时必须链式
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 P2/3 Ch3 三角学 §3.1、§3.2、§3.3、§3.4
+· 速览 §3.1 cosec / sec / cot、§3.2 和角公式、§3.3 倍角公式、§3.4 进阶三角恒等式（p.53、p.58、p.61、p.66，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. cosecant, cosec = 余割
+· 2. secant, sec = 正割
+· 3. cotangent, cot = 余切
+· 4. reciprocal trigonometric ratios = 倒数三角比
+· 5. trigonometrical identities = 三角恒等式
+· 6. compound angle formulae = 和角公式
+· 7. double angle formulae = 倍角公式
+· 8. auxiliary angle / R-form = 辅助角／R 形式
+· 9. exact value = 精确值
+· 10. maximum / minimum value = 最大值／最小值
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch3 Trigonometry 三角学]]（本章共 10 条）</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -6477,12 +6565,13 @@
           <t>4月8日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch13 波的叠加
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：叠加与干涉、双缝、衍射光栅
-· 过关自测：能默写 λ=ax/D；能判断相干条件；能算条纹间距；Chapter 13 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 Phy Ch12 波（§12.3、§12.4）
+· 节末 Questions 题 全部（约 25 分钟，p.316）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.319）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -6531,7 +6620,7 @@
           <t>4月11日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch4 ｜ Phy Ch13 ｜ S1 Ch6
+· 回顾：P2/3 Ch3 ｜ Phy Ch12 ｜ S1 Ch6
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -6550,22 +6639,13 @@
           <t>4月12日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P2/3 Ch5 积分 §5.1、§5.2、§5.3、§5.4
-· 速览 §5.1 指数函数的积分、§5.2 1/(ax+b) 的积分、§5.3 sin/cos/sec²(ax+b) 的积分、§5.4 进一步的三角函数积分（p.112、p.115、p.118、p.121，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. integration = 积分
-· 2. indefinite integral = 不定积分
-· 3. definite integral = 定积分
-· 4. arbitrary constant of integration = 积分任意常数
-· 5. integrand = 被积函数
-· 6. validity = 适用范围
-· 7. trapezium rule = 梯形法则
-· 8. strip / interval = 条／区间
-· 9. ordinate = 纵坐标值
-· 10. overestimate / underestimate = 高估／低估
-· 11. double angle identities = 倍角公式
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch5 Integration 积分]]（本章共 11 条）</t>
+格式训练 P2/3 Ch3 三角学（§3.1、§3.2）
+· Ex 3A 题 1–14（约 31 分钟，p.56）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3B 题 1–17（约 35 分钟，p.60）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -6573,20 +6653,10 @@
           <t>4月13日 周二
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch14 驻波 §14.1、§14.2、§14.3、§14.4
-· 速览 §14.1 从行波到驻波、§14.2 波节与波腹、§14.3 驻波的形成、§14.4 测定声波的波长与速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. stationary wave = 驻波
-· 2. standing wave = 驻波
-· 3. node = 波节
-· 4. antinode = 波腹
-· 5. progressive wave = 行进波
-· 6. fundamental frequency = 基频
-· 7. first harmonic = 一次谐波
-· 8. in phase = 同相
-· 9. antiphase = 反相
-· 全部抄完后回看一遍：[[06_物理#Ch14 Stationary waves 驻波]]（本章共 9 条）</t>
+术语与格式 Phy Ch12 波 §12.5、§12.6、§12.7、§12.8
+· 速览 §12.5 声波的多普勒效应、§12.6 电磁波、§12.7 电磁辐射、§12.8 数量级（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 15 条）：[[06_物理#Ch12 Waves 波]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -6594,10 +6664,10 @@
           <t>4月14日 周三
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch5 积分（§5.1、§5.2）
-· Ex 5A 题 1–12（约 28 分钟，p.113）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 5B 题 1–10（约 25 分钟，p.117）
+格式训练 P2/3 Ch3 三角学（§3.3、§3.4）
+· Ex 3C 题 1–19（约 35 分钟，p.64）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 3D 题 1–6（约 19 分钟，p.67）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -6608,18 +6678,13 @@
           <t>4月15日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch14 驻波（§14.1、§14.2）
-· 节末 Questions 题 全部（约 25 分钟，p.369）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.370）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-章末复习 Phy Ch14 驻波
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：驻波与共振、弦与气柱的基频与泛音
-· 过关自测：能画各阶驻波图；能算弦频率 f=(1/2L)√(T/μ)；Chapter 14 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 Phy Ch12 波（§12.5、§12.6）
+· 节末 Questions 题 全部（约 25 分钟，p.320）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.323）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -6640,7 +6705,7 @@
         <is>
           <t>4月17日 周六
 ────────────
-14:00-15:00 应用数学
+14:00-15:15 应用数学
 格式训练 S1 Ch6 概率分布（§6.1、§6.2）
 · Ex 6A 题 1–20（约 35 分钟，p.153）
 · 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
@@ -6662,7 +6727,7 @@
           <t>4月18日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch5 ｜ Phy Ch14 ｜ S1 Ch6
+· 回顾：P2/3 Ch3 ｜ Phy Ch12 ｜ S1 Ch6
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -6686,16 +6751,10 @@
           <t>4月19日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch5 积分（§5.3、§5.4）
-· Ex 5C 题 1–10（约 25 分钟，p.120）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 5D 题 1–12（约 28 分钟，p.125）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-术语与格式 P2/3 Ch5 积分 §5.5
-· 速览 §5.5 梯形法则（p.126，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 11 条）：[[02_纯数学 P2-3#Ch5 Integration 积分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+术语与格式 P2/3 Ch3 三角学 §3.5
+· 速览 §3.5 a sinθ + b cosθ 化为 R sin(θ±α)（p.68，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 10 条）：[[02_纯数学 P2-3#Ch3 Trigonometry 三角学]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -6703,33 +6762,13 @@
           <t>4月20日 周二
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch15 原子结构 §15.1、§15.2、§15.3、§15.4
-· 速览 §15.1 观察原子内部、§15.2 α 粒子散射与原子核、§15.3 原子的简单模型、§15.4 核子与电子（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 22 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. nucleus = 原子核
-· 2. nucleon = 核子
-· 3. proton = 质子
-· 4. neutron = 中子
-· 5. proton number = 质子数
-· 6. nucleon number = 核子数
-· 7. isotope = 同位素
-· 8. nuclide = 核素
-· 9. α-particle scattering = α 粒子散射
-· 10. radioactivity = 放射性
-· 11. β-particle = β 粒子
-· 12. γ-radiation = γ 射线
-· 13. neutrino = 中微子
-· 14. antineutrino = 反中微子
-· 15. positron = 正电子
-· 16. quark = 夸克
-· 17. lepton = 轻子
-· 18. hadron = 强子
-· 19. baryon = 重子
-· 20. meson = 介子
-· 21. mass–energy = 质能
-· 22. annihilation = 湮灭
-· 全部抄完后回看一遍：[[06_物理#Ch15 Atomic structure 原子结构]]（本章共 22 条）</t>
+格式训练 Phy Ch12 波（§12.7、§12.8）
+· 节末 Questions 题 全部（约 25 分钟，p.325）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.326）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -6737,10 +6776,10 @@
           <t>4月21日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch5 积分
-· 章末复习题 End-of-chapter review p.131，限时 30 分钟
-· 本章要会：分部积分、分式拆分法、定积分的换元、梯形法则数值积分
-· 过关自测：分部积分的 LIATE 顺序能默写；梯形法则能徒手算 4 条带；Ex 5A–5E 错题清零
+章末复习 P2/3 Ch3 三角学
+· 章末复习题 End-of-chapter review p.74，限时 30 分钟
+· 本章要会：反三角与小角度近似、R 形式求解、更复杂的三角方程
+· 过关自测：能默写 asin/acos/atan 的值域（这是考点）；Ex 3A–3E 错题清零；能把 a sinθ+b cosθ 化成 R sin(θ+α)
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
@@ -6750,13 +6789,10 @@
           <t>4月22日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch15 原子结构（§15.1、§15.2）
-· 节末 Questions 题 全部（约 25 分钟，p.389）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.392）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 Phy Ch12 波 §12.9、§12.10
+· 速览 §12.9 电磁波的本质、§12.10 偏振（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 15 条）：[[06_物理#Ch12 Waves 波]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -6825,21 +6861,23 @@
           <t>4月26日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P2/3 Ch6 方程的数值解法 §6.1、§6.2、§6.3
-· 速览 §6.1 寻找初始近似值、§6.2 改进解的精度、§6.3 迭代法的跨领域应用（p.135、p.140、p.149，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. root = 根
-· 2. approximation = 近似值
-· 3. iterative process / iteration = 迭代法
-· 4. converges = 收敛
-· 5. diverges = 发散
-· 6. change of sign = 变号
-· 7. continuous = 连续
-· 8. starting point / initial value = 初始近似值
-· 9. rearrangement = 变形／重新整理
-· 10. prescribed degree of accuracy = 指定精度
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch6 Numerical solutions of equations 方程的数值解法]]（本章共 10 条）</t>
+术语与格式 P2/3 Ch4 微分 §4.1、§4.2、§4.3、§4.4
+· 速览 §4.1 乘积法则、§4.2 商法则、§4.3 指数函数的导数、§4.4 自然对数函数的导数（p.81、p.84、p.87、p.91，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. derivative, gradient function = 导数／梯度函数
+· 2. chain rule = 链式法则
+· 3. product rule = 乘积法则
+· 4. quotient rule = 商法则
+· 5. explicit function = 显函数
+· 6. implicit function = 隐函数
+· 7. implicit differentiation = 隐函数求导
+· 8. parametric equations = 参数方程
+· 9. parameter = 参数
+· 10. tangent = 切线
+· 11. normal = 法线
+· 12. composite function = 复合函数
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch4 Differentiation 微分]]（本章共 12 条）</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -6847,13 +6885,12 @@
           <t>4月27日 周二
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch15 原子结构（§15.3、§15.4）
-· 节末 Questions 题 全部（约 25 分钟，p.393）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.397）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+章末复习 Phy Ch12 波
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：波的基本性质：频率、波长、波速、横波纵波、电磁波
+· 过关自测：能默写 v=fλ；能区分横波纵波与偏振；能读示波器波形；Chapter 12 EXAM-STYLE QUESTIONS 限时做完并批改
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -6861,10 +6898,10 @@
           <t>4月28日 周三
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch6 方程的数值解法（§6.1、§6.2）
-· Ex 6A 题 1–15（约 32 分钟，p.137）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 6B 题 1–14（约 31 分钟，p.146）
+格式训练 P2/3 Ch4 微分（§4.1、§4.2）
+· Ex 4A 题 1–8（约 22 分钟，p.83）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4B 题 1–13（约 30 分钟，p.87）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -6875,16 +6912,24 @@
           <t>4月29日 周四
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch15 原子结构 §15.5、§15.6、§15.7、§15.8
-· 速览 §15.5 原子核内的力、§15.6 放射性的发现、§15.7 放射性物质发出的射线、§15.8 α 与 β 衰变中的能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 22 条）：[[06_物理#Ch15 Atomic structure 原子结构]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
-格式训练 Phy Ch15 原子结构（§15.5、§15.6）
-· 节末 Questions 题 全部（约 25 分钟，p.400）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.401）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+术语与格式 Phy Ch13 波的叠加 §13.1、§13.2、§13.3、§13.4
+· 速览 §13.1 波的叠加原理、§13.2 波的衍射、§13.3 干涉、§13.4 杨氏双缝实验（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. superposition = 叠加
+· 2. diffraction = 衍射
+· 3. interference = 干涉
+· 4. coherent = 相干
+· 5. path difference = 波程差
+· 6. constructive interference = 相长干涉
+· 7. destructive interference = 相消干涉
+· 8. monochromatic = 单色
+· 9. fringe = 条纹
+· 10. double slit = 双缝
+· 11. diffraction grating = 衍射光栅
+· 12. grating spacing = 光栅间距
+· 13. order = 级次
+· 全部抄完后回看一遍：[[06_物理#Ch13 Superposition of waves 波的叠加]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -7008,7 +7053,7 @@
           <t>5月2日 周日 ◆劳动节假期
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch6 ｜ Phy Ch15 ｜ S1 Ch8
+· 回顾：P2/3 Ch4 ｜ Phy Ch13 ｜ S1 Ch8
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -7026,32 +7071,19 @@
         <is>
           <t>5月3日 周一 ◆劳动节假期
 ────────────
-14:00-15:00 纯数
-章末复习 P2/3 Ch6 方程的数值解法
-· 章末复习题 End-of-chapter review p.155，限时 30 分钟
-· 本章要会：用迭代法（不动点/牛顿—拉夫森）求方程近似解
-· 过关自测：能默写牛顿—拉夫森迭代式；能判断迭代是否收敛（|f'(x)|&lt;1）；Ex 6A–6C 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+14:00-15:05 纯数
+格式训练 P2/3 Ch4 微分（§4.3、§4.4）
+· Ex 4C 题 1–14（约 31 分钟，p.90）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4D 题 1–12（约 28 分钟，p.94）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 纯数
-术语与格式 P2/3 Ch7 进阶代数 §7.1、§7.2、§7.3、§7.4
-· 速览 §7.1 假分式、§7.2 部分分式、§7.3 二项式展开 (1+x)^n（n 非正整数）、§7.4 二项式展开 (a+x)^n（n 非正整数）（p.166、p.168、p.174、p.177，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. rational function = 有理函数
-· 2. proper / improper algebraic fraction = 真／假分式
-· 3. partial fractions = 部分分式
-· 4. decompose / decomposition = 分解
-· 5. repeated linear factor = 重线性因式
-· 6. irreducible quadratic factor = 不可约二次因式
-· 7. equating coefficients = 比较系数
-· 8. cover-up method = 遮盖法
-· 9. binomial expansion = 二项式展开
-· 10. general binomial theorem = 广义二项式定理
-· 11. ascending powers = 升幂
-· 12. validity / range of validity = 成立范围
-· 13. identically equal ($\equiv$) = 恒等于
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch7 Further algebra 进阶代数（P3）]]（本章共 13 条）</t>
+术语与格式 P2/3 Ch4 微分 §4.5、§4.6、§4.7
+· 速览 §4.5 三角函数的导数、§4.6 隐函数求导、§4.7 参数方程求导（p.95、p.99、p.103，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 12 条）：[[02_纯数学 P2-3#Ch4 Differentiation 微分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -7059,40 +7091,42 @@
           <t>5月4日 周二 ◆劳动节假期
 ────────────
 14:00-15:00 物理
-格式训练 Phy Ch15 原子结构（§15.7、§15.8）
-· 节末 Questions 题 全部（约 25 分钟，p.402）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.405）
+格式训练 Phy Ch13 波的叠加（§13.1、§13.2）
+· 节末 Questions 题 全部（约 25 分钟，p.341）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.343）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
 15:15-16:15 物理
-术语与格式 Phy Ch15 原子结构 §15.9、§15.10、§15.11、§15.12
-· 速览 §15.9 放射性衰变方程、§15.10 基本粒子、§15.11 粒子家族、§15.12 再看 β 衰变（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 22 条）：[[06_物理#Ch15 Atomic structure 原子结构]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 Phy Ch13 波的叠加（§13.3、§13.4）
+· 节末 Questions 题 全部（约 25 分钟，p.347）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.356）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
           <t>5月5日 周三 ◆劳动节假期
 ────────────
-14:00-15:00 纯数
-格式训练 P2/3 Ch7 进阶代数（§7.1、§7.2）
-· Ex 7A 题 1–4（约 16 分钟，p.167）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 7B 题 1–10（约 25 分钟，p.173）
+14:00-15:15 纯数
+格式训练 P2/3 Ch4 微分（§4.5、§4.6）
+· Ex 4E 题 1–17（约 35 分钟，p.98）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 4F 题 1–14（约 31 分钟，p.101）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟
 15:15-16:15 纯数
-格式训练 P2/3 Ch7 进阶代数（§7.3、§7.4）
-· Ex 7C 题 1–11（约 26 分钟，p.176）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 7D 题 1–8（约 22 分钟，p.178）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+章末复习 P2/3 Ch4 微分
+· 章末复习题 End-of-chapter review p.108，限时 30 分钟
+· 本章要会：乘积/商/链式法则的综合运用、隐函数与参数方程二阶导、导数用于变化率
+· 过关自测：参数方程求二阶导能独立做对；Ex 4A–4G 错题清零；能说清隐函数求导何时必须链式
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -7100,13 +7134,10 @@
           <t>5月6日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch15 原子结构（§15.9、§15.10）
-· 节末 Questions 题 全部（约 25 分钟，p.406）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.407）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 Phy Ch13 波的叠加 §13.5
+· 速览 §13.5 衍射光栅（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[06_物理#Ch13 Superposition of waves 波的叠加]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -7142,7 +7173,7 @@
           <t>5月9日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch7 ｜ Phy Ch15
+· 回顾：P2/3 Ch4 ｜ Phy Ch13
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -7164,62 +7195,70 @@
           <t>5月10日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P2/3 Ch7 进阶代数 §7.5
-· 速览 §7.5 部分分式与二项式展开（p.179，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 13 条）：[[02_纯数学 P2-3#Ch7 Further algebra 进阶代数（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
-章末复习 P2/3 Ch7 进阶代数
-· 章末复习题 End-of-chapter review p.182，限时 30 分钟
-· 本章要会：部分分式、除法算式与余数定理、代数式的组合运算
-· 过关自测：能把真分式拆成部分分式；能处理假分式（先做除法）；Ex 7A–7E 错题清零
+术语与格式 P2/3 Ch5 积分 §5.1、§5.2、§5.3、§5.4
+· 速览 §5.1 指数函数的积分、§5.2 1/(ax+b) 的积分、§5.3 sin/cos/sec²(ax+b) 的积分、§5.4 进一步的三角函数积分（p.112、p.115、p.118、p.121，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. integration = 积分
+· 2. indefinite integral = 不定积分
+· 3. definite integral = 定积分
+· 4. arbitrary constant of integration = 积分任意常数
+· 5. integrand = 被积函数
+· 6. validity = 适用范围
+· 7. trapezium rule = 梯形法则
+· 8. strip / interval = 条／区间
+· 9. ordinate = 纵坐标值
+· 10. overestimate / underestimate = 高估／低估
+· 11. double angle identities = 倍角公式
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch5 Integration 积分]]（本章共 11 条）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>5月11日 周二
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch13 波的叠加
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：叠加与干涉、双缝、衍射光栅
+· 过关自测：能默写 λ=ax/D；能判断相干条件；能算条纹间距；Chapter 13 EXAM-STYLE QUESTIONS 限时做完并批改
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>5月11日 周二
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>5月12日 周三
+────────────
+21:00-22:15 纯数
+格式训练 P2/3 Ch5 积分（§5.1、§5.2）
+· Ex 5A 题 1–12（约 28 分钟，p.113）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5B 题 1–10（约 25 分钟，p.117）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>5月13日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch15 原子结构（§15.11、§15.12）
-· 节末 Questions 题 全部（约 25 分钟，p.409）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.410）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>5月12日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch8 进阶微积分 §8.1、§8.2、§8.3、§8.4
-· 速览 §8.1 tan⁻¹x 的导数、§8.2 1/(x²+a²) 的积分、§8.3 k f′(x)/f(x) 的积分、§8.4 换元积分法（p.186、p.187、p.189、p.191，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+术语与格式 Phy Ch14 驻波 §14.1、§14.2、§14.3、§14.4
+· 速览 §14.1 从行波到驻波、§14.2 波节与波腹、§14.3 驻波的形成、§14.4 测定声波的波长与速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
 · 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
 · 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. inverse tangent = 反正切
-· 2. integration by substitution = 换元积分法
-· 3. integration by parts = 分部积分法
-· 4. recognise the form $kf'(x)/f(x)$ = 识别 $kf'/f$ 型
-· 5. partial fractions in integration = 用部分分式积分
-· 6. limits of integration = 积分上下限
-· 7. change the limits = 换限
-· 8. dummy variable = 哑变量
-· 9. integrand = 被积函数
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch8 Further calculus 进阶微积分（P3）]]（本章共 9 条）</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>5月13日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch15 原子结构 §15.13
-· 速览 §15.13 另一种核力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 22 条）：[[06_物理#Ch15 Atomic structure 原子结构]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+· 1. stationary wave = 驻波
+· 2. standing wave = 驻波
+· 3. node = 波节
+· 4. antinode = 波腹
+· 5. progressive wave = 行进波
+· 6. fundamental frequency = 基频
+· 7. first harmonic = 一次谐波
+· 8. in phase = 同相
+· 9. antiphase = 反相
+· 全部抄完后回看一遍：[[06_物理#Ch14 Stationary waves 驻波]]（本章共 9 条）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -7259,7 +7298,7 @@
           <t>5月16日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch8 ｜ Phy Ch15 ｜ S1 Ch8
+· 回顾：P2/3 Ch5 ｜ Phy Ch14 ｜ S1 Ch8
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -7278,10 +7317,10 @@
           <t>5月17日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch8 进阶微积分（§8.1、§8.2）
-· Ex 8A 题 1–5（约 18 分钟，p.187）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 8B 题 1–6（约 19 分钟，p.188）
+格式训练 P2/3 Ch5 积分（§5.3、§5.4）
+· Ex 5C 题 1–10（约 25 分钟，p.120）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 5D 题 1–12（约 28 分钟，p.125）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -7292,41 +7331,35 @@
           <t>5月18日 周二
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch15 原子结构
+格式训练 Phy Ch14 驻波（§14.1、§14.2）
+· 节末 Questions 题 全部（约 25 分钟，p.369）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.370）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>5月19日 周三
+────────────
+21:00-22:15 纯数
+术语与格式 P2/3 Ch5 积分 §5.5
+· 速览 §5.5 梯形法则（p.126，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 11 条）：[[02_纯数学 P2-3#Ch5 Integration 积分]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>5月20日 周四
+────────────
+21:00-22:15 物理
+章末复习 Phy Ch14 驻波
 · 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：原子结构、光电效应、能级与光谱、波粒二象性
-· 过关自测：能默写 E=hf 与 hf=Φ+KE_max；能解释「存在红限频率」；Chapter 15 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
-术语与格式 Phy P1 实验技能 §P1.1–P1.5、§P1.6–P1.11
-· 速览 §P1.1–P1.5 实验操作与不确定度（一）、§P1.6–P1.11 数据处理与误差合成（二）（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡：打开 [[06_物理#P1]] 的术语表，把英文说法抄进 Anki（牌组「数理术语」，只抄术语，不抄公式），抄完打勾</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>5月19日 周三
-────────────
-21:00-22:15 纯数
-格式训练 P2/3 Ch8 进阶微积分（§8.3、§8.4）
-· Ex 8C 题 1–5（约 18 分钟，p.190）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 8D 题 1–9（约 24 分钟，p.193）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>5月20日 周四
-────────────
-21:00-22:15 物理
-章末复习 Phy P1 实验技能
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：测量不确定度、作图求斜率、误差分析、实验设计
-· 过关自测：能给结果配上绝对/相对不确定度；能画最佳拟合直线并求斜率；能识别系统误差与随机误差；P1.1–P1.11 全部读一遍并做笔记
+· 本章要会：驻波与共振、弦与气柱的基频与泛音
+· 过关自测：能画各阶驻波图；能算弦频率 f=(1/2L)√(T/μ)；Chapter 14 EXAM-STYLE QUESTIONS 限时做完并批改
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
@@ -7366,7 +7399,7 @@
           <t>5月23日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch8 ｜ Phy Ch15
+· 回顾：P2/3 Ch5 ｜ Phy Ch14
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -7391,16 +7424,12 @@
           <t>5月24日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P2/3 Ch8 进阶微积分 §8.5、§8.6、§8.7
-· 速览 §8.5 部分分式在积分中的应用、§8.6 分部积分法、§8.7 进阶积分技巧（p.194、p.197、p.201，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 9 条）：[[02_纯数学 P2-3#Ch8 Further calculus 进阶微积分（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾
-格式训练 P2/3 Ch8 进阶微积分（§8.5、§8.6）
-· Ex 8E 题 1–6（约 19 分钟，p.196）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 8F 题 1–27（约 35 分钟，p.200）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
+章末复习 P2/3 Ch5 积分
+· 章末复习题 End-of-chapter review p.131，限时 30 分钟
+· 本章要会：分部积分、分式拆分法、定积分的换元、梯形法则数值积分
+· 过关自测：分部积分的 LIATE 顺序能默写；梯形法则能徒手算 4 条带；Ex 5A–5E 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -7408,20 +7437,33 @@
           <t>5月25日 周二
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch16 圆周运动 §16.1、§16.2、§16.3、§16.4
-· 速览 §16.1 描述圆周运动、§16.2 弧度、§16.3 恒定速率、变化速度、§16.4 角速度（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. radian = 弧度
-· 2. angular displacement = 角位移
-· 3. angular speed = 角速度
-· 4. period = 周期
-· 5. frequency = 频率
-· 6. centripetal acceleration = 向心加速度
-· 7. centripetal force = 向心力
-· 8. tangent = 切线
-· 9. conical pendulum = 锥摆
-· 全部抄完后回看一遍：[[06_物理#Ch16 Circular motion 圆周运动]]（本章共 9 条）</t>
+术语与格式 Phy Ch15 原子结构 §15.1、§15.2、§15.3、§15.4
+· 速览 §15.1 观察原子内部、§15.2 α 粒子散射与原子核、§15.3 原子的简单模型、§15.4 核子与电子（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 22 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. nucleus = 原子核
+· 2. nucleon = 核子
+· 3. proton = 质子
+· 4. neutron = 中子
+· 5. proton number = 质子数
+· 6. nucleon number = 核子数
+· 7. isotope = 同位素
+· 8. nuclide = 核素
+· 9. α-particle scattering = α 粒子散射
+· 10. radioactivity = 放射性
+· 11. β-particle = β 粒子
+· 12. γ-radiation = γ 射线
+· 13. neutrino = 中微子
+· 14. antineutrino = 反中微子
+· 15. positron = 正电子
+· 16. quark = 夸克
+· 17. lepton = 轻子
+· 18. hadron = 强子
+· 19. baryon = 重子
+· 20. meson = 介子
+· 21. mass–energy = 质能
+· 22. annihilation = 湮灭
+· 全部抄完后回看一遍：[[06_物理#Ch15 Atomic structure 原子结构]]（本章共 22 条）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -7429,12 +7471,21 @@
           <t>5月26日 周三
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch8 进阶微积分
-· 章末复习题 End-of-chapter review p.203，限时 30 分钟
-· 本章要会：用导数画曲线（驻点/拐点/渐近线）、参数方程与隐函数的积分
-· 过关自测：能列「画曲线 6 步」清单并照做；Ex 8A–8G 错题清零；能说清拐点与二阶导为零的关系
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 P2/3 Ch6 方程的数值解法 §6.1、§6.2、§6.3
+· 速览 §6.1 寻找初始近似值、§6.2 改进解的精度、§6.3 迭代法的跨领域应用（p.135、p.140、p.149，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 10 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. root = 根
+· 2. approximation = 近似值
+· 3. iterative process / iteration = 迭代法
+· 4. converges = 收敛
+· 5. diverges = 发散
+· 6. change of sign = 变号
+· 7. continuous = 连续
+· 8. starting point / initial value = 初始近似值
+· 9. rearrangement = 变形／重新整理
+· 10. prescribed degree of accuracy = 指定精度
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch6 Numerical solutions of equations 方程的数值解法]]（本章共 10 条）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -7442,10 +7493,10 @@
           <t>5月27日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch16 圆周运动（§16.1、§16.2）
-· 节末 Questions 题 全部（约 25 分钟，p.454）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.455）
+格式训练 Phy Ch15 原子结构（§15.1、§15.2）
+· 节末 Questions 题 全部（约 25 分钟，p.389）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.392）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -7504,23 +7555,13 @@
           <t>5月31日 周一
 ────────────
 21:00-22:15 纯数
-术语与格式 P2/3 Ch9 向量 §9.1、§9.2、§9.3、§9.4
-· 速览 §9.1 位移（平移）向量、§9.2 位置向量、§9.3 数量积、§9.4 直线的向量方程（p.211、p.220、p.225、p.231，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 12 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. displacement vector = 位移向量
-· 2. position vector = 位置向量
-· 3. magnitude (modulus) of a vector = 向量的模
-· 4. unit vector = 单位向量
-· 5. direction vector = 方向向量
-· 6. parameter = 参数
-· 7. scalar product / dot product = 数量积／点积
-· 8. parallel vectors = 平行向量
-· 9. perpendicular vectors = 垂直向量
-· 10. skew lines = 异面直线
-· 11. intersection = 交点
-· 12. vector equation of a line = 直线的向量方程
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch9 Vectors 向量（P3）]]（本章共 12 条）</t>
+格式训练 P2/3 Ch6 方程的数值解法（§6.1、§6.2）
+· Ex 6A 题 1–15（约 32 分钟，p.137）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 6B 题 1–14（约 31 分钟，p.146）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
@@ -7597,16 +7638,13 @@
           <t>6月1日 周二
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch16 圆周运动（§16.3、§16.4）
-· 节末 Questions 题 全部（约 25 分钟，p.457）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.458）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-术语与格式 Phy Ch16 圆周运动 §16.5、§16.6、§16.7
-· 速览 §16.5 向心力、§16.6 计算加速度与力、§16.7 向心力的来源（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 9 条）：[[06_物理#Ch16 Circular motion 圆周运动]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 Phy Ch15 原子结构（§15.3、§15.4）
+· 节末 Questions 题 全部（约 25 分钟，p.393）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.397）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -7614,13 +7652,12 @@
           <t>6月2日 周三
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch9 向量（§9.1、§9.2）
-· Ex 9A 题 1–7（约 20 分钟，p.218）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9B 题 1–13（约 30 分钟，p.223）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+章末复习 P2/3 Ch6 方程的数值解法
+· 章末复习题 End-of-chapter review p.155，限时 30 分钟
+· 本章要会：用迭代法（不动点/牛顿—拉夫森）求方程近似解
+· 过关自测：能默写牛顿—拉夫森迭代式；能判断迭代是否收敛（|f'(x)|&lt;1）；Ex 6A–6C 错题清零
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -7628,13 +7665,10 @@
           <t>6月3日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch16 圆周运动（§16.5、§16.6）
-· 节末 Questions 题 全部（约 25 分钟，p.461）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.464）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 Phy Ch15 原子结构 §15.5、§15.6、§15.7、§15.8
+· 速览 §15.5 原子核内的力、§15.6 放射性的发现、§15.7 放射性物质发出的射线、§15.8 α 与 β 衰变中的能量（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 22 条）：[[06_物理#Ch15 Atomic structure 原子结构]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -7672,7 +7706,7 @@
           <t>6月6日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch9 ｜ Phy Ch16
+· 回顾：P2/3 Ch6 ｜ Phy Ch15
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -7696,16 +7730,24 @@
           <t>6月7日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch9 向量（§9.3、§9.4）
-· Ex 9C 题 1–10（约 25 分钟，p.230）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 9D 题 1–13（约 30 分钟，p.235）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-术语与格式 P2/3 Ch9 向量 §9.5
-· 速览 §9.5 两直线的交点（p.236，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 12 条）：[[02_纯数学 P2-3#Ch9 Vectors 向量（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+术语与格式 P2/3 Ch7 进阶代数 §7.1、§7.2、§7.3、§7.4
+· 速览 §7.1 假分式、§7.2 部分分式、§7.3 二项式展开 (1+x)^n（n 非正整数）、§7.4 二项式展开 (a+x)^n（n 非正整数）（p.166、p.168、p.174、p.177，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. rational function = 有理函数
+· 2. proper / improper algebraic fraction = 真／假分式
+· 3. partial fractions = 部分分式
+· 4. decompose / decomposition = 分解
+· 5. repeated linear factor = 重线性因式
+· 6. irreducible quadratic factor = 不可约二次因式
+· 7. equating coefficients = 比较系数
+· 8. cover-up method = 遮盖法
+· 9. binomial expansion = 二项式展开
+· 10. general binomial theorem = 广义二项式定理
+· 11. ascending powers = 升幂
+· 12. validity / range of validity = 成立范围
+· 13. identically equal ($\equiv$) = 恒等于
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch7 Further algebra 进阶代数（P3）]]（本章共 13 条）</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -7713,12 +7755,13 @@
           <t>6月8日 周二
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch16 圆周运动
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：圆周运动、向心加速度、转动惯量概念
-· 过关自测：能默写 a=v²/r 与 F=mv²/r；能分析竖直圆周运动的临界点；Chapter 16 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+格式训练 Phy Ch15 原子结构（§15.5、§15.6）
+· 节末 Questions 题 全部（约 25 分钟，p.400）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.401）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -7726,31 +7769,21 @@
           <t>6月9日 周三 ◆端午节假期
 ────────────
 14:00-15:00 纯数
-章末复习 P2/3 Ch9 向量
-· 章末复习题 End-of-chapter review p.240，限时 30 分钟
-· 本章要会：三维向量运算、数量积、直线与平面的向量方程、夹角与交点
-· 过关自测：能默写直线与平面的向量方程；能求两直线夹角与交点；Ex 9A–9E 错题清零
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+格式训练 P2/3 Ch7 进阶代数（§7.1、§7.2）
+· Ex 7A 题 1–4（约 16 分钟，p.167）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 7B 题 1–10（约 25 分钟，p.173）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 纯数
-术语与格式 P2/3 Ch10 微分方程 §10.1、§10.2
-· 速览 §10.1 分离变量法、§10.2 由实际问题建立微分方程（p.245、p.252，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 13 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. differential equation = 微分方程
-· 2. first order = 一阶
-· 3. separable = 可分离变量
-· 4. separating the variables = 分离变量
-· 5. general solution = 通解
-· 6. particular solution = 特解
-· 7. initial condition = 初始条件
-· 8. arbitrary constant = 任意常数
-· 9. rate of change = 变化率
-· 10. proportional to = 与……成正比
-· 11. exponential growth / decay = 指数增长／衰减
-· 12. Newton's law of cooling/heating = 牛顿冷却（加热）定律
-· 13. limiting value = 极限值
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch10 Differential equations 微分方程（P3）]]（本章共 13 条）</t>
+格式训练 P2/3 Ch7 进阶代数（§7.3、§7.4）
+· Ex 7C 题 1–11（约 26 分钟，p.176）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 7D 题 1–8（约 22 分钟，p.178）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -7758,22 +7791,13 @@
           <t>6月10日 周四
 ────────────
 21:00-22:15 物理
-术语与格式 Phy Ch17 引力场 §17.1、§17.2、§17.3、§17.4
-· 速览 §17.1 表示引力场、§17.2 重力场强度 g、§17.3 引力场中的能量、§17.4 引力势（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 11 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. gravitational field = 引力场
-· 2. field line = 场线
-· 3. Newton's law of gravitation = 万有引力定律
-· 4. gravitational constant = 引力常量
-· 5. gravitational field strength = 重力场强度
-· 6. gravitational potential = 引力势
-· 7. gravitational potential energy = 引力势能
-· 8. inverse square law = 平方反比定律
-· 9. orbital period = 轨道周期
-· 10. geostationary orbit = 地球同步轨道
-· 11. centripetal force = 向心力
-· 全部抄完后回看一遍：[[06_物理#Ch17 Gravitational fields 引力场]]（本章共 11 条）</t>
+格式训练 Phy Ch15 原子结构（§15.7、§15.8）
+· 节末 Questions 题 全部（约 25 分钟，p.402）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.405）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -7814,7 +7838,7 @@
           <t>6月13日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch10 ｜ Phy Ch17 ｜ FM Ch8
+· 回顾：P2/3 Ch7 ｜ Phy Ch15 ｜ FM Ch8
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -7833,71 +7857,48 @@
           <t>6月14日 周一
 ────────────
 21:00-22:15 纯数
-章末复习 P2/3 Ch10 微分方程
-· 章末复习题 End-of-chapter review p.262，限时 30 分钟
-· 本章要会：识别并求解一阶可分离变量微分方程、用初始条件定常数
-· 过关自测：能判断方程是否可分离变量；Ex 10A–10B 错题清零；能完整写出「分离→积分→代初值→写解」四步
+术语与格式 P2/3 Ch7 进阶代数 §7.5
+· 速览 §7.5 部分分式与二项式展开（p.179，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 13 条）：[[02_纯数学 P2-3#Ch7 Further algebra 进阶代数（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>6月15日 周二
+────────────
+21:00-22:15 物理
+术语与格式 Phy Ch15 原子结构 §15.9、§15.10、§15.11、§15.12
+· 速览 §15.9 放射性衰变方程、§15.10 基本粒子、§15.11 粒子家族、§15.12 再看 β 衰变（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 22 条）：[[06_物理#Ch15 Atomic structure 原子结构]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>6月16日 周三
+────────────
+21:00-22:15 纯数
+章末复习 P2/3 Ch7 进阶代数
+· 章末复习题 End-of-chapter review p.182，限时 30 分钟
+· 本章要会：部分分式、除法算式与余数定理、代数式的组合运算
+· 过关自测：能把真分式拆成部分分式；能处理假分式（先做除法）；Ex 7A–7E 错题清零
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>6月15日 周二
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>6月17日 周四
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch17 引力场（§17.1、§17.2）
-· 节末 Questions 题 全部（约 25 分钟，p.480）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.482）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-格式训练 Phy Ch17 引力场（§17.3、§17.4）
-· 节末 Questions 题 全部（约 25 分钟，p.484）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.486）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>6月16日 周三
-────────────
-21:00-22:15 纯数
-术语与格式 P2/3 Ch11 复数 §11.1、§11.2、§11.3、§11.4
-· 速览 §11.1 虚数、§11.2 复数、§11.3 复平面、§11.4 解方程（p.267、p.269、p.273、p.283，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 17 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. imaginary unit $\mathrm{i}$ = 虚数单位
-· 2. imaginary number = 虚数
-· 3. complex number = 复数
-· 4. Cartesian form = 笛卡尔形式
-· 5. real part / imaginary part = 实部／虚部
-· 6. conjugate ($z^*$) = 共轭
-· 7. modulus ($\lvert z\rvert$) = 模
-· 8. argument ($\arg z$) = 辐角
-· 9. principal argument = 主辐角
-· 10. Argand diagram = 阿冈图
-· 11. modulus-argument form = 模-辐角形式
-· 12. polar form = 极坐标形式
-· 13. exponential form = 指数形式
-· 14. locus (plural loci) = 轨迹
-· 15. perpendicular bisector = 垂直平分线
-· 16. conjugate pairs = 共轭对
-· 17. cube roots of unity = 单位立方根
-· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch11 Complex numbers 复数（P3）]]（本章共 17 条）</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>6月17日 周四
-────────────
-21:00-22:15 物理
-术语与格式 Phy Ch17 引力场 §17.5、§17.6、§17.7
-· 速览 §17.5 在引力下运行、§17.6 轨道周期、§17.7 绕地球运行（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 11 条）：[[06_物理#Ch17 Gravitational fields 引力场]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 Phy Ch15 原子结构（§15.9、§15.10）
+· 节末 Questions 题 全部（约 25 分钟，p.406）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.407）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -7947,7 +7948,7 @@
           <t>6月20日 周日
 ────────────
 14:00-15:00 复习/测试
-· 回顾：P2/3 Ch11 ｜ Phy Ch17 ｜ FM Ch9
+· 回顾：P2/3 Ch7 ｜ Phy Ch15 ｜ FM Ch9
 · Anki 术语卡 15′ + 错题本整理
 · 预习下周内容，制定周计划
 20:00-21:00 进阶数学
@@ -7967,13 +7968,20 @@
           <t>6月21日 周一
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch11 复数（§11.1、§11.2）
-· Ex 11A 题 1–6（约 19 分钟，p.269）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 11B 题 1–10（约 25 分钟，p.272）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
+术语与格式 P2/3 Ch8 进阶微积分 §8.1、§8.2、§8.3、§8.4
+· 速览 §8.1 tan⁻¹x 的导数、§8.2 1/(x²+a²) 的积分、§8.3 k f′(x)/f(x) 的积分、§8.4 换元积分法（p.186、p.187、p.189、p.191，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡共 9 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
+· 1. inverse tangent = 反正切
+· 2. integration by substitution = 换元积分法
+· 3. integration by parts = 分部积分法
+· 4. recognise the form $kf'(x)/f(x)$ = 识别 $kf'/f$ 型
+· 5. partial fractions in integration = 用部分分式积分
+· 6. limits of integration = 积分上下限
+· 7. change the limits = 换限
+· 8. dummy variable = 哑变量
+· 9. integrand = 被积函数
+· 全部抄完后回看一遍：[[02_纯数学 P2-3#Ch8 Further calculus 进阶微积分（P3）]]（本章共 9 条）</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -7981,10 +7989,10 @@
           <t>6月22日 周二
 ────────────
 21:00-22:15 物理
-格式训练 Phy Ch17 引力场（§17.5、§17.6）
-· 节末 Questions 题 全部（约 25 分钟，p.488）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.490）
+格式训练 Phy Ch15 原子结构（§15.11、§15.12）
+· 节末 Questions 题 全部（约 25 分钟，p.409）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· 节末 Questions 题 全部（约 25 分钟，p.410）
 · 只做要写过程 / 要解释的题；纯基础计算题直接跳过
 · 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
 · Anki 术语卡复习 5 分钟</t>
@@ -7995,16 +8003,13 @@
           <t>6月23日 周三
 ────────────
 21:00-22:15 纯数
-格式训练 P2/3 Ch11 复数（§11.3、§11.4）
-· Ex 11C 题 1–12（约 28 分钟，p.282）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· Ex 11D 题 1–10（约 25 分钟，p.288）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-术语与格式 P2/3 Ch11 复数 §11.5
-· 速览 §11.5 轨迹（p.288，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡复习（本章共 17 条）：[[02_纯数学 P2-3#Ch11 Complex numbers 复数（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+格式训练 P2/3 Ch8 进阶微积分（§8.1、§8.2）
+· Ex 8A 题 1–5（约 18 分钟，p.187）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8B 题 1–6（约 19 分钟，p.188）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -8012,12 +8017,10 @@
           <t>6月24日 周四
 ────────────
 21:00-22:15 物理
-章末复习 Phy Ch17 引力场
-· 章末复习题 End-of-chapter review，限时 30 分钟
-· 本章要会：引力场、场强、引力势与轨道运动
-· 过关自测：能默写 F=GMm/r² 与 g=GM/r²；能区分场强与势；Chapter 17 EXAM-STYLE QUESTIONS 限时做完并批改
-· 本章公式/术语卡入 Anki
-· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
+术语与格式 Phy Ch15 原子结构 §15.13
+· 速览 §15.13 另一种核力（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 22 条）：[[06_物理#Ch15 Atomic structure 原子结构]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -8081,67 +8084,57 @@
           <t>6月28日 周一 ◆暑假
 ────────────
 14:00-15:00 纯数
-章末复习 P2/3 Ch11 复数
-· 章末复习题 End-of-chapter review p.297，限时 30 分钟
-· 本章要会：复数四则运算、模与辐角、Argand 图、复数方程与几何意义
-· 过关自测：能默写 i²=−1、模与辐角定义；能把复数在 Argand 图上表示；Ex 11A–11E 错题清零
+格式训练 P2/3 Ch8 进阶微积分（§8.3、§8.4）
+· Ex 8C 题 1–5（约 18 分钟，p.190）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8D 题 1–9（约 24 分钟，p.193）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
+15:15-16:15 纯数
+术语与格式 P2/3 Ch8 进阶微积分 §8.5、§8.6、§8.7
+· 速览 §8.5 部分分式在积分中的应用、§8.6 分部积分法、§8.7 进阶积分技巧（p.194、p.197、p.201，每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡复习（本章共 9 条）：[[02_纯数学 P2-3#Ch8 Further calculus 进阶微积分（P3）]] —— 上次抄过的今天先复习，还没抄的补上，全抄完打勾</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>6月29日 周二 ◆暑假
+────────────
+14:00-15:00 物理
+章末复习 Phy Ch15 原子结构
+· 章末复习题 End-of-chapter review，限时 30 分钟
+· 本章要会：原子结构、光电效应、能级与光谱、波粒二象性
+· 过关自测：能默写 E=hf 与 hf=Φ+KE_max；能解释「存在红限频率」；Chapter 15 EXAM-STYLE QUESTIONS 限时做完并批改
 · 本章公式/术语卡入 Anki
 · 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）
+15:15-16:15 物理
+术语与格式 Phy P1 实验技能 §P1.1–P1.5、§P1.6–P1.11
+· 速览 §P1.1–P1.5 实验操作与不确定度（一）、§P1.6–P1.11 数据处理与误差合成（二）（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
+· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
+· 本章术语卡：打开 [[06_物理#P1]] 的术语表，把英文说法抄进 Anki（牌组「数理术语」，只抄术语，不抄公式），抄完打勾</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>6月30日 周三 ◆暑假
+────────────
+14:00-15:00 纯数
+格式训练 P2/3 Ch8 进阶微积分（§8.5、§8.6）
+· Ex 8E 题 1–6（约 19 分钟，p.196）
+· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
+· Ex 8F 题 1–27（约 35 分钟，p.200）
+· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
+· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
+· Anki 术语卡复习 5 分钟
 15:15-16:15 纯数
-真题精练 9709 P1 2019 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>6月29日 周二 ◆暑假
-────────────
-14:00-15:00 物理
-术语与格式 Phy Ch18 振动 §18.1、§18.2、§18.3、§18.4
-· 速览 §18.1 自由振动与受迫振动、§18.2 观察振动、§18.3 描述振动、§18.4 简谐运动（每节 5 分钟）：只看定义、符号、单位与例题的写法，不做题
-· 照抄课本例题的「标准答题格式」：已知 → 公式 → 代入 → 带单位的结果
-· 本章术语卡共 14 条，下面就是今天要抄的全部内容。打开 Anki → 牌组「数理术语」→ 添加卡片：正面写英文，背面写中文，一条一张卡（只抄术语，不抄公式）。抄一条，就在那一条后面打一个勾：
-· 1. oscillation = 振动
-· 2. free oscillation = 自由振动
-· 3. forced oscillation = 受迫振动
-· 4. simple harmonic motion = 简谐运动
-· 5. displacement = 位移
-· 6. amplitude = 振幅
-· 7. period = 周期
-· 8. frequency = 频率
-· 9. angular frequency = 角频率
-· 10. damping = 阻尼
-· 11. critical damping = 临界阻尼
-· 12. natural frequency = 固有频率
-· 13. resonance = 共振
-· 14. driving frequency = 驱动频率
-· 全部抄完后回看一遍：[[06_物理#Ch18 Oscillations 振动]]（本章共 14 条）
-15:15-16:15 物理
-格式训练 Phy Ch18 振动（§18.1、§18.2）
-· 节末 Questions 题 全部（约 25 分钟，p.502）
-· 逐题批改；错题抄进 Obsidian「错题与卡点」，写「我为什么错」
-· 节末 Questions 题 全部（约 25 分钟，p.504）
-· 只做要写过程 / 要解释的题；纯基础计算题直接跳过
-· 做完对照答案，红笔标出「每 1 分对应哪句话、哪一步」
-· Anki 术语卡复习 5 分钟</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>6月30日 周三 ◆暑假
-────────────
-14:00-15:00 纯数
-真题精练 9709 P3 2019 Paper 3
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题
-15:15-16:15 纯数
-真题精练 9709 P1 2020 Paper 1
-· 纯数真题卷，限时 1 小时 50 分
-· 限时 55 分钟作答 + 即时对答案
-· 错题归档，次日二刷错题</t>
+章末复习 P2/3 Ch8 进阶微积分
+· 章末复习题 End-of-chapter review p.203，限时 30 分钟
+· 本章要会：用导数画曲线（驻点/拐点/渐近线）、参数方程与隐函数的积分
+· 过关自测：能列「画曲线 6 步」清单并照做；Ex 8A–8G 错题清零；能说清拐点与二阶导为零的关系
+· 本章公式/术语卡入 Anki
+· 对照答案，用红笔标出每 1 分对应哪句话、哪一步（答题格式）</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
